--- a/caseload-tracker/Antenatal_Caseload_Tracker.xlsx
+++ b/caseload-tracker/Antenatal_Caseload_Tracker.xlsx
@@ -399,10 +399,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E7E6E6"/>
+          <bgColor rgb="00E7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -425,12 +436,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="009C0006"/>
+        <b val="1"/>
+        <color rgb="007F6000"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F8CBCB"/>
-          <bgColor rgb="00F8CBCB"/>
+          <fgColor rgb="00FFE699"/>
+          <bgColor rgb="00FFE699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -447,13 +459,12 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
-        <color rgb="007F6000"/>
+        <color rgb="009C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFE699"/>
-          <bgColor rgb="00FFE699"/>
+          <fgColor rgb="00F8CBCB"/>
+          <bgColor rgb="00F8CBCB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1039,7 +1050,7 @@
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Overdue / next appt not booked</t>
+          <t>Overdue / not confirmed</t>
         </is>
       </c>
       <c r="O2" s="12" t="inlineStr">
@@ -1049,7 +1060,7 @@
       </c>
       <c r="P2" s="13" t="inlineStr">
         <is>
-          <t>Seen / done</t>
+          <t>Confirmed / done</t>
         </is>
       </c>
       <c r="Q2" s="14" t="inlineStr">
@@ -1284,7 +1295,7 @@
         <v/>
       </c>
       <c r="I5" s="32">
-        <f>IF(NOT(AND($A5&lt;&gt;"",OR($G5="",$G5="Active"))),"",IF(AND(MAX($M5:$U5)&gt;0,MAX($M5:$U5)&lt;TODAY(),COUNTBLANK($N5:$U5)&gt;0,COUNTIF($N5:$U5,"DNA")=0),1,0)+COUNTIF($N5:$U5,"DNA")+COUNTIF($V5:$Z5,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A5&lt;&gt;"",OR($G5="",$G5="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M5:$U5)+($M5:$U5="DNA")),$M5:$U5),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M5:$U5)+($M5:$U5="DNA")),$M5:$U5),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M5:$U5)+($M5:$U5="DNA")),$M5:$U5),"")&lt;TODAY())),1,0)+COUNTIF($V5:$Z5,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J5" s="32">
@@ -1292,7 +1303,7 @@
         <v/>
       </c>
       <c r="K5" s="32">
-        <f>IF(NOT(AND($A5&lt;&gt;"",OR($G5="",$G5="Active"))),"",IF($L5&lt;&gt;"",IF($L5=$M5,"Booking",INDEX($N$4:$U$4,MATCH($L5,$N5:$U5,0))),IF(COUNTIF($N5:$U5,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N5:$U5)=0,"All done",IF(MAX($M5:$U5)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A5&lt;&gt;"",OR($G5="",$G5="Active"))),"",IF($L5&lt;&gt;"",IF($L5=$M5,"Booking",INDEX($N$4:$U$4,MATCH($L5,$N5:$U5,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M5:$U5)+($M5:$U5="DNA")),$M5:$U5),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M5:$U5)+($M5:$U5="DNA")),$M5:$U5),"")),IF(ISNUMBER($U5),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L5" s="33">
@@ -1330,7 +1341,7 @@
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>IF(NOT(AND($A6&lt;&gt;"",OR($G6="",$G6="Active"))),"",IF(AND(MAX($M6:$U6)&gt;0,MAX($M6:$U6)&lt;TODAY(),COUNTBLANK($N6:$U6)&gt;0,COUNTIF($N6:$U6,"DNA")=0),1,0)+COUNTIF($N6:$U6,"DNA")+COUNTIF($V6:$Z6,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A6&lt;&gt;"",OR($G6="",$G6="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M6:$U6)+($M6:$U6="DNA")),$M6:$U6),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M6:$U6)+($M6:$U6="DNA")),$M6:$U6),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M6:$U6)+($M6:$U6="DNA")),$M6:$U6),"")&lt;TODAY())),1,0)+COUNTIF($V6:$Z6,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J6" s="32">
@@ -1338,7 +1349,7 @@
         <v/>
       </c>
       <c r="K6" s="32">
-        <f>IF(NOT(AND($A6&lt;&gt;"",OR($G6="",$G6="Active"))),"",IF($L6&lt;&gt;"",IF($L6=$M6,"Booking",INDEX($N$4:$U$4,MATCH($L6,$N6:$U6,0))),IF(COUNTIF($N6:$U6,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N6:$U6)=0,"All done",IF(MAX($M6:$U6)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A6&lt;&gt;"",OR($G6="",$G6="Active"))),"",IF($L6&lt;&gt;"",IF($L6=$M6,"Booking",INDEX($N$4:$U$4,MATCH($L6,$N6:$U6,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M6:$U6)+($M6:$U6="DNA")),$M6:$U6),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M6:$U6)+($M6:$U6="DNA")),$M6:$U6),"")),IF(ISNUMBER($U6),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L6" s="33">
@@ -1376,7 +1387,7 @@
         <v/>
       </c>
       <c r="I7" s="32">
-        <f>IF(NOT(AND($A7&lt;&gt;"",OR($G7="",$G7="Active"))),"",IF(AND(MAX($M7:$U7)&gt;0,MAX($M7:$U7)&lt;TODAY(),COUNTBLANK($N7:$U7)&gt;0,COUNTIF($N7:$U7,"DNA")=0),1,0)+COUNTIF($N7:$U7,"DNA")+COUNTIF($V7:$Z7,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A7&lt;&gt;"",OR($G7="",$G7="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M7:$U7)+($M7:$U7="DNA")),$M7:$U7),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M7:$U7)+($M7:$U7="DNA")),$M7:$U7),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M7:$U7)+($M7:$U7="DNA")),$M7:$U7),"")&lt;TODAY())),1,0)+COUNTIF($V7:$Z7,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J7" s="32">
@@ -1384,7 +1395,7 @@
         <v/>
       </c>
       <c r="K7" s="32">
-        <f>IF(NOT(AND($A7&lt;&gt;"",OR($G7="",$G7="Active"))),"",IF($L7&lt;&gt;"",IF($L7=$M7,"Booking",INDEX($N$4:$U$4,MATCH($L7,$N7:$U7,0))),IF(COUNTIF($N7:$U7,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N7:$U7)=0,"All done",IF(MAX($M7:$U7)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A7&lt;&gt;"",OR($G7="",$G7="Active"))),"",IF($L7&lt;&gt;"",IF($L7=$M7,"Booking",INDEX($N$4:$U$4,MATCH($L7,$N7:$U7,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M7:$U7)+($M7:$U7="DNA")),$M7:$U7),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M7:$U7)+($M7:$U7="DNA")),$M7:$U7),"")),IF(ISNUMBER($U7),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L7" s="33">
@@ -1422,7 +1433,7 @@
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>IF(NOT(AND($A8&lt;&gt;"",OR($G8="",$G8="Active"))),"",IF(AND(MAX($M8:$U8)&gt;0,MAX($M8:$U8)&lt;TODAY(),COUNTBLANK($N8:$U8)&gt;0,COUNTIF($N8:$U8,"DNA")=0),1,0)+COUNTIF($N8:$U8,"DNA")+COUNTIF($V8:$Z8,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A8&lt;&gt;"",OR($G8="",$G8="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M8:$U8)+($M8:$U8="DNA")),$M8:$U8),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M8:$U8)+($M8:$U8="DNA")),$M8:$U8),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M8:$U8)+($M8:$U8="DNA")),$M8:$U8),"")&lt;TODAY())),1,0)+COUNTIF($V8:$Z8,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J8" s="32">
@@ -1430,7 +1441,7 @@
         <v/>
       </c>
       <c r="K8" s="32">
-        <f>IF(NOT(AND($A8&lt;&gt;"",OR($G8="",$G8="Active"))),"",IF($L8&lt;&gt;"",IF($L8=$M8,"Booking",INDEX($N$4:$U$4,MATCH($L8,$N8:$U8,0))),IF(COUNTIF($N8:$U8,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N8:$U8)=0,"All done",IF(MAX($M8:$U8)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A8&lt;&gt;"",OR($G8="",$G8="Active"))),"",IF($L8&lt;&gt;"",IF($L8=$M8,"Booking",INDEX($N$4:$U$4,MATCH($L8,$N8:$U8,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M8:$U8)+($M8:$U8="DNA")),$M8:$U8),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M8:$U8)+($M8:$U8="DNA")),$M8:$U8),"")),IF(ISNUMBER($U8),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L8" s="33">
@@ -1468,7 +1479,7 @@
         <v/>
       </c>
       <c r="I9" s="32">
-        <f>IF(NOT(AND($A9&lt;&gt;"",OR($G9="",$G9="Active"))),"",IF(AND(MAX($M9:$U9)&gt;0,MAX($M9:$U9)&lt;TODAY(),COUNTBLANK($N9:$U9)&gt;0,COUNTIF($N9:$U9,"DNA")=0),1,0)+COUNTIF($N9:$U9,"DNA")+COUNTIF($V9:$Z9,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A9&lt;&gt;"",OR($G9="",$G9="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M9:$U9)+($M9:$U9="DNA")),$M9:$U9),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M9:$U9)+($M9:$U9="DNA")),$M9:$U9),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M9:$U9)+($M9:$U9="DNA")),$M9:$U9),"")&lt;TODAY())),1,0)+COUNTIF($V9:$Z9,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J9" s="32">
@@ -1476,7 +1487,7 @@
         <v/>
       </c>
       <c r="K9" s="32">
-        <f>IF(NOT(AND($A9&lt;&gt;"",OR($G9="",$G9="Active"))),"",IF($L9&lt;&gt;"",IF($L9=$M9,"Booking",INDEX($N$4:$U$4,MATCH($L9,$N9:$U9,0))),IF(COUNTIF($N9:$U9,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N9:$U9)=0,"All done",IF(MAX($M9:$U9)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A9&lt;&gt;"",OR($G9="",$G9="Active"))),"",IF($L9&lt;&gt;"",IF($L9=$M9,"Booking",INDEX($N$4:$U$4,MATCH($L9,$N9:$U9,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M9:$U9)+($M9:$U9="DNA")),$M9:$U9),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M9:$U9)+($M9:$U9="DNA")),$M9:$U9),"")),IF(ISNUMBER($U9),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L9" s="33">
@@ -1514,7 +1525,7 @@
         <v/>
       </c>
       <c r="I10" s="32">
-        <f>IF(NOT(AND($A10&lt;&gt;"",OR($G10="",$G10="Active"))),"",IF(AND(MAX($M10:$U10)&gt;0,MAX($M10:$U10)&lt;TODAY(),COUNTBLANK($N10:$U10)&gt;0,COUNTIF($N10:$U10,"DNA")=0),1,0)+COUNTIF($N10:$U10,"DNA")+COUNTIF($V10:$Z10,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A10&lt;&gt;"",OR($G10="",$G10="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M10:$U10)+($M10:$U10="DNA")),$M10:$U10),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M10:$U10)+($M10:$U10="DNA")),$M10:$U10),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M10:$U10)+($M10:$U10="DNA")),$M10:$U10),"")&lt;TODAY())),1,0)+COUNTIF($V10:$Z10,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J10" s="32">
@@ -1522,7 +1533,7 @@
         <v/>
       </c>
       <c r="K10" s="32">
-        <f>IF(NOT(AND($A10&lt;&gt;"",OR($G10="",$G10="Active"))),"",IF($L10&lt;&gt;"",IF($L10=$M10,"Booking",INDEX($N$4:$U$4,MATCH($L10,$N10:$U10,0))),IF(COUNTIF($N10:$U10,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N10:$U10)=0,"All done",IF(MAX($M10:$U10)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A10&lt;&gt;"",OR($G10="",$G10="Active"))),"",IF($L10&lt;&gt;"",IF($L10=$M10,"Booking",INDEX($N$4:$U$4,MATCH($L10,$N10:$U10,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M10:$U10)+($M10:$U10="DNA")),$M10:$U10),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M10:$U10)+($M10:$U10="DNA")),$M10:$U10),"")),IF(ISNUMBER($U10),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L10" s="33">
@@ -1560,7 +1571,7 @@
         <v/>
       </c>
       <c r="I11" s="32">
-        <f>IF(NOT(AND($A11&lt;&gt;"",OR($G11="",$G11="Active"))),"",IF(AND(MAX($M11:$U11)&gt;0,MAX($M11:$U11)&lt;TODAY(),COUNTBLANK($N11:$U11)&gt;0,COUNTIF($N11:$U11,"DNA")=0),1,0)+COUNTIF($N11:$U11,"DNA")+COUNTIF($V11:$Z11,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A11&lt;&gt;"",OR($G11="",$G11="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M11:$U11)+($M11:$U11="DNA")),$M11:$U11),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M11:$U11)+($M11:$U11="DNA")),$M11:$U11),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M11:$U11)+($M11:$U11="DNA")),$M11:$U11),"")&lt;TODAY())),1,0)+COUNTIF($V11:$Z11,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J11" s="32">
@@ -1568,7 +1579,7 @@
         <v/>
       </c>
       <c r="K11" s="32">
-        <f>IF(NOT(AND($A11&lt;&gt;"",OR($G11="",$G11="Active"))),"",IF($L11&lt;&gt;"",IF($L11=$M11,"Booking",INDEX($N$4:$U$4,MATCH($L11,$N11:$U11,0))),IF(COUNTIF($N11:$U11,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N11:$U11)=0,"All done",IF(MAX($M11:$U11)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A11&lt;&gt;"",OR($G11="",$G11="Active"))),"",IF($L11&lt;&gt;"",IF($L11=$M11,"Booking",INDEX($N$4:$U$4,MATCH($L11,$N11:$U11,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M11:$U11)+($M11:$U11="DNA")),$M11:$U11),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M11:$U11)+($M11:$U11="DNA")),$M11:$U11),"")),IF(ISNUMBER($U11),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L11" s="33">
@@ -1606,7 +1617,7 @@
         <v/>
       </c>
       <c r="I12" s="32">
-        <f>IF(NOT(AND($A12&lt;&gt;"",OR($G12="",$G12="Active"))),"",IF(AND(MAX($M12:$U12)&gt;0,MAX($M12:$U12)&lt;TODAY(),COUNTBLANK($N12:$U12)&gt;0,COUNTIF($N12:$U12,"DNA")=0),1,0)+COUNTIF($N12:$U12,"DNA")+COUNTIF($V12:$Z12,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A12&lt;&gt;"",OR($G12="",$G12="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M12:$U12)+($M12:$U12="DNA")),$M12:$U12),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M12:$U12)+($M12:$U12="DNA")),$M12:$U12),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M12:$U12)+($M12:$U12="DNA")),$M12:$U12),"")&lt;TODAY())),1,0)+COUNTIF($V12:$Z12,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J12" s="32">
@@ -1614,7 +1625,7 @@
         <v/>
       </c>
       <c r="K12" s="32">
-        <f>IF(NOT(AND($A12&lt;&gt;"",OR($G12="",$G12="Active"))),"",IF($L12&lt;&gt;"",IF($L12=$M12,"Booking",INDEX($N$4:$U$4,MATCH($L12,$N12:$U12,0))),IF(COUNTIF($N12:$U12,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N12:$U12)=0,"All done",IF(MAX($M12:$U12)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A12&lt;&gt;"",OR($G12="",$G12="Active"))),"",IF($L12&lt;&gt;"",IF($L12=$M12,"Booking",INDEX($N$4:$U$4,MATCH($L12,$N12:$U12,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M12:$U12)+($M12:$U12="DNA")),$M12:$U12),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M12:$U12)+($M12:$U12="DNA")),$M12:$U12),"")),IF(ISNUMBER($U12),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L12" s="33">
@@ -1652,7 +1663,7 @@
         <v/>
       </c>
       <c r="I13" s="32">
-        <f>IF(NOT(AND($A13&lt;&gt;"",OR($G13="",$G13="Active"))),"",IF(AND(MAX($M13:$U13)&gt;0,MAX($M13:$U13)&lt;TODAY(),COUNTBLANK($N13:$U13)&gt;0,COUNTIF($N13:$U13,"DNA")=0),1,0)+COUNTIF($N13:$U13,"DNA")+COUNTIF($V13:$Z13,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A13&lt;&gt;"",OR($G13="",$G13="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M13:$U13)+($M13:$U13="DNA")),$M13:$U13),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M13:$U13)+($M13:$U13="DNA")),$M13:$U13),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M13:$U13)+($M13:$U13="DNA")),$M13:$U13),"")&lt;TODAY())),1,0)+COUNTIF($V13:$Z13,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J13" s="32">
@@ -1660,7 +1671,7 @@
         <v/>
       </c>
       <c r="K13" s="32">
-        <f>IF(NOT(AND($A13&lt;&gt;"",OR($G13="",$G13="Active"))),"",IF($L13&lt;&gt;"",IF($L13=$M13,"Booking",INDEX($N$4:$U$4,MATCH($L13,$N13:$U13,0))),IF(COUNTIF($N13:$U13,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N13:$U13)=0,"All done",IF(MAX($M13:$U13)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A13&lt;&gt;"",OR($G13="",$G13="Active"))),"",IF($L13&lt;&gt;"",IF($L13=$M13,"Booking",INDEX($N$4:$U$4,MATCH($L13,$N13:$U13,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M13:$U13)+($M13:$U13="DNA")),$M13:$U13),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M13:$U13)+($M13:$U13="DNA")),$M13:$U13),"")),IF(ISNUMBER($U13),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L13" s="33">
@@ -1698,7 +1709,7 @@
         <v/>
       </c>
       <c r="I14" s="32">
-        <f>IF(NOT(AND($A14&lt;&gt;"",OR($G14="",$G14="Active"))),"",IF(AND(MAX($M14:$U14)&gt;0,MAX($M14:$U14)&lt;TODAY(),COUNTBLANK($N14:$U14)&gt;0,COUNTIF($N14:$U14,"DNA")=0),1,0)+COUNTIF($N14:$U14,"DNA")+COUNTIF($V14:$Z14,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A14&lt;&gt;"",OR($G14="",$G14="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M14:$U14)+($M14:$U14="DNA")),$M14:$U14),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M14:$U14)+($M14:$U14="DNA")),$M14:$U14),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M14:$U14)+($M14:$U14="DNA")),$M14:$U14),"")&lt;TODAY())),1,0)+COUNTIF($V14:$Z14,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J14" s="32">
@@ -1706,7 +1717,7 @@
         <v/>
       </c>
       <c r="K14" s="32">
-        <f>IF(NOT(AND($A14&lt;&gt;"",OR($G14="",$G14="Active"))),"",IF($L14&lt;&gt;"",IF($L14=$M14,"Booking",INDEX($N$4:$U$4,MATCH($L14,$N14:$U14,0))),IF(COUNTIF($N14:$U14,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N14:$U14)=0,"All done",IF(MAX($M14:$U14)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A14&lt;&gt;"",OR($G14="",$G14="Active"))),"",IF($L14&lt;&gt;"",IF($L14=$M14,"Booking",INDEX($N$4:$U$4,MATCH($L14,$N14:$U14,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M14:$U14)+($M14:$U14="DNA")),$M14:$U14),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M14:$U14)+($M14:$U14="DNA")),$M14:$U14),"")),IF(ISNUMBER($U14),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L14" s="33">
@@ -1744,7 +1755,7 @@
         <v/>
       </c>
       <c r="I15" s="32">
-        <f>IF(NOT(AND($A15&lt;&gt;"",OR($G15="",$G15="Active"))),"",IF(AND(MAX($M15:$U15)&gt;0,MAX($M15:$U15)&lt;TODAY(),COUNTBLANK($N15:$U15)&gt;0,COUNTIF($N15:$U15,"DNA")=0),1,0)+COUNTIF($N15:$U15,"DNA")+COUNTIF($V15:$Z15,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A15&lt;&gt;"",OR($G15="",$G15="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M15:$U15)+($M15:$U15="DNA")),$M15:$U15),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M15:$U15)+($M15:$U15="DNA")),$M15:$U15),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M15:$U15)+($M15:$U15="DNA")),$M15:$U15),"")&lt;TODAY())),1,0)+COUNTIF($V15:$Z15,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J15" s="32">
@@ -1752,7 +1763,7 @@
         <v/>
       </c>
       <c r="K15" s="32">
-        <f>IF(NOT(AND($A15&lt;&gt;"",OR($G15="",$G15="Active"))),"",IF($L15&lt;&gt;"",IF($L15=$M15,"Booking",INDEX($N$4:$U$4,MATCH($L15,$N15:$U15,0))),IF(COUNTIF($N15:$U15,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N15:$U15)=0,"All done",IF(MAX($M15:$U15)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A15&lt;&gt;"",OR($G15="",$G15="Active"))),"",IF($L15&lt;&gt;"",IF($L15=$M15,"Booking",INDEX($N$4:$U$4,MATCH($L15,$N15:$U15,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M15:$U15)+($M15:$U15="DNA")),$M15:$U15),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M15:$U15)+($M15:$U15="DNA")),$M15:$U15),"")),IF(ISNUMBER($U15),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L15" s="33">
@@ -1790,7 +1801,7 @@
         <v/>
       </c>
       <c r="I16" s="32">
-        <f>IF(NOT(AND($A16&lt;&gt;"",OR($G16="",$G16="Active"))),"",IF(AND(MAX($M16:$U16)&gt;0,MAX($M16:$U16)&lt;TODAY(),COUNTBLANK($N16:$U16)&gt;0,COUNTIF($N16:$U16,"DNA")=0),1,0)+COUNTIF($N16:$U16,"DNA")+COUNTIF($V16:$Z16,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A16&lt;&gt;"",OR($G16="",$G16="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M16:$U16)+($M16:$U16="DNA")),$M16:$U16),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M16:$U16)+($M16:$U16="DNA")),$M16:$U16),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M16:$U16)+($M16:$U16="DNA")),$M16:$U16),"")&lt;TODAY())),1,0)+COUNTIF($V16:$Z16,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J16" s="32">
@@ -1798,7 +1809,7 @@
         <v/>
       </c>
       <c r="K16" s="32">
-        <f>IF(NOT(AND($A16&lt;&gt;"",OR($G16="",$G16="Active"))),"",IF($L16&lt;&gt;"",IF($L16=$M16,"Booking",INDEX($N$4:$U$4,MATCH($L16,$N16:$U16,0))),IF(COUNTIF($N16:$U16,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N16:$U16)=0,"All done",IF(MAX($M16:$U16)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A16&lt;&gt;"",OR($G16="",$G16="Active"))),"",IF($L16&lt;&gt;"",IF($L16=$M16,"Booking",INDEX($N$4:$U$4,MATCH($L16,$N16:$U16,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M16:$U16)+($M16:$U16="DNA")),$M16:$U16),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M16:$U16)+($M16:$U16="DNA")),$M16:$U16),"")),IF(ISNUMBER($U16),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L16" s="33">
@@ -1836,7 +1847,7 @@
         <v/>
       </c>
       <c r="I17" s="32">
-        <f>IF(NOT(AND($A17&lt;&gt;"",OR($G17="",$G17="Active"))),"",IF(AND(MAX($M17:$U17)&gt;0,MAX($M17:$U17)&lt;TODAY(),COUNTBLANK($N17:$U17)&gt;0,COUNTIF($N17:$U17,"DNA")=0),1,0)+COUNTIF($N17:$U17,"DNA")+COUNTIF($V17:$Z17,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A17&lt;&gt;"",OR($G17="",$G17="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M17:$U17)+($M17:$U17="DNA")),$M17:$U17),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M17:$U17)+($M17:$U17="DNA")),$M17:$U17),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M17:$U17)+($M17:$U17="DNA")),$M17:$U17),"")&lt;TODAY())),1,0)+COUNTIF($V17:$Z17,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J17" s="32">
@@ -1844,7 +1855,7 @@
         <v/>
       </c>
       <c r="K17" s="32">
-        <f>IF(NOT(AND($A17&lt;&gt;"",OR($G17="",$G17="Active"))),"",IF($L17&lt;&gt;"",IF($L17=$M17,"Booking",INDEX($N$4:$U$4,MATCH($L17,$N17:$U17,0))),IF(COUNTIF($N17:$U17,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N17:$U17)=0,"All done",IF(MAX($M17:$U17)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A17&lt;&gt;"",OR($G17="",$G17="Active"))),"",IF($L17&lt;&gt;"",IF($L17=$M17,"Booking",INDEX($N$4:$U$4,MATCH($L17,$N17:$U17,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M17:$U17)+($M17:$U17="DNA")),$M17:$U17),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M17:$U17)+($M17:$U17="DNA")),$M17:$U17),"")),IF(ISNUMBER($U17),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L17" s="33">
@@ -1882,7 +1893,7 @@
         <v/>
       </c>
       <c r="I18" s="32">
-        <f>IF(NOT(AND($A18&lt;&gt;"",OR($G18="",$G18="Active"))),"",IF(AND(MAX($M18:$U18)&gt;0,MAX($M18:$U18)&lt;TODAY(),COUNTBLANK($N18:$U18)&gt;0,COUNTIF($N18:$U18,"DNA")=0),1,0)+COUNTIF($N18:$U18,"DNA")+COUNTIF($V18:$Z18,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A18&lt;&gt;"",OR($G18="",$G18="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M18:$U18)+($M18:$U18="DNA")),$M18:$U18),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M18:$U18)+($M18:$U18="DNA")),$M18:$U18),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M18:$U18)+($M18:$U18="DNA")),$M18:$U18),"")&lt;TODAY())),1,0)+COUNTIF($V18:$Z18,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J18" s="32">
@@ -1890,7 +1901,7 @@
         <v/>
       </c>
       <c r="K18" s="32">
-        <f>IF(NOT(AND($A18&lt;&gt;"",OR($G18="",$G18="Active"))),"",IF($L18&lt;&gt;"",IF($L18=$M18,"Booking",INDEX($N$4:$U$4,MATCH($L18,$N18:$U18,0))),IF(COUNTIF($N18:$U18,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N18:$U18)=0,"All done",IF(MAX($M18:$U18)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A18&lt;&gt;"",OR($G18="",$G18="Active"))),"",IF($L18&lt;&gt;"",IF($L18=$M18,"Booking",INDEX($N$4:$U$4,MATCH($L18,$N18:$U18,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M18:$U18)+($M18:$U18="DNA")),$M18:$U18),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M18:$U18)+($M18:$U18="DNA")),$M18:$U18),"")),IF(ISNUMBER($U18),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L18" s="33">
@@ -1928,7 +1939,7 @@
         <v/>
       </c>
       <c r="I19" s="32">
-        <f>IF(NOT(AND($A19&lt;&gt;"",OR($G19="",$G19="Active"))),"",IF(AND(MAX($M19:$U19)&gt;0,MAX($M19:$U19)&lt;TODAY(),COUNTBLANK($N19:$U19)&gt;0,COUNTIF($N19:$U19,"DNA")=0),1,0)+COUNTIF($N19:$U19,"DNA")+COUNTIF($V19:$Z19,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A19&lt;&gt;"",OR($G19="",$G19="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M19:$U19)+($M19:$U19="DNA")),$M19:$U19),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M19:$U19)+($M19:$U19="DNA")),$M19:$U19),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M19:$U19)+($M19:$U19="DNA")),$M19:$U19),"")&lt;TODAY())),1,0)+COUNTIF($V19:$Z19,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J19" s="32">
@@ -1936,7 +1947,7 @@
         <v/>
       </c>
       <c r="K19" s="32">
-        <f>IF(NOT(AND($A19&lt;&gt;"",OR($G19="",$G19="Active"))),"",IF($L19&lt;&gt;"",IF($L19=$M19,"Booking",INDEX($N$4:$U$4,MATCH($L19,$N19:$U19,0))),IF(COUNTIF($N19:$U19,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N19:$U19)=0,"All done",IF(MAX($M19:$U19)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A19&lt;&gt;"",OR($G19="",$G19="Active"))),"",IF($L19&lt;&gt;"",IF($L19=$M19,"Booking",INDEX($N$4:$U$4,MATCH($L19,$N19:$U19,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M19:$U19)+($M19:$U19="DNA")),$M19:$U19),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M19:$U19)+($M19:$U19="DNA")),$M19:$U19),"")),IF(ISNUMBER($U19),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L19" s="33">
@@ -1974,7 +1985,7 @@
         <v/>
       </c>
       <c r="I20" s="32">
-        <f>IF(NOT(AND($A20&lt;&gt;"",OR($G20="",$G20="Active"))),"",IF(AND(MAX($M20:$U20)&gt;0,MAX($M20:$U20)&lt;TODAY(),COUNTBLANK($N20:$U20)&gt;0,COUNTIF($N20:$U20,"DNA")=0),1,0)+COUNTIF($N20:$U20,"DNA")+COUNTIF($V20:$Z20,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A20&lt;&gt;"",OR($G20="",$G20="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M20:$U20)+($M20:$U20="DNA")),$M20:$U20),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M20:$U20)+($M20:$U20="DNA")),$M20:$U20),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M20:$U20)+($M20:$U20="DNA")),$M20:$U20),"")&lt;TODAY())),1,0)+COUNTIF($V20:$Z20,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J20" s="32">
@@ -1982,7 +1993,7 @@
         <v/>
       </c>
       <c r="K20" s="32">
-        <f>IF(NOT(AND($A20&lt;&gt;"",OR($G20="",$G20="Active"))),"",IF($L20&lt;&gt;"",IF($L20=$M20,"Booking",INDEX($N$4:$U$4,MATCH($L20,$N20:$U20,0))),IF(COUNTIF($N20:$U20,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N20:$U20)=0,"All done",IF(MAX($M20:$U20)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A20&lt;&gt;"",OR($G20="",$G20="Active"))),"",IF($L20&lt;&gt;"",IF($L20=$M20,"Booking",INDEX($N$4:$U$4,MATCH($L20,$N20:$U20,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M20:$U20)+($M20:$U20="DNA")),$M20:$U20),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M20:$U20)+($M20:$U20="DNA")),$M20:$U20),"")),IF(ISNUMBER($U20),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L20" s="33">
@@ -2020,7 +2031,7 @@
         <v/>
       </c>
       <c r="I21" s="32">
-        <f>IF(NOT(AND($A21&lt;&gt;"",OR($G21="",$G21="Active"))),"",IF(AND(MAX($M21:$U21)&gt;0,MAX($M21:$U21)&lt;TODAY(),COUNTBLANK($N21:$U21)&gt;0,COUNTIF($N21:$U21,"DNA")=0),1,0)+COUNTIF($N21:$U21,"DNA")+COUNTIF($V21:$Z21,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A21&lt;&gt;"",OR($G21="",$G21="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M21:$U21)+($M21:$U21="DNA")),$M21:$U21),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M21:$U21)+($M21:$U21="DNA")),$M21:$U21),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M21:$U21)+($M21:$U21="DNA")),$M21:$U21),"")&lt;TODAY())),1,0)+COUNTIF($V21:$Z21,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J21" s="32">
@@ -2028,7 +2039,7 @@
         <v/>
       </c>
       <c r="K21" s="32">
-        <f>IF(NOT(AND($A21&lt;&gt;"",OR($G21="",$G21="Active"))),"",IF($L21&lt;&gt;"",IF($L21=$M21,"Booking",INDEX($N$4:$U$4,MATCH($L21,$N21:$U21,0))),IF(COUNTIF($N21:$U21,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N21:$U21)=0,"All done",IF(MAX($M21:$U21)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A21&lt;&gt;"",OR($G21="",$G21="Active"))),"",IF($L21&lt;&gt;"",IF($L21=$M21,"Booking",INDEX($N$4:$U$4,MATCH($L21,$N21:$U21,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M21:$U21)+($M21:$U21="DNA")),$M21:$U21),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M21:$U21)+($M21:$U21="DNA")),$M21:$U21),"")),IF(ISNUMBER($U21),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L21" s="33">
@@ -2066,7 +2077,7 @@
         <v/>
       </c>
       <c r="I22" s="32">
-        <f>IF(NOT(AND($A22&lt;&gt;"",OR($G22="",$G22="Active"))),"",IF(AND(MAX($M22:$U22)&gt;0,MAX($M22:$U22)&lt;TODAY(),COUNTBLANK($N22:$U22)&gt;0,COUNTIF($N22:$U22,"DNA")=0),1,0)+COUNTIF($N22:$U22,"DNA")+COUNTIF($V22:$Z22,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A22&lt;&gt;"",OR($G22="",$G22="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M22:$U22)+($M22:$U22="DNA")),$M22:$U22),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M22:$U22)+($M22:$U22="DNA")),$M22:$U22),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M22:$U22)+($M22:$U22="DNA")),$M22:$U22),"")&lt;TODAY())),1,0)+COUNTIF($V22:$Z22,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J22" s="32">
@@ -2074,7 +2085,7 @@
         <v/>
       </c>
       <c r="K22" s="32">
-        <f>IF(NOT(AND($A22&lt;&gt;"",OR($G22="",$G22="Active"))),"",IF($L22&lt;&gt;"",IF($L22=$M22,"Booking",INDEX($N$4:$U$4,MATCH($L22,$N22:$U22,0))),IF(COUNTIF($N22:$U22,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N22:$U22)=0,"All done",IF(MAX($M22:$U22)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A22&lt;&gt;"",OR($G22="",$G22="Active"))),"",IF($L22&lt;&gt;"",IF($L22=$M22,"Booking",INDEX($N$4:$U$4,MATCH($L22,$N22:$U22,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M22:$U22)+($M22:$U22="DNA")),$M22:$U22),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M22:$U22)+($M22:$U22="DNA")),$M22:$U22),"")),IF(ISNUMBER($U22),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L22" s="33">
@@ -2112,7 +2123,7 @@
         <v/>
       </c>
       <c r="I23" s="32">
-        <f>IF(NOT(AND($A23&lt;&gt;"",OR($G23="",$G23="Active"))),"",IF(AND(MAX($M23:$U23)&gt;0,MAX($M23:$U23)&lt;TODAY(),COUNTBLANK($N23:$U23)&gt;0,COUNTIF($N23:$U23,"DNA")=0),1,0)+COUNTIF($N23:$U23,"DNA")+COUNTIF($V23:$Z23,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A23&lt;&gt;"",OR($G23="",$G23="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M23:$U23)+($M23:$U23="DNA")),$M23:$U23),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M23:$U23)+($M23:$U23="DNA")),$M23:$U23),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M23:$U23)+($M23:$U23="DNA")),$M23:$U23),"")&lt;TODAY())),1,0)+COUNTIF($V23:$Z23,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J23" s="32">
@@ -2120,7 +2131,7 @@
         <v/>
       </c>
       <c r="K23" s="32">
-        <f>IF(NOT(AND($A23&lt;&gt;"",OR($G23="",$G23="Active"))),"",IF($L23&lt;&gt;"",IF($L23=$M23,"Booking",INDEX($N$4:$U$4,MATCH($L23,$N23:$U23,0))),IF(COUNTIF($N23:$U23,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N23:$U23)=0,"All done",IF(MAX($M23:$U23)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A23&lt;&gt;"",OR($G23="",$G23="Active"))),"",IF($L23&lt;&gt;"",IF($L23=$M23,"Booking",INDEX($N$4:$U$4,MATCH($L23,$N23:$U23,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M23:$U23)+($M23:$U23="DNA")),$M23:$U23),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M23:$U23)+($M23:$U23="DNA")),$M23:$U23),"")),IF(ISNUMBER($U23),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L23" s="33">
@@ -2158,7 +2169,7 @@
         <v/>
       </c>
       <c r="I24" s="32">
-        <f>IF(NOT(AND($A24&lt;&gt;"",OR($G24="",$G24="Active"))),"",IF(AND(MAX($M24:$U24)&gt;0,MAX($M24:$U24)&lt;TODAY(),COUNTBLANK($N24:$U24)&gt;0,COUNTIF($N24:$U24,"DNA")=0),1,0)+COUNTIF($N24:$U24,"DNA")+COUNTIF($V24:$Z24,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A24&lt;&gt;"",OR($G24="",$G24="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M24:$U24)+($M24:$U24="DNA")),$M24:$U24),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M24:$U24)+($M24:$U24="DNA")),$M24:$U24),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M24:$U24)+($M24:$U24="DNA")),$M24:$U24),"")&lt;TODAY())),1,0)+COUNTIF($V24:$Z24,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J24" s="32">
@@ -2166,7 +2177,7 @@
         <v/>
       </c>
       <c r="K24" s="32">
-        <f>IF(NOT(AND($A24&lt;&gt;"",OR($G24="",$G24="Active"))),"",IF($L24&lt;&gt;"",IF($L24=$M24,"Booking",INDEX($N$4:$U$4,MATCH($L24,$N24:$U24,0))),IF(COUNTIF($N24:$U24,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N24:$U24)=0,"All done",IF(MAX($M24:$U24)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A24&lt;&gt;"",OR($G24="",$G24="Active"))),"",IF($L24&lt;&gt;"",IF($L24=$M24,"Booking",INDEX($N$4:$U$4,MATCH($L24,$N24:$U24,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M24:$U24)+($M24:$U24="DNA")),$M24:$U24),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M24:$U24)+($M24:$U24="DNA")),$M24:$U24),"")),IF(ISNUMBER($U24),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L24" s="33">
@@ -2204,7 +2215,7 @@
         <v/>
       </c>
       <c r="I25" s="32">
-        <f>IF(NOT(AND($A25&lt;&gt;"",OR($G25="",$G25="Active"))),"",IF(AND(MAX($M25:$U25)&gt;0,MAX($M25:$U25)&lt;TODAY(),COUNTBLANK($N25:$U25)&gt;0,COUNTIF($N25:$U25,"DNA")=0),1,0)+COUNTIF($N25:$U25,"DNA")+COUNTIF($V25:$Z25,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A25&lt;&gt;"",OR($G25="",$G25="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M25:$U25)+($M25:$U25="DNA")),$M25:$U25),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M25:$U25)+($M25:$U25="DNA")),$M25:$U25),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M25:$U25)+($M25:$U25="DNA")),$M25:$U25),"")&lt;TODAY())),1,0)+COUNTIF($V25:$Z25,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J25" s="32">
@@ -2212,7 +2223,7 @@
         <v/>
       </c>
       <c r="K25" s="32">
-        <f>IF(NOT(AND($A25&lt;&gt;"",OR($G25="",$G25="Active"))),"",IF($L25&lt;&gt;"",IF($L25=$M25,"Booking",INDEX($N$4:$U$4,MATCH($L25,$N25:$U25,0))),IF(COUNTIF($N25:$U25,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N25:$U25)=0,"All done",IF(MAX($M25:$U25)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A25&lt;&gt;"",OR($G25="",$G25="Active"))),"",IF($L25&lt;&gt;"",IF($L25=$M25,"Booking",INDEX($N$4:$U$4,MATCH($L25,$N25:$U25,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M25:$U25)+($M25:$U25="DNA")),$M25:$U25),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M25:$U25)+($M25:$U25="DNA")),$M25:$U25),"")),IF(ISNUMBER($U25),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L25" s="33">
@@ -2250,7 +2261,7 @@
         <v/>
       </c>
       <c r="I26" s="32">
-        <f>IF(NOT(AND($A26&lt;&gt;"",OR($G26="",$G26="Active"))),"",IF(AND(MAX($M26:$U26)&gt;0,MAX($M26:$U26)&lt;TODAY(),COUNTBLANK($N26:$U26)&gt;0,COUNTIF($N26:$U26,"DNA")=0),1,0)+COUNTIF($N26:$U26,"DNA")+COUNTIF($V26:$Z26,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A26&lt;&gt;"",OR($G26="",$G26="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M26:$U26)+($M26:$U26="DNA")),$M26:$U26),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M26:$U26)+($M26:$U26="DNA")),$M26:$U26),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M26:$U26)+($M26:$U26="DNA")),$M26:$U26),"")&lt;TODAY())),1,0)+COUNTIF($V26:$Z26,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J26" s="32">
@@ -2258,7 +2269,7 @@
         <v/>
       </c>
       <c r="K26" s="32">
-        <f>IF(NOT(AND($A26&lt;&gt;"",OR($G26="",$G26="Active"))),"",IF($L26&lt;&gt;"",IF($L26=$M26,"Booking",INDEX($N$4:$U$4,MATCH($L26,$N26:$U26,0))),IF(COUNTIF($N26:$U26,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N26:$U26)=0,"All done",IF(MAX($M26:$U26)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A26&lt;&gt;"",OR($G26="",$G26="Active"))),"",IF($L26&lt;&gt;"",IF($L26=$M26,"Booking",INDEX($N$4:$U$4,MATCH($L26,$N26:$U26,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M26:$U26)+($M26:$U26="DNA")),$M26:$U26),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M26:$U26)+($M26:$U26="DNA")),$M26:$U26),"")),IF(ISNUMBER($U26),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L26" s="33">
@@ -2296,7 +2307,7 @@
         <v/>
       </c>
       <c r="I27" s="32">
-        <f>IF(NOT(AND($A27&lt;&gt;"",OR($G27="",$G27="Active"))),"",IF(AND(MAX($M27:$U27)&gt;0,MAX($M27:$U27)&lt;TODAY(),COUNTBLANK($N27:$U27)&gt;0,COUNTIF($N27:$U27,"DNA")=0),1,0)+COUNTIF($N27:$U27,"DNA")+COUNTIF($V27:$Z27,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A27&lt;&gt;"",OR($G27="",$G27="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M27:$U27)+($M27:$U27="DNA")),$M27:$U27),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M27:$U27)+($M27:$U27="DNA")),$M27:$U27),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M27:$U27)+($M27:$U27="DNA")),$M27:$U27),"")&lt;TODAY())),1,0)+COUNTIF($V27:$Z27,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J27" s="32">
@@ -2304,7 +2315,7 @@
         <v/>
       </c>
       <c r="K27" s="32">
-        <f>IF(NOT(AND($A27&lt;&gt;"",OR($G27="",$G27="Active"))),"",IF($L27&lt;&gt;"",IF($L27=$M27,"Booking",INDEX($N$4:$U$4,MATCH($L27,$N27:$U27,0))),IF(COUNTIF($N27:$U27,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N27:$U27)=0,"All done",IF(MAX($M27:$U27)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A27&lt;&gt;"",OR($G27="",$G27="Active"))),"",IF($L27&lt;&gt;"",IF($L27=$M27,"Booking",INDEX($N$4:$U$4,MATCH($L27,$N27:$U27,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M27:$U27)+($M27:$U27="DNA")),$M27:$U27),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M27:$U27)+($M27:$U27="DNA")),$M27:$U27),"")),IF(ISNUMBER($U27),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L27" s="33">
@@ -2342,7 +2353,7 @@
         <v/>
       </c>
       <c r="I28" s="32">
-        <f>IF(NOT(AND($A28&lt;&gt;"",OR($G28="",$G28="Active"))),"",IF(AND(MAX($M28:$U28)&gt;0,MAX($M28:$U28)&lt;TODAY(),COUNTBLANK($N28:$U28)&gt;0,COUNTIF($N28:$U28,"DNA")=0),1,0)+COUNTIF($N28:$U28,"DNA")+COUNTIF($V28:$Z28,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A28&lt;&gt;"",OR($G28="",$G28="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M28:$U28)+($M28:$U28="DNA")),$M28:$U28),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M28:$U28)+($M28:$U28="DNA")),$M28:$U28),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M28:$U28)+($M28:$U28="DNA")),$M28:$U28),"")&lt;TODAY())),1,0)+COUNTIF($V28:$Z28,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J28" s="32">
@@ -2350,7 +2361,7 @@
         <v/>
       </c>
       <c r="K28" s="32">
-        <f>IF(NOT(AND($A28&lt;&gt;"",OR($G28="",$G28="Active"))),"",IF($L28&lt;&gt;"",IF($L28=$M28,"Booking",INDEX($N$4:$U$4,MATCH($L28,$N28:$U28,0))),IF(COUNTIF($N28:$U28,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N28:$U28)=0,"All done",IF(MAX($M28:$U28)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A28&lt;&gt;"",OR($G28="",$G28="Active"))),"",IF($L28&lt;&gt;"",IF($L28=$M28,"Booking",INDEX($N$4:$U$4,MATCH($L28,$N28:$U28,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M28:$U28)+($M28:$U28="DNA")),$M28:$U28),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M28:$U28)+($M28:$U28="DNA")),$M28:$U28),"")),IF(ISNUMBER($U28),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L28" s="33">
@@ -2388,7 +2399,7 @@
         <v/>
       </c>
       <c r="I29" s="32">
-        <f>IF(NOT(AND($A29&lt;&gt;"",OR($G29="",$G29="Active"))),"",IF(AND(MAX($M29:$U29)&gt;0,MAX($M29:$U29)&lt;TODAY(),COUNTBLANK($N29:$U29)&gt;0,COUNTIF($N29:$U29,"DNA")=0),1,0)+COUNTIF($N29:$U29,"DNA")+COUNTIF($V29:$Z29,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A29&lt;&gt;"",OR($G29="",$G29="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M29:$U29)+($M29:$U29="DNA")),$M29:$U29),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M29:$U29)+($M29:$U29="DNA")),$M29:$U29),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M29:$U29)+($M29:$U29="DNA")),$M29:$U29),"")&lt;TODAY())),1,0)+COUNTIF($V29:$Z29,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J29" s="32">
@@ -2396,7 +2407,7 @@
         <v/>
       </c>
       <c r="K29" s="32">
-        <f>IF(NOT(AND($A29&lt;&gt;"",OR($G29="",$G29="Active"))),"",IF($L29&lt;&gt;"",IF($L29=$M29,"Booking",INDEX($N$4:$U$4,MATCH($L29,$N29:$U29,0))),IF(COUNTIF($N29:$U29,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N29:$U29)=0,"All done",IF(MAX($M29:$U29)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A29&lt;&gt;"",OR($G29="",$G29="Active"))),"",IF($L29&lt;&gt;"",IF($L29=$M29,"Booking",INDEX($N$4:$U$4,MATCH($L29,$N29:$U29,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M29:$U29)+($M29:$U29="DNA")),$M29:$U29),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M29:$U29)+($M29:$U29="DNA")),$M29:$U29),"")),IF(ISNUMBER($U29),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L29" s="33">
@@ -2434,7 +2445,7 @@
         <v/>
       </c>
       <c r="I30" s="32">
-        <f>IF(NOT(AND($A30&lt;&gt;"",OR($G30="",$G30="Active"))),"",IF(AND(MAX($M30:$U30)&gt;0,MAX($M30:$U30)&lt;TODAY(),COUNTBLANK($N30:$U30)&gt;0,COUNTIF($N30:$U30,"DNA")=0),1,0)+COUNTIF($N30:$U30,"DNA")+COUNTIF($V30:$Z30,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A30&lt;&gt;"",OR($G30="",$G30="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M30:$U30)+($M30:$U30="DNA")),$M30:$U30),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M30:$U30)+($M30:$U30="DNA")),$M30:$U30),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M30:$U30)+($M30:$U30="DNA")),$M30:$U30),"")&lt;TODAY())),1,0)+COUNTIF($V30:$Z30,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J30" s="32">
@@ -2442,7 +2453,7 @@
         <v/>
       </c>
       <c r="K30" s="32">
-        <f>IF(NOT(AND($A30&lt;&gt;"",OR($G30="",$G30="Active"))),"",IF($L30&lt;&gt;"",IF($L30=$M30,"Booking",INDEX($N$4:$U$4,MATCH($L30,$N30:$U30,0))),IF(COUNTIF($N30:$U30,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N30:$U30)=0,"All done",IF(MAX($M30:$U30)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A30&lt;&gt;"",OR($G30="",$G30="Active"))),"",IF($L30&lt;&gt;"",IF($L30=$M30,"Booking",INDEX($N$4:$U$4,MATCH($L30,$N30:$U30,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M30:$U30)+($M30:$U30="DNA")),$M30:$U30),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M30:$U30)+($M30:$U30="DNA")),$M30:$U30),"")),IF(ISNUMBER($U30),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L30" s="33">
@@ -2480,7 +2491,7 @@
         <v/>
       </c>
       <c r="I31" s="32">
-        <f>IF(NOT(AND($A31&lt;&gt;"",OR($G31="",$G31="Active"))),"",IF(AND(MAX($M31:$U31)&gt;0,MAX($M31:$U31)&lt;TODAY(),COUNTBLANK($N31:$U31)&gt;0,COUNTIF($N31:$U31,"DNA")=0),1,0)+COUNTIF($N31:$U31,"DNA")+COUNTIF($V31:$Z31,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A31&lt;&gt;"",OR($G31="",$G31="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M31:$U31)+($M31:$U31="DNA")),$M31:$U31),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M31:$U31)+($M31:$U31="DNA")),$M31:$U31),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M31:$U31)+($M31:$U31="DNA")),$M31:$U31),"")&lt;TODAY())),1,0)+COUNTIF($V31:$Z31,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J31" s="32">
@@ -2488,7 +2499,7 @@
         <v/>
       </c>
       <c r="K31" s="32">
-        <f>IF(NOT(AND($A31&lt;&gt;"",OR($G31="",$G31="Active"))),"",IF($L31&lt;&gt;"",IF($L31=$M31,"Booking",INDEX($N$4:$U$4,MATCH($L31,$N31:$U31,0))),IF(COUNTIF($N31:$U31,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N31:$U31)=0,"All done",IF(MAX($M31:$U31)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A31&lt;&gt;"",OR($G31="",$G31="Active"))),"",IF($L31&lt;&gt;"",IF($L31=$M31,"Booking",INDEX($N$4:$U$4,MATCH($L31,$N31:$U31,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M31:$U31)+($M31:$U31="DNA")),$M31:$U31),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M31:$U31)+($M31:$U31="DNA")),$M31:$U31),"")),IF(ISNUMBER($U31),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L31" s="33">
@@ -2526,7 +2537,7 @@
         <v/>
       </c>
       <c r="I32" s="32">
-        <f>IF(NOT(AND($A32&lt;&gt;"",OR($G32="",$G32="Active"))),"",IF(AND(MAX($M32:$U32)&gt;0,MAX($M32:$U32)&lt;TODAY(),COUNTBLANK($N32:$U32)&gt;0,COUNTIF($N32:$U32,"DNA")=0),1,0)+COUNTIF($N32:$U32,"DNA")+COUNTIF($V32:$Z32,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A32&lt;&gt;"",OR($G32="",$G32="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M32:$U32)+($M32:$U32="DNA")),$M32:$U32),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M32:$U32)+($M32:$U32="DNA")),$M32:$U32),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M32:$U32)+($M32:$U32="DNA")),$M32:$U32),"")&lt;TODAY())),1,0)+COUNTIF($V32:$Z32,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J32" s="32">
@@ -2534,7 +2545,7 @@
         <v/>
       </c>
       <c r="K32" s="32">
-        <f>IF(NOT(AND($A32&lt;&gt;"",OR($G32="",$G32="Active"))),"",IF($L32&lt;&gt;"",IF($L32=$M32,"Booking",INDEX($N$4:$U$4,MATCH($L32,$N32:$U32,0))),IF(COUNTIF($N32:$U32,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N32:$U32)=0,"All done",IF(MAX($M32:$U32)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A32&lt;&gt;"",OR($G32="",$G32="Active"))),"",IF($L32&lt;&gt;"",IF($L32=$M32,"Booking",INDEX($N$4:$U$4,MATCH($L32,$N32:$U32,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M32:$U32)+($M32:$U32="DNA")),$M32:$U32),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M32:$U32)+($M32:$U32="DNA")),$M32:$U32),"")),IF(ISNUMBER($U32),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L32" s="33">
@@ -2572,7 +2583,7 @@
         <v/>
       </c>
       <c r="I33" s="32">
-        <f>IF(NOT(AND($A33&lt;&gt;"",OR($G33="",$G33="Active"))),"",IF(AND(MAX($M33:$U33)&gt;0,MAX($M33:$U33)&lt;TODAY(),COUNTBLANK($N33:$U33)&gt;0,COUNTIF($N33:$U33,"DNA")=0),1,0)+COUNTIF($N33:$U33,"DNA")+COUNTIF($V33:$Z33,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A33&lt;&gt;"",OR($G33="",$G33="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M33:$U33)+($M33:$U33="DNA")),$M33:$U33),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M33:$U33)+($M33:$U33="DNA")),$M33:$U33),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M33:$U33)+($M33:$U33="DNA")),$M33:$U33),"")&lt;TODAY())),1,0)+COUNTIF($V33:$Z33,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J33" s="32">
@@ -2580,7 +2591,7 @@
         <v/>
       </c>
       <c r="K33" s="32">
-        <f>IF(NOT(AND($A33&lt;&gt;"",OR($G33="",$G33="Active"))),"",IF($L33&lt;&gt;"",IF($L33=$M33,"Booking",INDEX($N$4:$U$4,MATCH($L33,$N33:$U33,0))),IF(COUNTIF($N33:$U33,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N33:$U33)=0,"All done",IF(MAX($M33:$U33)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A33&lt;&gt;"",OR($G33="",$G33="Active"))),"",IF($L33&lt;&gt;"",IF($L33=$M33,"Booking",INDEX($N$4:$U$4,MATCH($L33,$N33:$U33,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M33:$U33)+($M33:$U33="DNA")),$M33:$U33),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M33:$U33)+($M33:$U33="DNA")),$M33:$U33),"")),IF(ISNUMBER($U33),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L33" s="33">
@@ -2618,7 +2629,7 @@
         <v/>
       </c>
       <c r="I34" s="32">
-        <f>IF(NOT(AND($A34&lt;&gt;"",OR($G34="",$G34="Active"))),"",IF(AND(MAX($M34:$U34)&gt;0,MAX($M34:$U34)&lt;TODAY(),COUNTBLANK($N34:$U34)&gt;0,COUNTIF($N34:$U34,"DNA")=0),1,0)+COUNTIF($N34:$U34,"DNA")+COUNTIF($V34:$Z34,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A34&lt;&gt;"",OR($G34="",$G34="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M34:$U34)+($M34:$U34="DNA")),$M34:$U34),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M34:$U34)+($M34:$U34="DNA")),$M34:$U34),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M34:$U34)+($M34:$U34="DNA")),$M34:$U34),"")&lt;TODAY())),1,0)+COUNTIF($V34:$Z34,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J34" s="32">
@@ -2626,7 +2637,7 @@
         <v/>
       </c>
       <c r="K34" s="32">
-        <f>IF(NOT(AND($A34&lt;&gt;"",OR($G34="",$G34="Active"))),"",IF($L34&lt;&gt;"",IF($L34=$M34,"Booking",INDEX($N$4:$U$4,MATCH($L34,$N34:$U34,0))),IF(COUNTIF($N34:$U34,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N34:$U34)=0,"All done",IF(MAX($M34:$U34)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A34&lt;&gt;"",OR($G34="",$G34="Active"))),"",IF($L34&lt;&gt;"",IF($L34=$M34,"Booking",INDEX($N$4:$U$4,MATCH($L34,$N34:$U34,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M34:$U34)+($M34:$U34="DNA")),$M34:$U34),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M34:$U34)+($M34:$U34="DNA")),$M34:$U34),"")),IF(ISNUMBER($U34),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L34" s="33">
@@ -2664,7 +2675,7 @@
         <v/>
       </c>
       <c r="I35" s="32">
-        <f>IF(NOT(AND($A35&lt;&gt;"",OR($G35="",$G35="Active"))),"",IF(AND(MAX($M35:$U35)&gt;0,MAX($M35:$U35)&lt;TODAY(),COUNTBLANK($N35:$U35)&gt;0,COUNTIF($N35:$U35,"DNA")=0),1,0)+COUNTIF($N35:$U35,"DNA")+COUNTIF($V35:$Z35,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A35&lt;&gt;"",OR($G35="",$G35="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M35:$U35)+($M35:$U35="DNA")),$M35:$U35),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M35:$U35)+($M35:$U35="DNA")),$M35:$U35),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M35:$U35)+($M35:$U35="DNA")),$M35:$U35),"")&lt;TODAY())),1,0)+COUNTIF($V35:$Z35,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J35" s="32">
@@ -2672,7 +2683,7 @@
         <v/>
       </c>
       <c r="K35" s="32">
-        <f>IF(NOT(AND($A35&lt;&gt;"",OR($G35="",$G35="Active"))),"",IF($L35&lt;&gt;"",IF($L35=$M35,"Booking",INDEX($N$4:$U$4,MATCH($L35,$N35:$U35,0))),IF(COUNTIF($N35:$U35,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N35:$U35)=0,"All done",IF(MAX($M35:$U35)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A35&lt;&gt;"",OR($G35="",$G35="Active"))),"",IF($L35&lt;&gt;"",IF($L35=$M35,"Booking",INDEX($N$4:$U$4,MATCH($L35,$N35:$U35,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M35:$U35)+($M35:$U35="DNA")),$M35:$U35),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M35:$U35)+($M35:$U35="DNA")),$M35:$U35),"")),IF(ISNUMBER($U35),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L35" s="33">
@@ -2710,7 +2721,7 @@
         <v/>
       </c>
       <c r="I36" s="32">
-        <f>IF(NOT(AND($A36&lt;&gt;"",OR($G36="",$G36="Active"))),"",IF(AND(MAX($M36:$U36)&gt;0,MAX($M36:$U36)&lt;TODAY(),COUNTBLANK($N36:$U36)&gt;0,COUNTIF($N36:$U36,"DNA")=0),1,0)+COUNTIF($N36:$U36,"DNA")+COUNTIF($V36:$Z36,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A36&lt;&gt;"",OR($G36="",$G36="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M36:$U36)+($M36:$U36="DNA")),$M36:$U36),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M36:$U36)+($M36:$U36="DNA")),$M36:$U36),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M36:$U36)+($M36:$U36="DNA")),$M36:$U36),"")&lt;TODAY())),1,0)+COUNTIF($V36:$Z36,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J36" s="32">
@@ -2718,7 +2729,7 @@
         <v/>
       </c>
       <c r="K36" s="32">
-        <f>IF(NOT(AND($A36&lt;&gt;"",OR($G36="",$G36="Active"))),"",IF($L36&lt;&gt;"",IF($L36=$M36,"Booking",INDEX($N$4:$U$4,MATCH($L36,$N36:$U36,0))),IF(COUNTIF($N36:$U36,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N36:$U36)=0,"All done",IF(MAX($M36:$U36)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A36&lt;&gt;"",OR($G36="",$G36="Active"))),"",IF($L36&lt;&gt;"",IF($L36=$M36,"Booking",INDEX($N$4:$U$4,MATCH($L36,$N36:$U36,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M36:$U36)+($M36:$U36="DNA")),$M36:$U36),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M36:$U36)+($M36:$U36="DNA")),$M36:$U36),"")),IF(ISNUMBER($U36),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L36" s="33">
@@ -2756,7 +2767,7 @@
         <v/>
       </c>
       <c r="I37" s="32">
-        <f>IF(NOT(AND($A37&lt;&gt;"",OR($G37="",$G37="Active"))),"",IF(AND(MAX($M37:$U37)&gt;0,MAX($M37:$U37)&lt;TODAY(),COUNTBLANK($N37:$U37)&gt;0,COUNTIF($N37:$U37,"DNA")=0),1,0)+COUNTIF($N37:$U37,"DNA")+COUNTIF($V37:$Z37,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A37&lt;&gt;"",OR($G37="",$G37="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M37:$U37)+($M37:$U37="DNA")),$M37:$U37),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M37:$U37)+($M37:$U37="DNA")),$M37:$U37),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M37:$U37)+($M37:$U37="DNA")),$M37:$U37),"")&lt;TODAY())),1,0)+COUNTIF($V37:$Z37,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J37" s="32">
@@ -2764,7 +2775,7 @@
         <v/>
       </c>
       <c r="K37" s="32">
-        <f>IF(NOT(AND($A37&lt;&gt;"",OR($G37="",$G37="Active"))),"",IF($L37&lt;&gt;"",IF($L37=$M37,"Booking",INDEX($N$4:$U$4,MATCH($L37,$N37:$U37,0))),IF(COUNTIF($N37:$U37,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N37:$U37)=0,"All done",IF(MAX($M37:$U37)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A37&lt;&gt;"",OR($G37="",$G37="Active"))),"",IF($L37&lt;&gt;"",IF($L37=$M37,"Booking",INDEX($N$4:$U$4,MATCH($L37,$N37:$U37,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M37:$U37)+($M37:$U37="DNA")),$M37:$U37),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M37:$U37)+($M37:$U37="DNA")),$M37:$U37),"")),IF(ISNUMBER($U37),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L37" s="33">
@@ -2802,7 +2813,7 @@
         <v/>
       </c>
       <c r="I38" s="32">
-        <f>IF(NOT(AND($A38&lt;&gt;"",OR($G38="",$G38="Active"))),"",IF(AND(MAX($M38:$U38)&gt;0,MAX($M38:$U38)&lt;TODAY(),COUNTBLANK($N38:$U38)&gt;0,COUNTIF($N38:$U38,"DNA")=0),1,0)+COUNTIF($N38:$U38,"DNA")+COUNTIF($V38:$Z38,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A38&lt;&gt;"",OR($G38="",$G38="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M38:$U38)+($M38:$U38="DNA")),$M38:$U38),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M38:$U38)+($M38:$U38="DNA")),$M38:$U38),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M38:$U38)+($M38:$U38="DNA")),$M38:$U38),"")&lt;TODAY())),1,0)+COUNTIF($V38:$Z38,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J38" s="32">
@@ -2810,7 +2821,7 @@
         <v/>
       </c>
       <c r="K38" s="32">
-        <f>IF(NOT(AND($A38&lt;&gt;"",OR($G38="",$G38="Active"))),"",IF($L38&lt;&gt;"",IF($L38=$M38,"Booking",INDEX($N$4:$U$4,MATCH($L38,$N38:$U38,0))),IF(COUNTIF($N38:$U38,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N38:$U38)=0,"All done",IF(MAX($M38:$U38)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A38&lt;&gt;"",OR($G38="",$G38="Active"))),"",IF($L38&lt;&gt;"",IF($L38=$M38,"Booking",INDEX($N$4:$U$4,MATCH($L38,$N38:$U38,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M38:$U38)+($M38:$U38="DNA")),$M38:$U38),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M38:$U38)+($M38:$U38="DNA")),$M38:$U38),"")),IF(ISNUMBER($U38),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L38" s="33">
@@ -2848,7 +2859,7 @@
         <v/>
       </c>
       <c r="I39" s="32">
-        <f>IF(NOT(AND($A39&lt;&gt;"",OR($G39="",$G39="Active"))),"",IF(AND(MAX($M39:$U39)&gt;0,MAX($M39:$U39)&lt;TODAY(),COUNTBLANK($N39:$U39)&gt;0,COUNTIF($N39:$U39,"DNA")=0),1,0)+COUNTIF($N39:$U39,"DNA")+COUNTIF($V39:$Z39,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A39&lt;&gt;"",OR($G39="",$G39="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M39:$U39)+($M39:$U39="DNA")),$M39:$U39),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M39:$U39)+($M39:$U39="DNA")),$M39:$U39),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M39:$U39)+($M39:$U39="DNA")),$M39:$U39),"")&lt;TODAY())),1,0)+COUNTIF($V39:$Z39,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J39" s="32">
@@ -2856,7 +2867,7 @@
         <v/>
       </c>
       <c r="K39" s="32">
-        <f>IF(NOT(AND($A39&lt;&gt;"",OR($G39="",$G39="Active"))),"",IF($L39&lt;&gt;"",IF($L39=$M39,"Booking",INDEX($N$4:$U$4,MATCH($L39,$N39:$U39,0))),IF(COUNTIF($N39:$U39,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N39:$U39)=0,"All done",IF(MAX($M39:$U39)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A39&lt;&gt;"",OR($G39="",$G39="Active"))),"",IF($L39&lt;&gt;"",IF($L39=$M39,"Booking",INDEX($N$4:$U$4,MATCH($L39,$N39:$U39,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M39:$U39)+($M39:$U39="DNA")),$M39:$U39),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M39:$U39)+($M39:$U39="DNA")),$M39:$U39),"")),IF(ISNUMBER($U39),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L39" s="33">
@@ -2894,7 +2905,7 @@
         <v/>
       </c>
       <c r="I40" s="32">
-        <f>IF(NOT(AND($A40&lt;&gt;"",OR($G40="",$G40="Active"))),"",IF(AND(MAX($M40:$U40)&gt;0,MAX($M40:$U40)&lt;TODAY(),COUNTBLANK($N40:$U40)&gt;0,COUNTIF($N40:$U40,"DNA")=0),1,0)+COUNTIF($N40:$U40,"DNA")+COUNTIF($V40:$Z40,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A40&lt;&gt;"",OR($G40="",$G40="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M40:$U40)+($M40:$U40="DNA")),$M40:$U40),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M40:$U40)+($M40:$U40="DNA")),$M40:$U40),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M40:$U40)+($M40:$U40="DNA")),$M40:$U40),"")&lt;TODAY())),1,0)+COUNTIF($V40:$Z40,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J40" s="32">
@@ -2902,7 +2913,7 @@
         <v/>
       </c>
       <c r="K40" s="32">
-        <f>IF(NOT(AND($A40&lt;&gt;"",OR($G40="",$G40="Active"))),"",IF($L40&lt;&gt;"",IF($L40=$M40,"Booking",INDEX($N$4:$U$4,MATCH($L40,$N40:$U40,0))),IF(COUNTIF($N40:$U40,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N40:$U40)=0,"All done",IF(MAX($M40:$U40)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A40&lt;&gt;"",OR($G40="",$G40="Active"))),"",IF($L40&lt;&gt;"",IF($L40=$M40,"Booking",INDEX($N$4:$U$4,MATCH($L40,$N40:$U40,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M40:$U40)+($M40:$U40="DNA")),$M40:$U40),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M40:$U40)+($M40:$U40="DNA")),$M40:$U40),"")),IF(ISNUMBER($U40),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L40" s="33">
@@ -2940,7 +2951,7 @@
         <v/>
       </c>
       <c r="I41" s="32">
-        <f>IF(NOT(AND($A41&lt;&gt;"",OR($G41="",$G41="Active"))),"",IF(AND(MAX($M41:$U41)&gt;0,MAX($M41:$U41)&lt;TODAY(),COUNTBLANK($N41:$U41)&gt;0,COUNTIF($N41:$U41,"DNA")=0),1,0)+COUNTIF($N41:$U41,"DNA")+COUNTIF($V41:$Z41,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A41&lt;&gt;"",OR($G41="",$G41="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M41:$U41)+($M41:$U41="DNA")),$M41:$U41),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M41:$U41)+($M41:$U41="DNA")),$M41:$U41),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M41:$U41)+($M41:$U41="DNA")),$M41:$U41),"")&lt;TODAY())),1,0)+COUNTIF($V41:$Z41,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J41" s="32">
@@ -2948,7 +2959,7 @@
         <v/>
       </c>
       <c r="K41" s="32">
-        <f>IF(NOT(AND($A41&lt;&gt;"",OR($G41="",$G41="Active"))),"",IF($L41&lt;&gt;"",IF($L41=$M41,"Booking",INDEX($N$4:$U$4,MATCH($L41,$N41:$U41,0))),IF(COUNTIF($N41:$U41,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N41:$U41)=0,"All done",IF(MAX($M41:$U41)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A41&lt;&gt;"",OR($G41="",$G41="Active"))),"",IF($L41&lt;&gt;"",IF($L41=$M41,"Booking",INDEX($N$4:$U$4,MATCH($L41,$N41:$U41,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M41:$U41)+($M41:$U41="DNA")),$M41:$U41),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M41:$U41)+($M41:$U41="DNA")),$M41:$U41),"")),IF(ISNUMBER($U41),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L41" s="33">
@@ -2986,7 +2997,7 @@
         <v/>
       </c>
       <c r="I42" s="32">
-        <f>IF(NOT(AND($A42&lt;&gt;"",OR($G42="",$G42="Active"))),"",IF(AND(MAX($M42:$U42)&gt;0,MAX($M42:$U42)&lt;TODAY(),COUNTBLANK($N42:$U42)&gt;0,COUNTIF($N42:$U42,"DNA")=0),1,0)+COUNTIF($N42:$U42,"DNA")+COUNTIF($V42:$Z42,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A42&lt;&gt;"",OR($G42="",$G42="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M42:$U42)+($M42:$U42="DNA")),$M42:$U42),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M42:$U42)+($M42:$U42="DNA")),$M42:$U42),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M42:$U42)+($M42:$U42="DNA")),$M42:$U42),"")&lt;TODAY())),1,0)+COUNTIF($V42:$Z42,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J42" s="32">
@@ -2994,7 +3005,7 @@
         <v/>
       </c>
       <c r="K42" s="32">
-        <f>IF(NOT(AND($A42&lt;&gt;"",OR($G42="",$G42="Active"))),"",IF($L42&lt;&gt;"",IF($L42=$M42,"Booking",INDEX($N$4:$U$4,MATCH($L42,$N42:$U42,0))),IF(COUNTIF($N42:$U42,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N42:$U42)=0,"All done",IF(MAX($M42:$U42)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A42&lt;&gt;"",OR($G42="",$G42="Active"))),"",IF($L42&lt;&gt;"",IF($L42=$M42,"Booking",INDEX($N$4:$U$4,MATCH($L42,$N42:$U42,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M42:$U42)+($M42:$U42="DNA")),$M42:$U42),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M42:$U42)+($M42:$U42="DNA")),$M42:$U42),"")),IF(ISNUMBER($U42),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L42" s="33">
@@ -3032,7 +3043,7 @@
         <v/>
       </c>
       <c r="I43" s="32">
-        <f>IF(NOT(AND($A43&lt;&gt;"",OR($G43="",$G43="Active"))),"",IF(AND(MAX($M43:$U43)&gt;0,MAX($M43:$U43)&lt;TODAY(),COUNTBLANK($N43:$U43)&gt;0,COUNTIF($N43:$U43,"DNA")=0),1,0)+COUNTIF($N43:$U43,"DNA")+COUNTIF($V43:$Z43,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A43&lt;&gt;"",OR($G43="",$G43="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M43:$U43)+($M43:$U43="DNA")),$M43:$U43),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M43:$U43)+($M43:$U43="DNA")),$M43:$U43),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M43:$U43)+($M43:$U43="DNA")),$M43:$U43),"")&lt;TODAY())),1,0)+COUNTIF($V43:$Z43,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J43" s="32">
@@ -3040,7 +3051,7 @@
         <v/>
       </c>
       <c r="K43" s="32">
-        <f>IF(NOT(AND($A43&lt;&gt;"",OR($G43="",$G43="Active"))),"",IF($L43&lt;&gt;"",IF($L43=$M43,"Booking",INDEX($N$4:$U$4,MATCH($L43,$N43:$U43,0))),IF(COUNTIF($N43:$U43,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N43:$U43)=0,"All done",IF(MAX($M43:$U43)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A43&lt;&gt;"",OR($G43="",$G43="Active"))),"",IF($L43&lt;&gt;"",IF($L43=$M43,"Booking",INDEX($N$4:$U$4,MATCH($L43,$N43:$U43,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M43:$U43)+($M43:$U43="DNA")),$M43:$U43),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M43:$U43)+($M43:$U43="DNA")),$M43:$U43),"")),IF(ISNUMBER($U43),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L43" s="33">
@@ -3078,7 +3089,7 @@
         <v/>
       </c>
       <c r="I44" s="32">
-        <f>IF(NOT(AND($A44&lt;&gt;"",OR($G44="",$G44="Active"))),"",IF(AND(MAX($M44:$U44)&gt;0,MAX($M44:$U44)&lt;TODAY(),COUNTBLANK($N44:$U44)&gt;0,COUNTIF($N44:$U44,"DNA")=0),1,0)+COUNTIF($N44:$U44,"DNA")+COUNTIF($V44:$Z44,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A44&lt;&gt;"",OR($G44="",$G44="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M44:$U44)+($M44:$U44="DNA")),$M44:$U44),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M44:$U44)+($M44:$U44="DNA")),$M44:$U44),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M44:$U44)+($M44:$U44="DNA")),$M44:$U44),"")&lt;TODAY())),1,0)+COUNTIF($V44:$Z44,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J44" s="32">
@@ -3086,7 +3097,7 @@
         <v/>
       </c>
       <c r="K44" s="32">
-        <f>IF(NOT(AND($A44&lt;&gt;"",OR($G44="",$G44="Active"))),"",IF($L44&lt;&gt;"",IF($L44=$M44,"Booking",INDEX($N$4:$U$4,MATCH($L44,$N44:$U44,0))),IF(COUNTIF($N44:$U44,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N44:$U44)=0,"All done",IF(MAX($M44:$U44)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A44&lt;&gt;"",OR($G44="",$G44="Active"))),"",IF($L44&lt;&gt;"",IF($L44=$M44,"Booking",INDEX($N$4:$U$4,MATCH($L44,$N44:$U44,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M44:$U44)+($M44:$U44="DNA")),$M44:$U44),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M44:$U44)+($M44:$U44="DNA")),$M44:$U44),"")),IF(ISNUMBER($U44),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L44" s="33">
@@ -3124,7 +3135,7 @@
         <v/>
       </c>
       <c r="I45" s="32">
-        <f>IF(NOT(AND($A45&lt;&gt;"",OR($G45="",$G45="Active"))),"",IF(AND(MAX($M45:$U45)&gt;0,MAX($M45:$U45)&lt;TODAY(),COUNTBLANK($N45:$U45)&gt;0,COUNTIF($N45:$U45,"DNA")=0),1,0)+COUNTIF($N45:$U45,"DNA")+COUNTIF($V45:$Z45,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A45&lt;&gt;"",OR($G45="",$G45="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M45:$U45)+($M45:$U45="DNA")),$M45:$U45),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M45:$U45)+($M45:$U45="DNA")),$M45:$U45),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M45:$U45)+($M45:$U45="DNA")),$M45:$U45),"")&lt;TODAY())),1,0)+COUNTIF($V45:$Z45,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J45" s="32">
@@ -3132,7 +3143,7 @@
         <v/>
       </c>
       <c r="K45" s="32">
-        <f>IF(NOT(AND($A45&lt;&gt;"",OR($G45="",$G45="Active"))),"",IF($L45&lt;&gt;"",IF($L45=$M45,"Booking",INDEX($N$4:$U$4,MATCH($L45,$N45:$U45,0))),IF(COUNTIF($N45:$U45,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N45:$U45)=0,"All done",IF(MAX($M45:$U45)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A45&lt;&gt;"",OR($G45="",$G45="Active"))),"",IF($L45&lt;&gt;"",IF($L45=$M45,"Booking",INDEX($N$4:$U$4,MATCH($L45,$N45:$U45,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M45:$U45)+($M45:$U45="DNA")),$M45:$U45),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M45:$U45)+($M45:$U45="DNA")),$M45:$U45),"")),IF(ISNUMBER($U45),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L45" s="33">
@@ -3170,7 +3181,7 @@
         <v/>
       </c>
       <c r="I46" s="32">
-        <f>IF(NOT(AND($A46&lt;&gt;"",OR($G46="",$G46="Active"))),"",IF(AND(MAX($M46:$U46)&gt;0,MAX($M46:$U46)&lt;TODAY(),COUNTBLANK($N46:$U46)&gt;0,COUNTIF($N46:$U46,"DNA")=0),1,0)+COUNTIF($N46:$U46,"DNA")+COUNTIF($V46:$Z46,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A46&lt;&gt;"",OR($G46="",$G46="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M46:$U46)+($M46:$U46="DNA")),$M46:$U46),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M46:$U46)+($M46:$U46="DNA")),$M46:$U46),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M46:$U46)+($M46:$U46="DNA")),$M46:$U46),"")&lt;TODAY())),1,0)+COUNTIF($V46:$Z46,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J46" s="32">
@@ -3178,7 +3189,7 @@
         <v/>
       </c>
       <c r="K46" s="32">
-        <f>IF(NOT(AND($A46&lt;&gt;"",OR($G46="",$G46="Active"))),"",IF($L46&lt;&gt;"",IF($L46=$M46,"Booking",INDEX($N$4:$U$4,MATCH($L46,$N46:$U46,0))),IF(COUNTIF($N46:$U46,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N46:$U46)=0,"All done",IF(MAX($M46:$U46)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A46&lt;&gt;"",OR($G46="",$G46="Active"))),"",IF($L46&lt;&gt;"",IF($L46=$M46,"Booking",INDEX($N$4:$U$4,MATCH($L46,$N46:$U46,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M46:$U46)+($M46:$U46="DNA")),$M46:$U46),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M46:$U46)+($M46:$U46="DNA")),$M46:$U46),"")),IF(ISNUMBER($U46),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L46" s="33">
@@ -3216,7 +3227,7 @@
         <v/>
       </c>
       <c r="I47" s="32">
-        <f>IF(NOT(AND($A47&lt;&gt;"",OR($G47="",$G47="Active"))),"",IF(AND(MAX($M47:$U47)&gt;0,MAX($M47:$U47)&lt;TODAY(),COUNTBLANK($N47:$U47)&gt;0,COUNTIF($N47:$U47,"DNA")=0),1,0)+COUNTIF($N47:$U47,"DNA")+COUNTIF($V47:$Z47,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A47&lt;&gt;"",OR($G47="",$G47="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M47:$U47)+($M47:$U47="DNA")),$M47:$U47),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M47:$U47)+($M47:$U47="DNA")),$M47:$U47),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M47:$U47)+($M47:$U47="DNA")),$M47:$U47),"")&lt;TODAY())),1,0)+COUNTIF($V47:$Z47,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J47" s="32">
@@ -3224,7 +3235,7 @@
         <v/>
       </c>
       <c r="K47" s="32">
-        <f>IF(NOT(AND($A47&lt;&gt;"",OR($G47="",$G47="Active"))),"",IF($L47&lt;&gt;"",IF($L47=$M47,"Booking",INDEX($N$4:$U$4,MATCH($L47,$N47:$U47,0))),IF(COUNTIF($N47:$U47,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N47:$U47)=0,"All done",IF(MAX($M47:$U47)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A47&lt;&gt;"",OR($G47="",$G47="Active"))),"",IF($L47&lt;&gt;"",IF($L47=$M47,"Booking",INDEX($N$4:$U$4,MATCH($L47,$N47:$U47,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M47:$U47)+($M47:$U47="DNA")),$M47:$U47),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M47:$U47)+($M47:$U47="DNA")),$M47:$U47),"")),IF(ISNUMBER($U47),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L47" s="33">
@@ -3262,7 +3273,7 @@
         <v/>
       </c>
       <c r="I48" s="32">
-        <f>IF(NOT(AND($A48&lt;&gt;"",OR($G48="",$G48="Active"))),"",IF(AND(MAX($M48:$U48)&gt;0,MAX($M48:$U48)&lt;TODAY(),COUNTBLANK($N48:$U48)&gt;0,COUNTIF($N48:$U48,"DNA")=0),1,0)+COUNTIF($N48:$U48,"DNA")+COUNTIF($V48:$Z48,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A48&lt;&gt;"",OR($G48="",$G48="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M48:$U48)+($M48:$U48="DNA")),$M48:$U48),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M48:$U48)+($M48:$U48="DNA")),$M48:$U48),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M48:$U48)+($M48:$U48="DNA")),$M48:$U48),"")&lt;TODAY())),1,0)+COUNTIF($V48:$Z48,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J48" s="32">
@@ -3270,7 +3281,7 @@
         <v/>
       </c>
       <c r="K48" s="32">
-        <f>IF(NOT(AND($A48&lt;&gt;"",OR($G48="",$G48="Active"))),"",IF($L48&lt;&gt;"",IF($L48=$M48,"Booking",INDEX($N$4:$U$4,MATCH($L48,$N48:$U48,0))),IF(COUNTIF($N48:$U48,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N48:$U48)=0,"All done",IF(MAX($M48:$U48)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A48&lt;&gt;"",OR($G48="",$G48="Active"))),"",IF($L48&lt;&gt;"",IF($L48=$M48,"Booking",INDEX($N$4:$U$4,MATCH($L48,$N48:$U48,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M48:$U48)+($M48:$U48="DNA")),$M48:$U48),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M48:$U48)+($M48:$U48="DNA")),$M48:$U48),"")),IF(ISNUMBER($U48),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L48" s="33">
@@ -3308,7 +3319,7 @@
         <v/>
       </c>
       <c r="I49" s="32">
-        <f>IF(NOT(AND($A49&lt;&gt;"",OR($G49="",$G49="Active"))),"",IF(AND(MAX($M49:$U49)&gt;0,MAX($M49:$U49)&lt;TODAY(),COUNTBLANK($N49:$U49)&gt;0,COUNTIF($N49:$U49,"DNA")=0),1,0)+COUNTIF($N49:$U49,"DNA")+COUNTIF($V49:$Z49,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A49&lt;&gt;"",OR($G49="",$G49="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M49:$U49)+($M49:$U49="DNA")),$M49:$U49),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M49:$U49)+($M49:$U49="DNA")),$M49:$U49),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M49:$U49)+($M49:$U49="DNA")),$M49:$U49),"")&lt;TODAY())),1,0)+COUNTIF($V49:$Z49,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J49" s="32">
@@ -3316,7 +3327,7 @@
         <v/>
       </c>
       <c r="K49" s="32">
-        <f>IF(NOT(AND($A49&lt;&gt;"",OR($G49="",$G49="Active"))),"",IF($L49&lt;&gt;"",IF($L49=$M49,"Booking",INDEX($N$4:$U$4,MATCH($L49,$N49:$U49,0))),IF(COUNTIF($N49:$U49,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N49:$U49)=0,"All done",IF(MAX($M49:$U49)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A49&lt;&gt;"",OR($G49="",$G49="Active"))),"",IF($L49&lt;&gt;"",IF($L49=$M49,"Booking",INDEX($N$4:$U$4,MATCH($L49,$N49:$U49,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M49:$U49)+($M49:$U49="DNA")),$M49:$U49),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M49:$U49)+($M49:$U49="DNA")),$M49:$U49),"")),IF(ISNUMBER($U49),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L49" s="33">
@@ -3354,7 +3365,7 @@
         <v/>
       </c>
       <c r="I50" s="32">
-        <f>IF(NOT(AND($A50&lt;&gt;"",OR($G50="",$G50="Active"))),"",IF(AND(MAX($M50:$U50)&gt;0,MAX($M50:$U50)&lt;TODAY(),COUNTBLANK($N50:$U50)&gt;0,COUNTIF($N50:$U50,"DNA")=0),1,0)+COUNTIF($N50:$U50,"DNA")+COUNTIF($V50:$Z50,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A50&lt;&gt;"",OR($G50="",$G50="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M50:$U50)+($M50:$U50="DNA")),$M50:$U50),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M50:$U50)+($M50:$U50="DNA")),$M50:$U50),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M50:$U50)+($M50:$U50="DNA")),$M50:$U50),"")&lt;TODAY())),1,0)+COUNTIF($V50:$Z50,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J50" s="32">
@@ -3362,7 +3373,7 @@
         <v/>
       </c>
       <c r="K50" s="32">
-        <f>IF(NOT(AND($A50&lt;&gt;"",OR($G50="",$G50="Active"))),"",IF($L50&lt;&gt;"",IF($L50=$M50,"Booking",INDEX($N$4:$U$4,MATCH($L50,$N50:$U50,0))),IF(COUNTIF($N50:$U50,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N50:$U50)=0,"All done",IF(MAX($M50:$U50)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A50&lt;&gt;"",OR($G50="",$G50="Active"))),"",IF($L50&lt;&gt;"",IF($L50=$M50,"Booking",INDEX($N$4:$U$4,MATCH($L50,$N50:$U50,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M50:$U50)+($M50:$U50="DNA")),$M50:$U50),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M50:$U50)+($M50:$U50="DNA")),$M50:$U50),"")),IF(ISNUMBER($U50),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L50" s="33">
@@ -3400,7 +3411,7 @@
         <v/>
       </c>
       <c r="I51" s="32">
-        <f>IF(NOT(AND($A51&lt;&gt;"",OR($G51="",$G51="Active"))),"",IF(AND(MAX($M51:$U51)&gt;0,MAX($M51:$U51)&lt;TODAY(),COUNTBLANK($N51:$U51)&gt;0,COUNTIF($N51:$U51,"DNA")=0),1,0)+COUNTIF($N51:$U51,"DNA")+COUNTIF($V51:$Z51,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A51&lt;&gt;"",OR($G51="",$G51="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M51:$U51)+($M51:$U51="DNA")),$M51:$U51),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M51:$U51)+($M51:$U51="DNA")),$M51:$U51),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M51:$U51)+($M51:$U51="DNA")),$M51:$U51),"")&lt;TODAY())),1,0)+COUNTIF($V51:$Z51,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J51" s="32">
@@ -3408,7 +3419,7 @@
         <v/>
       </c>
       <c r="K51" s="32">
-        <f>IF(NOT(AND($A51&lt;&gt;"",OR($G51="",$G51="Active"))),"",IF($L51&lt;&gt;"",IF($L51=$M51,"Booking",INDEX($N$4:$U$4,MATCH($L51,$N51:$U51,0))),IF(COUNTIF($N51:$U51,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N51:$U51)=0,"All done",IF(MAX($M51:$U51)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A51&lt;&gt;"",OR($G51="",$G51="Active"))),"",IF($L51&lt;&gt;"",IF($L51=$M51,"Booking",INDEX($N$4:$U$4,MATCH($L51,$N51:$U51,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M51:$U51)+($M51:$U51="DNA")),$M51:$U51),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M51:$U51)+($M51:$U51="DNA")),$M51:$U51),"")),IF(ISNUMBER($U51),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L51" s="33">
@@ -3446,7 +3457,7 @@
         <v/>
       </c>
       <c r="I52" s="32">
-        <f>IF(NOT(AND($A52&lt;&gt;"",OR($G52="",$G52="Active"))),"",IF(AND(MAX($M52:$U52)&gt;0,MAX($M52:$U52)&lt;TODAY(),COUNTBLANK($N52:$U52)&gt;0,COUNTIF($N52:$U52,"DNA")=0),1,0)+COUNTIF($N52:$U52,"DNA")+COUNTIF($V52:$Z52,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A52&lt;&gt;"",OR($G52="",$G52="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M52:$U52)+($M52:$U52="DNA")),$M52:$U52),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M52:$U52)+($M52:$U52="DNA")),$M52:$U52),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M52:$U52)+($M52:$U52="DNA")),$M52:$U52),"")&lt;TODAY())),1,0)+COUNTIF($V52:$Z52,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J52" s="32">
@@ -3454,7 +3465,7 @@
         <v/>
       </c>
       <c r="K52" s="32">
-        <f>IF(NOT(AND($A52&lt;&gt;"",OR($G52="",$G52="Active"))),"",IF($L52&lt;&gt;"",IF($L52=$M52,"Booking",INDEX($N$4:$U$4,MATCH($L52,$N52:$U52,0))),IF(COUNTIF($N52:$U52,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N52:$U52)=0,"All done",IF(MAX($M52:$U52)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A52&lt;&gt;"",OR($G52="",$G52="Active"))),"",IF($L52&lt;&gt;"",IF($L52=$M52,"Booking",INDEX($N$4:$U$4,MATCH($L52,$N52:$U52,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M52:$U52)+($M52:$U52="DNA")),$M52:$U52),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M52:$U52)+($M52:$U52="DNA")),$M52:$U52),"")),IF(ISNUMBER($U52),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L52" s="33">
@@ -3492,7 +3503,7 @@
         <v/>
       </c>
       <c r="I53" s="32">
-        <f>IF(NOT(AND($A53&lt;&gt;"",OR($G53="",$G53="Active"))),"",IF(AND(MAX($M53:$U53)&gt;0,MAX($M53:$U53)&lt;TODAY(),COUNTBLANK($N53:$U53)&gt;0,COUNTIF($N53:$U53,"DNA")=0),1,0)+COUNTIF($N53:$U53,"DNA")+COUNTIF($V53:$Z53,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A53&lt;&gt;"",OR($G53="",$G53="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M53:$U53)+($M53:$U53="DNA")),$M53:$U53),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M53:$U53)+($M53:$U53="DNA")),$M53:$U53),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M53:$U53)+($M53:$U53="DNA")),$M53:$U53),"")&lt;TODAY())),1,0)+COUNTIF($V53:$Z53,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J53" s="32">
@@ -3500,7 +3511,7 @@
         <v/>
       </c>
       <c r="K53" s="32">
-        <f>IF(NOT(AND($A53&lt;&gt;"",OR($G53="",$G53="Active"))),"",IF($L53&lt;&gt;"",IF($L53=$M53,"Booking",INDEX($N$4:$U$4,MATCH($L53,$N53:$U53,0))),IF(COUNTIF($N53:$U53,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N53:$U53)=0,"All done",IF(MAX($M53:$U53)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A53&lt;&gt;"",OR($G53="",$G53="Active"))),"",IF($L53&lt;&gt;"",IF($L53=$M53,"Booking",INDEX($N$4:$U$4,MATCH($L53,$N53:$U53,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M53:$U53)+($M53:$U53="DNA")),$M53:$U53),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M53:$U53)+($M53:$U53="DNA")),$M53:$U53),"")),IF(ISNUMBER($U53),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L53" s="33">
@@ -3538,7 +3549,7 @@
         <v/>
       </c>
       <c r="I54" s="32">
-        <f>IF(NOT(AND($A54&lt;&gt;"",OR($G54="",$G54="Active"))),"",IF(AND(MAX($M54:$U54)&gt;0,MAX($M54:$U54)&lt;TODAY(),COUNTBLANK($N54:$U54)&gt;0,COUNTIF($N54:$U54,"DNA")=0),1,0)+COUNTIF($N54:$U54,"DNA")+COUNTIF($V54:$Z54,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A54&lt;&gt;"",OR($G54="",$G54="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M54:$U54)+($M54:$U54="DNA")),$M54:$U54),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M54:$U54)+($M54:$U54="DNA")),$M54:$U54),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M54:$U54)+($M54:$U54="DNA")),$M54:$U54),"")&lt;TODAY())),1,0)+COUNTIF($V54:$Z54,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J54" s="32">
@@ -3546,7 +3557,7 @@
         <v/>
       </c>
       <c r="K54" s="32">
-        <f>IF(NOT(AND($A54&lt;&gt;"",OR($G54="",$G54="Active"))),"",IF($L54&lt;&gt;"",IF($L54=$M54,"Booking",INDEX($N$4:$U$4,MATCH($L54,$N54:$U54,0))),IF(COUNTIF($N54:$U54,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N54:$U54)=0,"All done",IF(MAX($M54:$U54)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A54&lt;&gt;"",OR($G54="",$G54="Active"))),"",IF($L54&lt;&gt;"",IF($L54=$M54,"Booking",INDEX($N$4:$U$4,MATCH($L54,$N54:$U54,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M54:$U54)+($M54:$U54="DNA")),$M54:$U54),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M54:$U54)+($M54:$U54="DNA")),$M54:$U54),"")),IF(ISNUMBER($U54),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L54" s="33">
@@ -3584,7 +3595,7 @@
         <v/>
       </c>
       <c r="I55" s="32">
-        <f>IF(NOT(AND($A55&lt;&gt;"",OR($G55="",$G55="Active"))),"",IF(AND(MAX($M55:$U55)&gt;0,MAX($M55:$U55)&lt;TODAY(),COUNTBLANK($N55:$U55)&gt;0,COUNTIF($N55:$U55,"DNA")=0),1,0)+COUNTIF($N55:$U55,"DNA")+COUNTIF($V55:$Z55,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A55&lt;&gt;"",OR($G55="",$G55="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M55:$U55)+($M55:$U55="DNA")),$M55:$U55),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M55:$U55)+($M55:$U55="DNA")),$M55:$U55),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M55:$U55)+($M55:$U55="DNA")),$M55:$U55),"")&lt;TODAY())),1,0)+COUNTIF($V55:$Z55,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J55" s="32">
@@ -3592,7 +3603,7 @@
         <v/>
       </c>
       <c r="K55" s="32">
-        <f>IF(NOT(AND($A55&lt;&gt;"",OR($G55="",$G55="Active"))),"",IF($L55&lt;&gt;"",IF($L55=$M55,"Booking",INDEX($N$4:$U$4,MATCH($L55,$N55:$U55,0))),IF(COUNTIF($N55:$U55,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N55:$U55)=0,"All done",IF(MAX($M55:$U55)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A55&lt;&gt;"",OR($G55="",$G55="Active"))),"",IF($L55&lt;&gt;"",IF($L55=$M55,"Booking",INDEX($N$4:$U$4,MATCH($L55,$N55:$U55,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M55:$U55)+($M55:$U55="DNA")),$M55:$U55),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M55:$U55)+($M55:$U55="DNA")),$M55:$U55),"")),IF(ISNUMBER($U55),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L55" s="33">
@@ -3630,7 +3641,7 @@
         <v/>
       </c>
       <c r="I56" s="32">
-        <f>IF(NOT(AND($A56&lt;&gt;"",OR($G56="",$G56="Active"))),"",IF(AND(MAX($M56:$U56)&gt;0,MAX($M56:$U56)&lt;TODAY(),COUNTBLANK($N56:$U56)&gt;0,COUNTIF($N56:$U56,"DNA")=0),1,0)+COUNTIF($N56:$U56,"DNA")+COUNTIF($V56:$Z56,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A56&lt;&gt;"",OR($G56="",$G56="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M56:$U56)+($M56:$U56="DNA")),$M56:$U56),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M56:$U56)+($M56:$U56="DNA")),$M56:$U56),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M56:$U56)+($M56:$U56="DNA")),$M56:$U56),"")&lt;TODAY())),1,0)+COUNTIF($V56:$Z56,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J56" s="32">
@@ -3638,7 +3649,7 @@
         <v/>
       </c>
       <c r="K56" s="32">
-        <f>IF(NOT(AND($A56&lt;&gt;"",OR($G56="",$G56="Active"))),"",IF($L56&lt;&gt;"",IF($L56=$M56,"Booking",INDEX($N$4:$U$4,MATCH($L56,$N56:$U56,0))),IF(COUNTIF($N56:$U56,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N56:$U56)=0,"All done",IF(MAX($M56:$U56)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A56&lt;&gt;"",OR($G56="",$G56="Active"))),"",IF($L56&lt;&gt;"",IF($L56=$M56,"Booking",INDEX($N$4:$U$4,MATCH($L56,$N56:$U56,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M56:$U56)+($M56:$U56="DNA")),$M56:$U56),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M56:$U56)+($M56:$U56="DNA")),$M56:$U56),"")),IF(ISNUMBER($U56),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L56" s="33">
@@ -3676,7 +3687,7 @@
         <v/>
       </c>
       <c r="I57" s="32">
-        <f>IF(NOT(AND($A57&lt;&gt;"",OR($G57="",$G57="Active"))),"",IF(AND(MAX($M57:$U57)&gt;0,MAX($M57:$U57)&lt;TODAY(),COUNTBLANK($N57:$U57)&gt;0,COUNTIF($N57:$U57,"DNA")=0),1,0)+COUNTIF($N57:$U57,"DNA")+COUNTIF($V57:$Z57,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A57&lt;&gt;"",OR($G57="",$G57="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M57:$U57)+($M57:$U57="DNA")),$M57:$U57),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M57:$U57)+($M57:$U57="DNA")),$M57:$U57),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M57:$U57)+($M57:$U57="DNA")),$M57:$U57),"")&lt;TODAY())),1,0)+COUNTIF($V57:$Z57,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J57" s="32">
@@ -3684,7 +3695,7 @@
         <v/>
       </c>
       <c r="K57" s="32">
-        <f>IF(NOT(AND($A57&lt;&gt;"",OR($G57="",$G57="Active"))),"",IF($L57&lt;&gt;"",IF($L57=$M57,"Booking",INDEX($N$4:$U$4,MATCH($L57,$N57:$U57,0))),IF(COUNTIF($N57:$U57,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N57:$U57)=0,"All done",IF(MAX($M57:$U57)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A57&lt;&gt;"",OR($G57="",$G57="Active"))),"",IF($L57&lt;&gt;"",IF($L57=$M57,"Booking",INDEX($N$4:$U$4,MATCH($L57,$N57:$U57,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M57:$U57)+($M57:$U57="DNA")),$M57:$U57),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M57:$U57)+($M57:$U57="DNA")),$M57:$U57),"")),IF(ISNUMBER($U57),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L57" s="33">
@@ -3722,7 +3733,7 @@
         <v/>
       </c>
       <c r="I58" s="32">
-        <f>IF(NOT(AND($A58&lt;&gt;"",OR($G58="",$G58="Active"))),"",IF(AND(MAX($M58:$U58)&gt;0,MAX($M58:$U58)&lt;TODAY(),COUNTBLANK($N58:$U58)&gt;0,COUNTIF($N58:$U58,"DNA")=0),1,0)+COUNTIF($N58:$U58,"DNA")+COUNTIF($V58:$Z58,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A58&lt;&gt;"",OR($G58="",$G58="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M58:$U58)+($M58:$U58="DNA")),$M58:$U58),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M58:$U58)+($M58:$U58="DNA")),$M58:$U58),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M58:$U58)+($M58:$U58="DNA")),$M58:$U58),"")&lt;TODAY())),1,0)+COUNTIF($V58:$Z58,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J58" s="32">
@@ -3730,7 +3741,7 @@
         <v/>
       </c>
       <c r="K58" s="32">
-        <f>IF(NOT(AND($A58&lt;&gt;"",OR($G58="",$G58="Active"))),"",IF($L58&lt;&gt;"",IF($L58=$M58,"Booking",INDEX($N$4:$U$4,MATCH($L58,$N58:$U58,0))),IF(COUNTIF($N58:$U58,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N58:$U58)=0,"All done",IF(MAX($M58:$U58)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A58&lt;&gt;"",OR($G58="",$G58="Active"))),"",IF($L58&lt;&gt;"",IF($L58=$M58,"Booking",INDEX($N$4:$U$4,MATCH($L58,$N58:$U58,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M58:$U58)+($M58:$U58="DNA")),$M58:$U58),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M58:$U58)+($M58:$U58="DNA")),$M58:$U58),"")),IF(ISNUMBER($U58),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L58" s="33">
@@ -3768,7 +3779,7 @@
         <v/>
       </c>
       <c r="I59" s="32">
-        <f>IF(NOT(AND($A59&lt;&gt;"",OR($G59="",$G59="Active"))),"",IF(AND(MAX($M59:$U59)&gt;0,MAX($M59:$U59)&lt;TODAY(),COUNTBLANK($N59:$U59)&gt;0,COUNTIF($N59:$U59,"DNA")=0),1,0)+COUNTIF($N59:$U59,"DNA")+COUNTIF($V59:$Z59,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A59&lt;&gt;"",OR($G59="",$G59="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M59:$U59)+($M59:$U59="DNA")),$M59:$U59),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M59:$U59)+($M59:$U59="DNA")),$M59:$U59),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M59:$U59)+($M59:$U59="DNA")),$M59:$U59),"")&lt;TODAY())),1,0)+COUNTIF($V59:$Z59,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J59" s="32">
@@ -3776,7 +3787,7 @@
         <v/>
       </c>
       <c r="K59" s="32">
-        <f>IF(NOT(AND($A59&lt;&gt;"",OR($G59="",$G59="Active"))),"",IF($L59&lt;&gt;"",IF($L59=$M59,"Booking",INDEX($N$4:$U$4,MATCH($L59,$N59:$U59,0))),IF(COUNTIF($N59:$U59,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N59:$U59)=0,"All done",IF(MAX($M59:$U59)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A59&lt;&gt;"",OR($G59="",$G59="Active"))),"",IF($L59&lt;&gt;"",IF($L59=$M59,"Booking",INDEX($N$4:$U$4,MATCH($L59,$N59:$U59,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M59:$U59)+($M59:$U59="DNA")),$M59:$U59),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M59:$U59)+($M59:$U59="DNA")),$M59:$U59),"")),IF(ISNUMBER($U59),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L59" s="33">
@@ -3814,7 +3825,7 @@
         <v/>
       </c>
       <c r="I60" s="32">
-        <f>IF(NOT(AND($A60&lt;&gt;"",OR($G60="",$G60="Active"))),"",IF(AND(MAX($M60:$U60)&gt;0,MAX($M60:$U60)&lt;TODAY(),COUNTBLANK($N60:$U60)&gt;0,COUNTIF($N60:$U60,"DNA")=0),1,0)+COUNTIF($N60:$U60,"DNA")+COUNTIF($V60:$Z60,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A60&lt;&gt;"",OR($G60="",$G60="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M60:$U60)+($M60:$U60="DNA")),$M60:$U60),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M60:$U60)+($M60:$U60="DNA")),$M60:$U60),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M60:$U60)+($M60:$U60="DNA")),$M60:$U60),"")&lt;TODAY())),1,0)+COUNTIF($V60:$Z60,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J60" s="32">
@@ -3822,7 +3833,7 @@
         <v/>
       </c>
       <c r="K60" s="32">
-        <f>IF(NOT(AND($A60&lt;&gt;"",OR($G60="",$G60="Active"))),"",IF($L60&lt;&gt;"",IF($L60=$M60,"Booking",INDEX($N$4:$U$4,MATCH($L60,$N60:$U60,0))),IF(COUNTIF($N60:$U60,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N60:$U60)=0,"All done",IF(MAX($M60:$U60)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A60&lt;&gt;"",OR($G60="",$G60="Active"))),"",IF($L60&lt;&gt;"",IF($L60=$M60,"Booking",INDEX($N$4:$U$4,MATCH($L60,$N60:$U60,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M60:$U60)+($M60:$U60="DNA")),$M60:$U60),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M60:$U60)+($M60:$U60="DNA")),$M60:$U60),"")),IF(ISNUMBER($U60),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L60" s="33">
@@ -3860,7 +3871,7 @@
         <v/>
       </c>
       <c r="I61" s="32">
-        <f>IF(NOT(AND($A61&lt;&gt;"",OR($G61="",$G61="Active"))),"",IF(AND(MAX($M61:$U61)&gt;0,MAX($M61:$U61)&lt;TODAY(),COUNTBLANK($N61:$U61)&gt;0,COUNTIF($N61:$U61,"DNA")=0),1,0)+COUNTIF($N61:$U61,"DNA")+COUNTIF($V61:$Z61,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A61&lt;&gt;"",OR($G61="",$G61="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M61:$U61)+($M61:$U61="DNA")),$M61:$U61),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M61:$U61)+($M61:$U61="DNA")),$M61:$U61),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M61:$U61)+($M61:$U61="DNA")),$M61:$U61),"")&lt;TODAY())),1,0)+COUNTIF($V61:$Z61,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J61" s="32">
@@ -3868,7 +3879,7 @@
         <v/>
       </c>
       <c r="K61" s="32">
-        <f>IF(NOT(AND($A61&lt;&gt;"",OR($G61="",$G61="Active"))),"",IF($L61&lt;&gt;"",IF($L61=$M61,"Booking",INDEX($N$4:$U$4,MATCH($L61,$N61:$U61,0))),IF(COUNTIF($N61:$U61,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N61:$U61)=0,"All done",IF(MAX($M61:$U61)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A61&lt;&gt;"",OR($G61="",$G61="Active"))),"",IF($L61&lt;&gt;"",IF($L61=$M61,"Booking",INDEX($N$4:$U$4,MATCH($L61,$N61:$U61,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M61:$U61)+($M61:$U61="DNA")),$M61:$U61),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M61:$U61)+($M61:$U61="DNA")),$M61:$U61),"")),IF(ISNUMBER($U61),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L61" s="33">
@@ -3906,7 +3917,7 @@
         <v/>
       </c>
       <c r="I62" s="32">
-        <f>IF(NOT(AND($A62&lt;&gt;"",OR($G62="",$G62="Active"))),"",IF(AND(MAX($M62:$U62)&gt;0,MAX($M62:$U62)&lt;TODAY(),COUNTBLANK($N62:$U62)&gt;0,COUNTIF($N62:$U62,"DNA")=0),1,0)+COUNTIF($N62:$U62,"DNA")+COUNTIF($V62:$Z62,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A62&lt;&gt;"",OR($G62="",$G62="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M62:$U62)+($M62:$U62="DNA")),$M62:$U62),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M62:$U62)+($M62:$U62="DNA")),$M62:$U62),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M62:$U62)+($M62:$U62="DNA")),$M62:$U62),"")&lt;TODAY())),1,0)+COUNTIF($V62:$Z62,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J62" s="32">
@@ -3914,7 +3925,7 @@
         <v/>
       </c>
       <c r="K62" s="32">
-        <f>IF(NOT(AND($A62&lt;&gt;"",OR($G62="",$G62="Active"))),"",IF($L62&lt;&gt;"",IF($L62=$M62,"Booking",INDEX($N$4:$U$4,MATCH($L62,$N62:$U62,0))),IF(COUNTIF($N62:$U62,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N62:$U62)=0,"All done",IF(MAX($M62:$U62)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A62&lt;&gt;"",OR($G62="",$G62="Active"))),"",IF($L62&lt;&gt;"",IF($L62=$M62,"Booking",INDEX($N$4:$U$4,MATCH($L62,$N62:$U62,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M62:$U62)+($M62:$U62="DNA")),$M62:$U62),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M62:$U62)+($M62:$U62="DNA")),$M62:$U62),"")),IF(ISNUMBER($U62),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L62" s="33">
@@ -3952,7 +3963,7 @@
         <v/>
       </c>
       <c r="I63" s="32">
-        <f>IF(NOT(AND($A63&lt;&gt;"",OR($G63="",$G63="Active"))),"",IF(AND(MAX($M63:$U63)&gt;0,MAX($M63:$U63)&lt;TODAY(),COUNTBLANK($N63:$U63)&gt;0,COUNTIF($N63:$U63,"DNA")=0),1,0)+COUNTIF($N63:$U63,"DNA")+COUNTIF($V63:$Z63,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A63&lt;&gt;"",OR($G63="",$G63="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M63:$U63)+($M63:$U63="DNA")),$M63:$U63),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M63:$U63)+($M63:$U63="DNA")),$M63:$U63),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M63:$U63)+($M63:$U63="DNA")),$M63:$U63),"")&lt;TODAY())),1,0)+COUNTIF($V63:$Z63,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J63" s="32">
@@ -3960,7 +3971,7 @@
         <v/>
       </c>
       <c r="K63" s="32">
-        <f>IF(NOT(AND($A63&lt;&gt;"",OR($G63="",$G63="Active"))),"",IF($L63&lt;&gt;"",IF($L63=$M63,"Booking",INDEX($N$4:$U$4,MATCH($L63,$N63:$U63,0))),IF(COUNTIF($N63:$U63,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N63:$U63)=0,"All done",IF(MAX($M63:$U63)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A63&lt;&gt;"",OR($G63="",$G63="Active"))),"",IF($L63&lt;&gt;"",IF($L63=$M63,"Booking",INDEX($N$4:$U$4,MATCH($L63,$N63:$U63,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M63:$U63)+($M63:$U63="DNA")),$M63:$U63),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M63:$U63)+($M63:$U63="DNA")),$M63:$U63),"")),IF(ISNUMBER($U63),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L63" s="33">
@@ -3998,7 +4009,7 @@
         <v/>
       </c>
       <c r="I64" s="32">
-        <f>IF(NOT(AND($A64&lt;&gt;"",OR($G64="",$G64="Active"))),"",IF(AND(MAX($M64:$U64)&gt;0,MAX($M64:$U64)&lt;TODAY(),COUNTBLANK($N64:$U64)&gt;0,COUNTIF($N64:$U64,"DNA")=0),1,0)+COUNTIF($N64:$U64,"DNA")+COUNTIF($V64:$Z64,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A64&lt;&gt;"",OR($G64="",$G64="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M64:$U64)+($M64:$U64="DNA")),$M64:$U64),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M64:$U64)+($M64:$U64="DNA")),$M64:$U64),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M64:$U64)+($M64:$U64="DNA")),$M64:$U64),"")&lt;TODAY())),1,0)+COUNTIF($V64:$Z64,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J64" s="32">
@@ -4006,7 +4017,7 @@
         <v/>
       </c>
       <c r="K64" s="32">
-        <f>IF(NOT(AND($A64&lt;&gt;"",OR($G64="",$G64="Active"))),"",IF($L64&lt;&gt;"",IF($L64=$M64,"Booking",INDEX($N$4:$U$4,MATCH($L64,$N64:$U64,0))),IF(COUNTIF($N64:$U64,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N64:$U64)=0,"All done",IF(MAX($M64:$U64)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A64&lt;&gt;"",OR($G64="",$G64="Active"))),"",IF($L64&lt;&gt;"",IF($L64=$M64,"Booking",INDEX($N$4:$U$4,MATCH($L64,$N64:$U64,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M64:$U64)+($M64:$U64="DNA")),$M64:$U64),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M64:$U64)+($M64:$U64="DNA")),$M64:$U64),"")),IF(ISNUMBER($U64),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L64" s="33">
@@ -4044,7 +4055,7 @@
         <v/>
       </c>
       <c r="I65" s="32">
-        <f>IF(NOT(AND($A65&lt;&gt;"",OR($G65="",$G65="Active"))),"",IF(AND(MAX($M65:$U65)&gt;0,MAX($M65:$U65)&lt;TODAY(),COUNTBLANK($N65:$U65)&gt;0,COUNTIF($N65:$U65,"DNA")=0),1,0)+COUNTIF($N65:$U65,"DNA")+COUNTIF($V65:$Z65,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A65&lt;&gt;"",OR($G65="",$G65="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M65:$U65)+($M65:$U65="DNA")),$M65:$U65),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M65:$U65)+($M65:$U65="DNA")),$M65:$U65),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M65:$U65)+($M65:$U65="DNA")),$M65:$U65),"")&lt;TODAY())),1,0)+COUNTIF($V65:$Z65,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J65" s="32">
@@ -4052,7 +4063,7 @@
         <v/>
       </c>
       <c r="K65" s="32">
-        <f>IF(NOT(AND($A65&lt;&gt;"",OR($G65="",$G65="Active"))),"",IF($L65&lt;&gt;"",IF($L65=$M65,"Booking",INDEX($N$4:$U$4,MATCH($L65,$N65:$U65,0))),IF(COUNTIF($N65:$U65,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N65:$U65)=0,"All done",IF(MAX($M65:$U65)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A65&lt;&gt;"",OR($G65="",$G65="Active"))),"",IF($L65&lt;&gt;"",IF($L65=$M65,"Booking",INDEX($N$4:$U$4,MATCH($L65,$N65:$U65,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M65:$U65)+($M65:$U65="DNA")),$M65:$U65),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M65:$U65)+($M65:$U65="DNA")),$M65:$U65),"")),IF(ISNUMBER($U65),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L65" s="33">
@@ -4090,7 +4101,7 @@
         <v/>
       </c>
       <c r="I66" s="32">
-        <f>IF(NOT(AND($A66&lt;&gt;"",OR($G66="",$G66="Active"))),"",IF(AND(MAX($M66:$U66)&gt;0,MAX($M66:$U66)&lt;TODAY(),COUNTBLANK($N66:$U66)&gt;0,COUNTIF($N66:$U66,"DNA")=0),1,0)+COUNTIF($N66:$U66,"DNA")+COUNTIF($V66:$Z66,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A66&lt;&gt;"",OR($G66="",$G66="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M66:$U66)+($M66:$U66="DNA")),$M66:$U66),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M66:$U66)+($M66:$U66="DNA")),$M66:$U66),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M66:$U66)+($M66:$U66="DNA")),$M66:$U66),"")&lt;TODAY())),1,0)+COUNTIF($V66:$Z66,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J66" s="32">
@@ -4098,7 +4109,7 @@
         <v/>
       </c>
       <c r="K66" s="32">
-        <f>IF(NOT(AND($A66&lt;&gt;"",OR($G66="",$G66="Active"))),"",IF($L66&lt;&gt;"",IF($L66=$M66,"Booking",INDEX($N$4:$U$4,MATCH($L66,$N66:$U66,0))),IF(COUNTIF($N66:$U66,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N66:$U66)=0,"All done",IF(MAX($M66:$U66)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A66&lt;&gt;"",OR($G66="",$G66="Active"))),"",IF($L66&lt;&gt;"",IF($L66=$M66,"Booking",INDEX($N$4:$U$4,MATCH($L66,$N66:$U66,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M66:$U66)+($M66:$U66="DNA")),$M66:$U66),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M66:$U66)+($M66:$U66="DNA")),$M66:$U66),"")),IF(ISNUMBER($U66),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L66" s="33">
@@ -4136,7 +4147,7 @@
         <v/>
       </c>
       <c r="I67" s="32">
-        <f>IF(NOT(AND($A67&lt;&gt;"",OR($G67="",$G67="Active"))),"",IF(AND(MAX($M67:$U67)&gt;0,MAX($M67:$U67)&lt;TODAY(),COUNTBLANK($N67:$U67)&gt;0,COUNTIF($N67:$U67,"DNA")=0),1,0)+COUNTIF($N67:$U67,"DNA")+COUNTIF($V67:$Z67,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A67&lt;&gt;"",OR($G67="",$G67="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M67:$U67)+($M67:$U67="DNA")),$M67:$U67),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M67:$U67)+($M67:$U67="DNA")),$M67:$U67),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M67:$U67)+($M67:$U67="DNA")),$M67:$U67),"")&lt;TODAY())),1,0)+COUNTIF($V67:$Z67,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J67" s="32">
@@ -4144,7 +4155,7 @@
         <v/>
       </c>
       <c r="K67" s="32">
-        <f>IF(NOT(AND($A67&lt;&gt;"",OR($G67="",$G67="Active"))),"",IF($L67&lt;&gt;"",IF($L67=$M67,"Booking",INDEX($N$4:$U$4,MATCH($L67,$N67:$U67,0))),IF(COUNTIF($N67:$U67,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N67:$U67)=0,"All done",IF(MAX($M67:$U67)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A67&lt;&gt;"",OR($G67="",$G67="Active"))),"",IF($L67&lt;&gt;"",IF($L67=$M67,"Booking",INDEX($N$4:$U$4,MATCH($L67,$N67:$U67,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M67:$U67)+($M67:$U67="DNA")),$M67:$U67),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M67:$U67)+($M67:$U67="DNA")),$M67:$U67),"")),IF(ISNUMBER($U67),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L67" s="33">
@@ -4182,7 +4193,7 @@
         <v/>
       </c>
       <c r="I68" s="32">
-        <f>IF(NOT(AND($A68&lt;&gt;"",OR($G68="",$G68="Active"))),"",IF(AND(MAX($M68:$U68)&gt;0,MAX($M68:$U68)&lt;TODAY(),COUNTBLANK($N68:$U68)&gt;0,COUNTIF($N68:$U68,"DNA")=0),1,0)+COUNTIF($N68:$U68,"DNA")+COUNTIF($V68:$Z68,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A68&lt;&gt;"",OR($G68="",$G68="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M68:$U68)+($M68:$U68="DNA")),$M68:$U68),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M68:$U68)+($M68:$U68="DNA")),$M68:$U68),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M68:$U68)+($M68:$U68="DNA")),$M68:$U68),"")&lt;TODAY())),1,0)+COUNTIF($V68:$Z68,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J68" s="32">
@@ -4190,7 +4201,7 @@
         <v/>
       </c>
       <c r="K68" s="32">
-        <f>IF(NOT(AND($A68&lt;&gt;"",OR($G68="",$G68="Active"))),"",IF($L68&lt;&gt;"",IF($L68=$M68,"Booking",INDEX($N$4:$U$4,MATCH($L68,$N68:$U68,0))),IF(COUNTIF($N68:$U68,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N68:$U68)=0,"All done",IF(MAX($M68:$U68)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A68&lt;&gt;"",OR($G68="",$G68="Active"))),"",IF($L68&lt;&gt;"",IF($L68=$M68,"Booking",INDEX($N$4:$U$4,MATCH($L68,$N68:$U68,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M68:$U68)+($M68:$U68="DNA")),$M68:$U68),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M68:$U68)+($M68:$U68="DNA")),$M68:$U68),"")),IF(ISNUMBER($U68),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L68" s="33">
@@ -4228,7 +4239,7 @@
         <v/>
       </c>
       <c r="I69" s="32">
-        <f>IF(NOT(AND($A69&lt;&gt;"",OR($G69="",$G69="Active"))),"",IF(AND(MAX($M69:$U69)&gt;0,MAX($M69:$U69)&lt;TODAY(),COUNTBLANK($N69:$U69)&gt;0,COUNTIF($N69:$U69,"DNA")=0),1,0)+COUNTIF($N69:$U69,"DNA")+COUNTIF($V69:$Z69,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A69&lt;&gt;"",OR($G69="",$G69="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M69:$U69)+($M69:$U69="DNA")),$M69:$U69),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M69:$U69)+($M69:$U69="DNA")),$M69:$U69),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M69:$U69)+($M69:$U69="DNA")),$M69:$U69),"")&lt;TODAY())),1,0)+COUNTIF($V69:$Z69,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J69" s="32">
@@ -4236,7 +4247,7 @@
         <v/>
       </c>
       <c r="K69" s="32">
-        <f>IF(NOT(AND($A69&lt;&gt;"",OR($G69="",$G69="Active"))),"",IF($L69&lt;&gt;"",IF($L69=$M69,"Booking",INDEX($N$4:$U$4,MATCH($L69,$N69:$U69,0))),IF(COUNTIF($N69:$U69,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N69:$U69)=0,"All done",IF(MAX($M69:$U69)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A69&lt;&gt;"",OR($G69="",$G69="Active"))),"",IF($L69&lt;&gt;"",IF($L69=$M69,"Booking",INDEX($N$4:$U$4,MATCH($L69,$N69:$U69,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M69:$U69)+($M69:$U69="DNA")),$M69:$U69),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M69:$U69)+($M69:$U69="DNA")),$M69:$U69),"")),IF(ISNUMBER($U69),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L69" s="33">
@@ -4274,7 +4285,7 @@
         <v/>
       </c>
       <c r="I70" s="32">
-        <f>IF(NOT(AND($A70&lt;&gt;"",OR($G70="",$G70="Active"))),"",IF(AND(MAX($M70:$U70)&gt;0,MAX($M70:$U70)&lt;TODAY(),COUNTBLANK($N70:$U70)&gt;0,COUNTIF($N70:$U70,"DNA")=0),1,0)+COUNTIF($N70:$U70,"DNA")+COUNTIF($V70:$Z70,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A70&lt;&gt;"",OR($G70="",$G70="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M70:$U70)+($M70:$U70="DNA")),$M70:$U70),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M70:$U70)+($M70:$U70="DNA")),$M70:$U70),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M70:$U70)+($M70:$U70="DNA")),$M70:$U70),"")&lt;TODAY())),1,0)+COUNTIF($V70:$Z70,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J70" s="32">
@@ -4282,7 +4293,7 @@
         <v/>
       </c>
       <c r="K70" s="32">
-        <f>IF(NOT(AND($A70&lt;&gt;"",OR($G70="",$G70="Active"))),"",IF($L70&lt;&gt;"",IF($L70=$M70,"Booking",INDEX($N$4:$U$4,MATCH($L70,$N70:$U70,0))),IF(COUNTIF($N70:$U70,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N70:$U70)=0,"All done",IF(MAX($M70:$U70)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A70&lt;&gt;"",OR($G70="",$G70="Active"))),"",IF($L70&lt;&gt;"",IF($L70=$M70,"Booking",INDEX($N$4:$U$4,MATCH($L70,$N70:$U70,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M70:$U70)+($M70:$U70="DNA")),$M70:$U70),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M70:$U70)+($M70:$U70="DNA")),$M70:$U70),"")),IF(ISNUMBER($U70),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L70" s="33">
@@ -4320,7 +4331,7 @@
         <v/>
       </c>
       <c r="I71" s="32">
-        <f>IF(NOT(AND($A71&lt;&gt;"",OR($G71="",$G71="Active"))),"",IF(AND(MAX($M71:$U71)&gt;0,MAX($M71:$U71)&lt;TODAY(),COUNTBLANK($N71:$U71)&gt;0,COUNTIF($N71:$U71,"DNA")=0),1,0)+COUNTIF($N71:$U71,"DNA")+COUNTIF($V71:$Z71,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A71&lt;&gt;"",OR($G71="",$G71="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M71:$U71)+($M71:$U71="DNA")),$M71:$U71),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M71:$U71)+($M71:$U71="DNA")),$M71:$U71),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M71:$U71)+($M71:$U71="DNA")),$M71:$U71),"")&lt;TODAY())),1,0)+COUNTIF($V71:$Z71,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J71" s="32">
@@ -4328,7 +4339,7 @@
         <v/>
       </c>
       <c r="K71" s="32">
-        <f>IF(NOT(AND($A71&lt;&gt;"",OR($G71="",$G71="Active"))),"",IF($L71&lt;&gt;"",IF($L71=$M71,"Booking",INDEX($N$4:$U$4,MATCH($L71,$N71:$U71,0))),IF(COUNTIF($N71:$U71,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N71:$U71)=0,"All done",IF(MAX($M71:$U71)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A71&lt;&gt;"",OR($G71="",$G71="Active"))),"",IF($L71&lt;&gt;"",IF($L71=$M71,"Booking",INDEX($N$4:$U$4,MATCH($L71,$N71:$U71,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M71:$U71)+($M71:$U71="DNA")),$M71:$U71),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M71:$U71)+($M71:$U71="DNA")),$M71:$U71),"")),IF(ISNUMBER($U71),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L71" s="33">
@@ -4366,7 +4377,7 @@
         <v/>
       </c>
       <c r="I72" s="32">
-        <f>IF(NOT(AND($A72&lt;&gt;"",OR($G72="",$G72="Active"))),"",IF(AND(MAX($M72:$U72)&gt;0,MAX($M72:$U72)&lt;TODAY(),COUNTBLANK($N72:$U72)&gt;0,COUNTIF($N72:$U72,"DNA")=0),1,0)+COUNTIF($N72:$U72,"DNA")+COUNTIF($V72:$Z72,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A72&lt;&gt;"",OR($G72="",$G72="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M72:$U72)+($M72:$U72="DNA")),$M72:$U72),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M72:$U72)+($M72:$U72="DNA")),$M72:$U72),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M72:$U72)+($M72:$U72="DNA")),$M72:$U72),"")&lt;TODAY())),1,0)+COUNTIF($V72:$Z72,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J72" s="32">
@@ -4374,7 +4385,7 @@
         <v/>
       </c>
       <c r="K72" s="32">
-        <f>IF(NOT(AND($A72&lt;&gt;"",OR($G72="",$G72="Active"))),"",IF($L72&lt;&gt;"",IF($L72=$M72,"Booking",INDEX($N$4:$U$4,MATCH($L72,$N72:$U72,0))),IF(COUNTIF($N72:$U72,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N72:$U72)=0,"All done",IF(MAX($M72:$U72)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A72&lt;&gt;"",OR($G72="",$G72="Active"))),"",IF($L72&lt;&gt;"",IF($L72=$M72,"Booking",INDEX($N$4:$U$4,MATCH($L72,$N72:$U72,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M72:$U72)+($M72:$U72="DNA")),$M72:$U72),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M72:$U72)+($M72:$U72="DNA")),$M72:$U72),"")),IF(ISNUMBER($U72),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L72" s="33">
@@ -4412,7 +4423,7 @@
         <v/>
       </c>
       <c r="I73" s="32">
-        <f>IF(NOT(AND($A73&lt;&gt;"",OR($G73="",$G73="Active"))),"",IF(AND(MAX($M73:$U73)&gt;0,MAX($M73:$U73)&lt;TODAY(),COUNTBLANK($N73:$U73)&gt;0,COUNTIF($N73:$U73,"DNA")=0),1,0)+COUNTIF($N73:$U73,"DNA")+COUNTIF($V73:$Z73,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A73&lt;&gt;"",OR($G73="",$G73="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M73:$U73)+($M73:$U73="DNA")),$M73:$U73),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M73:$U73)+($M73:$U73="DNA")),$M73:$U73),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M73:$U73)+($M73:$U73="DNA")),$M73:$U73),"")&lt;TODAY())),1,0)+COUNTIF($V73:$Z73,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J73" s="32">
@@ -4420,7 +4431,7 @@
         <v/>
       </c>
       <c r="K73" s="32">
-        <f>IF(NOT(AND($A73&lt;&gt;"",OR($G73="",$G73="Active"))),"",IF($L73&lt;&gt;"",IF($L73=$M73,"Booking",INDEX($N$4:$U$4,MATCH($L73,$N73:$U73,0))),IF(COUNTIF($N73:$U73,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N73:$U73)=0,"All done",IF(MAX($M73:$U73)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A73&lt;&gt;"",OR($G73="",$G73="Active"))),"",IF($L73&lt;&gt;"",IF($L73=$M73,"Booking",INDEX($N$4:$U$4,MATCH($L73,$N73:$U73,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M73:$U73)+($M73:$U73="DNA")),$M73:$U73),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M73:$U73)+($M73:$U73="DNA")),$M73:$U73),"")),IF(ISNUMBER($U73),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L73" s="33">
@@ -4458,7 +4469,7 @@
         <v/>
       </c>
       <c r="I74" s="32">
-        <f>IF(NOT(AND($A74&lt;&gt;"",OR($G74="",$G74="Active"))),"",IF(AND(MAX($M74:$U74)&gt;0,MAX($M74:$U74)&lt;TODAY(),COUNTBLANK($N74:$U74)&gt;0,COUNTIF($N74:$U74,"DNA")=0),1,0)+COUNTIF($N74:$U74,"DNA")+COUNTIF($V74:$Z74,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A74&lt;&gt;"",OR($G74="",$G74="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M74:$U74)+($M74:$U74="DNA")),$M74:$U74),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M74:$U74)+($M74:$U74="DNA")),$M74:$U74),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M74:$U74)+($M74:$U74="DNA")),$M74:$U74),"")&lt;TODAY())),1,0)+COUNTIF($V74:$Z74,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J74" s="32">
@@ -4466,7 +4477,7 @@
         <v/>
       </c>
       <c r="K74" s="32">
-        <f>IF(NOT(AND($A74&lt;&gt;"",OR($G74="",$G74="Active"))),"",IF($L74&lt;&gt;"",IF($L74=$M74,"Booking",INDEX($N$4:$U$4,MATCH($L74,$N74:$U74,0))),IF(COUNTIF($N74:$U74,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N74:$U74)=0,"All done",IF(MAX($M74:$U74)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A74&lt;&gt;"",OR($G74="",$G74="Active"))),"",IF($L74&lt;&gt;"",IF($L74=$M74,"Booking",INDEX($N$4:$U$4,MATCH($L74,$N74:$U74,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M74:$U74)+($M74:$U74="DNA")),$M74:$U74),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M74:$U74)+($M74:$U74="DNA")),$M74:$U74),"")),IF(ISNUMBER($U74),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L74" s="33">
@@ -4504,7 +4515,7 @@
         <v/>
       </c>
       <c r="I75" s="32">
-        <f>IF(NOT(AND($A75&lt;&gt;"",OR($G75="",$G75="Active"))),"",IF(AND(MAX($M75:$U75)&gt;0,MAX($M75:$U75)&lt;TODAY(),COUNTBLANK($N75:$U75)&gt;0,COUNTIF($N75:$U75,"DNA")=0),1,0)+COUNTIF($N75:$U75,"DNA")+COUNTIF($V75:$Z75,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A75&lt;&gt;"",OR($G75="",$G75="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M75:$U75)+($M75:$U75="DNA")),$M75:$U75),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M75:$U75)+($M75:$U75="DNA")),$M75:$U75),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M75:$U75)+($M75:$U75="DNA")),$M75:$U75),"")&lt;TODAY())),1,0)+COUNTIF($V75:$Z75,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J75" s="32">
@@ -4512,7 +4523,7 @@
         <v/>
       </c>
       <c r="K75" s="32">
-        <f>IF(NOT(AND($A75&lt;&gt;"",OR($G75="",$G75="Active"))),"",IF($L75&lt;&gt;"",IF($L75=$M75,"Booking",INDEX($N$4:$U$4,MATCH($L75,$N75:$U75,0))),IF(COUNTIF($N75:$U75,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N75:$U75)=0,"All done",IF(MAX($M75:$U75)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A75&lt;&gt;"",OR($G75="",$G75="Active"))),"",IF($L75&lt;&gt;"",IF($L75=$M75,"Booking",INDEX($N$4:$U$4,MATCH($L75,$N75:$U75,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M75:$U75)+($M75:$U75="DNA")),$M75:$U75),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M75:$U75)+($M75:$U75="DNA")),$M75:$U75),"")),IF(ISNUMBER($U75),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L75" s="33">
@@ -4550,7 +4561,7 @@
         <v/>
       </c>
       <c r="I76" s="32">
-        <f>IF(NOT(AND($A76&lt;&gt;"",OR($G76="",$G76="Active"))),"",IF(AND(MAX($M76:$U76)&gt;0,MAX($M76:$U76)&lt;TODAY(),COUNTBLANK($N76:$U76)&gt;0,COUNTIF($N76:$U76,"DNA")=0),1,0)+COUNTIF($N76:$U76,"DNA")+COUNTIF($V76:$Z76,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A76&lt;&gt;"",OR($G76="",$G76="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M76:$U76)+($M76:$U76="DNA")),$M76:$U76),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M76:$U76)+($M76:$U76="DNA")),$M76:$U76),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M76:$U76)+($M76:$U76="DNA")),$M76:$U76),"")&lt;TODAY())),1,0)+COUNTIF($V76:$Z76,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J76" s="32">
@@ -4558,7 +4569,7 @@
         <v/>
       </c>
       <c r="K76" s="32">
-        <f>IF(NOT(AND($A76&lt;&gt;"",OR($G76="",$G76="Active"))),"",IF($L76&lt;&gt;"",IF($L76=$M76,"Booking",INDEX($N$4:$U$4,MATCH($L76,$N76:$U76,0))),IF(COUNTIF($N76:$U76,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N76:$U76)=0,"All done",IF(MAX($M76:$U76)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A76&lt;&gt;"",OR($G76="",$G76="Active"))),"",IF($L76&lt;&gt;"",IF($L76=$M76,"Booking",INDEX($N$4:$U$4,MATCH($L76,$N76:$U76,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M76:$U76)+($M76:$U76="DNA")),$M76:$U76),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M76:$U76)+($M76:$U76="DNA")),$M76:$U76),"")),IF(ISNUMBER($U76),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L76" s="33">
@@ -4596,7 +4607,7 @@
         <v/>
       </c>
       <c r="I77" s="32">
-        <f>IF(NOT(AND($A77&lt;&gt;"",OR($G77="",$G77="Active"))),"",IF(AND(MAX($M77:$U77)&gt;0,MAX($M77:$U77)&lt;TODAY(),COUNTBLANK($N77:$U77)&gt;0,COUNTIF($N77:$U77,"DNA")=0),1,0)+COUNTIF($N77:$U77,"DNA")+COUNTIF($V77:$Z77,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A77&lt;&gt;"",OR($G77="",$G77="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M77:$U77)+($M77:$U77="DNA")),$M77:$U77),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M77:$U77)+($M77:$U77="DNA")),$M77:$U77),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M77:$U77)+($M77:$U77="DNA")),$M77:$U77),"")&lt;TODAY())),1,0)+COUNTIF($V77:$Z77,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J77" s="32">
@@ -4604,7 +4615,7 @@
         <v/>
       </c>
       <c r="K77" s="32">
-        <f>IF(NOT(AND($A77&lt;&gt;"",OR($G77="",$G77="Active"))),"",IF($L77&lt;&gt;"",IF($L77=$M77,"Booking",INDEX($N$4:$U$4,MATCH($L77,$N77:$U77,0))),IF(COUNTIF($N77:$U77,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N77:$U77)=0,"All done",IF(MAX($M77:$U77)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A77&lt;&gt;"",OR($G77="",$G77="Active"))),"",IF($L77&lt;&gt;"",IF($L77=$M77,"Booking",INDEX($N$4:$U$4,MATCH($L77,$N77:$U77,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M77:$U77)+($M77:$U77="DNA")),$M77:$U77),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M77:$U77)+($M77:$U77="DNA")),$M77:$U77),"")),IF(ISNUMBER($U77),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L77" s="33">
@@ -4642,7 +4653,7 @@
         <v/>
       </c>
       <c r="I78" s="32">
-        <f>IF(NOT(AND($A78&lt;&gt;"",OR($G78="",$G78="Active"))),"",IF(AND(MAX($M78:$U78)&gt;0,MAX($M78:$U78)&lt;TODAY(),COUNTBLANK($N78:$U78)&gt;0,COUNTIF($N78:$U78,"DNA")=0),1,0)+COUNTIF($N78:$U78,"DNA")+COUNTIF($V78:$Z78,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A78&lt;&gt;"",OR($G78="",$G78="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M78:$U78)+($M78:$U78="DNA")),$M78:$U78),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M78:$U78)+($M78:$U78="DNA")),$M78:$U78),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M78:$U78)+($M78:$U78="DNA")),$M78:$U78),"")&lt;TODAY())),1,0)+COUNTIF($V78:$Z78,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J78" s="32">
@@ -4650,7 +4661,7 @@
         <v/>
       </c>
       <c r="K78" s="32">
-        <f>IF(NOT(AND($A78&lt;&gt;"",OR($G78="",$G78="Active"))),"",IF($L78&lt;&gt;"",IF($L78=$M78,"Booking",INDEX($N$4:$U$4,MATCH($L78,$N78:$U78,0))),IF(COUNTIF($N78:$U78,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N78:$U78)=0,"All done",IF(MAX($M78:$U78)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A78&lt;&gt;"",OR($G78="",$G78="Active"))),"",IF($L78&lt;&gt;"",IF($L78=$M78,"Booking",INDEX($N$4:$U$4,MATCH($L78,$N78:$U78,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M78:$U78)+($M78:$U78="DNA")),$M78:$U78),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M78:$U78)+($M78:$U78="DNA")),$M78:$U78),"")),IF(ISNUMBER($U78),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L78" s="33">
@@ -4688,7 +4699,7 @@
         <v/>
       </c>
       <c r="I79" s="32">
-        <f>IF(NOT(AND($A79&lt;&gt;"",OR($G79="",$G79="Active"))),"",IF(AND(MAX($M79:$U79)&gt;0,MAX($M79:$U79)&lt;TODAY(),COUNTBLANK($N79:$U79)&gt;0,COUNTIF($N79:$U79,"DNA")=0),1,0)+COUNTIF($N79:$U79,"DNA")+COUNTIF($V79:$Z79,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A79&lt;&gt;"",OR($G79="",$G79="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M79:$U79)+($M79:$U79="DNA")),$M79:$U79),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M79:$U79)+($M79:$U79="DNA")),$M79:$U79),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M79:$U79)+($M79:$U79="DNA")),$M79:$U79),"")&lt;TODAY())),1,0)+COUNTIF($V79:$Z79,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J79" s="32">
@@ -4696,7 +4707,7 @@
         <v/>
       </c>
       <c r="K79" s="32">
-        <f>IF(NOT(AND($A79&lt;&gt;"",OR($G79="",$G79="Active"))),"",IF($L79&lt;&gt;"",IF($L79=$M79,"Booking",INDEX($N$4:$U$4,MATCH($L79,$N79:$U79,0))),IF(COUNTIF($N79:$U79,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N79:$U79)=0,"All done",IF(MAX($M79:$U79)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A79&lt;&gt;"",OR($G79="",$G79="Active"))),"",IF($L79&lt;&gt;"",IF($L79=$M79,"Booking",INDEX($N$4:$U$4,MATCH($L79,$N79:$U79,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M79:$U79)+($M79:$U79="DNA")),$M79:$U79),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M79:$U79)+($M79:$U79="DNA")),$M79:$U79),"")),IF(ISNUMBER($U79),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L79" s="33">
@@ -4734,7 +4745,7 @@
         <v/>
       </c>
       <c r="I80" s="32">
-        <f>IF(NOT(AND($A80&lt;&gt;"",OR($G80="",$G80="Active"))),"",IF(AND(MAX($M80:$U80)&gt;0,MAX($M80:$U80)&lt;TODAY(),COUNTBLANK($N80:$U80)&gt;0,COUNTIF($N80:$U80,"DNA")=0),1,0)+COUNTIF($N80:$U80,"DNA")+COUNTIF($V80:$Z80,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A80&lt;&gt;"",OR($G80="",$G80="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M80:$U80)+($M80:$U80="DNA")),$M80:$U80),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M80:$U80)+($M80:$U80="DNA")),$M80:$U80),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M80:$U80)+($M80:$U80="DNA")),$M80:$U80),"")&lt;TODAY())),1,0)+COUNTIF($V80:$Z80,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J80" s="32">
@@ -4742,7 +4753,7 @@
         <v/>
       </c>
       <c r="K80" s="32">
-        <f>IF(NOT(AND($A80&lt;&gt;"",OR($G80="",$G80="Active"))),"",IF($L80&lt;&gt;"",IF($L80=$M80,"Booking",INDEX($N$4:$U$4,MATCH($L80,$N80:$U80,0))),IF(COUNTIF($N80:$U80,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N80:$U80)=0,"All done",IF(MAX($M80:$U80)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A80&lt;&gt;"",OR($G80="",$G80="Active"))),"",IF($L80&lt;&gt;"",IF($L80=$M80,"Booking",INDEX($N$4:$U$4,MATCH($L80,$N80:$U80,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M80:$U80)+($M80:$U80="DNA")),$M80:$U80),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M80:$U80)+($M80:$U80="DNA")),$M80:$U80),"")),IF(ISNUMBER($U80),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L80" s="33">
@@ -4780,7 +4791,7 @@
         <v/>
       </c>
       <c r="I81" s="32">
-        <f>IF(NOT(AND($A81&lt;&gt;"",OR($G81="",$G81="Active"))),"",IF(AND(MAX($M81:$U81)&gt;0,MAX($M81:$U81)&lt;TODAY(),COUNTBLANK($N81:$U81)&gt;0,COUNTIF($N81:$U81,"DNA")=0),1,0)+COUNTIF($N81:$U81,"DNA")+COUNTIF($V81:$Z81,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A81&lt;&gt;"",OR($G81="",$G81="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M81:$U81)+($M81:$U81="DNA")),$M81:$U81),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M81:$U81)+($M81:$U81="DNA")),$M81:$U81),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M81:$U81)+($M81:$U81="DNA")),$M81:$U81),"")&lt;TODAY())),1,0)+COUNTIF($V81:$Z81,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J81" s="32">
@@ -4788,7 +4799,7 @@
         <v/>
       </c>
       <c r="K81" s="32">
-        <f>IF(NOT(AND($A81&lt;&gt;"",OR($G81="",$G81="Active"))),"",IF($L81&lt;&gt;"",IF($L81=$M81,"Booking",INDEX($N$4:$U$4,MATCH($L81,$N81:$U81,0))),IF(COUNTIF($N81:$U81,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N81:$U81)=0,"All done",IF(MAX($M81:$U81)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A81&lt;&gt;"",OR($G81="",$G81="Active"))),"",IF($L81&lt;&gt;"",IF($L81=$M81,"Booking",INDEX($N$4:$U$4,MATCH($L81,$N81:$U81,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M81:$U81)+($M81:$U81="DNA")),$M81:$U81),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M81:$U81)+($M81:$U81="DNA")),$M81:$U81),"")),IF(ISNUMBER($U81),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L81" s="33">
@@ -4826,7 +4837,7 @@
         <v/>
       </c>
       <c r="I82" s="32">
-        <f>IF(NOT(AND($A82&lt;&gt;"",OR($G82="",$G82="Active"))),"",IF(AND(MAX($M82:$U82)&gt;0,MAX($M82:$U82)&lt;TODAY(),COUNTBLANK($N82:$U82)&gt;0,COUNTIF($N82:$U82,"DNA")=0),1,0)+COUNTIF($N82:$U82,"DNA")+COUNTIF($V82:$Z82,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A82&lt;&gt;"",OR($G82="",$G82="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M82:$U82)+($M82:$U82="DNA")),$M82:$U82),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M82:$U82)+($M82:$U82="DNA")),$M82:$U82),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M82:$U82)+($M82:$U82="DNA")),$M82:$U82),"")&lt;TODAY())),1,0)+COUNTIF($V82:$Z82,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J82" s="32">
@@ -4834,7 +4845,7 @@
         <v/>
       </c>
       <c r="K82" s="32">
-        <f>IF(NOT(AND($A82&lt;&gt;"",OR($G82="",$G82="Active"))),"",IF($L82&lt;&gt;"",IF($L82=$M82,"Booking",INDEX($N$4:$U$4,MATCH($L82,$N82:$U82,0))),IF(COUNTIF($N82:$U82,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N82:$U82)=0,"All done",IF(MAX($M82:$U82)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A82&lt;&gt;"",OR($G82="",$G82="Active"))),"",IF($L82&lt;&gt;"",IF($L82=$M82,"Booking",INDEX($N$4:$U$4,MATCH($L82,$N82:$U82,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M82:$U82)+($M82:$U82="DNA")),$M82:$U82),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M82:$U82)+($M82:$U82="DNA")),$M82:$U82),"")),IF(ISNUMBER($U82),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L82" s="33">
@@ -4872,7 +4883,7 @@
         <v/>
       </c>
       <c r="I83" s="32">
-        <f>IF(NOT(AND($A83&lt;&gt;"",OR($G83="",$G83="Active"))),"",IF(AND(MAX($M83:$U83)&gt;0,MAX($M83:$U83)&lt;TODAY(),COUNTBLANK($N83:$U83)&gt;0,COUNTIF($N83:$U83,"DNA")=0),1,0)+COUNTIF($N83:$U83,"DNA")+COUNTIF($V83:$Z83,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A83&lt;&gt;"",OR($G83="",$G83="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M83:$U83)+($M83:$U83="DNA")),$M83:$U83),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M83:$U83)+($M83:$U83="DNA")),$M83:$U83),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M83:$U83)+($M83:$U83="DNA")),$M83:$U83),"")&lt;TODAY())),1,0)+COUNTIF($V83:$Z83,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J83" s="32">
@@ -4880,7 +4891,7 @@
         <v/>
       </c>
       <c r="K83" s="32">
-        <f>IF(NOT(AND($A83&lt;&gt;"",OR($G83="",$G83="Active"))),"",IF($L83&lt;&gt;"",IF($L83=$M83,"Booking",INDEX($N$4:$U$4,MATCH($L83,$N83:$U83,0))),IF(COUNTIF($N83:$U83,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N83:$U83)=0,"All done",IF(MAX($M83:$U83)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A83&lt;&gt;"",OR($G83="",$G83="Active"))),"",IF($L83&lt;&gt;"",IF($L83=$M83,"Booking",INDEX($N$4:$U$4,MATCH($L83,$N83:$U83,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M83:$U83)+($M83:$U83="DNA")),$M83:$U83),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M83:$U83)+($M83:$U83="DNA")),$M83:$U83),"")),IF(ISNUMBER($U83),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L83" s="33">
@@ -4918,7 +4929,7 @@
         <v/>
       </c>
       <c r="I84" s="32">
-        <f>IF(NOT(AND($A84&lt;&gt;"",OR($G84="",$G84="Active"))),"",IF(AND(MAX($M84:$U84)&gt;0,MAX($M84:$U84)&lt;TODAY(),COUNTBLANK($N84:$U84)&gt;0,COUNTIF($N84:$U84,"DNA")=0),1,0)+COUNTIF($N84:$U84,"DNA")+COUNTIF($V84:$Z84,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A84&lt;&gt;"",OR($G84="",$G84="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M84:$U84)+($M84:$U84="DNA")),$M84:$U84),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M84:$U84)+($M84:$U84="DNA")),$M84:$U84),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M84:$U84)+($M84:$U84="DNA")),$M84:$U84),"")&lt;TODAY())),1,0)+COUNTIF($V84:$Z84,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J84" s="32">
@@ -4926,7 +4937,7 @@
         <v/>
       </c>
       <c r="K84" s="32">
-        <f>IF(NOT(AND($A84&lt;&gt;"",OR($G84="",$G84="Active"))),"",IF($L84&lt;&gt;"",IF($L84=$M84,"Booking",INDEX($N$4:$U$4,MATCH($L84,$N84:$U84,0))),IF(COUNTIF($N84:$U84,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N84:$U84)=0,"All done",IF(MAX($M84:$U84)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A84&lt;&gt;"",OR($G84="",$G84="Active"))),"",IF($L84&lt;&gt;"",IF($L84=$M84,"Booking",INDEX($N$4:$U$4,MATCH($L84,$N84:$U84,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M84:$U84)+($M84:$U84="DNA")),$M84:$U84),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M84:$U84)+($M84:$U84="DNA")),$M84:$U84),"")),IF(ISNUMBER($U84),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L84" s="33">
@@ -4964,7 +4975,7 @@
         <v/>
       </c>
       <c r="I85" s="32">
-        <f>IF(NOT(AND($A85&lt;&gt;"",OR($G85="",$G85="Active"))),"",IF(AND(MAX($M85:$U85)&gt;0,MAX($M85:$U85)&lt;TODAY(),COUNTBLANK($N85:$U85)&gt;0,COUNTIF($N85:$U85,"DNA")=0),1,0)+COUNTIF($N85:$U85,"DNA")+COUNTIF($V85:$Z85,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A85&lt;&gt;"",OR($G85="",$G85="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M85:$U85)+($M85:$U85="DNA")),$M85:$U85),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M85:$U85)+($M85:$U85="DNA")),$M85:$U85),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M85:$U85)+($M85:$U85="DNA")),$M85:$U85),"")&lt;TODAY())),1,0)+COUNTIF($V85:$Z85,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J85" s="32">
@@ -4972,7 +4983,7 @@
         <v/>
       </c>
       <c r="K85" s="32">
-        <f>IF(NOT(AND($A85&lt;&gt;"",OR($G85="",$G85="Active"))),"",IF($L85&lt;&gt;"",IF($L85=$M85,"Booking",INDEX($N$4:$U$4,MATCH($L85,$N85:$U85,0))),IF(COUNTIF($N85:$U85,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N85:$U85)=0,"All done",IF(MAX($M85:$U85)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A85&lt;&gt;"",OR($G85="",$G85="Active"))),"",IF($L85&lt;&gt;"",IF($L85=$M85,"Booking",INDEX($N$4:$U$4,MATCH($L85,$N85:$U85,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M85:$U85)+($M85:$U85="DNA")),$M85:$U85),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M85:$U85)+($M85:$U85="DNA")),$M85:$U85),"")),IF(ISNUMBER($U85),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L85" s="33">
@@ -5010,7 +5021,7 @@
         <v/>
       </c>
       <c r="I86" s="32">
-        <f>IF(NOT(AND($A86&lt;&gt;"",OR($G86="",$G86="Active"))),"",IF(AND(MAX($M86:$U86)&gt;0,MAX($M86:$U86)&lt;TODAY(),COUNTBLANK($N86:$U86)&gt;0,COUNTIF($N86:$U86,"DNA")=0),1,0)+COUNTIF($N86:$U86,"DNA")+COUNTIF($V86:$Z86,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A86&lt;&gt;"",OR($G86="",$G86="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M86:$U86)+($M86:$U86="DNA")),$M86:$U86),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M86:$U86)+($M86:$U86="DNA")),$M86:$U86),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M86:$U86)+($M86:$U86="DNA")),$M86:$U86),"")&lt;TODAY())),1,0)+COUNTIF($V86:$Z86,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J86" s="32">
@@ -5018,7 +5029,7 @@
         <v/>
       </c>
       <c r="K86" s="32">
-        <f>IF(NOT(AND($A86&lt;&gt;"",OR($G86="",$G86="Active"))),"",IF($L86&lt;&gt;"",IF($L86=$M86,"Booking",INDEX($N$4:$U$4,MATCH($L86,$N86:$U86,0))),IF(COUNTIF($N86:$U86,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N86:$U86)=0,"All done",IF(MAX($M86:$U86)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A86&lt;&gt;"",OR($G86="",$G86="Active"))),"",IF($L86&lt;&gt;"",IF($L86=$M86,"Booking",INDEX($N$4:$U$4,MATCH($L86,$N86:$U86,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M86:$U86)+($M86:$U86="DNA")),$M86:$U86),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M86:$U86)+($M86:$U86="DNA")),$M86:$U86),"")),IF(ISNUMBER($U86),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L86" s="33">
@@ -5056,7 +5067,7 @@
         <v/>
       </c>
       <c r="I87" s="32">
-        <f>IF(NOT(AND($A87&lt;&gt;"",OR($G87="",$G87="Active"))),"",IF(AND(MAX($M87:$U87)&gt;0,MAX($M87:$U87)&lt;TODAY(),COUNTBLANK($N87:$U87)&gt;0,COUNTIF($N87:$U87,"DNA")=0),1,0)+COUNTIF($N87:$U87,"DNA")+COUNTIF($V87:$Z87,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A87&lt;&gt;"",OR($G87="",$G87="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M87:$U87)+($M87:$U87="DNA")),$M87:$U87),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M87:$U87)+($M87:$U87="DNA")),$M87:$U87),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M87:$U87)+($M87:$U87="DNA")),$M87:$U87),"")&lt;TODAY())),1,0)+COUNTIF($V87:$Z87,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J87" s="32">
@@ -5064,7 +5075,7 @@
         <v/>
       </c>
       <c r="K87" s="32">
-        <f>IF(NOT(AND($A87&lt;&gt;"",OR($G87="",$G87="Active"))),"",IF($L87&lt;&gt;"",IF($L87=$M87,"Booking",INDEX($N$4:$U$4,MATCH($L87,$N87:$U87,0))),IF(COUNTIF($N87:$U87,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N87:$U87)=0,"All done",IF(MAX($M87:$U87)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A87&lt;&gt;"",OR($G87="",$G87="Active"))),"",IF($L87&lt;&gt;"",IF($L87=$M87,"Booking",INDEX($N$4:$U$4,MATCH($L87,$N87:$U87,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M87:$U87)+($M87:$U87="DNA")),$M87:$U87),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M87:$U87)+($M87:$U87="DNA")),$M87:$U87),"")),IF(ISNUMBER($U87),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L87" s="33">
@@ -5102,7 +5113,7 @@
         <v/>
       </c>
       <c r="I88" s="32">
-        <f>IF(NOT(AND($A88&lt;&gt;"",OR($G88="",$G88="Active"))),"",IF(AND(MAX($M88:$U88)&gt;0,MAX($M88:$U88)&lt;TODAY(),COUNTBLANK($N88:$U88)&gt;0,COUNTIF($N88:$U88,"DNA")=0),1,0)+COUNTIF($N88:$U88,"DNA")+COUNTIF($V88:$Z88,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A88&lt;&gt;"",OR($G88="",$G88="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M88:$U88)+($M88:$U88="DNA")),$M88:$U88),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M88:$U88)+($M88:$U88="DNA")),$M88:$U88),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M88:$U88)+($M88:$U88="DNA")),$M88:$U88),"")&lt;TODAY())),1,0)+COUNTIF($V88:$Z88,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J88" s="32">
@@ -5110,7 +5121,7 @@
         <v/>
       </c>
       <c r="K88" s="32">
-        <f>IF(NOT(AND($A88&lt;&gt;"",OR($G88="",$G88="Active"))),"",IF($L88&lt;&gt;"",IF($L88=$M88,"Booking",INDEX($N$4:$U$4,MATCH($L88,$N88:$U88,0))),IF(COUNTIF($N88:$U88,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N88:$U88)=0,"All done",IF(MAX($M88:$U88)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A88&lt;&gt;"",OR($G88="",$G88="Active"))),"",IF($L88&lt;&gt;"",IF($L88=$M88,"Booking",INDEX($N$4:$U$4,MATCH($L88,$N88:$U88,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M88:$U88)+($M88:$U88="DNA")),$M88:$U88),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M88:$U88)+($M88:$U88="DNA")),$M88:$U88),"")),IF(ISNUMBER($U88),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L88" s="33">
@@ -5148,7 +5159,7 @@
         <v/>
       </c>
       <c r="I89" s="32">
-        <f>IF(NOT(AND($A89&lt;&gt;"",OR($G89="",$G89="Active"))),"",IF(AND(MAX($M89:$U89)&gt;0,MAX($M89:$U89)&lt;TODAY(),COUNTBLANK($N89:$U89)&gt;0,COUNTIF($N89:$U89,"DNA")=0),1,0)+COUNTIF($N89:$U89,"DNA")+COUNTIF($V89:$Z89,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A89&lt;&gt;"",OR($G89="",$G89="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M89:$U89)+($M89:$U89="DNA")),$M89:$U89),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M89:$U89)+($M89:$U89="DNA")),$M89:$U89),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M89:$U89)+($M89:$U89="DNA")),$M89:$U89),"")&lt;TODAY())),1,0)+COUNTIF($V89:$Z89,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J89" s="32">
@@ -5156,7 +5167,7 @@
         <v/>
       </c>
       <c r="K89" s="32">
-        <f>IF(NOT(AND($A89&lt;&gt;"",OR($G89="",$G89="Active"))),"",IF($L89&lt;&gt;"",IF($L89=$M89,"Booking",INDEX($N$4:$U$4,MATCH($L89,$N89:$U89,0))),IF(COUNTIF($N89:$U89,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N89:$U89)=0,"All done",IF(MAX($M89:$U89)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A89&lt;&gt;"",OR($G89="",$G89="Active"))),"",IF($L89&lt;&gt;"",IF($L89=$M89,"Booking",INDEX($N$4:$U$4,MATCH($L89,$N89:$U89,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M89:$U89)+($M89:$U89="DNA")),$M89:$U89),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M89:$U89)+($M89:$U89="DNA")),$M89:$U89),"")),IF(ISNUMBER($U89),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L89" s="33">
@@ -5194,7 +5205,7 @@
         <v/>
       </c>
       <c r="I90" s="32">
-        <f>IF(NOT(AND($A90&lt;&gt;"",OR($G90="",$G90="Active"))),"",IF(AND(MAX($M90:$U90)&gt;0,MAX($M90:$U90)&lt;TODAY(),COUNTBLANK($N90:$U90)&gt;0,COUNTIF($N90:$U90,"DNA")=0),1,0)+COUNTIF($N90:$U90,"DNA")+COUNTIF($V90:$Z90,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A90&lt;&gt;"",OR($G90="",$G90="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M90:$U90)+($M90:$U90="DNA")),$M90:$U90),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M90:$U90)+($M90:$U90="DNA")),$M90:$U90),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M90:$U90)+($M90:$U90="DNA")),$M90:$U90),"")&lt;TODAY())),1,0)+COUNTIF($V90:$Z90,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J90" s="32">
@@ -5202,7 +5213,7 @@
         <v/>
       </c>
       <c r="K90" s="32">
-        <f>IF(NOT(AND($A90&lt;&gt;"",OR($G90="",$G90="Active"))),"",IF($L90&lt;&gt;"",IF($L90=$M90,"Booking",INDEX($N$4:$U$4,MATCH($L90,$N90:$U90,0))),IF(COUNTIF($N90:$U90,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N90:$U90)=0,"All done",IF(MAX($M90:$U90)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A90&lt;&gt;"",OR($G90="",$G90="Active"))),"",IF($L90&lt;&gt;"",IF($L90=$M90,"Booking",INDEX($N$4:$U$4,MATCH($L90,$N90:$U90,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M90:$U90)+($M90:$U90="DNA")),$M90:$U90),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M90:$U90)+($M90:$U90="DNA")),$M90:$U90),"")),IF(ISNUMBER($U90),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L90" s="33">
@@ -5240,7 +5251,7 @@
         <v/>
       </c>
       <c r="I91" s="32">
-        <f>IF(NOT(AND($A91&lt;&gt;"",OR($G91="",$G91="Active"))),"",IF(AND(MAX($M91:$U91)&gt;0,MAX($M91:$U91)&lt;TODAY(),COUNTBLANK($N91:$U91)&gt;0,COUNTIF($N91:$U91,"DNA")=0),1,0)+COUNTIF($N91:$U91,"DNA")+COUNTIF($V91:$Z91,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A91&lt;&gt;"",OR($G91="",$G91="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M91:$U91)+($M91:$U91="DNA")),$M91:$U91),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M91:$U91)+($M91:$U91="DNA")),$M91:$U91),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M91:$U91)+($M91:$U91="DNA")),$M91:$U91),"")&lt;TODAY())),1,0)+COUNTIF($V91:$Z91,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J91" s="32">
@@ -5248,7 +5259,7 @@
         <v/>
       </c>
       <c r="K91" s="32">
-        <f>IF(NOT(AND($A91&lt;&gt;"",OR($G91="",$G91="Active"))),"",IF($L91&lt;&gt;"",IF($L91=$M91,"Booking",INDEX($N$4:$U$4,MATCH($L91,$N91:$U91,0))),IF(COUNTIF($N91:$U91,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N91:$U91)=0,"All done",IF(MAX($M91:$U91)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A91&lt;&gt;"",OR($G91="",$G91="Active"))),"",IF($L91&lt;&gt;"",IF($L91=$M91,"Booking",INDEX($N$4:$U$4,MATCH($L91,$N91:$U91,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M91:$U91)+($M91:$U91="DNA")),$M91:$U91),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M91:$U91)+($M91:$U91="DNA")),$M91:$U91),"")),IF(ISNUMBER($U91),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L91" s="33">
@@ -5286,7 +5297,7 @@
         <v/>
       </c>
       <c r="I92" s="32">
-        <f>IF(NOT(AND($A92&lt;&gt;"",OR($G92="",$G92="Active"))),"",IF(AND(MAX($M92:$U92)&gt;0,MAX($M92:$U92)&lt;TODAY(),COUNTBLANK($N92:$U92)&gt;0,COUNTIF($N92:$U92,"DNA")=0),1,0)+COUNTIF($N92:$U92,"DNA")+COUNTIF($V92:$Z92,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A92&lt;&gt;"",OR($G92="",$G92="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M92:$U92)+($M92:$U92="DNA")),$M92:$U92),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M92:$U92)+($M92:$U92="DNA")),$M92:$U92),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M92:$U92)+($M92:$U92="DNA")),$M92:$U92),"")&lt;TODAY())),1,0)+COUNTIF($V92:$Z92,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J92" s="32">
@@ -5294,7 +5305,7 @@
         <v/>
       </c>
       <c r="K92" s="32">
-        <f>IF(NOT(AND($A92&lt;&gt;"",OR($G92="",$G92="Active"))),"",IF($L92&lt;&gt;"",IF($L92=$M92,"Booking",INDEX($N$4:$U$4,MATCH($L92,$N92:$U92,0))),IF(COUNTIF($N92:$U92,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N92:$U92)=0,"All done",IF(MAX($M92:$U92)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A92&lt;&gt;"",OR($G92="",$G92="Active"))),"",IF($L92&lt;&gt;"",IF($L92=$M92,"Booking",INDEX($N$4:$U$4,MATCH($L92,$N92:$U92,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M92:$U92)+($M92:$U92="DNA")),$M92:$U92),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M92:$U92)+($M92:$U92="DNA")),$M92:$U92),"")),IF(ISNUMBER($U92),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L92" s="33">
@@ -5332,7 +5343,7 @@
         <v/>
       </c>
       <c r="I93" s="32">
-        <f>IF(NOT(AND($A93&lt;&gt;"",OR($G93="",$G93="Active"))),"",IF(AND(MAX($M93:$U93)&gt;0,MAX($M93:$U93)&lt;TODAY(),COUNTBLANK($N93:$U93)&gt;0,COUNTIF($N93:$U93,"DNA")=0),1,0)+COUNTIF($N93:$U93,"DNA")+COUNTIF($V93:$Z93,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A93&lt;&gt;"",OR($G93="",$G93="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M93:$U93)+($M93:$U93="DNA")),$M93:$U93),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M93:$U93)+($M93:$U93="DNA")),$M93:$U93),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M93:$U93)+($M93:$U93="DNA")),$M93:$U93),"")&lt;TODAY())),1,0)+COUNTIF($V93:$Z93,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J93" s="32">
@@ -5340,7 +5351,7 @@
         <v/>
       </c>
       <c r="K93" s="32">
-        <f>IF(NOT(AND($A93&lt;&gt;"",OR($G93="",$G93="Active"))),"",IF($L93&lt;&gt;"",IF($L93=$M93,"Booking",INDEX($N$4:$U$4,MATCH($L93,$N93:$U93,0))),IF(COUNTIF($N93:$U93,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N93:$U93)=0,"All done",IF(MAX($M93:$U93)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A93&lt;&gt;"",OR($G93="",$G93="Active"))),"",IF($L93&lt;&gt;"",IF($L93=$M93,"Booking",INDEX($N$4:$U$4,MATCH($L93,$N93:$U93,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M93:$U93)+($M93:$U93="DNA")),$M93:$U93),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M93:$U93)+($M93:$U93="DNA")),$M93:$U93),"")),IF(ISNUMBER($U93),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L93" s="33">
@@ -5378,7 +5389,7 @@
         <v/>
       </c>
       <c r="I94" s="32">
-        <f>IF(NOT(AND($A94&lt;&gt;"",OR($G94="",$G94="Active"))),"",IF(AND(MAX($M94:$U94)&gt;0,MAX($M94:$U94)&lt;TODAY(),COUNTBLANK($N94:$U94)&gt;0,COUNTIF($N94:$U94,"DNA")=0),1,0)+COUNTIF($N94:$U94,"DNA")+COUNTIF($V94:$Z94,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A94&lt;&gt;"",OR($G94="",$G94="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M94:$U94)+($M94:$U94="DNA")),$M94:$U94),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M94:$U94)+($M94:$U94="DNA")),$M94:$U94),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M94:$U94)+($M94:$U94="DNA")),$M94:$U94),"")&lt;TODAY())),1,0)+COUNTIF($V94:$Z94,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J94" s="32">
@@ -5386,7 +5397,7 @@
         <v/>
       </c>
       <c r="K94" s="32">
-        <f>IF(NOT(AND($A94&lt;&gt;"",OR($G94="",$G94="Active"))),"",IF($L94&lt;&gt;"",IF($L94=$M94,"Booking",INDEX($N$4:$U$4,MATCH($L94,$N94:$U94,0))),IF(COUNTIF($N94:$U94,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N94:$U94)=0,"All done",IF(MAX($M94:$U94)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A94&lt;&gt;"",OR($G94="",$G94="Active"))),"",IF($L94&lt;&gt;"",IF($L94=$M94,"Booking",INDEX($N$4:$U$4,MATCH($L94,$N94:$U94,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M94:$U94)+($M94:$U94="DNA")),$M94:$U94),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M94:$U94)+($M94:$U94="DNA")),$M94:$U94),"")),IF(ISNUMBER($U94),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L94" s="33">
@@ -5424,7 +5435,7 @@
         <v/>
       </c>
       <c r="I95" s="32">
-        <f>IF(NOT(AND($A95&lt;&gt;"",OR($G95="",$G95="Active"))),"",IF(AND(MAX($M95:$U95)&gt;0,MAX($M95:$U95)&lt;TODAY(),COUNTBLANK($N95:$U95)&gt;0,COUNTIF($N95:$U95,"DNA")=0),1,0)+COUNTIF($N95:$U95,"DNA")+COUNTIF($V95:$Z95,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A95&lt;&gt;"",OR($G95="",$G95="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M95:$U95)+($M95:$U95="DNA")),$M95:$U95),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M95:$U95)+($M95:$U95="DNA")),$M95:$U95),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M95:$U95)+($M95:$U95="DNA")),$M95:$U95),"")&lt;TODAY())),1,0)+COUNTIF($V95:$Z95,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J95" s="32">
@@ -5432,7 +5443,7 @@
         <v/>
       </c>
       <c r="K95" s="32">
-        <f>IF(NOT(AND($A95&lt;&gt;"",OR($G95="",$G95="Active"))),"",IF($L95&lt;&gt;"",IF($L95=$M95,"Booking",INDEX($N$4:$U$4,MATCH($L95,$N95:$U95,0))),IF(COUNTIF($N95:$U95,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N95:$U95)=0,"All done",IF(MAX($M95:$U95)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A95&lt;&gt;"",OR($G95="",$G95="Active"))),"",IF($L95&lt;&gt;"",IF($L95=$M95,"Booking",INDEX($N$4:$U$4,MATCH($L95,$N95:$U95,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M95:$U95)+($M95:$U95="DNA")),$M95:$U95),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M95:$U95)+($M95:$U95="DNA")),$M95:$U95),"")),IF(ISNUMBER($U95),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L95" s="33">
@@ -5470,7 +5481,7 @@
         <v/>
       </c>
       <c r="I96" s="32">
-        <f>IF(NOT(AND($A96&lt;&gt;"",OR($G96="",$G96="Active"))),"",IF(AND(MAX($M96:$U96)&gt;0,MAX($M96:$U96)&lt;TODAY(),COUNTBLANK($N96:$U96)&gt;0,COUNTIF($N96:$U96,"DNA")=0),1,0)+COUNTIF($N96:$U96,"DNA")+COUNTIF($V96:$Z96,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A96&lt;&gt;"",OR($G96="",$G96="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M96:$U96)+($M96:$U96="DNA")),$M96:$U96),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M96:$U96)+($M96:$U96="DNA")),$M96:$U96),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M96:$U96)+($M96:$U96="DNA")),$M96:$U96),"")&lt;TODAY())),1,0)+COUNTIF($V96:$Z96,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J96" s="32">
@@ -5478,7 +5489,7 @@
         <v/>
       </c>
       <c r="K96" s="32">
-        <f>IF(NOT(AND($A96&lt;&gt;"",OR($G96="",$G96="Active"))),"",IF($L96&lt;&gt;"",IF($L96=$M96,"Booking",INDEX($N$4:$U$4,MATCH($L96,$N96:$U96,0))),IF(COUNTIF($N96:$U96,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N96:$U96)=0,"All done",IF(MAX($M96:$U96)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A96&lt;&gt;"",OR($G96="",$G96="Active"))),"",IF($L96&lt;&gt;"",IF($L96=$M96,"Booking",INDEX($N$4:$U$4,MATCH($L96,$N96:$U96,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M96:$U96)+($M96:$U96="DNA")),$M96:$U96),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M96:$U96)+($M96:$U96="DNA")),$M96:$U96),"")),IF(ISNUMBER($U96),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L96" s="33">
@@ -5516,7 +5527,7 @@
         <v/>
       </c>
       <c r="I97" s="32">
-        <f>IF(NOT(AND($A97&lt;&gt;"",OR($G97="",$G97="Active"))),"",IF(AND(MAX($M97:$U97)&gt;0,MAX($M97:$U97)&lt;TODAY(),COUNTBLANK($N97:$U97)&gt;0,COUNTIF($N97:$U97,"DNA")=0),1,0)+COUNTIF($N97:$U97,"DNA")+COUNTIF($V97:$Z97,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A97&lt;&gt;"",OR($G97="",$G97="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M97:$U97)+($M97:$U97="DNA")),$M97:$U97),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M97:$U97)+($M97:$U97="DNA")),$M97:$U97),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M97:$U97)+($M97:$U97="DNA")),$M97:$U97),"")&lt;TODAY())),1,0)+COUNTIF($V97:$Z97,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J97" s="32">
@@ -5524,7 +5535,7 @@
         <v/>
       </c>
       <c r="K97" s="32">
-        <f>IF(NOT(AND($A97&lt;&gt;"",OR($G97="",$G97="Active"))),"",IF($L97&lt;&gt;"",IF($L97=$M97,"Booking",INDEX($N$4:$U$4,MATCH($L97,$N97:$U97,0))),IF(COUNTIF($N97:$U97,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N97:$U97)=0,"All done",IF(MAX($M97:$U97)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A97&lt;&gt;"",OR($G97="",$G97="Active"))),"",IF($L97&lt;&gt;"",IF($L97=$M97,"Booking",INDEX($N$4:$U$4,MATCH($L97,$N97:$U97,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M97:$U97)+($M97:$U97="DNA")),$M97:$U97),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M97:$U97)+($M97:$U97="DNA")),$M97:$U97),"")),IF(ISNUMBER($U97),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L97" s="33">
@@ -5562,7 +5573,7 @@
         <v/>
       </c>
       <c r="I98" s="32">
-        <f>IF(NOT(AND($A98&lt;&gt;"",OR($G98="",$G98="Active"))),"",IF(AND(MAX($M98:$U98)&gt;0,MAX($M98:$U98)&lt;TODAY(),COUNTBLANK($N98:$U98)&gt;0,COUNTIF($N98:$U98,"DNA")=0),1,0)+COUNTIF($N98:$U98,"DNA")+COUNTIF($V98:$Z98,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A98&lt;&gt;"",OR($G98="",$G98="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M98:$U98)+($M98:$U98="DNA")),$M98:$U98),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M98:$U98)+($M98:$U98="DNA")),$M98:$U98),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M98:$U98)+($M98:$U98="DNA")),$M98:$U98),"")&lt;TODAY())),1,0)+COUNTIF($V98:$Z98,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J98" s="32">
@@ -5570,7 +5581,7 @@
         <v/>
       </c>
       <c r="K98" s="32">
-        <f>IF(NOT(AND($A98&lt;&gt;"",OR($G98="",$G98="Active"))),"",IF($L98&lt;&gt;"",IF($L98=$M98,"Booking",INDEX($N$4:$U$4,MATCH($L98,$N98:$U98,0))),IF(COUNTIF($N98:$U98,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N98:$U98)=0,"All done",IF(MAX($M98:$U98)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A98&lt;&gt;"",OR($G98="",$G98="Active"))),"",IF($L98&lt;&gt;"",IF($L98=$M98,"Booking",INDEX($N$4:$U$4,MATCH($L98,$N98:$U98,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M98:$U98)+($M98:$U98="DNA")),$M98:$U98),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M98:$U98)+($M98:$U98="DNA")),$M98:$U98),"")),IF(ISNUMBER($U98),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L98" s="33">
@@ -5608,7 +5619,7 @@
         <v/>
       </c>
       <c r="I99" s="32">
-        <f>IF(NOT(AND($A99&lt;&gt;"",OR($G99="",$G99="Active"))),"",IF(AND(MAX($M99:$U99)&gt;0,MAX($M99:$U99)&lt;TODAY(),COUNTBLANK($N99:$U99)&gt;0,COUNTIF($N99:$U99,"DNA")=0),1,0)+COUNTIF($N99:$U99,"DNA")+COUNTIF($V99:$Z99,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A99&lt;&gt;"",OR($G99="",$G99="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M99:$U99)+($M99:$U99="DNA")),$M99:$U99),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M99:$U99)+($M99:$U99="DNA")),$M99:$U99),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M99:$U99)+($M99:$U99="DNA")),$M99:$U99),"")&lt;TODAY())),1,0)+COUNTIF($V99:$Z99,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J99" s="32">
@@ -5616,7 +5627,7 @@
         <v/>
       </c>
       <c r="K99" s="32">
-        <f>IF(NOT(AND($A99&lt;&gt;"",OR($G99="",$G99="Active"))),"",IF($L99&lt;&gt;"",IF($L99=$M99,"Booking",INDEX($N$4:$U$4,MATCH($L99,$N99:$U99,0))),IF(COUNTIF($N99:$U99,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N99:$U99)=0,"All done",IF(MAX($M99:$U99)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A99&lt;&gt;"",OR($G99="",$G99="Active"))),"",IF($L99&lt;&gt;"",IF($L99=$M99,"Booking",INDEX($N$4:$U$4,MATCH($L99,$N99:$U99,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M99:$U99)+($M99:$U99="DNA")),$M99:$U99),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M99:$U99)+($M99:$U99="DNA")),$M99:$U99),"")),IF(ISNUMBER($U99),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L99" s="33">
@@ -5654,7 +5665,7 @@
         <v/>
       </c>
       <c r="I100" s="32">
-        <f>IF(NOT(AND($A100&lt;&gt;"",OR($G100="",$G100="Active"))),"",IF(AND(MAX($M100:$U100)&gt;0,MAX($M100:$U100)&lt;TODAY(),COUNTBLANK($N100:$U100)&gt;0,COUNTIF($N100:$U100,"DNA")=0),1,0)+COUNTIF($N100:$U100,"DNA")+COUNTIF($V100:$Z100,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A100&lt;&gt;"",OR($G100="",$G100="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M100:$U100)+($M100:$U100="DNA")),$M100:$U100),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M100:$U100)+($M100:$U100="DNA")),$M100:$U100),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M100:$U100)+($M100:$U100="DNA")),$M100:$U100),"")&lt;TODAY())),1,0)+COUNTIF($V100:$Z100,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J100" s="32">
@@ -5662,7 +5673,7 @@
         <v/>
       </c>
       <c r="K100" s="32">
-        <f>IF(NOT(AND($A100&lt;&gt;"",OR($G100="",$G100="Active"))),"",IF($L100&lt;&gt;"",IF($L100=$M100,"Booking",INDEX($N$4:$U$4,MATCH($L100,$N100:$U100,0))),IF(COUNTIF($N100:$U100,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N100:$U100)=0,"All done",IF(MAX($M100:$U100)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A100&lt;&gt;"",OR($G100="",$G100="Active"))),"",IF($L100&lt;&gt;"",IF($L100=$M100,"Booking",INDEX($N$4:$U$4,MATCH($L100,$N100:$U100,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M100:$U100)+($M100:$U100="DNA")),$M100:$U100),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M100:$U100)+($M100:$U100="DNA")),$M100:$U100),"")),IF(ISNUMBER($U100),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L100" s="33">
@@ -5700,7 +5711,7 @@
         <v/>
       </c>
       <c r="I101" s="32">
-        <f>IF(NOT(AND($A101&lt;&gt;"",OR($G101="",$G101="Active"))),"",IF(AND(MAX($M101:$U101)&gt;0,MAX($M101:$U101)&lt;TODAY(),COUNTBLANK($N101:$U101)&gt;0,COUNTIF($N101:$U101,"DNA")=0),1,0)+COUNTIF($N101:$U101,"DNA")+COUNTIF($V101:$Z101,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A101&lt;&gt;"",OR($G101="",$G101="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M101:$U101)+($M101:$U101="DNA")),$M101:$U101),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M101:$U101)+($M101:$U101="DNA")),$M101:$U101),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M101:$U101)+($M101:$U101="DNA")),$M101:$U101),"")&lt;TODAY())),1,0)+COUNTIF($V101:$Z101,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J101" s="32">
@@ -5708,7 +5719,7 @@
         <v/>
       </c>
       <c r="K101" s="32">
-        <f>IF(NOT(AND($A101&lt;&gt;"",OR($G101="",$G101="Active"))),"",IF($L101&lt;&gt;"",IF($L101=$M101,"Booking",INDEX($N$4:$U$4,MATCH($L101,$N101:$U101,0))),IF(COUNTIF($N101:$U101,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N101:$U101)=0,"All done",IF(MAX($M101:$U101)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A101&lt;&gt;"",OR($G101="",$G101="Active"))),"",IF($L101&lt;&gt;"",IF($L101=$M101,"Booking",INDEX($N$4:$U$4,MATCH($L101,$N101:$U101,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M101:$U101)+($M101:$U101="DNA")),$M101:$U101),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M101:$U101)+($M101:$U101="DNA")),$M101:$U101),"")),IF(ISNUMBER($U101),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L101" s="33">
@@ -5746,7 +5757,7 @@
         <v/>
       </c>
       <c r="I102" s="32">
-        <f>IF(NOT(AND($A102&lt;&gt;"",OR($G102="",$G102="Active"))),"",IF(AND(MAX($M102:$U102)&gt;0,MAX($M102:$U102)&lt;TODAY(),COUNTBLANK($N102:$U102)&gt;0,COUNTIF($N102:$U102,"DNA")=0),1,0)+COUNTIF($N102:$U102,"DNA")+COUNTIF($V102:$Z102,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A102&lt;&gt;"",OR($G102="",$G102="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M102:$U102)+($M102:$U102="DNA")),$M102:$U102),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M102:$U102)+($M102:$U102="DNA")),$M102:$U102),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M102:$U102)+($M102:$U102="DNA")),$M102:$U102),"")&lt;TODAY())),1,0)+COUNTIF($V102:$Z102,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J102" s="32">
@@ -5754,7 +5765,7 @@
         <v/>
       </c>
       <c r="K102" s="32">
-        <f>IF(NOT(AND($A102&lt;&gt;"",OR($G102="",$G102="Active"))),"",IF($L102&lt;&gt;"",IF($L102=$M102,"Booking",INDEX($N$4:$U$4,MATCH($L102,$N102:$U102,0))),IF(COUNTIF($N102:$U102,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N102:$U102)=0,"All done",IF(MAX($M102:$U102)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A102&lt;&gt;"",OR($G102="",$G102="Active"))),"",IF($L102&lt;&gt;"",IF($L102=$M102,"Booking",INDEX($N$4:$U$4,MATCH($L102,$N102:$U102,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M102:$U102)+($M102:$U102="DNA")),$M102:$U102),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M102:$U102)+($M102:$U102="DNA")),$M102:$U102),"")),IF(ISNUMBER($U102),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L102" s="33">
@@ -5792,7 +5803,7 @@
         <v/>
       </c>
       <c r="I103" s="32">
-        <f>IF(NOT(AND($A103&lt;&gt;"",OR($G103="",$G103="Active"))),"",IF(AND(MAX($M103:$U103)&gt;0,MAX($M103:$U103)&lt;TODAY(),COUNTBLANK($N103:$U103)&gt;0,COUNTIF($N103:$U103,"DNA")=0),1,0)+COUNTIF($N103:$U103,"DNA")+COUNTIF($V103:$Z103,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A103&lt;&gt;"",OR($G103="",$G103="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M103:$U103)+($M103:$U103="DNA")),$M103:$U103),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M103:$U103)+($M103:$U103="DNA")),$M103:$U103),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M103:$U103)+($M103:$U103="DNA")),$M103:$U103),"")&lt;TODAY())),1,0)+COUNTIF($V103:$Z103,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J103" s="32">
@@ -5800,7 +5811,7 @@
         <v/>
       </c>
       <c r="K103" s="32">
-        <f>IF(NOT(AND($A103&lt;&gt;"",OR($G103="",$G103="Active"))),"",IF($L103&lt;&gt;"",IF($L103=$M103,"Booking",INDEX($N$4:$U$4,MATCH($L103,$N103:$U103,0))),IF(COUNTIF($N103:$U103,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N103:$U103)=0,"All done",IF(MAX($M103:$U103)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A103&lt;&gt;"",OR($G103="",$G103="Active"))),"",IF($L103&lt;&gt;"",IF($L103=$M103,"Booking",INDEX($N$4:$U$4,MATCH($L103,$N103:$U103,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M103:$U103)+($M103:$U103="DNA")),$M103:$U103),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M103:$U103)+($M103:$U103="DNA")),$M103:$U103),"")),IF(ISNUMBER($U103),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L103" s="33">
@@ -5838,7 +5849,7 @@
         <v/>
       </c>
       <c r="I104" s="32">
-        <f>IF(NOT(AND($A104&lt;&gt;"",OR($G104="",$G104="Active"))),"",IF(AND(MAX($M104:$U104)&gt;0,MAX($M104:$U104)&lt;TODAY(),COUNTBLANK($N104:$U104)&gt;0,COUNTIF($N104:$U104,"DNA")=0),1,0)+COUNTIF($N104:$U104,"DNA")+COUNTIF($V104:$Z104,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A104&lt;&gt;"",OR($G104="",$G104="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M104:$U104)+($M104:$U104="DNA")),$M104:$U104),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M104:$U104)+($M104:$U104="DNA")),$M104:$U104),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M104:$U104)+($M104:$U104="DNA")),$M104:$U104),"")&lt;TODAY())),1,0)+COUNTIF($V104:$Z104,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J104" s="32">
@@ -5846,7 +5857,7 @@
         <v/>
       </c>
       <c r="K104" s="32">
-        <f>IF(NOT(AND($A104&lt;&gt;"",OR($G104="",$G104="Active"))),"",IF($L104&lt;&gt;"",IF($L104=$M104,"Booking",INDEX($N$4:$U$4,MATCH($L104,$N104:$U104,0))),IF(COUNTIF($N104:$U104,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N104:$U104)=0,"All done",IF(MAX($M104:$U104)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A104&lt;&gt;"",OR($G104="",$G104="Active"))),"",IF($L104&lt;&gt;"",IF($L104=$M104,"Booking",INDEX($N$4:$U$4,MATCH($L104,$N104:$U104,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M104:$U104)+($M104:$U104="DNA")),$M104:$U104),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M104:$U104)+($M104:$U104="DNA")),$M104:$U104),"")),IF(ISNUMBER($U104),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L104" s="33">
@@ -5884,7 +5895,7 @@
         <v/>
       </c>
       <c r="I105" s="32">
-        <f>IF(NOT(AND($A105&lt;&gt;"",OR($G105="",$G105="Active"))),"",IF(AND(MAX($M105:$U105)&gt;0,MAX($M105:$U105)&lt;TODAY(),COUNTBLANK($N105:$U105)&gt;0,COUNTIF($N105:$U105,"DNA")=0),1,0)+COUNTIF($N105:$U105,"DNA")+COUNTIF($V105:$Z105,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A105&lt;&gt;"",OR($G105="",$G105="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M105:$U105)+($M105:$U105="DNA")),$M105:$U105),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M105:$U105)+($M105:$U105="DNA")),$M105:$U105),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M105:$U105)+($M105:$U105="DNA")),$M105:$U105),"")&lt;TODAY())),1,0)+COUNTIF($V105:$Z105,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J105" s="32">
@@ -5892,7 +5903,7 @@
         <v/>
       </c>
       <c r="K105" s="32">
-        <f>IF(NOT(AND($A105&lt;&gt;"",OR($G105="",$G105="Active"))),"",IF($L105&lt;&gt;"",IF($L105=$M105,"Booking",INDEX($N$4:$U$4,MATCH($L105,$N105:$U105,0))),IF(COUNTIF($N105:$U105,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N105:$U105)=0,"All done",IF(MAX($M105:$U105)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A105&lt;&gt;"",OR($G105="",$G105="Active"))),"",IF($L105&lt;&gt;"",IF($L105=$M105,"Booking",INDEX($N$4:$U$4,MATCH($L105,$N105:$U105,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M105:$U105)+($M105:$U105="DNA")),$M105:$U105),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M105:$U105)+($M105:$U105="DNA")),$M105:$U105),"")),IF(ISNUMBER($U105),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L105" s="33">
@@ -5930,7 +5941,7 @@
         <v/>
       </c>
       <c r="I106" s="32">
-        <f>IF(NOT(AND($A106&lt;&gt;"",OR($G106="",$G106="Active"))),"",IF(AND(MAX($M106:$U106)&gt;0,MAX($M106:$U106)&lt;TODAY(),COUNTBLANK($N106:$U106)&gt;0,COUNTIF($N106:$U106,"DNA")=0),1,0)+COUNTIF($N106:$U106,"DNA")+COUNTIF($V106:$Z106,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A106&lt;&gt;"",OR($G106="",$G106="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M106:$U106)+($M106:$U106="DNA")),$M106:$U106),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M106:$U106)+($M106:$U106="DNA")),$M106:$U106),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M106:$U106)+($M106:$U106="DNA")),$M106:$U106),"")&lt;TODAY())),1,0)+COUNTIF($V106:$Z106,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J106" s="32">
@@ -5938,7 +5949,7 @@
         <v/>
       </c>
       <c r="K106" s="32">
-        <f>IF(NOT(AND($A106&lt;&gt;"",OR($G106="",$G106="Active"))),"",IF($L106&lt;&gt;"",IF($L106=$M106,"Booking",INDEX($N$4:$U$4,MATCH($L106,$N106:$U106,0))),IF(COUNTIF($N106:$U106,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N106:$U106)=0,"All done",IF(MAX($M106:$U106)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A106&lt;&gt;"",OR($G106="",$G106="Active"))),"",IF($L106&lt;&gt;"",IF($L106=$M106,"Booking",INDEX($N$4:$U$4,MATCH($L106,$N106:$U106,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M106:$U106)+($M106:$U106="DNA")),$M106:$U106),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M106:$U106)+($M106:$U106="DNA")),$M106:$U106),"")),IF(ISNUMBER($U106),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L106" s="33">
@@ -5976,7 +5987,7 @@
         <v/>
       </c>
       <c r="I107" s="32">
-        <f>IF(NOT(AND($A107&lt;&gt;"",OR($G107="",$G107="Active"))),"",IF(AND(MAX($M107:$U107)&gt;0,MAX($M107:$U107)&lt;TODAY(),COUNTBLANK($N107:$U107)&gt;0,COUNTIF($N107:$U107,"DNA")=0),1,0)+COUNTIF($N107:$U107,"DNA")+COUNTIF($V107:$Z107,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A107&lt;&gt;"",OR($G107="",$G107="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M107:$U107)+($M107:$U107="DNA")),$M107:$U107),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M107:$U107)+($M107:$U107="DNA")),$M107:$U107),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M107:$U107)+($M107:$U107="DNA")),$M107:$U107),"")&lt;TODAY())),1,0)+COUNTIF($V107:$Z107,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J107" s="32">
@@ -5984,7 +5995,7 @@
         <v/>
       </c>
       <c r="K107" s="32">
-        <f>IF(NOT(AND($A107&lt;&gt;"",OR($G107="",$G107="Active"))),"",IF($L107&lt;&gt;"",IF($L107=$M107,"Booking",INDEX($N$4:$U$4,MATCH($L107,$N107:$U107,0))),IF(COUNTIF($N107:$U107,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N107:$U107)=0,"All done",IF(MAX($M107:$U107)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A107&lt;&gt;"",OR($G107="",$G107="Active"))),"",IF($L107&lt;&gt;"",IF($L107=$M107,"Booking",INDEX($N$4:$U$4,MATCH($L107,$N107:$U107,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M107:$U107)+($M107:$U107="DNA")),$M107:$U107),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M107:$U107)+($M107:$U107="DNA")),$M107:$U107),"")),IF(ISNUMBER($U107),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L107" s="33">
@@ -6022,7 +6033,7 @@
         <v/>
       </c>
       <c r="I108" s="32">
-        <f>IF(NOT(AND($A108&lt;&gt;"",OR($G108="",$G108="Active"))),"",IF(AND(MAX($M108:$U108)&gt;0,MAX($M108:$U108)&lt;TODAY(),COUNTBLANK($N108:$U108)&gt;0,COUNTIF($N108:$U108,"DNA")=0),1,0)+COUNTIF($N108:$U108,"DNA")+COUNTIF($V108:$Z108,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A108&lt;&gt;"",OR($G108="",$G108="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M108:$U108)+($M108:$U108="DNA")),$M108:$U108),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M108:$U108)+($M108:$U108="DNA")),$M108:$U108),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M108:$U108)+($M108:$U108="DNA")),$M108:$U108),"")&lt;TODAY())),1,0)+COUNTIF($V108:$Z108,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J108" s="32">
@@ -6030,7 +6041,7 @@
         <v/>
       </c>
       <c r="K108" s="32">
-        <f>IF(NOT(AND($A108&lt;&gt;"",OR($G108="",$G108="Active"))),"",IF($L108&lt;&gt;"",IF($L108=$M108,"Booking",INDEX($N$4:$U$4,MATCH($L108,$N108:$U108,0))),IF(COUNTIF($N108:$U108,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N108:$U108)=0,"All done",IF(MAX($M108:$U108)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A108&lt;&gt;"",OR($G108="",$G108="Active"))),"",IF($L108&lt;&gt;"",IF($L108=$M108,"Booking",INDEX($N$4:$U$4,MATCH($L108,$N108:$U108,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M108:$U108)+($M108:$U108="DNA")),$M108:$U108),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M108:$U108)+($M108:$U108="DNA")),$M108:$U108),"")),IF(ISNUMBER($U108),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L108" s="33">
@@ -6068,7 +6079,7 @@
         <v/>
       </c>
       <c r="I109" s="32">
-        <f>IF(NOT(AND($A109&lt;&gt;"",OR($G109="",$G109="Active"))),"",IF(AND(MAX($M109:$U109)&gt;0,MAX($M109:$U109)&lt;TODAY(),COUNTBLANK($N109:$U109)&gt;0,COUNTIF($N109:$U109,"DNA")=0),1,0)+COUNTIF($N109:$U109,"DNA")+COUNTIF($V109:$Z109,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A109&lt;&gt;"",OR($G109="",$G109="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M109:$U109)+($M109:$U109="DNA")),$M109:$U109),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M109:$U109)+($M109:$U109="DNA")),$M109:$U109),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M109:$U109)+($M109:$U109="DNA")),$M109:$U109),"")&lt;TODAY())),1,0)+COUNTIF($V109:$Z109,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J109" s="32">
@@ -6076,7 +6087,7 @@
         <v/>
       </c>
       <c r="K109" s="32">
-        <f>IF(NOT(AND($A109&lt;&gt;"",OR($G109="",$G109="Active"))),"",IF($L109&lt;&gt;"",IF($L109=$M109,"Booking",INDEX($N$4:$U$4,MATCH($L109,$N109:$U109,0))),IF(COUNTIF($N109:$U109,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N109:$U109)=0,"All done",IF(MAX($M109:$U109)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A109&lt;&gt;"",OR($G109="",$G109="Active"))),"",IF($L109&lt;&gt;"",IF($L109=$M109,"Booking",INDEX($N$4:$U$4,MATCH($L109,$N109:$U109,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M109:$U109)+($M109:$U109="DNA")),$M109:$U109),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M109:$U109)+($M109:$U109="DNA")),$M109:$U109),"")),IF(ISNUMBER($U109),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L109" s="33">
@@ -6114,7 +6125,7 @@
         <v/>
       </c>
       <c r="I110" s="32">
-        <f>IF(NOT(AND($A110&lt;&gt;"",OR($G110="",$G110="Active"))),"",IF(AND(MAX($M110:$U110)&gt;0,MAX($M110:$U110)&lt;TODAY(),COUNTBLANK($N110:$U110)&gt;0,COUNTIF($N110:$U110,"DNA")=0),1,0)+COUNTIF($N110:$U110,"DNA")+COUNTIF($V110:$Z110,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A110&lt;&gt;"",OR($G110="",$G110="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M110:$U110)+($M110:$U110="DNA")),$M110:$U110),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M110:$U110)+($M110:$U110="DNA")),$M110:$U110),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M110:$U110)+($M110:$U110="DNA")),$M110:$U110),"")&lt;TODAY())),1,0)+COUNTIF($V110:$Z110,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J110" s="32">
@@ -6122,7 +6133,7 @@
         <v/>
       </c>
       <c r="K110" s="32">
-        <f>IF(NOT(AND($A110&lt;&gt;"",OR($G110="",$G110="Active"))),"",IF($L110&lt;&gt;"",IF($L110=$M110,"Booking",INDEX($N$4:$U$4,MATCH($L110,$N110:$U110,0))),IF(COUNTIF($N110:$U110,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N110:$U110)=0,"All done",IF(MAX($M110:$U110)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A110&lt;&gt;"",OR($G110="",$G110="Active"))),"",IF($L110&lt;&gt;"",IF($L110=$M110,"Booking",INDEX($N$4:$U$4,MATCH($L110,$N110:$U110,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M110:$U110)+($M110:$U110="DNA")),$M110:$U110),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M110:$U110)+($M110:$U110="DNA")),$M110:$U110),"")),IF(ISNUMBER($U110),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L110" s="33">
@@ -6160,7 +6171,7 @@
         <v/>
       </c>
       <c r="I111" s="32">
-        <f>IF(NOT(AND($A111&lt;&gt;"",OR($G111="",$G111="Active"))),"",IF(AND(MAX($M111:$U111)&gt;0,MAX($M111:$U111)&lt;TODAY(),COUNTBLANK($N111:$U111)&gt;0,COUNTIF($N111:$U111,"DNA")=0),1,0)+COUNTIF($N111:$U111,"DNA")+COUNTIF($V111:$Z111,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A111&lt;&gt;"",OR($G111="",$G111="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M111:$U111)+($M111:$U111="DNA")),$M111:$U111),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M111:$U111)+($M111:$U111="DNA")),$M111:$U111),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M111:$U111)+($M111:$U111="DNA")),$M111:$U111),"")&lt;TODAY())),1,0)+COUNTIF($V111:$Z111,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J111" s="32">
@@ -6168,7 +6179,7 @@
         <v/>
       </c>
       <c r="K111" s="32">
-        <f>IF(NOT(AND($A111&lt;&gt;"",OR($G111="",$G111="Active"))),"",IF($L111&lt;&gt;"",IF($L111=$M111,"Booking",INDEX($N$4:$U$4,MATCH($L111,$N111:$U111,0))),IF(COUNTIF($N111:$U111,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N111:$U111)=0,"All done",IF(MAX($M111:$U111)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A111&lt;&gt;"",OR($G111="",$G111="Active"))),"",IF($L111&lt;&gt;"",IF($L111=$M111,"Booking",INDEX($N$4:$U$4,MATCH($L111,$N111:$U111,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M111:$U111)+($M111:$U111="DNA")),$M111:$U111),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M111:$U111)+($M111:$U111="DNA")),$M111:$U111),"")),IF(ISNUMBER($U111),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L111" s="33">
@@ -6206,7 +6217,7 @@
         <v/>
       </c>
       <c r="I112" s="32">
-        <f>IF(NOT(AND($A112&lt;&gt;"",OR($G112="",$G112="Active"))),"",IF(AND(MAX($M112:$U112)&gt;0,MAX($M112:$U112)&lt;TODAY(),COUNTBLANK($N112:$U112)&gt;0,COUNTIF($N112:$U112,"DNA")=0),1,0)+COUNTIF($N112:$U112,"DNA")+COUNTIF($V112:$Z112,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A112&lt;&gt;"",OR($G112="",$G112="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M112:$U112)+($M112:$U112="DNA")),$M112:$U112),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M112:$U112)+($M112:$U112="DNA")),$M112:$U112),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M112:$U112)+($M112:$U112="DNA")),$M112:$U112),"")&lt;TODAY())),1,0)+COUNTIF($V112:$Z112,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J112" s="32">
@@ -6214,7 +6225,7 @@
         <v/>
       </c>
       <c r="K112" s="32">
-        <f>IF(NOT(AND($A112&lt;&gt;"",OR($G112="",$G112="Active"))),"",IF($L112&lt;&gt;"",IF($L112=$M112,"Booking",INDEX($N$4:$U$4,MATCH($L112,$N112:$U112,0))),IF(COUNTIF($N112:$U112,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N112:$U112)=0,"All done",IF(MAX($M112:$U112)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A112&lt;&gt;"",OR($G112="",$G112="Active"))),"",IF($L112&lt;&gt;"",IF($L112=$M112,"Booking",INDEX($N$4:$U$4,MATCH($L112,$N112:$U112,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M112:$U112)+($M112:$U112="DNA")),$M112:$U112),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M112:$U112)+($M112:$U112="DNA")),$M112:$U112),"")),IF(ISNUMBER($U112),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L112" s="33">
@@ -6252,7 +6263,7 @@
         <v/>
       </c>
       <c r="I113" s="32">
-        <f>IF(NOT(AND($A113&lt;&gt;"",OR($G113="",$G113="Active"))),"",IF(AND(MAX($M113:$U113)&gt;0,MAX($M113:$U113)&lt;TODAY(),COUNTBLANK($N113:$U113)&gt;0,COUNTIF($N113:$U113,"DNA")=0),1,0)+COUNTIF($N113:$U113,"DNA")+COUNTIF($V113:$Z113,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A113&lt;&gt;"",OR($G113="",$G113="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M113:$U113)+($M113:$U113="DNA")),$M113:$U113),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M113:$U113)+($M113:$U113="DNA")),$M113:$U113),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M113:$U113)+($M113:$U113="DNA")),$M113:$U113),"")&lt;TODAY())),1,0)+COUNTIF($V113:$Z113,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J113" s="32">
@@ -6260,7 +6271,7 @@
         <v/>
       </c>
       <c r="K113" s="32">
-        <f>IF(NOT(AND($A113&lt;&gt;"",OR($G113="",$G113="Active"))),"",IF($L113&lt;&gt;"",IF($L113=$M113,"Booking",INDEX($N$4:$U$4,MATCH($L113,$N113:$U113,0))),IF(COUNTIF($N113:$U113,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N113:$U113)=0,"All done",IF(MAX($M113:$U113)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A113&lt;&gt;"",OR($G113="",$G113="Active"))),"",IF($L113&lt;&gt;"",IF($L113=$M113,"Booking",INDEX($N$4:$U$4,MATCH($L113,$N113:$U113,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M113:$U113)+($M113:$U113="DNA")),$M113:$U113),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M113:$U113)+($M113:$U113="DNA")),$M113:$U113),"")),IF(ISNUMBER($U113),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L113" s="33">
@@ -6298,7 +6309,7 @@
         <v/>
       </c>
       <c r="I114" s="32">
-        <f>IF(NOT(AND($A114&lt;&gt;"",OR($G114="",$G114="Active"))),"",IF(AND(MAX($M114:$U114)&gt;0,MAX($M114:$U114)&lt;TODAY(),COUNTBLANK($N114:$U114)&gt;0,COUNTIF($N114:$U114,"DNA")=0),1,0)+COUNTIF($N114:$U114,"DNA")+COUNTIF($V114:$Z114,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A114&lt;&gt;"",OR($G114="",$G114="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M114:$U114)+($M114:$U114="DNA")),$M114:$U114),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M114:$U114)+($M114:$U114="DNA")),$M114:$U114),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M114:$U114)+($M114:$U114="DNA")),$M114:$U114),"")&lt;TODAY())),1,0)+COUNTIF($V114:$Z114,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J114" s="32">
@@ -6306,7 +6317,7 @@
         <v/>
       </c>
       <c r="K114" s="32">
-        <f>IF(NOT(AND($A114&lt;&gt;"",OR($G114="",$G114="Active"))),"",IF($L114&lt;&gt;"",IF($L114=$M114,"Booking",INDEX($N$4:$U$4,MATCH($L114,$N114:$U114,0))),IF(COUNTIF($N114:$U114,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N114:$U114)=0,"All done",IF(MAX($M114:$U114)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A114&lt;&gt;"",OR($G114="",$G114="Active"))),"",IF($L114&lt;&gt;"",IF($L114=$M114,"Booking",INDEX($N$4:$U$4,MATCH($L114,$N114:$U114,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M114:$U114)+($M114:$U114="DNA")),$M114:$U114),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M114:$U114)+($M114:$U114="DNA")),$M114:$U114),"")),IF(ISNUMBER($U114),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L114" s="33">
@@ -6344,7 +6355,7 @@
         <v/>
       </c>
       <c r="I115" s="32">
-        <f>IF(NOT(AND($A115&lt;&gt;"",OR($G115="",$G115="Active"))),"",IF(AND(MAX($M115:$U115)&gt;0,MAX($M115:$U115)&lt;TODAY(),COUNTBLANK($N115:$U115)&gt;0,COUNTIF($N115:$U115,"DNA")=0),1,0)+COUNTIF($N115:$U115,"DNA")+COUNTIF($V115:$Z115,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A115&lt;&gt;"",OR($G115="",$G115="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M115:$U115)+($M115:$U115="DNA")),$M115:$U115),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M115:$U115)+($M115:$U115="DNA")),$M115:$U115),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M115:$U115)+($M115:$U115="DNA")),$M115:$U115),"")&lt;TODAY())),1,0)+COUNTIF($V115:$Z115,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J115" s="32">
@@ -6352,7 +6363,7 @@
         <v/>
       </c>
       <c r="K115" s="32">
-        <f>IF(NOT(AND($A115&lt;&gt;"",OR($G115="",$G115="Active"))),"",IF($L115&lt;&gt;"",IF($L115=$M115,"Booking",INDEX($N$4:$U$4,MATCH($L115,$N115:$U115,0))),IF(COUNTIF($N115:$U115,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N115:$U115)=0,"All done",IF(MAX($M115:$U115)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A115&lt;&gt;"",OR($G115="",$G115="Active"))),"",IF($L115&lt;&gt;"",IF($L115=$M115,"Booking",INDEX($N$4:$U$4,MATCH($L115,$N115:$U115,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M115:$U115)+($M115:$U115="DNA")),$M115:$U115),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M115:$U115)+($M115:$U115="DNA")),$M115:$U115),"")),IF(ISNUMBER($U115),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L115" s="33">
@@ -6390,7 +6401,7 @@
         <v/>
       </c>
       <c r="I116" s="32">
-        <f>IF(NOT(AND($A116&lt;&gt;"",OR($G116="",$G116="Active"))),"",IF(AND(MAX($M116:$U116)&gt;0,MAX($M116:$U116)&lt;TODAY(),COUNTBLANK($N116:$U116)&gt;0,COUNTIF($N116:$U116,"DNA")=0),1,0)+COUNTIF($N116:$U116,"DNA")+COUNTIF($V116:$Z116,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A116&lt;&gt;"",OR($G116="",$G116="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M116:$U116)+($M116:$U116="DNA")),$M116:$U116),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M116:$U116)+($M116:$U116="DNA")),$M116:$U116),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M116:$U116)+($M116:$U116="DNA")),$M116:$U116),"")&lt;TODAY())),1,0)+COUNTIF($V116:$Z116,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J116" s="32">
@@ -6398,7 +6409,7 @@
         <v/>
       </c>
       <c r="K116" s="32">
-        <f>IF(NOT(AND($A116&lt;&gt;"",OR($G116="",$G116="Active"))),"",IF($L116&lt;&gt;"",IF($L116=$M116,"Booking",INDEX($N$4:$U$4,MATCH($L116,$N116:$U116,0))),IF(COUNTIF($N116:$U116,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N116:$U116)=0,"All done",IF(MAX($M116:$U116)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A116&lt;&gt;"",OR($G116="",$G116="Active"))),"",IF($L116&lt;&gt;"",IF($L116=$M116,"Booking",INDEX($N$4:$U$4,MATCH($L116,$N116:$U116,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M116:$U116)+($M116:$U116="DNA")),$M116:$U116),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M116:$U116)+($M116:$U116="DNA")),$M116:$U116),"")),IF(ISNUMBER($U116),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L116" s="33">
@@ -6436,7 +6447,7 @@
         <v/>
       </c>
       <c r="I117" s="32">
-        <f>IF(NOT(AND($A117&lt;&gt;"",OR($G117="",$G117="Active"))),"",IF(AND(MAX($M117:$U117)&gt;0,MAX($M117:$U117)&lt;TODAY(),COUNTBLANK($N117:$U117)&gt;0,COUNTIF($N117:$U117,"DNA")=0),1,0)+COUNTIF($N117:$U117,"DNA")+COUNTIF($V117:$Z117,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A117&lt;&gt;"",OR($G117="",$G117="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M117:$U117)+($M117:$U117="DNA")),$M117:$U117),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M117:$U117)+($M117:$U117="DNA")),$M117:$U117),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M117:$U117)+($M117:$U117="DNA")),$M117:$U117),"")&lt;TODAY())),1,0)+COUNTIF($V117:$Z117,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J117" s="32">
@@ -6444,7 +6455,7 @@
         <v/>
       </c>
       <c r="K117" s="32">
-        <f>IF(NOT(AND($A117&lt;&gt;"",OR($G117="",$G117="Active"))),"",IF($L117&lt;&gt;"",IF($L117=$M117,"Booking",INDEX($N$4:$U$4,MATCH($L117,$N117:$U117,0))),IF(COUNTIF($N117:$U117,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N117:$U117)=0,"All done",IF(MAX($M117:$U117)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A117&lt;&gt;"",OR($G117="",$G117="Active"))),"",IF($L117&lt;&gt;"",IF($L117=$M117,"Booking",INDEX($N$4:$U$4,MATCH($L117,$N117:$U117,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M117:$U117)+($M117:$U117="DNA")),$M117:$U117),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M117:$U117)+($M117:$U117="DNA")),$M117:$U117),"")),IF(ISNUMBER($U117),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L117" s="33">
@@ -6482,7 +6493,7 @@
         <v/>
       </c>
       <c r="I118" s="32">
-        <f>IF(NOT(AND($A118&lt;&gt;"",OR($G118="",$G118="Active"))),"",IF(AND(MAX($M118:$U118)&gt;0,MAX($M118:$U118)&lt;TODAY(),COUNTBLANK($N118:$U118)&gt;0,COUNTIF($N118:$U118,"DNA")=0),1,0)+COUNTIF($N118:$U118,"DNA")+COUNTIF($V118:$Z118,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A118&lt;&gt;"",OR($G118="",$G118="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M118:$U118)+($M118:$U118="DNA")),$M118:$U118),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M118:$U118)+($M118:$U118="DNA")),$M118:$U118),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M118:$U118)+($M118:$U118="DNA")),$M118:$U118),"")&lt;TODAY())),1,0)+COUNTIF($V118:$Z118,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J118" s="32">
@@ -6490,7 +6501,7 @@
         <v/>
       </c>
       <c r="K118" s="32">
-        <f>IF(NOT(AND($A118&lt;&gt;"",OR($G118="",$G118="Active"))),"",IF($L118&lt;&gt;"",IF($L118=$M118,"Booking",INDEX($N$4:$U$4,MATCH($L118,$N118:$U118,0))),IF(COUNTIF($N118:$U118,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N118:$U118)=0,"All done",IF(MAX($M118:$U118)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A118&lt;&gt;"",OR($G118="",$G118="Active"))),"",IF($L118&lt;&gt;"",IF($L118=$M118,"Booking",INDEX($N$4:$U$4,MATCH($L118,$N118:$U118,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M118:$U118)+($M118:$U118="DNA")),$M118:$U118),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M118:$U118)+($M118:$U118="DNA")),$M118:$U118),"")),IF(ISNUMBER($U118),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L118" s="33">
@@ -6528,7 +6539,7 @@
         <v/>
       </c>
       <c r="I119" s="32">
-        <f>IF(NOT(AND($A119&lt;&gt;"",OR($G119="",$G119="Active"))),"",IF(AND(MAX($M119:$U119)&gt;0,MAX($M119:$U119)&lt;TODAY(),COUNTBLANK($N119:$U119)&gt;0,COUNTIF($N119:$U119,"DNA")=0),1,0)+COUNTIF($N119:$U119,"DNA")+COUNTIF($V119:$Z119,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A119&lt;&gt;"",OR($G119="",$G119="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M119:$U119)+($M119:$U119="DNA")),$M119:$U119),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M119:$U119)+($M119:$U119="DNA")),$M119:$U119),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M119:$U119)+($M119:$U119="DNA")),$M119:$U119),"")&lt;TODAY())),1,0)+COUNTIF($V119:$Z119,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J119" s="32">
@@ -6536,7 +6547,7 @@
         <v/>
       </c>
       <c r="K119" s="32">
-        <f>IF(NOT(AND($A119&lt;&gt;"",OR($G119="",$G119="Active"))),"",IF($L119&lt;&gt;"",IF($L119=$M119,"Booking",INDEX($N$4:$U$4,MATCH($L119,$N119:$U119,0))),IF(COUNTIF($N119:$U119,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N119:$U119)=0,"All done",IF(MAX($M119:$U119)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A119&lt;&gt;"",OR($G119="",$G119="Active"))),"",IF($L119&lt;&gt;"",IF($L119=$M119,"Booking",INDEX($N$4:$U$4,MATCH($L119,$N119:$U119,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M119:$U119)+($M119:$U119="DNA")),$M119:$U119),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M119:$U119)+($M119:$U119="DNA")),$M119:$U119),"")),IF(ISNUMBER($U119),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L119" s="33">
@@ -6574,7 +6585,7 @@
         <v/>
       </c>
       <c r="I120" s="32">
-        <f>IF(NOT(AND($A120&lt;&gt;"",OR($G120="",$G120="Active"))),"",IF(AND(MAX($M120:$U120)&gt;0,MAX($M120:$U120)&lt;TODAY(),COUNTBLANK($N120:$U120)&gt;0,COUNTIF($N120:$U120,"DNA")=0),1,0)+COUNTIF($N120:$U120,"DNA")+COUNTIF($V120:$Z120,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A120&lt;&gt;"",OR($G120="",$G120="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M120:$U120)+($M120:$U120="DNA")),$M120:$U120),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M120:$U120)+($M120:$U120="DNA")),$M120:$U120),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M120:$U120)+($M120:$U120="DNA")),$M120:$U120),"")&lt;TODAY())),1,0)+COUNTIF($V120:$Z120,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J120" s="32">
@@ -6582,7 +6593,7 @@
         <v/>
       </c>
       <c r="K120" s="32">
-        <f>IF(NOT(AND($A120&lt;&gt;"",OR($G120="",$G120="Active"))),"",IF($L120&lt;&gt;"",IF($L120=$M120,"Booking",INDEX($N$4:$U$4,MATCH($L120,$N120:$U120,0))),IF(COUNTIF($N120:$U120,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N120:$U120)=0,"All done",IF(MAX($M120:$U120)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A120&lt;&gt;"",OR($G120="",$G120="Active"))),"",IF($L120&lt;&gt;"",IF($L120=$M120,"Booking",INDEX($N$4:$U$4,MATCH($L120,$N120:$U120,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M120:$U120)+($M120:$U120="DNA")),$M120:$U120),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M120:$U120)+($M120:$U120="DNA")),$M120:$U120),"")),IF(ISNUMBER($U120),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L120" s="33">
@@ -6620,7 +6631,7 @@
         <v/>
       </c>
       <c r="I121" s="32">
-        <f>IF(NOT(AND($A121&lt;&gt;"",OR($G121="",$G121="Active"))),"",IF(AND(MAX($M121:$U121)&gt;0,MAX($M121:$U121)&lt;TODAY(),COUNTBLANK($N121:$U121)&gt;0,COUNTIF($N121:$U121,"DNA")=0),1,0)+COUNTIF($N121:$U121,"DNA")+COUNTIF($V121:$Z121,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A121&lt;&gt;"",OR($G121="",$G121="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M121:$U121)+($M121:$U121="DNA")),$M121:$U121),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M121:$U121)+($M121:$U121="DNA")),$M121:$U121),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M121:$U121)+($M121:$U121="DNA")),$M121:$U121),"")&lt;TODAY())),1,0)+COUNTIF($V121:$Z121,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J121" s="32">
@@ -6628,7 +6639,7 @@
         <v/>
       </c>
       <c r="K121" s="32">
-        <f>IF(NOT(AND($A121&lt;&gt;"",OR($G121="",$G121="Active"))),"",IF($L121&lt;&gt;"",IF($L121=$M121,"Booking",INDEX($N$4:$U$4,MATCH($L121,$N121:$U121,0))),IF(COUNTIF($N121:$U121,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N121:$U121)=0,"All done",IF(MAX($M121:$U121)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A121&lt;&gt;"",OR($G121="",$G121="Active"))),"",IF($L121&lt;&gt;"",IF($L121=$M121,"Booking",INDEX($N$4:$U$4,MATCH($L121,$N121:$U121,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M121:$U121)+($M121:$U121="DNA")),$M121:$U121),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M121:$U121)+($M121:$U121="DNA")),$M121:$U121),"")),IF(ISNUMBER($U121),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L121" s="33">
@@ -6666,7 +6677,7 @@
         <v/>
       </c>
       <c r="I122" s="32">
-        <f>IF(NOT(AND($A122&lt;&gt;"",OR($G122="",$G122="Active"))),"",IF(AND(MAX($M122:$U122)&gt;0,MAX($M122:$U122)&lt;TODAY(),COUNTBLANK($N122:$U122)&gt;0,COUNTIF($N122:$U122,"DNA")=0),1,0)+COUNTIF($N122:$U122,"DNA")+COUNTIF($V122:$Z122,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A122&lt;&gt;"",OR($G122="",$G122="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M122:$U122)+($M122:$U122="DNA")),$M122:$U122),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M122:$U122)+($M122:$U122="DNA")),$M122:$U122),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M122:$U122)+($M122:$U122="DNA")),$M122:$U122),"")&lt;TODAY())),1,0)+COUNTIF($V122:$Z122,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J122" s="32">
@@ -6674,7 +6685,7 @@
         <v/>
       </c>
       <c r="K122" s="32">
-        <f>IF(NOT(AND($A122&lt;&gt;"",OR($G122="",$G122="Active"))),"",IF($L122&lt;&gt;"",IF($L122=$M122,"Booking",INDEX($N$4:$U$4,MATCH($L122,$N122:$U122,0))),IF(COUNTIF($N122:$U122,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N122:$U122)=0,"All done",IF(MAX($M122:$U122)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A122&lt;&gt;"",OR($G122="",$G122="Active"))),"",IF($L122&lt;&gt;"",IF($L122=$M122,"Booking",INDEX($N$4:$U$4,MATCH($L122,$N122:$U122,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M122:$U122)+($M122:$U122="DNA")),$M122:$U122),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M122:$U122)+($M122:$U122="DNA")),$M122:$U122),"")),IF(ISNUMBER($U122),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L122" s="33">
@@ -6712,7 +6723,7 @@
         <v/>
       </c>
       <c r="I123" s="32">
-        <f>IF(NOT(AND($A123&lt;&gt;"",OR($G123="",$G123="Active"))),"",IF(AND(MAX($M123:$U123)&gt;0,MAX($M123:$U123)&lt;TODAY(),COUNTBLANK($N123:$U123)&gt;0,COUNTIF($N123:$U123,"DNA")=0),1,0)+COUNTIF($N123:$U123,"DNA")+COUNTIF($V123:$Z123,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A123&lt;&gt;"",OR($G123="",$G123="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M123:$U123)+($M123:$U123="DNA")),$M123:$U123),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M123:$U123)+($M123:$U123="DNA")),$M123:$U123),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M123:$U123)+($M123:$U123="DNA")),$M123:$U123),"")&lt;TODAY())),1,0)+COUNTIF($V123:$Z123,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J123" s="32">
@@ -6720,7 +6731,7 @@
         <v/>
       </c>
       <c r="K123" s="32">
-        <f>IF(NOT(AND($A123&lt;&gt;"",OR($G123="",$G123="Active"))),"",IF($L123&lt;&gt;"",IF($L123=$M123,"Booking",INDEX($N$4:$U$4,MATCH($L123,$N123:$U123,0))),IF(COUNTIF($N123:$U123,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N123:$U123)=0,"All done",IF(MAX($M123:$U123)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A123&lt;&gt;"",OR($G123="",$G123="Active"))),"",IF($L123&lt;&gt;"",IF($L123=$M123,"Booking",INDEX($N$4:$U$4,MATCH($L123,$N123:$U123,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M123:$U123)+($M123:$U123="DNA")),$M123:$U123),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M123:$U123)+($M123:$U123="DNA")),$M123:$U123),"")),IF(ISNUMBER($U123),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L123" s="33">
@@ -6758,7 +6769,7 @@
         <v/>
       </c>
       <c r="I124" s="32">
-        <f>IF(NOT(AND($A124&lt;&gt;"",OR($G124="",$G124="Active"))),"",IF(AND(MAX($M124:$U124)&gt;0,MAX($M124:$U124)&lt;TODAY(),COUNTBLANK($N124:$U124)&gt;0,COUNTIF($N124:$U124,"DNA")=0),1,0)+COUNTIF($N124:$U124,"DNA")+COUNTIF($V124:$Z124,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A124&lt;&gt;"",OR($G124="",$G124="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M124:$U124)+($M124:$U124="DNA")),$M124:$U124),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M124:$U124)+($M124:$U124="DNA")),$M124:$U124),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M124:$U124)+($M124:$U124="DNA")),$M124:$U124),"")&lt;TODAY())),1,0)+COUNTIF($V124:$Z124,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J124" s="32">
@@ -6766,7 +6777,7 @@
         <v/>
       </c>
       <c r="K124" s="32">
-        <f>IF(NOT(AND($A124&lt;&gt;"",OR($G124="",$G124="Active"))),"",IF($L124&lt;&gt;"",IF($L124=$M124,"Booking",INDEX($N$4:$U$4,MATCH($L124,$N124:$U124,0))),IF(COUNTIF($N124:$U124,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N124:$U124)=0,"All done",IF(MAX($M124:$U124)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A124&lt;&gt;"",OR($G124="",$G124="Active"))),"",IF($L124&lt;&gt;"",IF($L124=$M124,"Booking",INDEX($N$4:$U$4,MATCH($L124,$N124:$U124,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M124:$U124)+($M124:$U124="DNA")),$M124:$U124),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M124:$U124)+($M124:$U124="DNA")),$M124:$U124),"")),IF(ISNUMBER($U124),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L124" s="33">
@@ -6804,7 +6815,7 @@
         <v/>
       </c>
       <c r="I125" s="32">
-        <f>IF(NOT(AND($A125&lt;&gt;"",OR($G125="",$G125="Active"))),"",IF(AND(MAX($M125:$U125)&gt;0,MAX($M125:$U125)&lt;TODAY(),COUNTBLANK($N125:$U125)&gt;0,COUNTIF($N125:$U125,"DNA")=0),1,0)+COUNTIF($N125:$U125,"DNA")+COUNTIF($V125:$Z125,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A125&lt;&gt;"",OR($G125="",$G125="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M125:$U125)+($M125:$U125="DNA")),$M125:$U125),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M125:$U125)+($M125:$U125="DNA")),$M125:$U125),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M125:$U125)+($M125:$U125="DNA")),$M125:$U125),"")&lt;TODAY())),1,0)+COUNTIF($V125:$Z125,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J125" s="32">
@@ -6812,7 +6823,7 @@
         <v/>
       </c>
       <c r="K125" s="32">
-        <f>IF(NOT(AND($A125&lt;&gt;"",OR($G125="",$G125="Active"))),"",IF($L125&lt;&gt;"",IF($L125=$M125,"Booking",INDEX($N$4:$U$4,MATCH($L125,$N125:$U125,0))),IF(COUNTIF($N125:$U125,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N125:$U125)=0,"All done",IF(MAX($M125:$U125)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A125&lt;&gt;"",OR($G125="",$G125="Active"))),"",IF($L125&lt;&gt;"",IF($L125=$M125,"Booking",INDEX($N$4:$U$4,MATCH($L125,$N125:$U125,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M125:$U125)+($M125:$U125="DNA")),$M125:$U125),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M125:$U125)+($M125:$U125="DNA")),$M125:$U125),"")),IF(ISNUMBER($U125),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L125" s="33">
@@ -6850,7 +6861,7 @@
         <v/>
       </c>
       <c r="I126" s="32">
-        <f>IF(NOT(AND($A126&lt;&gt;"",OR($G126="",$G126="Active"))),"",IF(AND(MAX($M126:$U126)&gt;0,MAX($M126:$U126)&lt;TODAY(),COUNTBLANK($N126:$U126)&gt;0,COUNTIF($N126:$U126,"DNA")=0),1,0)+COUNTIF($N126:$U126,"DNA")+COUNTIF($V126:$Z126,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A126&lt;&gt;"",OR($G126="",$G126="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M126:$U126)+($M126:$U126="DNA")),$M126:$U126),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M126:$U126)+($M126:$U126="DNA")),$M126:$U126),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M126:$U126)+($M126:$U126="DNA")),$M126:$U126),"")&lt;TODAY())),1,0)+COUNTIF($V126:$Z126,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J126" s="32">
@@ -6858,7 +6869,7 @@
         <v/>
       </c>
       <c r="K126" s="32">
-        <f>IF(NOT(AND($A126&lt;&gt;"",OR($G126="",$G126="Active"))),"",IF($L126&lt;&gt;"",IF($L126=$M126,"Booking",INDEX($N$4:$U$4,MATCH($L126,$N126:$U126,0))),IF(COUNTIF($N126:$U126,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N126:$U126)=0,"All done",IF(MAX($M126:$U126)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A126&lt;&gt;"",OR($G126="",$G126="Active"))),"",IF($L126&lt;&gt;"",IF($L126=$M126,"Booking",INDEX($N$4:$U$4,MATCH($L126,$N126:$U126,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M126:$U126)+($M126:$U126="DNA")),$M126:$U126),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M126:$U126)+($M126:$U126="DNA")),$M126:$U126),"")),IF(ISNUMBER($U126),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L126" s="33">
@@ -6896,7 +6907,7 @@
         <v/>
       </c>
       <c r="I127" s="32">
-        <f>IF(NOT(AND($A127&lt;&gt;"",OR($G127="",$G127="Active"))),"",IF(AND(MAX($M127:$U127)&gt;0,MAX($M127:$U127)&lt;TODAY(),COUNTBLANK($N127:$U127)&gt;0,COUNTIF($N127:$U127,"DNA")=0),1,0)+COUNTIF($N127:$U127,"DNA")+COUNTIF($V127:$Z127,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A127&lt;&gt;"",OR($G127="",$G127="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M127:$U127)+($M127:$U127="DNA")),$M127:$U127),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M127:$U127)+($M127:$U127="DNA")),$M127:$U127),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M127:$U127)+($M127:$U127="DNA")),$M127:$U127),"")&lt;TODAY())),1,0)+COUNTIF($V127:$Z127,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J127" s="32">
@@ -6904,7 +6915,7 @@
         <v/>
       </c>
       <c r="K127" s="32">
-        <f>IF(NOT(AND($A127&lt;&gt;"",OR($G127="",$G127="Active"))),"",IF($L127&lt;&gt;"",IF($L127=$M127,"Booking",INDEX($N$4:$U$4,MATCH($L127,$N127:$U127,0))),IF(COUNTIF($N127:$U127,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N127:$U127)=0,"All done",IF(MAX($M127:$U127)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A127&lt;&gt;"",OR($G127="",$G127="Active"))),"",IF($L127&lt;&gt;"",IF($L127=$M127,"Booking",INDEX($N$4:$U$4,MATCH($L127,$N127:$U127,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M127:$U127)+($M127:$U127="DNA")),$M127:$U127),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M127:$U127)+($M127:$U127="DNA")),$M127:$U127),"")),IF(ISNUMBER($U127),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L127" s="33">
@@ -6942,7 +6953,7 @@
         <v/>
       </c>
       <c r="I128" s="32">
-        <f>IF(NOT(AND($A128&lt;&gt;"",OR($G128="",$G128="Active"))),"",IF(AND(MAX($M128:$U128)&gt;0,MAX($M128:$U128)&lt;TODAY(),COUNTBLANK($N128:$U128)&gt;0,COUNTIF($N128:$U128,"DNA")=0),1,0)+COUNTIF($N128:$U128,"DNA")+COUNTIF($V128:$Z128,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A128&lt;&gt;"",OR($G128="",$G128="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M128:$U128)+($M128:$U128="DNA")),$M128:$U128),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M128:$U128)+($M128:$U128="DNA")),$M128:$U128),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M128:$U128)+($M128:$U128="DNA")),$M128:$U128),"")&lt;TODAY())),1,0)+COUNTIF($V128:$Z128,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J128" s="32">
@@ -6950,7 +6961,7 @@
         <v/>
       </c>
       <c r="K128" s="32">
-        <f>IF(NOT(AND($A128&lt;&gt;"",OR($G128="",$G128="Active"))),"",IF($L128&lt;&gt;"",IF($L128=$M128,"Booking",INDEX($N$4:$U$4,MATCH($L128,$N128:$U128,0))),IF(COUNTIF($N128:$U128,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N128:$U128)=0,"All done",IF(MAX($M128:$U128)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A128&lt;&gt;"",OR($G128="",$G128="Active"))),"",IF($L128&lt;&gt;"",IF($L128=$M128,"Booking",INDEX($N$4:$U$4,MATCH($L128,$N128:$U128,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M128:$U128)+($M128:$U128="DNA")),$M128:$U128),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M128:$U128)+($M128:$U128="DNA")),$M128:$U128),"")),IF(ISNUMBER($U128),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L128" s="33">
@@ -6988,7 +6999,7 @@
         <v/>
       </c>
       <c r="I129" s="32">
-        <f>IF(NOT(AND($A129&lt;&gt;"",OR($G129="",$G129="Active"))),"",IF(AND(MAX($M129:$U129)&gt;0,MAX($M129:$U129)&lt;TODAY(),COUNTBLANK($N129:$U129)&gt;0,COUNTIF($N129:$U129,"DNA")=0),1,0)+COUNTIF($N129:$U129,"DNA")+COUNTIF($V129:$Z129,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A129&lt;&gt;"",OR($G129="",$G129="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M129:$U129)+($M129:$U129="DNA")),$M129:$U129),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M129:$U129)+($M129:$U129="DNA")),$M129:$U129),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M129:$U129)+($M129:$U129="DNA")),$M129:$U129),"")&lt;TODAY())),1,0)+COUNTIF($V129:$Z129,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J129" s="32">
@@ -6996,7 +7007,7 @@
         <v/>
       </c>
       <c r="K129" s="32">
-        <f>IF(NOT(AND($A129&lt;&gt;"",OR($G129="",$G129="Active"))),"",IF($L129&lt;&gt;"",IF($L129=$M129,"Booking",INDEX($N$4:$U$4,MATCH($L129,$N129:$U129,0))),IF(COUNTIF($N129:$U129,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N129:$U129)=0,"All done",IF(MAX($M129:$U129)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A129&lt;&gt;"",OR($G129="",$G129="Active"))),"",IF($L129&lt;&gt;"",IF($L129=$M129,"Booking",INDEX($N$4:$U$4,MATCH($L129,$N129:$U129,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M129:$U129)+($M129:$U129="DNA")),$M129:$U129),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M129:$U129)+($M129:$U129="DNA")),$M129:$U129),"")),IF(ISNUMBER($U129),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L129" s="33">
@@ -7034,7 +7045,7 @@
         <v/>
       </c>
       <c r="I130" s="32">
-        <f>IF(NOT(AND($A130&lt;&gt;"",OR($G130="",$G130="Active"))),"",IF(AND(MAX($M130:$U130)&gt;0,MAX($M130:$U130)&lt;TODAY(),COUNTBLANK($N130:$U130)&gt;0,COUNTIF($N130:$U130,"DNA")=0),1,0)+COUNTIF($N130:$U130,"DNA")+COUNTIF($V130:$Z130,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A130&lt;&gt;"",OR($G130="",$G130="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M130:$U130)+($M130:$U130="DNA")),$M130:$U130),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M130:$U130)+($M130:$U130="DNA")),$M130:$U130),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M130:$U130)+($M130:$U130="DNA")),$M130:$U130),"")&lt;TODAY())),1,0)+COUNTIF($V130:$Z130,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J130" s="32">
@@ -7042,7 +7053,7 @@
         <v/>
       </c>
       <c r="K130" s="32">
-        <f>IF(NOT(AND($A130&lt;&gt;"",OR($G130="",$G130="Active"))),"",IF($L130&lt;&gt;"",IF($L130=$M130,"Booking",INDEX($N$4:$U$4,MATCH($L130,$N130:$U130,0))),IF(COUNTIF($N130:$U130,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N130:$U130)=0,"All done",IF(MAX($M130:$U130)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A130&lt;&gt;"",OR($G130="",$G130="Active"))),"",IF($L130&lt;&gt;"",IF($L130=$M130,"Booking",INDEX($N$4:$U$4,MATCH($L130,$N130:$U130,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M130:$U130)+($M130:$U130="DNA")),$M130:$U130),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M130:$U130)+($M130:$U130="DNA")),$M130:$U130),"")),IF(ISNUMBER($U130),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L130" s="33">
@@ -7080,7 +7091,7 @@
         <v/>
       </c>
       <c r="I131" s="32">
-        <f>IF(NOT(AND($A131&lt;&gt;"",OR($G131="",$G131="Active"))),"",IF(AND(MAX($M131:$U131)&gt;0,MAX($M131:$U131)&lt;TODAY(),COUNTBLANK($N131:$U131)&gt;0,COUNTIF($N131:$U131,"DNA")=0),1,0)+COUNTIF($N131:$U131,"DNA")+COUNTIF($V131:$Z131,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A131&lt;&gt;"",OR($G131="",$G131="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M131:$U131)+($M131:$U131="DNA")),$M131:$U131),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M131:$U131)+($M131:$U131="DNA")),$M131:$U131),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M131:$U131)+($M131:$U131="DNA")),$M131:$U131),"")&lt;TODAY())),1,0)+COUNTIF($V131:$Z131,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J131" s="32">
@@ -7088,7 +7099,7 @@
         <v/>
       </c>
       <c r="K131" s="32">
-        <f>IF(NOT(AND($A131&lt;&gt;"",OR($G131="",$G131="Active"))),"",IF($L131&lt;&gt;"",IF($L131=$M131,"Booking",INDEX($N$4:$U$4,MATCH($L131,$N131:$U131,0))),IF(COUNTIF($N131:$U131,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N131:$U131)=0,"All done",IF(MAX($M131:$U131)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A131&lt;&gt;"",OR($G131="",$G131="Active"))),"",IF($L131&lt;&gt;"",IF($L131=$M131,"Booking",INDEX($N$4:$U$4,MATCH($L131,$N131:$U131,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M131:$U131)+($M131:$U131="DNA")),$M131:$U131),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M131:$U131)+($M131:$U131="DNA")),$M131:$U131),"")),IF(ISNUMBER($U131),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L131" s="33">
@@ -7126,7 +7137,7 @@
         <v/>
       </c>
       <c r="I132" s="32">
-        <f>IF(NOT(AND($A132&lt;&gt;"",OR($G132="",$G132="Active"))),"",IF(AND(MAX($M132:$U132)&gt;0,MAX($M132:$U132)&lt;TODAY(),COUNTBLANK($N132:$U132)&gt;0,COUNTIF($N132:$U132,"DNA")=0),1,0)+COUNTIF($N132:$U132,"DNA")+COUNTIF($V132:$Z132,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A132&lt;&gt;"",OR($G132="",$G132="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M132:$U132)+($M132:$U132="DNA")),$M132:$U132),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M132:$U132)+($M132:$U132="DNA")),$M132:$U132),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M132:$U132)+($M132:$U132="DNA")),$M132:$U132),"")&lt;TODAY())),1,0)+COUNTIF($V132:$Z132,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J132" s="32">
@@ -7134,7 +7145,7 @@
         <v/>
       </c>
       <c r="K132" s="32">
-        <f>IF(NOT(AND($A132&lt;&gt;"",OR($G132="",$G132="Active"))),"",IF($L132&lt;&gt;"",IF($L132=$M132,"Booking",INDEX($N$4:$U$4,MATCH($L132,$N132:$U132,0))),IF(COUNTIF($N132:$U132,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N132:$U132)=0,"All done",IF(MAX($M132:$U132)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A132&lt;&gt;"",OR($G132="",$G132="Active"))),"",IF($L132&lt;&gt;"",IF($L132=$M132,"Booking",INDEX($N$4:$U$4,MATCH($L132,$N132:$U132,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M132:$U132)+($M132:$U132="DNA")),$M132:$U132),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M132:$U132)+($M132:$U132="DNA")),$M132:$U132),"")),IF(ISNUMBER($U132),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L132" s="33">
@@ -7172,7 +7183,7 @@
         <v/>
       </c>
       <c r="I133" s="32">
-        <f>IF(NOT(AND($A133&lt;&gt;"",OR($G133="",$G133="Active"))),"",IF(AND(MAX($M133:$U133)&gt;0,MAX($M133:$U133)&lt;TODAY(),COUNTBLANK($N133:$U133)&gt;0,COUNTIF($N133:$U133,"DNA")=0),1,0)+COUNTIF($N133:$U133,"DNA")+COUNTIF($V133:$Z133,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A133&lt;&gt;"",OR($G133="",$G133="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M133:$U133)+($M133:$U133="DNA")),$M133:$U133),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M133:$U133)+($M133:$U133="DNA")),$M133:$U133),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M133:$U133)+($M133:$U133="DNA")),$M133:$U133),"")&lt;TODAY())),1,0)+COUNTIF($V133:$Z133,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J133" s="32">
@@ -7180,7 +7191,7 @@
         <v/>
       </c>
       <c r="K133" s="32">
-        <f>IF(NOT(AND($A133&lt;&gt;"",OR($G133="",$G133="Active"))),"",IF($L133&lt;&gt;"",IF($L133=$M133,"Booking",INDEX($N$4:$U$4,MATCH($L133,$N133:$U133,0))),IF(COUNTIF($N133:$U133,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N133:$U133)=0,"All done",IF(MAX($M133:$U133)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A133&lt;&gt;"",OR($G133="",$G133="Active"))),"",IF($L133&lt;&gt;"",IF($L133=$M133,"Booking",INDEX($N$4:$U$4,MATCH($L133,$N133:$U133,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M133:$U133)+($M133:$U133="DNA")),$M133:$U133),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M133:$U133)+($M133:$U133="DNA")),$M133:$U133),"")),IF(ISNUMBER($U133),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L133" s="33">
@@ -7218,7 +7229,7 @@
         <v/>
       </c>
       <c r="I134" s="32">
-        <f>IF(NOT(AND($A134&lt;&gt;"",OR($G134="",$G134="Active"))),"",IF(AND(MAX($M134:$U134)&gt;0,MAX($M134:$U134)&lt;TODAY(),COUNTBLANK($N134:$U134)&gt;0,COUNTIF($N134:$U134,"DNA")=0),1,0)+COUNTIF($N134:$U134,"DNA")+COUNTIF($V134:$Z134,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A134&lt;&gt;"",OR($G134="",$G134="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M134:$U134)+($M134:$U134="DNA")),$M134:$U134),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M134:$U134)+($M134:$U134="DNA")),$M134:$U134),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M134:$U134)+($M134:$U134="DNA")),$M134:$U134),"")&lt;TODAY())),1,0)+COUNTIF($V134:$Z134,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J134" s="32">
@@ -7226,7 +7237,7 @@
         <v/>
       </c>
       <c r="K134" s="32">
-        <f>IF(NOT(AND($A134&lt;&gt;"",OR($G134="",$G134="Active"))),"",IF($L134&lt;&gt;"",IF($L134=$M134,"Booking",INDEX($N$4:$U$4,MATCH($L134,$N134:$U134,0))),IF(COUNTIF($N134:$U134,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N134:$U134)=0,"All done",IF(MAX($M134:$U134)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A134&lt;&gt;"",OR($G134="",$G134="Active"))),"",IF($L134&lt;&gt;"",IF($L134=$M134,"Booking",INDEX($N$4:$U$4,MATCH($L134,$N134:$U134,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M134:$U134)+($M134:$U134="DNA")),$M134:$U134),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M134:$U134)+($M134:$U134="DNA")),$M134:$U134),"")),IF(ISNUMBER($U134),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L134" s="33">
@@ -7264,7 +7275,7 @@
         <v/>
       </c>
       <c r="I135" s="32">
-        <f>IF(NOT(AND($A135&lt;&gt;"",OR($G135="",$G135="Active"))),"",IF(AND(MAX($M135:$U135)&gt;0,MAX($M135:$U135)&lt;TODAY(),COUNTBLANK($N135:$U135)&gt;0,COUNTIF($N135:$U135,"DNA")=0),1,0)+COUNTIF($N135:$U135,"DNA")+COUNTIF($V135:$Z135,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A135&lt;&gt;"",OR($G135="",$G135="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M135:$U135)+($M135:$U135="DNA")),$M135:$U135),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M135:$U135)+($M135:$U135="DNA")),$M135:$U135),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M135:$U135)+($M135:$U135="DNA")),$M135:$U135),"")&lt;TODAY())),1,0)+COUNTIF($V135:$Z135,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J135" s="32">
@@ -7272,7 +7283,7 @@
         <v/>
       </c>
       <c r="K135" s="32">
-        <f>IF(NOT(AND($A135&lt;&gt;"",OR($G135="",$G135="Active"))),"",IF($L135&lt;&gt;"",IF($L135=$M135,"Booking",INDEX($N$4:$U$4,MATCH($L135,$N135:$U135,0))),IF(COUNTIF($N135:$U135,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N135:$U135)=0,"All done",IF(MAX($M135:$U135)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A135&lt;&gt;"",OR($G135="",$G135="Active"))),"",IF($L135&lt;&gt;"",IF($L135=$M135,"Booking",INDEX($N$4:$U$4,MATCH($L135,$N135:$U135,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M135:$U135)+($M135:$U135="DNA")),$M135:$U135),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M135:$U135)+($M135:$U135="DNA")),$M135:$U135),"")),IF(ISNUMBER($U135),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L135" s="33">
@@ -7310,7 +7321,7 @@
         <v/>
       </c>
       <c r="I136" s="32">
-        <f>IF(NOT(AND($A136&lt;&gt;"",OR($G136="",$G136="Active"))),"",IF(AND(MAX($M136:$U136)&gt;0,MAX($M136:$U136)&lt;TODAY(),COUNTBLANK($N136:$U136)&gt;0,COUNTIF($N136:$U136,"DNA")=0),1,0)+COUNTIF($N136:$U136,"DNA")+COUNTIF($V136:$Z136,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A136&lt;&gt;"",OR($G136="",$G136="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M136:$U136)+($M136:$U136="DNA")),$M136:$U136),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M136:$U136)+($M136:$U136="DNA")),$M136:$U136),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M136:$U136)+($M136:$U136="DNA")),$M136:$U136),"")&lt;TODAY())),1,0)+COUNTIF($V136:$Z136,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J136" s="32">
@@ -7318,7 +7329,7 @@
         <v/>
       </c>
       <c r="K136" s="32">
-        <f>IF(NOT(AND($A136&lt;&gt;"",OR($G136="",$G136="Active"))),"",IF($L136&lt;&gt;"",IF($L136=$M136,"Booking",INDEX($N$4:$U$4,MATCH($L136,$N136:$U136,0))),IF(COUNTIF($N136:$U136,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N136:$U136)=0,"All done",IF(MAX($M136:$U136)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A136&lt;&gt;"",OR($G136="",$G136="Active"))),"",IF($L136&lt;&gt;"",IF($L136=$M136,"Booking",INDEX($N$4:$U$4,MATCH($L136,$N136:$U136,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M136:$U136)+($M136:$U136="DNA")),$M136:$U136),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M136:$U136)+($M136:$U136="DNA")),$M136:$U136),"")),IF(ISNUMBER($U136),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L136" s="33">
@@ -7356,7 +7367,7 @@
         <v/>
       </c>
       <c r="I137" s="32">
-        <f>IF(NOT(AND($A137&lt;&gt;"",OR($G137="",$G137="Active"))),"",IF(AND(MAX($M137:$U137)&gt;0,MAX($M137:$U137)&lt;TODAY(),COUNTBLANK($N137:$U137)&gt;0,COUNTIF($N137:$U137,"DNA")=0),1,0)+COUNTIF($N137:$U137,"DNA")+COUNTIF($V137:$Z137,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A137&lt;&gt;"",OR($G137="",$G137="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M137:$U137)+($M137:$U137="DNA")),$M137:$U137),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M137:$U137)+($M137:$U137="DNA")),$M137:$U137),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M137:$U137)+($M137:$U137="DNA")),$M137:$U137),"")&lt;TODAY())),1,0)+COUNTIF($V137:$Z137,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J137" s="32">
@@ -7364,7 +7375,7 @@
         <v/>
       </c>
       <c r="K137" s="32">
-        <f>IF(NOT(AND($A137&lt;&gt;"",OR($G137="",$G137="Active"))),"",IF($L137&lt;&gt;"",IF($L137=$M137,"Booking",INDEX($N$4:$U$4,MATCH($L137,$N137:$U137,0))),IF(COUNTIF($N137:$U137,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N137:$U137)=0,"All done",IF(MAX($M137:$U137)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A137&lt;&gt;"",OR($G137="",$G137="Active"))),"",IF($L137&lt;&gt;"",IF($L137=$M137,"Booking",INDEX($N$4:$U$4,MATCH($L137,$N137:$U137,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M137:$U137)+($M137:$U137="DNA")),$M137:$U137),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M137:$U137)+($M137:$U137="DNA")),$M137:$U137),"")),IF(ISNUMBER($U137),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L137" s="33">
@@ -7402,7 +7413,7 @@
         <v/>
       </c>
       <c r="I138" s="32">
-        <f>IF(NOT(AND($A138&lt;&gt;"",OR($G138="",$G138="Active"))),"",IF(AND(MAX($M138:$U138)&gt;0,MAX($M138:$U138)&lt;TODAY(),COUNTBLANK($N138:$U138)&gt;0,COUNTIF($N138:$U138,"DNA")=0),1,0)+COUNTIF($N138:$U138,"DNA")+COUNTIF($V138:$Z138,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A138&lt;&gt;"",OR($G138="",$G138="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M138:$U138)+($M138:$U138="DNA")),$M138:$U138),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M138:$U138)+($M138:$U138="DNA")),$M138:$U138),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M138:$U138)+($M138:$U138="DNA")),$M138:$U138),"")&lt;TODAY())),1,0)+COUNTIF($V138:$Z138,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J138" s="32">
@@ -7410,7 +7421,7 @@
         <v/>
       </c>
       <c r="K138" s="32">
-        <f>IF(NOT(AND($A138&lt;&gt;"",OR($G138="",$G138="Active"))),"",IF($L138&lt;&gt;"",IF($L138=$M138,"Booking",INDEX($N$4:$U$4,MATCH($L138,$N138:$U138,0))),IF(COUNTIF($N138:$U138,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N138:$U138)=0,"All done",IF(MAX($M138:$U138)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A138&lt;&gt;"",OR($G138="",$G138="Active"))),"",IF($L138&lt;&gt;"",IF($L138=$M138,"Booking",INDEX($N$4:$U$4,MATCH($L138,$N138:$U138,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M138:$U138)+($M138:$U138="DNA")),$M138:$U138),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M138:$U138)+($M138:$U138="DNA")),$M138:$U138),"")),IF(ISNUMBER($U138),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L138" s="33">
@@ -7448,7 +7459,7 @@
         <v/>
       </c>
       <c r="I139" s="32">
-        <f>IF(NOT(AND($A139&lt;&gt;"",OR($G139="",$G139="Active"))),"",IF(AND(MAX($M139:$U139)&gt;0,MAX($M139:$U139)&lt;TODAY(),COUNTBLANK($N139:$U139)&gt;0,COUNTIF($N139:$U139,"DNA")=0),1,0)+COUNTIF($N139:$U139,"DNA")+COUNTIF($V139:$Z139,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A139&lt;&gt;"",OR($G139="",$G139="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M139:$U139)+($M139:$U139="DNA")),$M139:$U139),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M139:$U139)+($M139:$U139="DNA")),$M139:$U139),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M139:$U139)+($M139:$U139="DNA")),$M139:$U139),"")&lt;TODAY())),1,0)+COUNTIF($V139:$Z139,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J139" s="32">
@@ -7456,7 +7467,7 @@
         <v/>
       </c>
       <c r="K139" s="32">
-        <f>IF(NOT(AND($A139&lt;&gt;"",OR($G139="",$G139="Active"))),"",IF($L139&lt;&gt;"",IF($L139=$M139,"Booking",INDEX($N$4:$U$4,MATCH($L139,$N139:$U139,0))),IF(COUNTIF($N139:$U139,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N139:$U139)=0,"All done",IF(MAX($M139:$U139)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A139&lt;&gt;"",OR($G139="",$G139="Active"))),"",IF($L139&lt;&gt;"",IF($L139=$M139,"Booking",INDEX($N$4:$U$4,MATCH($L139,$N139:$U139,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M139:$U139)+($M139:$U139="DNA")),$M139:$U139),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M139:$U139)+($M139:$U139="DNA")),$M139:$U139),"")),IF(ISNUMBER($U139),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L139" s="33">
@@ -7494,7 +7505,7 @@
         <v/>
       </c>
       <c r="I140" s="32">
-        <f>IF(NOT(AND($A140&lt;&gt;"",OR($G140="",$G140="Active"))),"",IF(AND(MAX($M140:$U140)&gt;0,MAX($M140:$U140)&lt;TODAY(),COUNTBLANK($N140:$U140)&gt;0,COUNTIF($N140:$U140,"DNA")=0),1,0)+COUNTIF($N140:$U140,"DNA")+COUNTIF($V140:$Z140,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A140&lt;&gt;"",OR($G140="",$G140="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M140:$U140)+($M140:$U140="DNA")),$M140:$U140),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M140:$U140)+($M140:$U140="DNA")),$M140:$U140),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M140:$U140)+($M140:$U140="DNA")),$M140:$U140),"")&lt;TODAY())),1,0)+COUNTIF($V140:$Z140,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J140" s="32">
@@ -7502,7 +7513,7 @@
         <v/>
       </c>
       <c r="K140" s="32">
-        <f>IF(NOT(AND($A140&lt;&gt;"",OR($G140="",$G140="Active"))),"",IF($L140&lt;&gt;"",IF($L140=$M140,"Booking",INDEX($N$4:$U$4,MATCH($L140,$N140:$U140,0))),IF(COUNTIF($N140:$U140,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N140:$U140)=0,"All done",IF(MAX($M140:$U140)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A140&lt;&gt;"",OR($G140="",$G140="Active"))),"",IF($L140&lt;&gt;"",IF($L140=$M140,"Booking",INDEX($N$4:$U$4,MATCH($L140,$N140:$U140,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M140:$U140)+($M140:$U140="DNA")),$M140:$U140),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M140:$U140)+($M140:$U140="DNA")),$M140:$U140),"")),IF(ISNUMBER($U140),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L140" s="33">
@@ -7540,7 +7551,7 @@
         <v/>
       </c>
       <c r="I141" s="32">
-        <f>IF(NOT(AND($A141&lt;&gt;"",OR($G141="",$G141="Active"))),"",IF(AND(MAX($M141:$U141)&gt;0,MAX($M141:$U141)&lt;TODAY(),COUNTBLANK($N141:$U141)&gt;0,COUNTIF($N141:$U141,"DNA")=0),1,0)+COUNTIF($N141:$U141,"DNA")+COUNTIF($V141:$Z141,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A141&lt;&gt;"",OR($G141="",$G141="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M141:$U141)+($M141:$U141="DNA")),$M141:$U141),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M141:$U141)+($M141:$U141="DNA")),$M141:$U141),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M141:$U141)+($M141:$U141="DNA")),$M141:$U141),"")&lt;TODAY())),1,0)+COUNTIF($V141:$Z141,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J141" s="32">
@@ -7548,7 +7559,7 @@
         <v/>
       </c>
       <c r="K141" s="32">
-        <f>IF(NOT(AND($A141&lt;&gt;"",OR($G141="",$G141="Active"))),"",IF($L141&lt;&gt;"",IF($L141=$M141,"Booking",INDEX($N$4:$U$4,MATCH($L141,$N141:$U141,0))),IF(COUNTIF($N141:$U141,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N141:$U141)=0,"All done",IF(MAX($M141:$U141)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A141&lt;&gt;"",OR($G141="",$G141="Active"))),"",IF($L141&lt;&gt;"",IF($L141=$M141,"Booking",INDEX($N$4:$U$4,MATCH($L141,$N141:$U141,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M141:$U141)+($M141:$U141="DNA")),$M141:$U141),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M141:$U141)+($M141:$U141="DNA")),$M141:$U141),"")),IF(ISNUMBER($U141),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L141" s="33">
@@ -7586,7 +7597,7 @@
         <v/>
       </c>
       <c r="I142" s="32">
-        <f>IF(NOT(AND($A142&lt;&gt;"",OR($G142="",$G142="Active"))),"",IF(AND(MAX($M142:$U142)&gt;0,MAX($M142:$U142)&lt;TODAY(),COUNTBLANK($N142:$U142)&gt;0,COUNTIF($N142:$U142,"DNA")=0),1,0)+COUNTIF($N142:$U142,"DNA")+COUNTIF($V142:$Z142,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A142&lt;&gt;"",OR($G142="",$G142="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M142:$U142)+($M142:$U142="DNA")),$M142:$U142),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M142:$U142)+($M142:$U142="DNA")),$M142:$U142),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M142:$U142)+($M142:$U142="DNA")),$M142:$U142),"")&lt;TODAY())),1,0)+COUNTIF($V142:$Z142,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J142" s="32">
@@ -7594,7 +7605,7 @@
         <v/>
       </c>
       <c r="K142" s="32">
-        <f>IF(NOT(AND($A142&lt;&gt;"",OR($G142="",$G142="Active"))),"",IF($L142&lt;&gt;"",IF($L142=$M142,"Booking",INDEX($N$4:$U$4,MATCH($L142,$N142:$U142,0))),IF(COUNTIF($N142:$U142,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N142:$U142)=0,"All done",IF(MAX($M142:$U142)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A142&lt;&gt;"",OR($G142="",$G142="Active"))),"",IF($L142&lt;&gt;"",IF($L142=$M142,"Booking",INDEX($N$4:$U$4,MATCH($L142,$N142:$U142,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M142:$U142)+($M142:$U142="DNA")),$M142:$U142),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M142:$U142)+($M142:$U142="DNA")),$M142:$U142),"")),IF(ISNUMBER($U142),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L142" s="33">
@@ -7632,7 +7643,7 @@
         <v/>
       </c>
       <c r="I143" s="32">
-        <f>IF(NOT(AND($A143&lt;&gt;"",OR($G143="",$G143="Active"))),"",IF(AND(MAX($M143:$U143)&gt;0,MAX($M143:$U143)&lt;TODAY(),COUNTBLANK($N143:$U143)&gt;0,COUNTIF($N143:$U143,"DNA")=0),1,0)+COUNTIF($N143:$U143,"DNA")+COUNTIF($V143:$Z143,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A143&lt;&gt;"",OR($G143="",$G143="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M143:$U143)+($M143:$U143="DNA")),$M143:$U143),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M143:$U143)+($M143:$U143="DNA")),$M143:$U143),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M143:$U143)+($M143:$U143="DNA")),$M143:$U143),"")&lt;TODAY())),1,0)+COUNTIF($V143:$Z143,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J143" s="32">
@@ -7640,7 +7651,7 @@
         <v/>
       </c>
       <c r="K143" s="32">
-        <f>IF(NOT(AND($A143&lt;&gt;"",OR($G143="",$G143="Active"))),"",IF($L143&lt;&gt;"",IF($L143=$M143,"Booking",INDEX($N$4:$U$4,MATCH($L143,$N143:$U143,0))),IF(COUNTIF($N143:$U143,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N143:$U143)=0,"All done",IF(MAX($M143:$U143)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A143&lt;&gt;"",OR($G143="",$G143="Active"))),"",IF($L143&lt;&gt;"",IF($L143=$M143,"Booking",INDEX($N$4:$U$4,MATCH($L143,$N143:$U143,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M143:$U143)+($M143:$U143="DNA")),$M143:$U143),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M143:$U143)+($M143:$U143="DNA")),$M143:$U143),"")),IF(ISNUMBER($U143),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L143" s="33">
@@ -7678,7 +7689,7 @@
         <v/>
       </c>
       <c r="I144" s="32">
-        <f>IF(NOT(AND($A144&lt;&gt;"",OR($G144="",$G144="Active"))),"",IF(AND(MAX($M144:$U144)&gt;0,MAX($M144:$U144)&lt;TODAY(),COUNTBLANK($N144:$U144)&gt;0,COUNTIF($N144:$U144,"DNA")=0),1,0)+COUNTIF($N144:$U144,"DNA")+COUNTIF($V144:$Z144,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A144&lt;&gt;"",OR($G144="",$G144="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M144:$U144)+($M144:$U144="DNA")),$M144:$U144),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M144:$U144)+($M144:$U144="DNA")),$M144:$U144),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M144:$U144)+($M144:$U144="DNA")),$M144:$U144),"")&lt;TODAY())),1,0)+COUNTIF($V144:$Z144,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J144" s="32">
@@ -7686,7 +7697,7 @@
         <v/>
       </c>
       <c r="K144" s="32">
-        <f>IF(NOT(AND($A144&lt;&gt;"",OR($G144="",$G144="Active"))),"",IF($L144&lt;&gt;"",IF($L144=$M144,"Booking",INDEX($N$4:$U$4,MATCH($L144,$N144:$U144,0))),IF(COUNTIF($N144:$U144,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N144:$U144)=0,"All done",IF(MAX($M144:$U144)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A144&lt;&gt;"",OR($G144="",$G144="Active"))),"",IF($L144&lt;&gt;"",IF($L144=$M144,"Booking",INDEX($N$4:$U$4,MATCH($L144,$N144:$U144,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M144:$U144)+($M144:$U144="DNA")),$M144:$U144),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M144:$U144)+($M144:$U144="DNA")),$M144:$U144),"")),IF(ISNUMBER($U144),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L144" s="33">
@@ -7724,7 +7735,7 @@
         <v/>
       </c>
       <c r="I145" s="32">
-        <f>IF(NOT(AND($A145&lt;&gt;"",OR($G145="",$G145="Active"))),"",IF(AND(MAX($M145:$U145)&gt;0,MAX($M145:$U145)&lt;TODAY(),COUNTBLANK($N145:$U145)&gt;0,COUNTIF($N145:$U145,"DNA")=0),1,0)+COUNTIF($N145:$U145,"DNA")+COUNTIF($V145:$Z145,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A145&lt;&gt;"",OR($G145="",$G145="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M145:$U145)+($M145:$U145="DNA")),$M145:$U145),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M145:$U145)+($M145:$U145="DNA")),$M145:$U145),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M145:$U145)+($M145:$U145="DNA")),$M145:$U145),"")&lt;TODAY())),1,0)+COUNTIF($V145:$Z145,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J145" s="32">
@@ -7732,7 +7743,7 @@
         <v/>
       </c>
       <c r="K145" s="32">
-        <f>IF(NOT(AND($A145&lt;&gt;"",OR($G145="",$G145="Active"))),"",IF($L145&lt;&gt;"",IF($L145=$M145,"Booking",INDEX($N$4:$U$4,MATCH($L145,$N145:$U145,0))),IF(COUNTIF($N145:$U145,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N145:$U145)=0,"All done",IF(MAX($M145:$U145)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A145&lt;&gt;"",OR($G145="",$G145="Active"))),"",IF($L145&lt;&gt;"",IF($L145=$M145,"Booking",INDEX($N$4:$U$4,MATCH($L145,$N145:$U145,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M145:$U145)+($M145:$U145="DNA")),$M145:$U145),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M145:$U145)+($M145:$U145="DNA")),$M145:$U145),"")),IF(ISNUMBER($U145),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L145" s="33">
@@ -7770,7 +7781,7 @@
         <v/>
       </c>
       <c r="I146" s="32">
-        <f>IF(NOT(AND($A146&lt;&gt;"",OR($G146="",$G146="Active"))),"",IF(AND(MAX($M146:$U146)&gt;0,MAX($M146:$U146)&lt;TODAY(),COUNTBLANK($N146:$U146)&gt;0,COUNTIF($N146:$U146,"DNA")=0),1,0)+COUNTIF($N146:$U146,"DNA")+COUNTIF($V146:$Z146,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A146&lt;&gt;"",OR($G146="",$G146="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M146:$U146)+($M146:$U146="DNA")),$M146:$U146),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M146:$U146)+($M146:$U146="DNA")),$M146:$U146),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M146:$U146)+($M146:$U146="DNA")),$M146:$U146),"")&lt;TODAY())),1,0)+COUNTIF($V146:$Z146,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J146" s="32">
@@ -7778,7 +7789,7 @@
         <v/>
       </c>
       <c r="K146" s="32">
-        <f>IF(NOT(AND($A146&lt;&gt;"",OR($G146="",$G146="Active"))),"",IF($L146&lt;&gt;"",IF($L146=$M146,"Booking",INDEX($N$4:$U$4,MATCH($L146,$N146:$U146,0))),IF(COUNTIF($N146:$U146,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N146:$U146)=0,"All done",IF(MAX($M146:$U146)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A146&lt;&gt;"",OR($G146="",$G146="Active"))),"",IF($L146&lt;&gt;"",IF($L146=$M146,"Booking",INDEX($N$4:$U$4,MATCH($L146,$N146:$U146,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M146:$U146)+($M146:$U146="DNA")),$M146:$U146),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M146:$U146)+($M146:$U146="DNA")),$M146:$U146),"")),IF(ISNUMBER($U146),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L146" s="33">
@@ -7816,7 +7827,7 @@
         <v/>
       </c>
       <c r="I147" s="32">
-        <f>IF(NOT(AND($A147&lt;&gt;"",OR($G147="",$G147="Active"))),"",IF(AND(MAX($M147:$U147)&gt;0,MAX($M147:$U147)&lt;TODAY(),COUNTBLANK($N147:$U147)&gt;0,COUNTIF($N147:$U147,"DNA")=0),1,0)+COUNTIF($N147:$U147,"DNA")+COUNTIF($V147:$Z147,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A147&lt;&gt;"",OR($G147="",$G147="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M147:$U147)+($M147:$U147="DNA")),$M147:$U147),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M147:$U147)+($M147:$U147="DNA")),$M147:$U147),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M147:$U147)+($M147:$U147="DNA")),$M147:$U147),"")&lt;TODAY())),1,0)+COUNTIF($V147:$Z147,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J147" s="32">
@@ -7824,7 +7835,7 @@
         <v/>
       </c>
       <c r="K147" s="32">
-        <f>IF(NOT(AND($A147&lt;&gt;"",OR($G147="",$G147="Active"))),"",IF($L147&lt;&gt;"",IF($L147=$M147,"Booking",INDEX($N$4:$U$4,MATCH($L147,$N147:$U147,0))),IF(COUNTIF($N147:$U147,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N147:$U147)=0,"All done",IF(MAX($M147:$U147)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A147&lt;&gt;"",OR($G147="",$G147="Active"))),"",IF($L147&lt;&gt;"",IF($L147=$M147,"Booking",INDEX($N$4:$U$4,MATCH($L147,$N147:$U147,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M147:$U147)+($M147:$U147="DNA")),$M147:$U147),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M147:$U147)+($M147:$U147="DNA")),$M147:$U147),"")),IF(ISNUMBER($U147),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L147" s="33">
@@ -7862,7 +7873,7 @@
         <v/>
       </c>
       <c r="I148" s="32">
-        <f>IF(NOT(AND($A148&lt;&gt;"",OR($G148="",$G148="Active"))),"",IF(AND(MAX($M148:$U148)&gt;0,MAX($M148:$U148)&lt;TODAY(),COUNTBLANK($N148:$U148)&gt;0,COUNTIF($N148:$U148,"DNA")=0),1,0)+COUNTIF($N148:$U148,"DNA")+COUNTIF($V148:$Z148,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A148&lt;&gt;"",OR($G148="",$G148="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M148:$U148)+($M148:$U148="DNA")),$M148:$U148),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M148:$U148)+($M148:$U148="DNA")),$M148:$U148),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M148:$U148)+($M148:$U148="DNA")),$M148:$U148),"")&lt;TODAY())),1,0)+COUNTIF($V148:$Z148,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J148" s="32">
@@ -7870,7 +7881,7 @@
         <v/>
       </c>
       <c r="K148" s="32">
-        <f>IF(NOT(AND($A148&lt;&gt;"",OR($G148="",$G148="Active"))),"",IF($L148&lt;&gt;"",IF($L148=$M148,"Booking",INDEX($N$4:$U$4,MATCH($L148,$N148:$U148,0))),IF(COUNTIF($N148:$U148,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N148:$U148)=0,"All done",IF(MAX($M148:$U148)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A148&lt;&gt;"",OR($G148="",$G148="Active"))),"",IF($L148&lt;&gt;"",IF($L148=$M148,"Booking",INDEX($N$4:$U$4,MATCH($L148,$N148:$U148,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M148:$U148)+($M148:$U148="DNA")),$M148:$U148),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M148:$U148)+($M148:$U148="DNA")),$M148:$U148),"")),IF(ISNUMBER($U148),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L148" s="33">
@@ -7908,7 +7919,7 @@
         <v/>
       </c>
       <c r="I149" s="32">
-        <f>IF(NOT(AND($A149&lt;&gt;"",OR($G149="",$G149="Active"))),"",IF(AND(MAX($M149:$U149)&gt;0,MAX($M149:$U149)&lt;TODAY(),COUNTBLANK($N149:$U149)&gt;0,COUNTIF($N149:$U149,"DNA")=0),1,0)+COUNTIF($N149:$U149,"DNA")+COUNTIF($V149:$Z149,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A149&lt;&gt;"",OR($G149="",$G149="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M149:$U149)+($M149:$U149="DNA")),$M149:$U149),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M149:$U149)+($M149:$U149="DNA")),$M149:$U149),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M149:$U149)+($M149:$U149="DNA")),$M149:$U149),"")&lt;TODAY())),1,0)+COUNTIF($V149:$Z149,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J149" s="32">
@@ -7916,7 +7927,7 @@
         <v/>
       </c>
       <c r="K149" s="32">
-        <f>IF(NOT(AND($A149&lt;&gt;"",OR($G149="",$G149="Active"))),"",IF($L149&lt;&gt;"",IF($L149=$M149,"Booking",INDEX($N$4:$U$4,MATCH($L149,$N149:$U149,0))),IF(COUNTIF($N149:$U149,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N149:$U149)=0,"All done",IF(MAX($M149:$U149)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A149&lt;&gt;"",OR($G149="",$G149="Active"))),"",IF($L149&lt;&gt;"",IF($L149=$M149,"Booking",INDEX($N$4:$U$4,MATCH($L149,$N149:$U149,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M149:$U149)+($M149:$U149="DNA")),$M149:$U149),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M149:$U149)+($M149:$U149="DNA")),$M149:$U149),"")),IF(ISNUMBER($U149),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L149" s="33">
@@ -7954,7 +7965,7 @@
         <v/>
       </c>
       <c r="I150" s="32">
-        <f>IF(NOT(AND($A150&lt;&gt;"",OR($G150="",$G150="Active"))),"",IF(AND(MAX($M150:$U150)&gt;0,MAX($M150:$U150)&lt;TODAY(),COUNTBLANK($N150:$U150)&gt;0,COUNTIF($N150:$U150,"DNA")=0),1,0)+COUNTIF($N150:$U150,"DNA")+COUNTIF($V150:$Z150,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A150&lt;&gt;"",OR($G150="",$G150="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M150:$U150)+($M150:$U150="DNA")),$M150:$U150),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M150:$U150)+($M150:$U150="DNA")),$M150:$U150),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M150:$U150)+($M150:$U150="DNA")),$M150:$U150),"")&lt;TODAY())),1,0)+COUNTIF($V150:$Z150,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J150" s="32">
@@ -7962,7 +7973,7 @@
         <v/>
       </c>
       <c r="K150" s="32">
-        <f>IF(NOT(AND($A150&lt;&gt;"",OR($G150="",$G150="Active"))),"",IF($L150&lt;&gt;"",IF($L150=$M150,"Booking",INDEX($N$4:$U$4,MATCH($L150,$N150:$U150,0))),IF(COUNTIF($N150:$U150,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N150:$U150)=0,"All done",IF(MAX($M150:$U150)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A150&lt;&gt;"",OR($G150="",$G150="Active"))),"",IF($L150&lt;&gt;"",IF($L150=$M150,"Booking",INDEX($N$4:$U$4,MATCH($L150,$N150:$U150,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M150:$U150)+($M150:$U150="DNA")),$M150:$U150),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M150:$U150)+($M150:$U150="DNA")),$M150:$U150),"")),IF(ISNUMBER($U150),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L150" s="33">
@@ -8000,7 +8011,7 @@
         <v/>
       </c>
       <c r="I151" s="32">
-        <f>IF(NOT(AND($A151&lt;&gt;"",OR($G151="",$G151="Active"))),"",IF(AND(MAX($M151:$U151)&gt;0,MAX($M151:$U151)&lt;TODAY(),COUNTBLANK($N151:$U151)&gt;0,COUNTIF($N151:$U151,"DNA")=0),1,0)+COUNTIF($N151:$U151,"DNA")+COUNTIF($V151:$Z151,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A151&lt;&gt;"",OR($G151="",$G151="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M151:$U151)+($M151:$U151="DNA")),$M151:$U151),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M151:$U151)+($M151:$U151="DNA")),$M151:$U151),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M151:$U151)+($M151:$U151="DNA")),$M151:$U151),"")&lt;TODAY())),1,0)+COUNTIF($V151:$Z151,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J151" s="32">
@@ -8008,7 +8019,7 @@
         <v/>
       </c>
       <c r="K151" s="32">
-        <f>IF(NOT(AND($A151&lt;&gt;"",OR($G151="",$G151="Active"))),"",IF($L151&lt;&gt;"",IF($L151=$M151,"Booking",INDEX($N$4:$U$4,MATCH($L151,$N151:$U151,0))),IF(COUNTIF($N151:$U151,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N151:$U151)=0,"All done",IF(MAX($M151:$U151)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A151&lt;&gt;"",OR($G151="",$G151="Active"))),"",IF($L151&lt;&gt;"",IF($L151=$M151,"Booking",INDEX($N$4:$U$4,MATCH($L151,$N151:$U151,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M151:$U151)+($M151:$U151="DNA")),$M151:$U151),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M151:$U151)+($M151:$U151="DNA")),$M151:$U151),"")),IF(ISNUMBER($U151),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L151" s="33">
@@ -8046,7 +8057,7 @@
         <v/>
       </c>
       <c r="I152" s="32">
-        <f>IF(NOT(AND($A152&lt;&gt;"",OR($G152="",$G152="Active"))),"",IF(AND(MAX($M152:$U152)&gt;0,MAX($M152:$U152)&lt;TODAY(),COUNTBLANK($N152:$U152)&gt;0,COUNTIF($N152:$U152,"DNA")=0),1,0)+COUNTIF($N152:$U152,"DNA")+COUNTIF($V152:$Z152,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A152&lt;&gt;"",OR($G152="",$G152="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M152:$U152)+($M152:$U152="DNA")),$M152:$U152),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M152:$U152)+($M152:$U152="DNA")),$M152:$U152),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M152:$U152)+($M152:$U152="DNA")),$M152:$U152),"")&lt;TODAY())),1,0)+COUNTIF($V152:$Z152,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J152" s="32">
@@ -8054,7 +8065,7 @@
         <v/>
       </c>
       <c r="K152" s="32">
-        <f>IF(NOT(AND($A152&lt;&gt;"",OR($G152="",$G152="Active"))),"",IF($L152&lt;&gt;"",IF($L152=$M152,"Booking",INDEX($N$4:$U$4,MATCH($L152,$N152:$U152,0))),IF(COUNTIF($N152:$U152,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N152:$U152)=0,"All done",IF(MAX($M152:$U152)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A152&lt;&gt;"",OR($G152="",$G152="Active"))),"",IF($L152&lt;&gt;"",IF($L152=$M152,"Booking",INDEX($N$4:$U$4,MATCH($L152,$N152:$U152,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M152:$U152)+($M152:$U152="DNA")),$M152:$U152),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M152:$U152)+($M152:$U152="DNA")),$M152:$U152),"")),IF(ISNUMBER($U152),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L152" s="33">
@@ -8092,7 +8103,7 @@
         <v/>
       </c>
       <c r="I153" s="32">
-        <f>IF(NOT(AND($A153&lt;&gt;"",OR($G153="",$G153="Active"))),"",IF(AND(MAX($M153:$U153)&gt;0,MAX($M153:$U153)&lt;TODAY(),COUNTBLANK($N153:$U153)&gt;0,COUNTIF($N153:$U153,"DNA")=0),1,0)+COUNTIF($N153:$U153,"DNA")+COUNTIF($V153:$Z153,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A153&lt;&gt;"",OR($G153="",$G153="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M153:$U153)+($M153:$U153="DNA")),$M153:$U153),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M153:$U153)+($M153:$U153="DNA")),$M153:$U153),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M153:$U153)+($M153:$U153="DNA")),$M153:$U153),"")&lt;TODAY())),1,0)+COUNTIF($V153:$Z153,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J153" s="32">
@@ -8100,7 +8111,7 @@
         <v/>
       </c>
       <c r="K153" s="32">
-        <f>IF(NOT(AND($A153&lt;&gt;"",OR($G153="",$G153="Active"))),"",IF($L153&lt;&gt;"",IF($L153=$M153,"Booking",INDEX($N$4:$U$4,MATCH($L153,$N153:$U153,0))),IF(COUNTIF($N153:$U153,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N153:$U153)=0,"All done",IF(MAX($M153:$U153)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A153&lt;&gt;"",OR($G153="",$G153="Active"))),"",IF($L153&lt;&gt;"",IF($L153=$M153,"Booking",INDEX($N$4:$U$4,MATCH($L153,$N153:$U153,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M153:$U153)+($M153:$U153="DNA")),$M153:$U153),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M153:$U153)+($M153:$U153="DNA")),$M153:$U153),"")),IF(ISNUMBER($U153),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L153" s="33">
@@ -8138,7 +8149,7 @@
         <v/>
       </c>
       <c r="I154" s="32">
-        <f>IF(NOT(AND($A154&lt;&gt;"",OR($G154="",$G154="Active"))),"",IF(AND(MAX($M154:$U154)&gt;0,MAX($M154:$U154)&lt;TODAY(),COUNTBLANK($N154:$U154)&gt;0,COUNTIF($N154:$U154,"DNA")=0),1,0)+COUNTIF($N154:$U154,"DNA")+COUNTIF($V154:$Z154,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A154&lt;&gt;"",OR($G154="",$G154="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M154:$U154)+($M154:$U154="DNA")),$M154:$U154),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M154:$U154)+($M154:$U154="DNA")),$M154:$U154),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M154:$U154)+($M154:$U154="DNA")),$M154:$U154),"")&lt;TODAY())),1,0)+COUNTIF($V154:$Z154,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J154" s="32">
@@ -8146,7 +8157,7 @@
         <v/>
       </c>
       <c r="K154" s="32">
-        <f>IF(NOT(AND($A154&lt;&gt;"",OR($G154="",$G154="Active"))),"",IF($L154&lt;&gt;"",IF($L154=$M154,"Booking",INDEX($N$4:$U$4,MATCH($L154,$N154:$U154,0))),IF(COUNTIF($N154:$U154,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N154:$U154)=0,"All done",IF(MAX($M154:$U154)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A154&lt;&gt;"",OR($G154="",$G154="Active"))),"",IF($L154&lt;&gt;"",IF($L154=$M154,"Booking",INDEX($N$4:$U$4,MATCH($L154,$N154:$U154,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M154:$U154)+($M154:$U154="DNA")),$M154:$U154),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M154:$U154)+($M154:$U154="DNA")),$M154:$U154),"")),IF(ISNUMBER($U154),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L154" s="33">
@@ -8184,7 +8195,7 @@
         <v/>
       </c>
       <c r="I155" s="32">
-        <f>IF(NOT(AND($A155&lt;&gt;"",OR($G155="",$G155="Active"))),"",IF(AND(MAX($M155:$U155)&gt;0,MAX($M155:$U155)&lt;TODAY(),COUNTBLANK($N155:$U155)&gt;0,COUNTIF($N155:$U155,"DNA")=0),1,0)+COUNTIF($N155:$U155,"DNA")+COUNTIF($V155:$Z155,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A155&lt;&gt;"",OR($G155="",$G155="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M155:$U155)+($M155:$U155="DNA")),$M155:$U155),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M155:$U155)+($M155:$U155="DNA")),$M155:$U155),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M155:$U155)+($M155:$U155="DNA")),$M155:$U155),"")&lt;TODAY())),1,0)+COUNTIF($V155:$Z155,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J155" s="32">
@@ -8192,7 +8203,7 @@
         <v/>
       </c>
       <c r="K155" s="32">
-        <f>IF(NOT(AND($A155&lt;&gt;"",OR($G155="",$G155="Active"))),"",IF($L155&lt;&gt;"",IF($L155=$M155,"Booking",INDEX($N$4:$U$4,MATCH($L155,$N155:$U155,0))),IF(COUNTIF($N155:$U155,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N155:$U155)=0,"All done",IF(MAX($M155:$U155)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A155&lt;&gt;"",OR($G155="",$G155="Active"))),"",IF($L155&lt;&gt;"",IF($L155=$M155,"Booking",INDEX($N$4:$U$4,MATCH($L155,$N155:$U155,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M155:$U155)+($M155:$U155="DNA")),$M155:$U155),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M155:$U155)+($M155:$U155="DNA")),$M155:$U155),"")),IF(ISNUMBER($U155),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L155" s="33">
@@ -8230,7 +8241,7 @@
         <v/>
       </c>
       <c r="I156" s="32">
-        <f>IF(NOT(AND($A156&lt;&gt;"",OR($G156="",$G156="Active"))),"",IF(AND(MAX($M156:$U156)&gt;0,MAX($M156:$U156)&lt;TODAY(),COUNTBLANK($N156:$U156)&gt;0,COUNTIF($N156:$U156,"DNA")=0),1,0)+COUNTIF($N156:$U156,"DNA")+COUNTIF($V156:$Z156,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A156&lt;&gt;"",OR($G156="",$G156="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M156:$U156)+($M156:$U156="DNA")),$M156:$U156),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M156:$U156)+($M156:$U156="DNA")),$M156:$U156),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M156:$U156)+($M156:$U156="DNA")),$M156:$U156),"")&lt;TODAY())),1,0)+COUNTIF($V156:$Z156,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J156" s="32">
@@ -8238,7 +8249,7 @@
         <v/>
       </c>
       <c r="K156" s="32">
-        <f>IF(NOT(AND($A156&lt;&gt;"",OR($G156="",$G156="Active"))),"",IF($L156&lt;&gt;"",IF($L156=$M156,"Booking",INDEX($N$4:$U$4,MATCH($L156,$N156:$U156,0))),IF(COUNTIF($N156:$U156,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N156:$U156)=0,"All done",IF(MAX($M156:$U156)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A156&lt;&gt;"",OR($G156="",$G156="Active"))),"",IF($L156&lt;&gt;"",IF($L156=$M156,"Booking",INDEX($N$4:$U$4,MATCH($L156,$N156:$U156,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M156:$U156)+($M156:$U156="DNA")),$M156:$U156),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M156:$U156)+($M156:$U156="DNA")),$M156:$U156),"")),IF(ISNUMBER($U156),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L156" s="33">
@@ -8276,7 +8287,7 @@
         <v/>
       </c>
       <c r="I157" s="32">
-        <f>IF(NOT(AND($A157&lt;&gt;"",OR($G157="",$G157="Active"))),"",IF(AND(MAX($M157:$U157)&gt;0,MAX($M157:$U157)&lt;TODAY(),COUNTBLANK($N157:$U157)&gt;0,COUNTIF($N157:$U157,"DNA")=0),1,0)+COUNTIF($N157:$U157,"DNA")+COUNTIF($V157:$Z157,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A157&lt;&gt;"",OR($G157="",$G157="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M157:$U157)+($M157:$U157="DNA")),$M157:$U157),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M157:$U157)+($M157:$U157="DNA")),$M157:$U157),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M157:$U157)+($M157:$U157="DNA")),$M157:$U157),"")&lt;TODAY())),1,0)+COUNTIF($V157:$Z157,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J157" s="32">
@@ -8284,7 +8295,7 @@
         <v/>
       </c>
       <c r="K157" s="32">
-        <f>IF(NOT(AND($A157&lt;&gt;"",OR($G157="",$G157="Active"))),"",IF($L157&lt;&gt;"",IF($L157=$M157,"Booking",INDEX($N$4:$U$4,MATCH($L157,$N157:$U157,0))),IF(COUNTIF($N157:$U157,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N157:$U157)=0,"All done",IF(MAX($M157:$U157)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A157&lt;&gt;"",OR($G157="",$G157="Active"))),"",IF($L157&lt;&gt;"",IF($L157=$M157,"Booking",INDEX($N$4:$U$4,MATCH($L157,$N157:$U157,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M157:$U157)+($M157:$U157="DNA")),$M157:$U157),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M157:$U157)+($M157:$U157="DNA")),$M157:$U157),"")),IF(ISNUMBER($U157),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L157" s="33">
@@ -8322,7 +8333,7 @@
         <v/>
       </c>
       <c r="I158" s="32">
-        <f>IF(NOT(AND($A158&lt;&gt;"",OR($G158="",$G158="Active"))),"",IF(AND(MAX($M158:$U158)&gt;0,MAX($M158:$U158)&lt;TODAY(),COUNTBLANK($N158:$U158)&gt;0,COUNTIF($N158:$U158,"DNA")=0),1,0)+COUNTIF($N158:$U158,"DNA")+COUNTIF($V158:$Z158,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A158&lt;&gt;"",OR($G158="",$G158="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M158:$U158)+($M158:$U158="DNA")),$M158:$U158),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M158:$U158)+($M158:$U158="DNA")),$M158:$U158),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M158:$U158)+($M158:$U158="DNA")),$M158:$U158),"")&lt;TODAY())),1,0)+COUNTIF($V158:$Z158,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J158" s="32">
@@ -8330,7 +8341,7 @@
         <v/>
       </c>
       <c r="K158" s="32">
-        <f>IF(NOT(AND($A158&lt;&gt;"",OR($G158="",$G158="Active"))),"",IF($L158&lt;&gt;"",IF($L158=$M158,"Booking",INDEX($N$4:$U$4,MATCH($L158,$N158:$U158,0))),IF(COUNTIF($N158:$U158,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N158:$U158)=0,"All done",IF(MAX($M158:$U158)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A158&lt;&gt;"",OR($G158="",$G158="Active"))),"",IF($L158&lt;&gt;"",IF($L158=$M158,"Booking",INDEX($N$4:$U$4,MATCH($L158,$N158:$U158,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M158:$U158)+($M158:$U158="DNA")),$M158:$U158),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M158:$U158)+($M158:$U158="DNA")),$M158:$U158),"")),IF(ISNUMBER($U158),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L158" s="33">
@@ -8368,7 +8379,7 @@
         <v/>
       </c>
       <c r="I159" s="32">
-        <f>IF(NOT(AND($A159&lt;&gt;"",OR($G159="",$G159="Active"))),"",IF(AND(MAX($M159:$U159)&gt;0,MAX($M159:$U159)&lt;TODAY(),COUNTBLANK($N159:$U159)&gt;0,COUNTIF($N159:$U159,"DNA")=0),1,0)+COUNTIF($N159:$U159,"DNA")+COUNTIF($V159:$Z159,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A159&lt;&gt;"",OR($G159="",$G159="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M159:$U159)+($M159:$U159="DNA")),$M159:$U159),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M159:$U159)+($M159:$U159="DNA")),$M159:$U159),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M159:$U159)+($M159:$U159="DNA")),$M159:$U159),"")&lt;TODAY())),1,0)+COUNTIF($V159:$Z159,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J159" s="32">
@@ -8376,7 +8387,7 @@
         <v/>
       </c>
       <c r="K159" s="32">
-        <f>IF(NOT(AND($A159&lt;&gt;"",OR($G159="",$G159="Active"))),"",IF($L159&lt;&gt;"",IF($L159=$M159,"Booking",INDEX($N$4:$U$4,MATCH($L159,$N159:$U159,0))),IF(COUNTIF($N159:$U159,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N159:$U159)=0,"All done",IF(MAX($M159:$U159)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A159&lt;&gt;"",OR($G159="",$G159="Active"))),"",IF($L159&lt;&gt;"",IF($L159=$M159,"Booking",INDEX($N$4:$U$4,MATCH($L159,$N159:$U159,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M159:$U159)+($M159:$U159="DNA")),$M159:$U159),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M159:$U159)+($M159:$U159="DNA")),$M159:$U159),"")),IF(ISNUMBER($U159),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L159" s="33">
@@ -8414,7 +8425,7 @@
         <v/>
       </c>
       <c r="I160" s="32">
-        <f>IF(NOT(AND($A160&lt;&gt;"",OR($G160="",$G160="Active"))),"",IF(AND(MAX($M160:$U160)&gt;0,MAX($M160:$U160)&lt;TODAY(),COUNTBLANK($N160:$U160)&gt;0,COUNTIF($N160:$U160,"DNA")=0),1,0)+COUNTIF($N160:$U160,"DNA")+COUNTIF($V160:$Z160,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A160&lt;&gt;"",OR($G160="",$G160="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M160:$U160)+($M160:$U160="DNA")),$M160:$U160),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M160:$U160)+($M160:$U160="DNA")),$M160:$U160),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M160:$U160)+($M160:$U160="DNA")),$M160:$U160),"")&lt;TODAY())),1,0)+COUNTIF($V160:$Z160,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J160" s="32">
@@ -8422,7 +8433,7 @@
         <v/>
       </c>
       <c r="K160" s="32">
-        <f>IF(NOT(AND($A160&lt;&gt;"",OR($G160="",$G160="Active"))),"",IF($L160&lt;&gt;"",IF($L160=$M160,"Booking",INDEX($N$4:$U$4,MATCH($L160,$N160:$U160,0))),IF(COUNTIF($N160:$U160,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N160:$U160)=0,"All done",IF(MAX($M160:$U160)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A160&lt;&gt;"",OR($G160="",$G160="Active"))),"",IF($L160&lt;&gt;"",IF($L160=$M160,"Booking",INDEX($N$4:$U$4,MATCH($L160,$N160:$U160,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M160:$U160)+($M160:$U160="DNA")),$M160:$U160),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M160:$U160)+($M160:$U160="DNA")),$M160:$U160),"")),IF(ISNUMBER($U160),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L160" s="33">
@@ -8460,7 +8471,7 @@
         <v/>
       </c>
       <c r="I161" s="32">
-        <f>IF(NOT(AND($A161&lt;&gt;"",OR($G161="",$G161="Active"))),"",IF(AND(MAX($M161:$U161)&gt;0,MAX($M161:$U161)&lt;TODAY(),COUNTBLANK($N161:$U161)&gt;0,COUNTIF($N161:$U161,"DNA")=0),1,0)+COUNTIF($N161:$U161,"DNA")+COUNTIF($V161:$Z161,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A161&lt;&gt;"",OR($G161="",$G161="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M161:$U161)+($M161:$U161="DNA")),$M161:$U161),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M161:$U161)+($M161:$U161="DNA")),$M161:$U161),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M161:$U161)+($M161:$U161="DNA")),$M161:$U161),"")&lt;TODAY())),1,0)+COUNTIF($V161:$Z161,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J161" s="32">
@@ -8468,7 +8479,7 @@
         <v/>
       </c>
       <c r="K161" s="32">
-        <f>IF(NOT(AND($A161&lt;&gt;"",OR($G161="",$G161="Active"))),"",IF($L161&lt;&gt;"",IF($L161=$M161,"Booking",INDEX($N$4:$U$4,MATCH($L161,$N161:$U161,0))),IF(COUNTIF($N161:$U161,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N161:$U161)=0,"All done",IF(MAX($M161:$U161)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A161&lt;&gt;"",OR($G161="",$G161="Active"))),"",IF($L161&lt;&gt;"",IF($L161=$M161,"Booking",INDEX($N$4:$U$4,MATCH($L161,$N161:$U161,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M161:$U161)+($M161:$U161="DNA")),$M161:$U161),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M161:$U161)+($M161:$U161="DNA")),$M161:$U161),"")),IF(ISNUMBER($U161),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L161" s="33">
@@ -8506,7 +8517,7 @@
         <v/>
       </c>
       <c r="I162" s="32">
-        <f>IF(NOT(AND($A162&lt;&gt;"",OR($G162="",$G162="Active"))),"",IF(AND(MAX($M162:$U162)&gt;0,MAX($M162:$U162)&lt;TODAY(),COUNTBLANK($N162:$U162)&gt;0,COUNTIF($N162:$U162,"DNA")=0),1,0)+COUNTIF($N162:$U162,"DNA")+COUNTIF($V162:$Z162,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A162&lt;&gt;"",OR($G162="",$G162="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M162:$U162)+($M162:$U162="DNA")),$M162:$U162),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M162:$U162)+($M162:$U162="DNA")),$M162:$U162),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M162:$U162)+($M162:$U162="DNA")),$M162:$U162),"")&lt;TODAY())),1,0)+COUNTIF($V162:$Z162,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J162" s="32">
@@ -8514,7 +8525,7 @@
         <v/>
       </c>
       <c r="K162" s="32">
-        <f>IF(NOT(AND($A162&lt;&gt;"",OR($G162="",$G162="Active"))),"",IF($L162&lt;&gt;"",IF($L162=$M162,"Booking",INDEX($N$4:$U$4,MATCH($L162,$N162:$U162,0))),IF(COUNTIF($N162:$U162,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N162:$U162)=0,"All done",IF(MAX($M162:$U162)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A162&lt;&gt;"",OR($G162="",$G162="Active"))),"",IF($L162&lt;&gt;"",IF($L162=$M162,"Booking",INDEX($N$4:$U$4,MATCH($L162,$N162:$U162,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M162:$U162)+($M162:$U162="DNA")),$M162:$U162),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M162:$U162)+($M162:$U162="DNA")),$M162:$U162),"")),IF(ISNUMBER($U162),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L162" s="33">
@@ -8552,7 +8563,7 @@
         <v/>
       </c>
       <c r="I163" s="32">
-        <f>IF(NOT(AND($A163&lt;&gt;"",OR($G163="",$G163="Active"))),"",IF(AND(MAX($M163:$U163)&gt;0,MAX($M163:$U163)&lt;TODAY(),COUNTBLANK($N163:$U163)&gt;0,COUNTIF($N163:$U163,"DNA")=0),1,0)+COUNTIF($N163:$U163,"DNA")+COUNTIF($V163:$Z163,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A163&lt;&gt;"",OR($G163="",$G163="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M163:$U163)+($M163:$U163="DNA")),$M163:$U163),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M163:$U163)+($M163:$U163="DNA")),$M163:$U163),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M163:$U163)+($M163:$U163="DNA")),$M163:$U163),"")&lt;TODAY())),1,0)+COUNTIF($V163:$Z163,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J163" s="32">
@@ -8560,7 +8571,7 @@
         <v/>
       </c>
       <c r="K163" s="32">
-        <f>IF(NOT(AND($A163&lt;&gt;"",OR($G163="",$G163="Active"))),"",IF($L163&lt;&gt;"",IF($L163=$M163,"Booking",INDEX($N$4:$U$4,MATCH($L163,$N163:$U163,0))),IF(COUNTIF($N163:$U163,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N163:$U163)=0,"All done",IF(MAX($M163:$U163)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A163&lt;&gt;"",OR($G163="",$G163="Active"))),"",IF($L163&lt;&gt;"",IF($L163=$M163,"Booking",INDEX($N$4:$U$4,MATCH($L163,$N163:$U163,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M163:$U163)+($M163:$U163="DNA")),$M163:$U163),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M163:$U163)+($M163:$U163="DNA")),$M163:$U163),"")),IF(ISNUMBER($U163),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L163" s="33">
@@ -8598,7 +8609,7 @@
         <v/>
       </c>
       <c r="I164" s="32">
-        <f>IF(NOT(AND($A164&lt;&gt;"",OR($G164="",$G164="Active"))),"",IF(AND(MAX($M164:$U164)&gt;0,MAX($M164:$U164)&lt;TODAY(),COUNTBLANK($N164:$U164)&gt;0,COUNTIF($N164:$U164,"DNA")=0),1,0)+COUNTIF($N164:$U164,"DNA")+COUNTIF($V164:$Z164,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A164&lt;&gt;"",OR($G164="",$G164="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M164:$U164)+($M164:$U164="DNA")),$M164:$U164),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M164:$U164)+($M164:$U164="DNA")),$M164:$U164),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M164:$U164)+($M164:$U164="DNA")),$M164:$U164),"")&lt;TODAY())),1,0)+COUNTIF($V164:$Z164,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J164" s="32">
@@ -8606,7 +8617,7 @@
         <v/>
       </c>
       <c r="K164" s="32">
-        <f>IF(NOT(AND($A164&lt;&gt;"",OR($G164="",$G164="Active"))),"",IF($L164&lt;&gt;"",IF($L164=$M164,"Booking",INDEX($N$4:$U$4,MATCH($L164,$N164:$U164,0))),IF(COUNTIF($N164:$U164,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N164:$U164)=0,"All done",IF(MAX($M164:$U164)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A164&lt;&gt;"",OR($G164="",$G164="Active"))),"",IF($L164&lt;&gt;"",IF($L164=$M164,"Booking",INDEX($N$4:$U$4,MATCH($L164,$N164:$U164,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M164:$U164)+($M164:$U164="DNA")),$M164:$U164),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M164:$U164)+($M164:$U164="DNA")),$M164:$U164),"")),IF(ISNUMBER($U164),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L164" s="33">
@@ -8644,7 +8655,7 @@
         <v/>
       </c>
       <c r="I165" s="32">
-        <f>IF(NOT(AND($A165&lt;&gt;"",OR($G165="",$G165="Active"))),"",IF(AND(MAX($M165:$U165)&gt;0,MAX($M165:$U165)&lt;TODAY(),COUNTBLANK($N165:$U165)&gt;0,COUNTIF($N165:$U165,"DNA")=0),1,0)+COUNTIF($N165:$U165,"DNA")+COUNTIF($V165:$Z165,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A165&lt;&gt;"",OR($G165="",$G165="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M165:$U165)+($M165:$U165="DNA")),$M165:$U165),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M165:$U165)+($M165:$U165="DNA")),$M165:$U165),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M165:$U165)+($M165:$U165="DNA")),$M165:$U165),"")&lt;TODAY())),1,0)+COUNTIF($V165:$Z165,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J165" s="32">
@@ -8652,7 +8663,7 @@
         <v/>
       </c>
       <c r="K165" s="32">
-        <f>IF(NOT(AND($A165&lt;&gt;"",OR($G165="",$G165="Active"))),"",IF($L165&lt;&gt;"",IF($L165=$M165,"Booking",INDEX($N$4:$U$4,MATCH($L165,$N165:$U165,0))),IF(COUNTIF($N165:$U165,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N165:$U165)=0,"All done",IF(MAX($M165:$U165)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A165&lt;&gt;"",OR($G165="",$G165="Active"))),"",IF($L165&lt;&gt;"",IF($L165=$M165,"Booking",INDEX($N$4:$U$4,MATCH($L165,$N165:$U165,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M165:$U165)+($M165:$U165="DNA")),$M165:$U165),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M165:$U165)+($M165:$U165="DNA")),$M165:$U165),"")),IF(ISNUMBER($U165),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L165" s="33">
@@ -8690,7 +8701,7 @@
         <v/>
       </c>
       <c r="I166" s="32">
-        <f>IF(NOT(AND($A166&lt;&gt;"",OR($G166="",$G166="Active"))),"",IF(AND(MAX($M166:$U166)&gt;0,MAX($M166:$U166)&lt;TODAY(),COUNTBLANK($N166:$U166)&gt;0,COUNTIF($N166:$U166,"DNA")=0),1,0)+COUNTIF($N166:$U166,"DNA")+COUNTIF($V166:$Z166,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A166&lt;&gt;"",OR($G166="",$G166="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M166:$U166)+($M166:$U166="DNA")),$M166:$U166),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M166:$U166)+($M166:$U166="DNA")),$M166:$U166),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M166:$U166)+($M166:$U166="DNA")),$M166:$U166),"")&lt;TODAY())),1,0)+COUNTIF($V166:$Z166,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J166" s="32">
@@ -8698,7 +8709,7 @@
         <v/>
       </c>
       <c r="K166" s="32">
-        <f>IF(NOT(AND($A166&lt;&gt;"",OR($G166="",$G166="Active"))),"",IF($L166&lt;&gt;"",IF($L166=$M166,"Booking",INDEX($N$4:$U$4,MATCH($L166,$N166:$U166,0))),IF(COUNTIF($N166:$U166,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N166:$U166)=0,"All done",IF(MAX($M166:$U166)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A166&lt;&gt;"",OR($G166="",$G166="Active"))),"",IF($L166&lt;&gt;"",IF($L166=$M166,"Booking",INDEX($N$4:$U$4,MATCH($L166,$N166:$U166,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M166:$U166)+($M166:$U166="DNA")),$M166:$U166),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M166:$U166)+($M166:$U166="DNA")),$M166:$U166),"")),IF(ISNUMBER($U166),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L166" s="33">
@@ -8736,7 +8747,7 @@
         <v/>
       </c>
       <c r="I167" s="32">
-        <f>IF(NOT(AND($A167&lt;&gt;"",OR($G167="",$G167="Active"))),"",IF(AND(MAX($M167:$U167)&gt;0,MAX($M167:$U167)&lt;TODAY(),COUNTBLANK($N167:$U167)&gt;0,COUNTIF($N167:$U167,"DNA")=0),1,0)+COUNTIF($N167:$U167,"DNA")+COUNTIF($V167:$Z167,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A167&lt;&gt;"",OR($G167="",$G167="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M167:$U167)+($M167:$U167="DNA")),$M167:$U167),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M167:$U167)+($M167:$U167="DNA")),$M167:$U167),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M167:$U167)+($M167:$U167="DNA")),$M167:$U167),"")&lt;TODAY())),1,0)+COUNTIF($V167:$Z167,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J167" s="32">
@@ -8744,7 +8755,7 @@
         <v/>
       </c>
       <c r="K167" s="32">
-        <f>IF(NOT(AND($A167&lt;&gt;"",OR($G167="",$G167="Active"))),"",IF($L167&lt;&gt;"",IF($L167=$M167,"Booking",INDEX($N$4:$U$4,MATCH($L167,$N167:$U167,0))),IF(COUNTIF($N167:$U167,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N167:$U167)=0,"All done",IF(MAX($M167:$U167)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A167&lt;&gt;"",OR($G167="",$G167="Active"))),"",IF($L167&lt;&gt;"",IF($L167=$M167,"Booking",INDEX($N$4:$U$4,MATCH($L167,$N167:$U167,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M167:$U167)+($M167:$U167="DNA")),$M167:$U167),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M167:$U167)+($M167:$U167="DNA")),$M167:$U167),"")),IF(ISNUMBER($U167),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L167" s="33">
@@ -8782,7 +8793,7 @@
         <v/>
       </c>
       <c r="I168" s="32">
-        <f>IF(NOT(AND($A168&lt;&gt;"",OR($G168="",$G168="Active"))),"",IF(AND(MAX($M168:$U168)&gt;0,MAX($M168:$U168)&lt;TODAY(),COUNTBLANK($N168:$U168)&gt;0,COUNTIF($N168:$U168,"DNA")=0),1,0)+COUNTIF($N168:$U168,"DNA")+COUNTIF($V168:$Z168,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A168&lt;&gt;"",OR($G168="",$G168="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M168:$U168)+($M168:$U168="DNA")),$M168:$U168),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M168:$U168)+($M168:$U168="DNA")),$M168:$U168),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M168:$U168)+($M168:$U168="DNA")),$M168:$U168),"")&lt;TODAY())),1,0)+COUNTIF($V168:$Z168,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J168" s="32">
@@ -8790,7 +8801,7 @@
         <v/>
       </c>
       <c r="K168" s="32">
-        <f>IF(NOT(AND($A168&lt;&gt;"",OR($G168="",$G168="Active"))),"",IF($L168&lt;&gt;"",IF($L168=$M168,"Booking",INDEX($N$4:$U$4,MATCH($L168,$N168:$U168,0))),IF(COUNTIF($N168:$U168,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N168:$U168)=0,"All done",IF(MAX($M168:$U168)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A168&lt;&gt;"",OR($G168="",$G168="Active"))),"",IF($L168&lt;&gt;"",IF($L168=$M168,"Booking",INDEX($N$4:$U$4,MATCH($L168,$N168:$U168,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M168:$U168)+($M168:$U168="DNA")),$M168:$U168),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M168:$U168)+($M168:$U168="DNA")),$M168:$U168),"")),IF(ISNUMBER($U168),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L168" s="33">
@@ -8828,7 +8839,7 @@
         <v/>
       </c>
       <c r="I169" s="32">
-        <f>IF(NOT(AND($A169&lt;&gt;"",OR($G169="",$G169="Active"))),"",IF(AND(MAX($M169:$U169)&gt;0,MAX($M169:$U169)&lt;TODAY(),COUNTBLANK($N169:$U169)&gt;0,COUNTIF($N169:$U169,"DNA")=0),1,0)+COUNTIF($N169:$U169,"DNA")+COUNTIF($V169:$Z169,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A169&lt;&gt;"",OR($G169="",$G169="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M169:$U169)+($M169:$U169="DNA")),$M169:$U169),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M169:$U169)+($M169:$U169="DNA")),$M169:$U169),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M169:$U169)+($M169:$U169="DNA")),$M169:$U169),"")&lt;TODAY())),1,0)+COUNTIF($V169:$Z169,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J169" s="32">
@@ -8836,7 +8847,7 @@
         <v/>
       </c>
       <c r="K169" s="32">
-        <f>IF(NOT(AND($A169&lt;&gt;"",OR($G169="",$G169="Active"))),"",IF($L169&lt;&gt;"",IF($L169=$M169,"Booking",INDEX($N$4:$U$4,MATCH($L169,$N169:$U169,0))),IF(COUNTIF($N169:$U169,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N169:$U169)=0,"All done",IF(MAX($M169:$U169)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A169&lt;&gt;"",OR($G169="",$G169="Active"))),"",IF($L169&lt;&gt;"",IF($L169=$M169,"Booking",INDEX($N$4:$U$4,MATCH($L169,$N169:$U169,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M169:$U169)+($M169:$U169="DNA")),$M169:$U169),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M169:$U169)+($M169:$U169="DNA")),$M169:$U169),"")),IF(ISNUMBER($U169),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L169" s="33">
@@ -8874,7 +8885,7 @@
         <v/>
       </c>
       <c r="I170" s="32">
-        <f>IF(NOT(AND($A170&lt;&gt;"",OR($G170="",$G170="Active"))),"",IF(AND(MAX($M170:$U170)&gt;0,MAX($M170:$U170)&lt;TODAY(),COUNTBLANK($N170:$U170)&gt;0,COUNTIF($N170:$U170,"DNA")=0),1,0)+COUNTIF($N170:$U170,"DNA")+COUNTIF($V170:$Z170,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A170&lt;&gt;"",OR($G170="",$G170="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M170:$U170)+($M170:$U170="DNA")),$M170:$U170),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M170:$U170)+($M170:$U170="DNA")),$M170:$U170),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M170:$U170)+($M170:$U170="DNA")),$M170:$U170),"")&lt;TODAY())),1,0)+COUNTIF($V170:$Z170,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J170" s="32">
@@ -8882,7 +8893,7 @@
         <v/>
       </c>
       <c r="K170" s="32">
-        <f>IF(NOT(AND($A170&lt;&gt;"",OR($G170="",$G170="Active"))),"",IF($L170&lt;&gt;"",IF($L170=$M170,"Booking",INDEX($N$4:$U$4,MATCH($L170,$N170:$U170,0))),IF(COUNTIF($N170:$U170,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N170:$U170)=0,"All done",IF(MAX($M170:$U170)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A170&lt;&gt;"",OR($G170="",$G170="Active"))),"",IF($L170&lt;&gt;"",IF($L170=$M170,"Booking",INDEX($N$4:$U$4,MATCH($L170,$N170:$U170,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M170:$U170)+($M170:$U170="DNA")),$M170:$U170),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M170:$U170)+($M170:$U170="DNA")),$M170:$U170),"")),IF(ISNUMBER($U170),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L170" s="33">
@@ -8920,7 +8931,7 @@
         <v/>
       </c>
       <c r="I171" s="32">
-        <f>IF(NOT(AND($A171&lt;&gt;"",OR($G171="",$G171="Active"))),"",IF(AND(MAX($M171:$U171)&gt;0,MAX($M171:$U171)&lt;TODAY(),COUNTBLANK($N171:$U171)&gt;0,COUNTIF($N171:$U171,"DNA")=0),1,0)+COUNTIF($N171:$U171,"DNA")+COUNTIF($V171:$Z171,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A171&lt;&gt;"",OR($G171="",$G171="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M171:$U171)+($M171:$U171="DNA")),$M171:$U171),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M171:$U171)+($M171:$U171="DNA")),$M171:$U171),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M171:$U171)+($M171:$U171="DNA")),$M171:$U171),"")&lt;TODAY())),1,0)+COUNTIF($V171:$Z171,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J171" s="32">
@@ -8928,7 +8939,7 @@
         <v/>
       </c>
       <c r="K171" s="32">
-        <f>IF(NOT(AND($A171&lt;&gt;"",OR($G171="",$G171="Active"))),"",IF($L171&lt;&gt;"",IF($L171=$M171,"Booking",INDEX($N$4:$U$4,MATCH($L171,$N171:$U171,0))),IF(COUNTIF($N171:$U171,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N171:$U171)=0,"All done",IF(MAX($M171:$U171)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A171&lt;&gt;"",OR($G171="",$G171="Active"))),"",IF($L171&lt;&gt;"",IF($L171=$M171,"Booking",INDEX($N$4:$U$4,MATCH($L171,$N171:$U171,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M171:$U171)+($M171:$U171="DNA")),$M171:$U171),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M171:$U171)+($M171:$U171="DNA")),$M171:$U171),"")),IF(ISNUMBER($U171),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L171" s="33">
@@ -8966,7 +8977,7 @@
         <v/>
       </c>
       <c r="I172" s="32">
-        <f>IF(NOT(AND($A172&lt;&gt;"",OR($G172="",$G172="Active"))),"",IF(AND(MAX($M172:$U172)&gt;0,MAX($M172:$U172)&lt;TODAY(),COUNTBLANK($N172:$U172)&gt;0,COUNTIF($N172:$U172,"DNA")=0),1,0)+COUNTIF($N172:$U172,"DNA")+COUNTIF($V172:$Z172,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A172&lt;&gt;"",OR($G172="",$G172="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M172:$U172)+($M172:$U172="DNA")),$M172:$U172),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M172:$U172)+($M172:$U172="DNA")),$M172:$U172),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M172:$U172)+($M172:$U172="DNA")),$M172:$U172),"")&lt;TODAY())),1,0)+COUNTIF($V172:$Z172,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J172" s="32">
@@ -8974,7 +8985,7 @@
         <v/>
       </c>
       <c r="K172" s="32">
-        <f>IF(NOT(AND($A172&lt;&gt;"",OR($G172="",$G172="Active"))),"",IF($L172&lt;&gt;"",IF($L172=$M172,"Booking",INDEX($N$4:$U$4,MATCH($L172,$N172:$U172,0))),IF(COUNTIF($N172:$U172,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N172:$U172)=0,"All done",IF(MAX($M172:$U172)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A172&lt;&gt;"",OR($G172="",$G172="Active"))),"",IF($L172&lt;&gt;"",IF($L172=$M172,"Booking",INDEX($N$4:$U$4,MATCH($L172,$N172:$U172,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M172:$U172)+($M172:$U172="DNA")),$M172:$U172),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M172:$U172)+($M172:$U172="DNA")),$M172:$U172),"")),IF(ISNUMBER($U172),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L172" s="33">
@@ -9012,7 +9023,7 @@
         <v/>
       </c>
       <c r="I173" s="32">
-        <f>IF(NOT(AND($A173&lt;&gt;"",OR($G173="",$G173="Active"))),"",IF(AND(MAX($M173:$U173)&gt;0,MAX($M173:$U173)&lt;TODAY(),COUNTBLANK($N173:$U173)&gt;0,COUNTIF($N173:$U173,"DNA")=0),1,0)+COUNTIF($N173:$U173,"DNA")+COUNTIF($V173:$Z173,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A173&lt;&gt;"",OR($G173="",$G173="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M173:$U173)+($M173:$U173="DNA")),$M173:$U173),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M173:$U173)+($M173:$U173="DNA")),$M173:$U173),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M173:$U173)+($M173:$U173="DNA")),$M173:$U173),"")&lt;TODAY())),1,0)+COUNTIF($V173:$Z173,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J173" s="32">
@@ -9020,7 +9031,7 @@
         <v/>
       </c>
       <c r="K173" s="32">
-        <f>IF(NOT(AND($A173&lt;&gt;"",OR($G173="",$G173="Active"))),"",IF($L173&lt;&gt;"",IF($L173=$M173,"Booking",INDEX($N$4:$U$4,MATCH($L173,$N173:$U173,0))),IF(COUNTIF($N173:$U173,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N173:$U173)=0,"All done",IF(MAX($M173:$U173)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A173&lt;&gt;"",OR($G173="",$G173="Active"))),"",IF($L173&lt;&gt;"",IF($L173=$M173,"Booking",INDEX($N$4:$U$4,MATCH($L173,$N173:$U173,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M173:$U173)+($M173:$U173="DNA")),$M173:$U173),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M173:$U173)+($M173:$U173="DNA")),$M173:$U173),"")),IF(ISNUMBER($U173),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L173" s="33">
@@ -9058,7 +9069,7 @@
         <v/>
       </c>
       <c r="I174" s="32">
-        <f>IF(NOT(AND($A174&lt;&gt;"",OR($G174="",$G174="Active"))),"",IF(AND(MAX($M174:$U174)&gt;0,MAX($M174:$U174)&lt;TODAY(),COUNTBLANK($N174:$U174)&gt;0,COUNTIF($N174:$U174,"DNA")=0),1,0)+COUNTIF($N174:$U174,"DNA")+COUNTIF($V174:$Z174,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A174&lt;&gt;"",OR($G174="",$G174="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M174:$U174)+($M174:$U174="DNA")),$M174:$U174),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M174:$U174)+($M174:$U174="DNA")),$M174:$U174),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M174:$U174)+($M174:$U174="DNA")),$M174:$U174),"")&lt;TODAY())),1,0)+COUNTIF($V174:$Z174,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J174" s="32">
@@ -9066,7 +9077,7 @@
         <v/>
       </c>
       <c r="K174" s="32">
-        <f>IF(NOT(AND($A174&lt;&gt;"",OR($G174="",$G174="Active"))),"",IF($L174&lt;&gt;"",IF($L174=$M174,"Booking",INDEX($N$4:$U$4,MATCH($L174,$N174:$U174,0))),IF(COUNTIF($N174:$U174,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N174:$U174)=0,"All done",IF(MAX($M174:$U174)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A174&lt;&gt;"",OR($G174="",$G174="Active"))),"",IF($L174&lt;&gt;"",IF($L174=$M174,"Booking",INDEX($N$4:$U$4,MATCH($L174,$N174:$U174,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M174:$U174)+($M174:$U174="DNA")),$M174:$U174),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M174:$U174)+($M174:$U174="DNA")),$M174:$U174),"")),IF(ISNUMBER($U174),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L174" s="33">
@@ -9104,7 +9115,7 @@
         <v/>
       </c>
       <c r="I175" s="32">
-        <f>IF(NOT(AND($A175&lt;&gt;"",OR($G175="",$G175="Active"))),"",IF(AND(MAX($M175:$U175)&gt;0,MAX($M175:$U175)&lt;TODAY(),COUNTBLANK($N175:$U175)&gt;0,COUNTIF($N175:$U175,"DNA")=0),1,0)+COUNTIF($N175:$U175,"DNA")+COUNTIF($V175:$Z175,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A175&lt;&gt;"",OR($G175="",$G175="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M175:$U175)+($M175:$U175="DNA")),$M175:$U175),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M175:$U175)+($M175:$U175="DNA")),$M175:$U175),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M175:$U175)+($M175:$U175="DNA")),$M175:$U175),"")&lt;TODAY())),1,0)+COUNTIF($V175:$Z175,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J175" s="32">
@@ -9112,7 +9123,7 @@
         <v/>
       </c>
       <c r="K175" s="32">
-        <f>IF(NOT(AND($A175&lt;&gt;"",OR($G175="",$G175="Active"))),"",IF($L175&lt;&gt;"",IF($L175=$M175,"Booking",INDEX($N$4:$U$4,MATCH($L175,$N175:$U175,0))),IF(COUNTIF($N175:$U175,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N175:$U175)=0,"All done",IF(MAX($M175:$U175)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A175&lt;&gt;"",OR($G175="",$G175="Active"))),"",IF($L175&lt;&gt;"",IF($L175=$M175,"Booking",INDEX($N$4:$U$4,MATCH($L175,$N175:$U175,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M175:$U175)+($M175:$U175="DNA")),$M175:$U175),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M175:$U175)+($M175:$U175="DNA")),$M175:$U175),"")),IF(ISNUMBER($U175),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L175" s="33">
@@ -9150,7 +9161,7 @@
         <v/>
       </c>
       <c r="I176" s="32">
-        <f>IF(NOT(AND($A176&lt;&gt;"",OR($G176="",$G176="Active"))),"",IF(AND(MAX($M176:$U176)&gt;0,MAX($M176:$U176)&lt;TODAY(),COUNTBLANK($N176:$U176)&gt;0,COUNTIF($N176:$U176,"DNA")=0),1,0)+COUNTIF($N176:$U176,"DNA")+COUNTIF($V176:$Z176,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A176&lt;&gt;"",OR($G176="",$G176="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M176:$U176)+($M176:$U176="DNA")),$M176:$U176),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M176:$U176)+($M176:$U176="DNA")),$M176:$U176),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M176:$U176)+($M176:$U176="DNA")),$M176:$U176),"")&lt;TODAY())),1,0)+COUNTIF($V176:$Z176,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J176" s="32">
@@ -9158,7 +9169,7 @@
         <v/>
       </c>
       <c r="K176" s="32">
-        <f>IF(NOT(AND($A176&lt;&gt;"",OR($G176="",$G176="Active"))),"",IF($L176&lt;&gt;"",IF($L176=$M176,"Booking",INDEX($N$4:$U$4,MATCH($L176,$N176:$U176,0))),IF(COUNTIF($N176:$U176,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N176:$U176)=0,"All done",IF(MAX($M176:$U176)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A176&lt;&gt;"",OR($G176="",$G176="Active"))),"",IF($L176&lt;&gt;"",IF($L176=$M176,"Booking",INDEX($N$4:$U$4,MATCH($L176,$N176:$U176,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M176:$U176)+($M176:$U176="DNA")),$M176:$U176),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M176:$U176)+($M176:$U176="DNA")),$M176:$U176),"")),IF(ISNUMBER($U176),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L176" s="33">
@@ -9196,7 +9207,7 @@
         <v/>
       </c>
       <c r="I177" s="32">
-        <f>IF(NOT(AND($A177&lt;&gt;"",OR($G177="",$G177="Active"))),"",IF(AND(MAX($M177:$U177)&gt;0,MAX($M177:$U177)&lt;TODAY(),COUNTBLANK($N177:$U177)&gt;0,COUNTIF($N177:$U177,"DNA")=0),1,0)+COUNTIF($N177:$U177,"DNA")+COUNTIF($V177:$Z177,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A177&lt;&gt;"",OR($G177="",$G177="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M177:$U177)+($M177:$U177="DNA")),$M177:$U177),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M177:$U177)+($M177:$U177="DNA")),$M177:$U177),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M177:$U177)+($M177:$U177="DNA")),$M177:$U177),"")&lt;TODAY())),1,0)+COUNTIF($V177:$Z177,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J177" s="32">
@@ -9204,7 +9215,7 @@
         <v/>
       </c>
       <c r="K177" s="32">
-        <f>IF(NOT(AND($A177&lt;&gt;"",OR($G177="",$G177="Active"))),"",IF($L177&lt;&gt;"",IF($L177=$M177,"Booking",INDEX($N$4:$U$4,MATCH($L177,$N177:$U177,0))),IF(COUNTIF($N177:$U177,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N177:$U177)=0,"All done",IF(MAX($M177:$U177)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A177&lt;&gt;"",OR($G177="",$G177="Active"))),"",IF($L177&lt;&gt;"",IF($L177=$M177,"Booking",INDEX($N$4:$U$4,MATCH($L177,$N177:$U177,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M177:$U177)+($M177:$U177="DNA")),$M177:$U177),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M177:$U177)+($M177:$U177="DNA")),$M177:$U177),"")),IF(ISNUMBER($U177),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L177" s="33">
@@ -9242,7 +9253,7 @@
         <v/>
       </c>
       <c r="I178" s="32">
-        <f>IF(NOT(AND($A178&lt;&gt;"",OR($G178="",$G178="Active"))),"",IF(AND(MAX($M178:$U178)&gt;0,MAX($M178:$U178)&lt;TODAY(),COUNTBLANK($N178:$U178)&gt;0,COUNTIF($N178:$U178,"DNA")=0),1,0)+COUNTIF($N178:$U178,"DNA")+COUNTIF($V178:$Z178,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A178&lt;&gt;"",OR($G178="",$G178="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M178:$U178)+($M178:$U178="DNA")),$M178:$U178),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M178:$U178)+($M178:$U178="DNA")),$M178:$U178),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M178:$U178)+($M178:$U178="DNA")),$M178:$U178),"")&lt;TODAY())),1,0)+COUNTIF($V178:$Z178,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J178" s="32">
@@ -9250,7 +9261,7 @@
         <v/>
       </c>
       <c r="K178" s="32">
-        <f>IF(NOT(AND($A178&lt;&gt;"",OR($G178="",$G178="Active"))),"",IF($L178&lt;&gt;"",IF($L178=$M178,"Booking",INDEX($N$4:$U$4,MATCH($L178,$N178:$U178,0))),IF(COUNTIF($N178:$U178,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N178:$U178)=0,"All done",IF(MAX($M178:$U178)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A178&lt;&gt;"",OR($G178="",$G178="Active"))),"",IF($L178&lt;&gt;"",IF($L178=$M178,"Booking",INDEX($N$4:$U$4,MATCH($L178,$N178:$U178,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M178:$U178)+($M178:$U178="DNA")),$M178:$U178),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M178:$U178)+($M178:$U178="DNA")),$M178:$U178),"")),IF(ISNUMBER($U178),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L178" s="33">
@@ -9288,7 +9299,7 @@
         <v/>
       </c>
       <c r="I179" s="32">
-        <f>IF(NOT(AND($A179&lt;&gt;"",OR($G179="",$G179="Active"))),"",IF(AND(MAX($M179:$U179)&gt;0,MAX($M179:$U179)&lt;TODAY(),COUNTBLANK($N179:$U179)&gt;0,COUNTIF($N179:$U179,"DNA")=0),1,0)+COUNTIF($N179:$U179,"DNA")+COUNTIF($V179:$Z179,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A179&lt;&gt;"",OR($G179="",$G179="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M179:$U179)+($M179:$U179="DNA")),$M179:$U179),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M179:$U179)+($M179:$U179="DNA")),$M179:$U179),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M179:$U179)+($M179:$U179="DNA")),$M179:$U179),"")&lt;TODAY())),1,0)+COUNTIF($V179:$Z179,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J179" s="32">
@@ -9296,7 +9307,7 @@
         <v/>
       </c>
       <c r="K179" s="32">
-        <f>IF(NOT(AND($A179&lt;&gt;"",OR($G179="",$G179="Active"))),"",IF($L179&lt;&gt;"",IF($L179=$M179,"Booking",INDEX($N$4:$U$4,MATCH($L179,$N179:$U179,0))),IF(COUNTIF($N179:$U179,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N179:$U179)=0,"All done",IF(MAX($M179:$U179)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A179&lt;&gt;"",OR($G179="",$G179="Active"))),"",IF($L179&lt;&gt;"",IF($L179=$M179,"Booking",INDEX($N$4:$U$4,MATCH($L179,$N179:$U179,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M179:$U179)+($M179:$U179="DNA")),$M179:$U179),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M179:$U179)+($M179:$U179="DNA")),$M179:$U179),"")),IF(ISNUMBER($U179),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L179" s="33">
@@ -9334,7 +9345,7 @@
         <v/>
       </c>
       <c r="I180" s="32">
-        <f>IF(NOT(AND($A180&lt;&gt;"",OR($G180="",$G180="Active"))),"",IF(AND(MAX($M180:$U180)&gt;0,MAX($M180:$U180)&lt;TODAY(),COUNTBLANK($N180:$U180)&gt;0,COUNTIF($N180:$U180,"DNA")=0),1,0)+COUNTIF($N180:$U180,"DNA")+COUNTIF($V180:$Z180,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A180&lt;&gt;"",OR($G180="",$G180="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M180:$U180)+($M180:$U180="DNA")),$M180:$U180),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M180:$U180)+($M180:$U180="DNA")),$M180:$U180),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M180:$U180)+($M180:$U180="DNA")),$M180:$U180),"")&lt;TODAY())),1,0)+COUNTIF($V180:$Z180,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J180" s="32">
@@ -9342,7 +9353,7 @@
         <v/>
       </c>
       <c r="K180" s="32">
-        <f>IF(NOT(AND($A180&lt;&gt;"",OR($G180="",$G180="Active"))),"",IF($L180&lt;&gt;"",IF($L180=$M180,"Booking",INDEX($N$4:$U$4,MATCH($L180,$N180:$U180,0))),IF(COUNTIF($N180:$U180,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N180:$U180)=0,"All done",IF(MAX($M180:$U180)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A180&lt;&gt;"",OR($G180="",$G180="Active"))),"",IF($L180&lt;&gt;"",IF($L180=$M180,"Booking",INDEX($N$4:$U$4,MATCH($L180,$N180:$U180,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M180:$U180)+($M180:$U180="DNA")),$M180:$U180),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M180:$U180)+($M180:$U180="DNA")),$M180:$U180),"")),IF(ISNUMBER($U180),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L180" s="33">
@@ -9380,7 +9391,7 @@
         <v/>
       </c>
       <c r="I181" s="32">
-        <f>IF(NOT(AND($A181&lt;&gt;"",OR($G181="",$G181="Active"))),"",IF(AND(MAX($M181:$U181)&gt;0,MAX($M181:$U181)&lt;TODAY(),COUNTBLANK($N181:$U181)&gt;0,COUNTIF($N181:$U181,"DNA")=0),1,0)+COUNTIF($N181:$U181,"DNA")+COUNTIF($V181:$Z181,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A181&lt;&gt;"",OR($G181="",$G181="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M181:$U181)+($M181:$U181="DNA")),$M181:$U181),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M181:$U181)+($M181:$U181="DNA")),$M181:$U181),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M181:$U181)+($M181:$U181="DNA")),$M181:$U181),"")&lt;TODAY())),1,0)+COUNTIF($V181:$Z181,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J181" s="32">
@@ -9388,7 +9399,7 @@
         <v/>
       </c>
       <c r="K181" s="32">
-        <f>IF(NOT(AND($A181&lt;&gt;"",OR($G181="",$G181="Active"))),"",IF($L181&lt;&gt;"",IF($L181=$M181,"Booking",INDEX($N$4:$U$4,MATCH($L181,$N181:$U181,0))),IF(COUNTIF($N181:$U181,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N181:$U181)=0,"All done",IF(MAX($M181:$U181)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A181&lt;&gt;"",OR($G181="",$G181="Active"))),"",IF($L181&lt;&gt;"",IF($L181=$M181,"Booking",INDEX($N$4:$U$4,MATCH($L181,$N181:$U181,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M181:$U181)+($M181:$U181="DNA")),$M181:$U181),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M181:$U181)+($M181:$U181="DNA")),$M181:$U181),"")),IF(ISNUMBER($U181),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L181" s="33">
@@ -9426,7 +9437,7 @@
         <v/>
       </c>
       <c r="I182" s="32">
-        <f>IF(NOT(AND($A182&lt;&gt;"",OR($G182="",$G182="Active"))),"",IF(AND(MAX($M182:$U182)&gt;0,MAX($M182:$U182)&lt;TODAY(),COUNTBLANK($N182:$U182)&gt;0,COUNTIF($N182:$U182,"DNA")=0),1,0)+COUNTIF($N182:$U182,"DNA")+COUNTIF($V182:$Z182,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A182&lt;&gt;"",OR($G182="",$G182="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M182:$U182)+($M182:$U182="DNA")),$M182:$U182),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M182:$U182)+($M182:$U182="DNA")),$M182:$U182),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M182:$U182)+($M182:$U182="DNA")),$M182:$U182),"")&lt;TODAY())),1,0)+COUNTIF($V182:$Z182,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J182" s="32">
@@ -9434,7 +9445,7 @@
         <v/>
       </c>
       <c r="K182" s="32">
-        <f>IF(NOT(AND($A182&lt;&gt;"",OR($G182="",$G182="Active"))),"",IF($L182&lt;&gt;"",IF($L182=$M182,"Booking",INDEX($N$4:$U$4,MATCH($L182,$N182:$U182,0))),IF(COUNTIF($N182:$U182,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N182:$U182)=0,"All done",IF(MAX($M182:$U182)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A182&lt;&gt;"",OR($G182="",$G182="Active"))),"",IF($L182&lt;&gt;"",IF($L182=$M182,"Booking",INDEX($N$4:$U$4,MATCH($L182,$N182:$U182,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M182:$U182)+($M182:$U182="DNA")),$M182:$U182),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M182:$U182)+($M182:$U182="DNA")),$M182:$U182),"")),IF(ISNUMBER($U182),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L182" s="33">
@@ -9472,7 +9483,7 @@
         <v/>
       </c>
       <c r="I183" s="32">
-        <f>IF(NOT(AND($A183&lt;&gt;"",OR($G183="",$G183="Active"))),"",IF(AND(MAX($M183:$U183)&gt;0,MAX($M183:$U183)&lt;TODAY(),COUNTBLANK($N183:$U183)&gt;0,COUNTIF($N183:$U183,"DNA")=0),1,0)+COUNTIF($N183:$U183,"DNA")+COUNTIF($V183:$Z183,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A183&lt;&gt;"",OR($G183="",$G183="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M183:$U183)+($M183:$U183="DNA")),$M183:$U183),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M183:$U183)+($M183:$U183="DNA")),$M183:$U183),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M183:$U183)+($M183:$U183="DNA")),$M183:$U183),"")&lt;TODAY())),1,0)+COUNTIF($V183:$Z183,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J183" s="32">
@@ -9480,7 +9491,7 @@
         <v/>
       </c>
       <c r="K183" s="32">
-        <f>IF(NOT(AND($A183&lt;&gt;"",OR($G183="",$G183="Active"))),"",IF($L183&lt;&gt;"",IF($L183=$M183,"Booking",INDEX($N$4:$U$4,MATCH($L183,$N183:$U183,0))),IF(COUNTIF($N183:$U183,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N183:$U183)=0,"All done",IF(MAX($M183:$U183)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A183&lt;&gt;"",OR($G183="",$G183="Active"))),"",IF($L183&lt;&gt;"",IF($L183=$M183,"Booking",INDEX($N$4:$U$4,MATCH($L183,$N183:$U183,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M183:$U183)+($M183:$U183="DNA")),$M183:$U183),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M183:$U183)+($M183:$U183="DNA")),$M183:$U183),"")),IF(ISNUMBER($U183),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L183" s="33">
@@ -9518,7 +9529,7 @@
         <v/>
       </c>
       <c r="I184" s="32">
-        <f>IF(NOT(AND($A184&lt;&gt;"",OR($G184="",$G184="Active"))),"",IF(AND(MAX($M184:$U184)&gt;0,MAX($M184:$U184)&lt;TODAY(),COUNTBLANK($N184:$U184)&gt;0,COUNTIF($N184:$U184,"DNA")=0),1,0)+COUNTIF($N184:$U184,"DNA")+COUNTIF($V184:$Z184,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A184&lt;&gt;"",OR($G184="",$G184="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M184:$U184)+($M184:$U184="DNA")),$M184:$U184),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M184:$U184)+($M184:$U184="DNA")),$M184:$U184),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M184:$U184)+($M184:$U184="DNA")),$M184:$U184),"")&lt;TODAY())),1,0)+COUNTIF($V184:$Z184,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J184" s="32">
@@ -9526,7 +9537,7 @@
         <v/>
       </c>
       <c r="K184" s="32">
-        <f>IF(NOT(AND($A184&lt;&gt;"",OR($G184="",$G184="Active"))),"",IF($L184&lt;&gt;"",IF($L184=$M184,"Booking",INDEX($N$4:$U$4,MATCH($L184,$N184:$U184,0))),IF(COUNTIF($N184:$U184,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N184:$U184)=0,"All done",IF(MAX($M184:$U184)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A184&lt;&gt;"",OR($G184="",$G184="Active"))),"",IF($L184&lt;&gt;"",IF($L184=$M184,"Booking",INDEX($N$4:$U$4,MATCH($L184,$N184:$U184,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M184:$U184)+($M184:$U184="DNA")),$M184:$U184),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M184:$U184)+($M184:$U184="DNA")),$M184:$U184),"")),IF(ISNUMBER($U184),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L184" s="33">
@@ -9564,7 +9575,7 @@
         <v/>
       </c>
       <c r="I185" s="32">
-        <f>IF(NOT(AND($A185&lt;&gt;"",OR($G185="",$G185="Active"))),"",IF(AND(MAX($M185:$U185)&gt;0,MAX($M185:$U185)&lt;TODAY(),COUNTBLANK($N185:$U185)&gt;0,COUNTIF($N185:$U185,"DNA")=0),1,0)+COUNTIF($N185:$U185,"DNA")+COUNTIF($V185:$Z185,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A185&lt;&gt;"",OR($G185="",$G185="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M185:$U185)+($M185:$U185="DNA")),$M185:$U185),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M185:$U185)+($M185:$U185="DNA")),$M185:$U185),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M185:$U185)+($M185:$U185="DNA")),$M185:$U185),"")&lt;TODAY())),1,0)+COUNTIF($V185:$Z185,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J185" s="32">
@@ -9572,7 +9583,7 @@
         <v/>
       </c>
       <c r="K185" s="32">
-        <f>IF(NOT(AND($A185&lt;&gt;"",OR($G185="",$G185="Active"))),"",IF($L185&lt;&gt;"",IF($L185=$M185,"Booking",INDEX($N$4:$U$4,MATCH($L185,$N185:$U185,0))),IF(COUNTIF($N185:$U185,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N185:$U185)=0,"All done",IF(MAX($M185:$U185)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A185&lt;&gt;"",OR($G185="",$G185="Active"))),"",IF($L185&lt;&gt;"",IF($L185=$M185,"Booking",INDEX($N$4:$U$4,MATCH($L185,$N185:$U185,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M185:$U185)+($M185:$U185="DNA")),$M185:$U185),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M185:$U185)+($M185:$U185="DNA")),$M185:$U185),"")),IF(ISNUMBER($U185),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L185" s="33">
@@ -9610,7 +9621,7 @@
         <v/>
       </c>
       <c r="I186" s="32">
-        <f>IF(NOT(AND($A186&lt;&gt;"",OR($G186="",$G186="Active"))),"",IF(AND(MAX($M186:$U186)&gt;0,MAX($M186:$U186)&lt;TODAY(),COUNTBLANK($N186:$U186)&gt;0,COUNTIF($N186:$U186,"DNA")=0),1,0)+COUNTIF($N186:$U186,"DNA")+COUNTIF($V186:$Z186,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A186&lt;&gt;"",OR($G186="",$G186="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M186:$U186)+($M186:$U186="DNA")),$M186:$U186),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M186:$U186)+($M186:$U186="DNA")),$M186:$U186),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M186:$U186)+($M186:$U186="DNA")),$M186:$U186),"")&lt;TODAY())),1,0)+COUNTIF($V186:$Z186,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J186" s="32">
@@ -9618,7 +9629,7 @@
         <v/>
       </c>
       <c r="K186" s="32">
-        <f>IF(NOT(AND($A186&lt;&gt;"",OR($G186="",$G186="Active"))),"",IF($L186&lt;&gt;"",IF($L186=$M186,"Booking",INDEX($N$4:$U$4,MATCH($L186,$N186:$U186,0))),IF(COUNTIF($N186:$U186,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N186:$U186)=0,"All done",IF(MAX($M186:$U186)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A186&lt;&gt;"",OR($G186="",$G186="Active"))),"",IF($L186&lt;&gt;"",IF($L186=$M186,"Booking",INDEX($N$4:$U$4,MATCH($L186,$N186:$U186,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M186:$U186)+($M186:$U186="DNA")),$M186:$U186),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M186:$U186)+($M186:$U186="DNA")),$M186:$U186),"")),IF(ISNUMBER($U186),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L186" s="33">
@@ -9656,7 +9667,7 @@
         <v/>
       </c>
       <c r="I187" s="32">
-        <f>IF(NOT(AND($A187&lt;&gt;"",OR($G187="",$G187="Active"))),"",IF(AND(MAX($M187:$U187)&gt;0,MAX($M187:$U187)&lt;TODAY(),COUNTBLANK($N187:$U187)&gt;0,COUNTIF($N187:$U187,"DNA")=0),1,0)+COUNTIF($N187:$U187,"DNA")+COUNTIF($V187:$Z187,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A187&lt;&gt;"",OR($G187="",$G187="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M187:$U187)+($M187:$U187="DNA")),$M187:$U187),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M187:$U187)+($M187:$U187="DNA")),$M187:$U187),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M187:$U187)+($M187:$U187="DNA")),$M187:$U187),"")&lt;TODAY())),1,0)+COUNTIF($V187:$Z187,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J187" s="32">
@@ -9664,7 +9675,7 @@
         <v/>
       </c>
       <c r="K187" s="32">
-        <f>IF(NOT(AND($A187&lt;&gt;"",OR($G187="",$G187="Active"))),"",IF($L187&lt;&gt;"",IF($L187=$M187,"Booking",INDEX($N$4:$U$4,MATCH($L187,$N187:$U187,0))),IF(COUNTIF($N187:$U187,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N187:$U187)=0,"All done",IF(MAX($M187:$U187)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A187&lt;&gt;"",OR($G187="",$G187="Active"))),"",IF($L187&lt;&gt;"",IF($L187=$M187,"Booking",INDEX($N$4:$U$4,MATCH($L187,$N187:$U187,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M187:$U187)+($M187:$U187="DNA")),$M187:$U187),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M187:$U187)+($M187:$U187="DNA")),$M187:$U187),"")),IF(ISNUMBER($U187),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L187" s="33">
@@ -9702,7 +9713,7 @@
         <v/>
       </c>
       <c r="I188" s="32">
-        <f>IF(NOT(AND($A188&lt;&gt;"",OR($G188="",$G188="Active"))),"",IF(AND(MAX($M188:$U188)&gt;0,MAX($M188:$U188)&lt;TODAY(),COUNTBLANK($N188:$U188)&gt;0,COUNTIF($N188:$U188,"DNA")=0),1,0)+COUNTIF($N188:$U188,"DNA")+COUNTIF($V188:$Z188,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A188&lt;&gt;"",OR($G188="",$G188="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M188:$U188)+($M188:$U188="DNA")),$M188:$U188),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M188:$U188)+($M188:$U188="DNA")),$M188:$U188),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M188:$U188)+($M188:$U188="DNA")),$M188:$U188),"")&lt;TODAY())),1,0)+COUNTIF($V188:$Z188,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J188" s="32">
@@ -9710,7 +9721,7 @@
         <v/>
       </c>
       <c r="K188" s="32">
-        <f>IF(NOT(AND($A188&lt;&gt;"",OR($G188="",$G188="Active"))),"",IF($L188&lt;&gt;"",IF($L188=$M188,"Booking",INDEX($N$4:$U$4,MATCH($L188,$N188:$U188,0))),IF(COUNTIF($N188:$U188,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N188:$U188)=0,"All done",IF(MAX($M188:$U188)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A188&lt;&gt;"",OR($G188="",$G188="Active"))),"",IF($L188&lt;&gt;"",IF($L188=$M188,"Booking",INDEX($N$4:$U$4,MATCH($L188,$N188:$U188,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M188:$U188)+($M188:$U188="DNA")),$M188:$U188),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M188:$U188)+($M188:$U188="DNA")),$M188:$U188),"")),IF(ISNUMBER($U188),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L188" s="33">
@@ -9748,7 +9759,7 @@
         <v/>
       </c>
       <c r="I189" s="32">
-        <f>IF(NOT(AND($A189&lt;&gt;"",OR($G189="",$G189="Active"))),"",IF(AND(MAX($M189:$U189)&gt;0,MAX($M189:$U189)&lt;TODAY(),COUNTBLANK($N189:$U189)&gt;0,COUNTIF($N189:$U189,"DNA")=0),1,0)+COUNTIF($N189:$U189,"DNA")+COUNTIF($V189:$Z189,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A189&lt;&gt;"",OR($G189="",$G189="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M189:$U189)+($M189:$U189="DNA")),$M189:$U189),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M189:$U189)+($M189:$U189="DNA")),$M189:$U189),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M189:$U189)+($M189:$U189="DNA")),$M189:$U189),"")&lt;TODAY())),1,0)+COUNTIF($V189:$Z189,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J189" s="32">
@@ -9756,7 +9767,7 @@
         <v/>
       </c>
       <c r="K189" s="32">
-        <f>IF(NOT(AND($A189&lt;&gt;"",OR($G189="",$G189="Active"))),"",IF($L189&lt;&gt;"",IF($L189=$M189,"Booking",INDEX($N$4:$U$4,MATCH($L189,$N189:$U189,0))),IF(COUNTIF($N189:$U189,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N189:$U189)=0,"All done",IF(MAX($M189:$U189)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A189&lt;&gt;"",OR($G189="",$G189="Active"))),"",IF($L189&lt;&gt;"",IF($L189=$M189,"Booking",INDEX($N$4:$U$4,MATCH($L189,$N189:$U189,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M189:$U189)+($M189:$U189="DNA")),$M189:$U189),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M189:$U189)+($M189:$U189="DNA")),$M189:$U189),"")),IF(ISNUMBER($U189),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L189" s="33">
@@ -9794,7 +9805,7 @@
         <v/>
       </c>
       <c r="I190" s="32">
-        <f>IF(NOT(AND($A190&lt;&gt;"",OR($G190="",$G190="Active"))),"",IF(AND(MAX($M190:$U190)&gt;0,MAX($M190:$U190)&lt;TODAY(),COUNTBLANK($N190:$U190)&gt;0,COUNTIF($N190:$U190,"DNA")=0),1,0)+COUNTIF($N190:$U190,"DNA")+COUNTIF($V190:$Z190,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A190&lt;&gt;"",OR($G190="",$G190="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M190:$U190)+($M190:$U190="DNA")),$M190:$U190),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M190:$U190)+($M190:$U190="DNA")),$M190:$U190),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M190:$U190)+($M190:$U190="DNA")),$M190:$U190),"")&lt;TODAY())),1,0)+COUNTIF($V190:$Z190,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J190" s="32">
@@ -9802,7 +9813,7 @@
         <v/>
       </c>
       <c r="K190" s="32">
-        <f>IF(NOT(AND($A190&lt;&gt;"",OR($G190="",$G190="Active"))),"",IF($L190&lt;&gt;"",IF($L190=$M190,"Booking",INDEX($N$4:$U$4,MATCH($L190,$N190:$U190,0))),IF(COUNTIF($N190:$U190,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N190:$U190)=0,"All done",IF(MAX($M190:$U190)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A190&lt;&gt;"",OR($G190="",$G190="Active"))),"",IF($L190&lt;&gt;"",IF($L190=$M190,"Booking",INDEX($N$4:$U$4,MATCH($L190,$N190:$U190,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M190:$U190)+($M190:$U190="DNA")),$M190:$U190),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M190:$U190)+($M190:$U190="DNA")),$M190:$U190),"")),IF(ISNUMBER($U190),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L190" s="33">
@@ -9840,7 +9851,7 @@
         <v/>
       </c>
       <c r="I191" s="32">
-        <f>IF(NOT(AND($A191&lt;&gt;"",OR($G191="",$G191="Active"))),"",IF(AND(MAX($M191:$U191)&gt;0,MAX($M191:$U191)&lt;TODAY(),COUNTBLANK($N191:$U191)&gt;0,COUNTIF($N191:$U191,"DNA")=0),1,0)+COUNTIF($N191:$U191,"DNA")+COUNTIF($V191:$Z191,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A191&lt;&gt;"",OR($G191="",$G191="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M191:$U191)+($M191:$U191="DNA")),$M191:$U191),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M191:$U191)+($M191:$U191="DNA")),$M191:$U191),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M191:$U191)+($M191:$U191="DNA")),$M191:$U191),"")&lt;TODAY())),1,0)+COUNTIF($V191:$Z191,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J191" s="32">
@@ -9848,7 +9859,7 @@
         <v/>
       </c>
       <c r="K191" s="32">
-        <f>IF(NOT(AND($A191&lt;&gt;"",OR($G191="",$G191="Active"))),"",IF($L191&lt;&gt;"",IF($L191=$M191,"Booking",INDEX($N$4:$U$4,MATCH($L191,$N191:$U191,0))),IF(COUNTIF($N191:$U191,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N191:$U191)=0,"All done",IF(MAX($M191:$U191)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A191&lt;&gt;"",OR($G191="",$G191="Active"))),"",IF($L191&lt;&gt;"",IF($L191=$M191,"Booking",INDEX($N$4:$U$4,MATCH($L191,$N191:$U191,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M191:$U191)+($M191:$U191="DNA")),$M191:$U191),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M191:$U191)+($M191:$U191="DNA")),$M191:$U191),"")),IF(ISNUMBER($U191),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L191" s="33">
@@ -9886,7 +9897,7 @@
         <v/>
       </c>
       <c r="I192" s="32">
-        <f>IF(NOT(AND($A192&lt;&gt;"",OR($G192="",$G192="Active"))),"",IF(AND(MAX($M192:$U192)&gt;0,MAX($M192:$U192)&lt;TODAY(),COUNTBLANK($N192:$U192)&gt;0,COUNTIF($N192:$U192,"DNA")=0),1,0)+COUNTIF($N192:$U192,"DNA")+COUNTIF($V192:$Z192,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A192&lt;&gt;"",OR($G192="",$G192="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M192:$U192)+($M192:$U192="DNA")),$M192:$U192),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M192:$U192)+($M192:$U192="DNA")),$M192:$U192),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M192:$U192)+($M192:$U192="DNA")),$M192:$U192),"")&lt;TODAY())),1,0)+COUNTIF($V192:$Z192,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J192" s="32">
@@ -9894,7 +9905,7 @@
         <v/>
       </c>
       <c r="K192" s="32">
-        <f>IF(NOT(AND($A192&lt;&gt;"",OR($G192="",$G192="Active"))),"",IF($L192&lt;&gt;"",IF($L192=$M192,"Booking",INDEX($N$4:$U$4,MATCH($L192,$N192:$U192,0))),IF(COUNTIF($N192:$U192,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N192:$U192)=0,"All done",IF(MAX($M192:$U192)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A192&lt;&gt;"",OR($G192="",$G192="Active"))),"",IF($L192&lt;&gt;"",IF($L192=$M192,"Booking",INDEX($N$4:$U$4,MATCH($L192,$N192:$U192,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M192:$U192)+($M192:$U192="DNA")),$M192:$U192),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M192:$U192)+($M192:$U192="DNA")),$M192:$U192),"")),IF(ISNUMBER($U192),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L192" s="33">
@@ -9932,7 +9943,7 @@
         <v/>
       </c>
       <c r="I193" s="32">
-        <f>IF(NOT(AND($A193&lt;&gt;"",OR($G193="",$G193="Active"))),"",IF(AND(MAX($M193:$U193)&gt;0,MAX($M193:$U193)&lt;TODAY(),COUNTBLANK($N193:$U193)&gt;0,COUNTIF($N193:$U193,"DNA")=0),1,0)+COUNTIF($N193:$U193,"DNA")+COUNTIF($V193:$Z193,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A193&lt;&gt;"",OR($G193="",$G193="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M193:$U193)+($M193:$U193="DNA")),$M193:$U193),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M193:$U193)+($M193:$U193="DNA")),$M193:$U193),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M193:$U193)+($M193:$U193="DNA")),$M193:$U193),"")&lt;TODAY())),1,0)+COUNTIF($V193:$Z193,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J193" s="32">
@@ -9940,7 +9951,7 @@
         <v/>
       </c>
       <c r="K193" s="32">
-        <f>IF(NOT(AND($A193&lt;&gt;"",OR($G193="",$G193="Active"))),"",IF($L193&lt;&gt;"",IF($L193=$M193,"Booking",INDEX($N$4:$U$4,MATCH($L193,$N193:$U193,0))),IF(COUNTIF($N193:$U193,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N193:$U193)=0,"All done",IF(MAX($M193:$U193)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A193&lt;&gt;"",OR($G193="",$G193="Active"))),"",IF($L193&lt;&gt;"",IF($L193=$M193,"Booking",INDEX($N$4:$U$4,MATCH($L193,$N193:$U193,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M193:$U193)+($M193:$U193="DNA")),$M193:$U193),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M193:$U193)+($M193:$U193="DNA")),$M193:$U193),"")),IF(ISNUMBER($U193),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L193" s="33">
@@ -9978,7 +9989,7 @@
         <v/>
       </c>
       <c r="I194" s="32">
-        <f>IF(NOT(AND($A194&lt;&gt;"",OR($G194="",$G194="Active"))),"",IF(AND(MAX($M194:$U194)&gt;0,MAX($M194:$U194)&lt;TODAY(),COUNTBLANK($N194:$U194)&gt;0,COUNTIF($N194:$U194,"DNA")=0),1,0)+COUNTIF($N194:$U194,"DNA")+COUNTIF($V194:$Z194,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A194&lt;&gt;"",OR($G194="",$G194="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M194:$U194)+($M194:$U194="DNA")),$M194:$U194),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M194:$U194)+($M194:$U194="DNA")),$M194:$U194),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M194:$U194)+($M194:$U194="DNA")),$M194:$U194),"")&lt;TODAY())),1,0)+COUNTIF($V194:$Z194,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J194" s="32">
@@ -9986,7 +9997,7 @@
         <v/>
       </c>
       <c r="K194" s="32">
-        <f>IF(NOT(AND($A194&lt;&gt;"",OR($G194="",$G194="Active"))),"",IF($L194&lt;&gt;"",IF($L194=$M194,"Booking",INDEX($N$4:$U$4,MATCH($L194,$N194:$U194,0))),IF(COUNTIF($N194:$U194,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N194:$U194)=0,"All done",IF(MAX($M194:$U194)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A194&lt;&gt;"",OR($G194="",$G194="Active"))),"",IF($L194&lt;&gt;"",IF($L194=$M194,"Booking",INDEX($N$4:$U$4,MATCH($L194,$N194:$U194,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M194:$U194)+($M194:$U194="DNA")),$M194:$U194),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M194:$U194)+($M194:$U194="DNA")),$M194:$U194),"")),IF(ISNUMBER($U194),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L194" s="33">
@@ -10024,7 +10035,7 @@
         <v/>
       </c>
       <c r="I195" s="32">
-        <f>IF(NOT(AND($A195&lt;&gt;"",OR($G195="",$G195="Active"))),"",IF(AND(MAX($M195:$U195)&gt;0,MAX($M195:$U195)&lt;TODAY(),COUNTBLANK($N195:$U195)&gt;0,COUNTIF($N195:$U195,"DNA")=0),1,0)+COUNTIF($N195:$U195,"DNA")+COUNTIF($V195:$Z195,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A195&lt;&gt;"",OR($G195="",$G195="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M195:$U195)+($M195:$U195="DNA")),$M195:$U195),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M195:$U195)+($M195:$U195="DNA")),$M195:$U195),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M195:$U195)+($M195:$U195="DNA")),$M195:$U195),"")&lt;TODAY())),1,0)+COUNTIF($V195:$Z195,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J195" s="32">
@@ -10032,7 +10043,7 @@
         <v/>
       </c>
       <c r="K195" s="32">
-        <f>IF(NOT(AND($A195&lt;&gt;"",OR($G195="",$G195="Active"))),"",IF($L195&lt;&gt;"",IF($L195=$M195,"Booking",INDEX($N$4:$U$4,MATCH($L195,$N195:$U195,0))),IF(COUNTIF($N195:$U195,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N195:$U195)=0,"All done",IF(MAX($M195:$U195)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A195&lt;&gt;"",OR($G195="",$G195="Active"))),"",IF($L195&lt;&gt;"",IF($L195=$M195,"Booking",INDEX($N$4:$U$4,MATCH($L195,$N195:$U195,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M195:$U195)+($M195:$U195="DNA")),$M195:$U195),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M195:$U195)+($M195:$U195="DNA")),$M195:$U195),"")),IF(ISNUMBER($U195),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L195" s="33">
@@ -10070,7 +10081,7 @@
         <v/>
       </c>
       <c r="I196" s="32">
-        <f>IF(NOT(AND($A196&lt;&gt;"",OR($G196="",$G196="Active"))),"",IF(AND(MAX($M196:$U196)&gt;0,MAX($M196:$U196)&lt;TODAY(),COUNTBLANK($N196:$U196)&gt;0,COUNTIF($N196:$U196,"DNA")=0),1,0)+COUNTIF($N196:$U196,"DNA")+COUNTIF($V196:$Z196,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A196&lt;&gt;"",OR($G196="",$G196="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M196:$U196)+($M196:$U196="DNA")),$M196:$U196),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M196:$U196)+($M196:$U196="DNA")),$M196:$U196),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M196:$U196)+($M196:$U196="DNA")),$M196:$U196),"")&lt;TODAY())),1,0)+COUNTIF($V196:$Z196,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J196" s="32">
@@ -10078,7 +10089,7 @@
         <v/>
       </c>
       <c r="K196" s="32">
-        <f>IF(NOT(AND($A196&lt;&gt;"",OR($G196="",$G196="Active"))),"",IF($L196&lt;&gt;"",IF($L196=$M196,"Booking",INDEX($N$4:$U$4,MATCH($L196,$N196:$U196,0))),IF(COUNTIF($N196:$U196,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N196:$U196)=0,"All done",IF(MAX($M196:$U196)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A196&lt;&gt;"",OR($G196="",$G196="Active"))),"",IF($L196&lt;&gt;"",IF($L196=$M196,"Booking",INDEX($N$4:$U$4,MATCH($L196,$N196:$U196,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M196:$U196)+($M196:$U196="DNA")),$M196:$U196),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M196:$U196)+($M196:$U196="DNA")),$M196:$U196),"")),IF(ISNUMBER($U196),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L196" s="33">
@@ -10116,7 +10127,7 @@
         <v/>
       </c>
       <c r="I197" s="32">
-        <f>IF(NOT(AND($A197&lt;&gt;"",OR($G197="",$G197="Active"))),"",IF(AND(MAX($M197:$U197)&gt;0,MAX($M197:$U197)&lt;TODAY(),COUNTBLANK($N197:$U197)&gt;0,COUNTIF($N197:$U197,"DNA")=0),1,0)+COUNTIF($N197:$U197,"DNA")+COUNTIF($V197:$Z197,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A197&lt;&gt;"",OR($G197="",$G197="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M197:$U197)+($M197:$U197="DNA")),$M197:$U197),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M197:$U197)+($M197:$U197="DNA")),$M197:$U197),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M197:$U197)+($M197:$U197="DNA")),$M197:$U197),"")&lt;TODAY())),1,0)+COUNTIF($V197:$Z197,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J197" s="32">
@@ -10124,7 +10135,7 @@
         <v/>
       </c>
       <c r="K197" s="32">
-        <f>IF(NOT(AND($A197&lt;&gt;"",OR($G197="",$G197="Active"))),"",IF($L197&lt;&gt;"",IF($L197=$M197,"Booking",INDEX($N$4:$U$4,MATCH($L197,$N197:$U197,0))),IF(COUNTIF($N197:$U197,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N197:$U197)=0,"All done",IF(MAX($M197:$U197)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A197&lt;&gt;"",OR($G197="",$G197="Active"))),"",IF($L197&lt;&gt;"",IF($L197=$M197,"Booking",INDEX($N$4:$U$4,MATCH($L197,$N197:$U197,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M197:$U197)+($M197:$U197="DNA")),$M197:$U197),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M197:$U197)+($M197:$U197="DNA")),$M197:$U197),"")),IF(ISNUMBER($U197),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L197" s="33">
@@ -10162,7 +10173,7 @@
         <v/>
       </c>
       <c r="I198" s="32">
-        <f>IF(NOT(AND($A198&lt;&gt;"",OR($G198="",$G198="Active"))),"",IF(AND(MAX($M198:$U198)&gt;0,MAX($M198:$U198)&lt;TODAY(),COUNTBLANK($N198:$U198)&gt;0,COUNTIF($N198:$U198,"DNA")=0),1,0)+COUNTIF($N198:$U198,"DNA")+COUNTIF($V198:$Z198,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A198&lt;&gt;"",OR($G198="",$G198="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M198:$U198)+($M198:$U198="DNA")),$M198:$U198),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M198:$U198)+($M198:$U198="DNA")),$M198:$U198),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M198:$U198)+($M198:$U198="DNA")),$M198:$U198),"")&lt;TODAY())),1,0)+COUNTIF($V198:$Z198,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J198" s="32">
@@ -10170,7 +10181,7 @@
         <v/>
       </c>
       <c r="K198" s="32">
-        <f>IF(NOT(AND($A198&lt;&gt;"",OR($G198="",$G198="Active"))),"",IF($L198&lt;&gt;"",IF($L198=$M198,"Booking",INDEX($N$4:$U$4,MATCH($L198,$N198:$U198,0))),IF(COUNTIF($N198:$U198,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N198:$U198)=0,"All done",IF(MAX($M198:$U198)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A198&lt;&gt;"",OR($G198="",$G198="Active"))),"",IF($L198&lt;&gt;"",IF($L198=$M198,"Booking",INDEX($N$4:$U$4,MATCH($L198,$N198:$U198,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M198:$U198)+($M198:$U198="DNA")),$M198:$U198),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M198:$U198)+($M198:$U198="DNA")),$M198:$U198),"")),IF(ISNUMBER($U198),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L198" s="33">
@@ -10208,7 +10219,7 @@
         <v/>
       </c>
       <c r="I199" s="32">
-        <f>IF(NOT(AND($A199&lt;&gt;"",OR($G199="",$G199="Active"))),"",IF(AND(MAX($M199:$U199)&gt;0,MAX($M199:$U199)&lt;TODAY(),COUNTBLANK($N199:$U199)&gt;0,COUNTIF($N199:$U199,"DNA")=0),1,0)+COUNTIF($N199:$U199,"DNA")+COUNTIF($V199:$Z199,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A199&lt;&gt;"",OR($G199="",$G199="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M199:$U199)+($M199:$U199="DNA")),$M199:$U199),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M199:$U199)+($M199:$U199="DNA")),$M199:$U199),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M199:$U199)+($M199:$U199="DNA")),$M199:$U199),"")&lt;TODAY())),1,0)+COUNTIF($V199:$Z199,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J199" s="32">
@@ -10216,7 +10227,7 @@
         <v/>
       </c>
       <c r="K199" s="32">
-        <f>IF(NOT(AND($A199&lt;&gt;"",OR($G199="",$G199="Active"))),"",IF($L199&lt;&gt;"",IF($L199=$M199,"Booking",INDEX($N$4:$U$4,MATCH($L199,$N199:$U199,0))),IF(COUNTIF($N199:$U199,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N199:$U199)=0,"All done",IF(MAX($M199:$U199)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A199&lt;&gt;"",OR($G199="",$G199="Active"))),"",IF($L199&lt;&gt;"",IF($L199=$M199,"Booking",INDEX($N$4:$U$4,MATCH($L199,$N199:$U199,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M199:$U199)+($M199:$U199="DNA")),$M199:$U199),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M199:$U199)+($M199:$U199="DNA")),$M199:$U199),"")),IF(ISNUMBER($U199),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L199" s="33">
@@ -10254,7 +10265,7 @@
         <v/>
       </c>
       <c r="I200" s="32">
-        <f>IF(NOT(AND($A200&lt;&gt;"",OR($G200="",$G200="Active"))),"",IF(AND(MAX($M200:$U200)&gt;0,MAX($M200:$U200)&lt;TODAY(),COUNTBLANK($N200:$U200)&gt;0,COUNTIF($N200:$U200,"DNA")=0),1,0)+COUNTIF($N200:$U200,"DNA")+COUNTIF($V200:$Z200,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A200&lt;&gt;"",OR($G200="",$G200="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M200:$U200)+($M200:$U200="DNA")),$M200:$U200),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M200:$U200)+($M200:$U200="DNA")),$M200:$U200),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M200:$U200)+($M200:$U200="DNA")),$M200:$U200),"")&lt;TODAY())),1,0)+COUNTIF($V200:$Z200,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J200" s="32">
@@ -10262,7 +10273,7 @@
         <v/>
       </c>
       <c r="K200" s="32">
-        <f>IF(NOT(AND($A200&lt;&gt;"",OR($G200="",$G200="Active"))),"",IF($L200&lt;&gt;"",IF($L200=$M200,"Booking",INDEX($N$4:$U$4,MATCH($L200,$N200:$U200,0))),IF(COUNTIF($N200:$U200,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N200:$U200)=0,"All done",IF(MAX($M200:$U200)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A200&lt;&gt;"",OR($G200="",$G200="Active"))),"",IF($L200&lt;&gt;"",IF($L200=$M200,"Booking",INDEX($N$4:$U$4,MATCH($L200,$N200:$U200,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M200:$U200)+($M200:$U200="DNA")),$M200:$U200),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M200:$U200)+($M200:$U200="DNA")),$M200:$U200),"")),IF(ISNUMBER($U200),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L200" s="33">
@@ -10300,7 +10311,7 @@
         <v/>
       </c>
       <c r="I201" s="32">
-        <f>IF(NOT(AND($A201&lt;&gt;"",OR($G201="",$G201="Active"))),"",IF(AND(MAX($M201:$U201)&gt;0,MAX($M201:$U201)&lt;TODAY(),COUNTBLANK($N201:$U201)&gt;0,COUNTIF($N201:$U201,"DNA")=0),1,0)+COUNTIF($N201:$U201,"DNA")+COUNTIF($V201:$Z201,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A201&lt;&gt;"",OR($G201="",$G201="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M201:$U201)+($M201:$U201="DNA")),$M201:$U201),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M201:$U201)+($M201:$U201="DNA")),$M201:$U201),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M201:$U201)+($M201:$U201="DNA")),$M201:$U201),"")&lt;TODAY())),1,0)+COUNTIF($V201:$Z201,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J201" s="32">
@@ -10308,7 +10319,7 @@
         <v/>
       </c>
       <c r="K201" s="32">
-        <f>IF(NOT(AND($A201&lt;&gt;"",OR($G201="",$G201="Active"))),"",IF($L201&lt;&gt;"",IF($L201=$M201,"Booking",INDEX($N$4:$U$4,MATCH($L201,$N201:$U201,0))),IF(COUNTIF($N201:$U201,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N201:$U201)=0,"All done",IF(MAX($M201:$U201)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A201&lt;&gt;"",OR($G201="",$G201="Active"))),"",IF($L201&lt;&gt;"",IF($L201=$M201,"Booking",INDEX($N$4:$U$4,MATCH($L201,$N201:$U201,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M201:$U201)+($M201:$U201="DNA")),$M201:$U201),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M201:$U201)+($M201:$U201="DNA")),$M201:$U201),"")),IF(ISNUMBER($U201),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L201" s="33">
@@ -10346,7 +10357,7 @@
         <v/>
       </c>
       <c r="I202" s="32">
-        <f>IF(NOT(AND($A202&lt;&gt;"",OR($G202="",$G202="Active"))),"",IF(AND(MAX($M202:$U202)&gt;0,MAX($M202:$U202)&lt;TODAY(),COUNTBLANK($N202:$U202)&gt;0,COUNTIF($N202:$U202,"DNA")=0),1,0)+COUNTIF($N202:$U202,"DNA")+COUNTIF($V202:$Z202,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A202&lt;&gt;"",OR($G202="",$G202="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M202:$U202)+($M202:$U202="DNA")),$M202:$U202),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M202:$U202)+($M202:$U202="DNA")),$M202:$U202),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M202:$U202)+($M202:$U202="DNA")),$M202:$U202),"")&lt;TODAY())),1,0)+COUNTIF($V202:$Z202,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J202" s="32">
@@ -10354,7 +10365,7 @@
         <v/>
       </c>
       <c r="K202" s="32">
-        <f>IF(NOT(AND($A202&lt;&gt;"",OR($G202="",$G202="Active"))),"",IF($L202&lt;&gt;"",IF($L202=$M202,"Booking",INDEX($N$4:$U$4,MATCH($L202,$N202:$U202,0))),IF(COUNTIF($N202:$U202,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N202:$U202)=0,"All done",IF(MAX($M202:$U202)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A202&lt;&gt;"",OR($G202="",$G202="Active"))),"",IF($L202&lt;&gt;"",IF($L202=$M202,"Booking",INDEX($N$4:$U$4,MATCH($L202,$N202:$U202,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M202:$U202)+($M202:$U202="DNA")),$M202:$U202),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M202:$U202)+($M202:$U202="DNA")),$M202:$U202),"")),IF(ISNUMBER($U202),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L202" s="33">
@@ -10392,7 +10403,7 @@
         <v/>
       </c>
       <c r="I203" s="32">
-        <f>IF(NOT(AND($A203&lt;&gt;"",OR($G203="",$G203="Active"))),"",IF(AND(MAX($M203:$U203)&gt;0,MAX($M203:$U203)&lt;TODAY(),COUNTBLANK($N203:$U203)&gt;0,COUNTIF($N203:$U203,"DNA")=0),1,0)+COUNTIF($N203:$U203,"DNA")+COUNTIF($V203:$Z203,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A203&lt;&gt;"",OR($G203="",$G203="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M203:$U203)+($M203:$U203="DNA")),$M203:$U203),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M203:$U203)+($M203:$U203="DNA")),$M203:$U203),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M203:$U203)+($M203:$U203="DNA")),$M203:$U203),"")&lt;TODAY())),1,0)+COUNTIF($V203:$Z203,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J203" s="32">
@@ -10400,7 +10411,7 @@
         <v/>
       </c>
       <c r="K203" s="32">
-        <f>IF(NOT(AND($A203&lt;&gt;"",OR($G203="",$G203="Active"))),"",IF($L203&lt;&gt;"",IF($L203=$M203,"Booking",INDEX($N$4:$U$4,MATCH($L203,$N203:$U203,0))),IF(COUNTIF($N203:$U203,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N203:$U203)=0,"All done",IF(MAX($M203:$U203)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A203&lt;&gt;"",OR($G203="",$G203="Active"))),"",IF($L203&lt;&gt;"",IF($L203=$M203,"Booking",INDEX($N$4:$U$4,MATCH($L203,$N203:$U203,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M203:$U203)+($M203:$U203="DNA")),$M203:$U203),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M203:$U203)+($M203:$U203="DNA")),$M203:$U203),"")),IF(ISNUMBER($U203),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L203" s="33">
@@ -10438,7 +10449,7 @@
         <v/>
       </c>
       <c r="I204" s="32">
-        <f>IF(NOT(AND($A204&lt;&gt;"",OR($G204="",$G204="Active"))),"",IF(AND(MAX($M204:$U204)&gt;0,MAX($M204:$U204)&lt;TODAY(),COUNTBLANK($N204:$U204)&gt;0,COUNTIF($N204:$U204,"DNA")=0),1,0)+COUNTIF($N204:$U204,"DNA")+COUNTIF($V204:$Z204,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A204&lt;&gt;"",OR($G204="",$G204="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M204:$U204)+($M204:$U204="DNA")),$M204:$U204),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M204:$U204)+($M204:$U204="DNA")),$M204:$U204),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M204:$U204)+($M204:$U204="DNA")),$M204:$U204),"")&lt;TODAY())),1,0)+COUNTIF($V204:$Z204,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J204" s="32">
@@ -10446,7 +10457,7 @@
         <v/>
       </c>
       <c r="K204" s="32">
-        <f>IF(NOT(AND($A204&lt;&gt;"",OR($G204="",$G204="Active"))),"",IF($L204&lt;&gt;"",IF($L204=$M204,"Booking",INDEX($N$4:$U$4,MATCH($L204,$N204:$U204,0))),IF(COUNTIF($N204:$U204,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N204:$U204)=0,"All done",IF(MAX($M204:$U204)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A204&lt;&gt;"",OR($G204="",$G204="Active"))),"",IF($L204&lt;&gt;"",IF($L204=$M204,"Booking",INDEX($N$4:$U$4,MATCH($L204,$N204:$U204,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M204:$U204)+($M204:$U204="DNA")),$M204:$U204),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M204:$U204)+($M204:$U204="DNA")),$M204:$U204),"")),IF(ISNUMBER($U204),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L204" s="33">
@@ -10484,7 +10495,7 @@
         <v/>
       </c>
       <c r="I205" s="32">
-        <f>IF(NOT(AND($A205&lt;&gt;"",OR($G205="",$G205="Active"))),"",IF(AND(MAX($M205:$U205)&gt;0,MAX($M205:$U205)&lt;TODAY(),COUNTBLANK($N205:$U205)&gt;0,COUNTIF($N205:$U205,"DNA")=0),1,0)+COUNTIF($N205:$U205,"DNA")+COUNTIF($V205:$Z205,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A205&lt;&gt;"",OR($G205="",$G205="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M205:$U205)+($M205:$U205="DNA")),$M205:$U205),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M205:$U205)+($M205:$U205="DNA")),$M205:$U205),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M205:$U205)+($M205:$U205="DNA")),$M205:$U205),"")&lt;TODAY())),1,0)+COUNTIF($V205:$Z205,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J205" s="32">
@@ -10492,7 +10503,7 @@
         <v/>
       </c>
       <c r="K205" s="32">
-        <f>IF(NOT(AND($A205&lt;&gt;"",OR($G205="",$G205="Active"))),"",IF($L205&lt;&gt;"",IF($L205=$M205,"Booking",INDEX($N$4:$U$4,MATCH($L205,$N205:$U205,0))),IF(COUNTIF($N205:$U205,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N205:$U205)=0,"All done",IF(MAX($M205:$U205)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A205&lt;&gt;"",OR($G205="",$G205="Active"))),"",IF($L205&lt;&gt;"",IF($L205=$M205,"Booking",INDEX($N$4:$U$4,MATCH($L205,$N205:$U205,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M205:$U205)+($M205:$U205="DNA")),$M205:$U205),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M205:$U205)+($M205:$U205="DNA")),$M205:$U205),"")),IF(ISNUMBER($U205),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L205" s="33">
@@ -10530,7 +10541,7 @@
         <v/>
       </c>
       <c r="I206" s="32">
-        <f>IF(NOT(AND($A206&lt;&gt;"",OR($G206="",$G206="Active"))),"",IF(AND(MAX($M206:$U206)&gt;0,MAX($M206:$U206)&lt;TODAY(),COUNTBLANK($N206:$U206)&gt;0,COUNTIF($N206:$U206,"DNA")=0),1,0)+COUNTIF($N206:$U206,"DNA")+COUNTIF($V206:$Z206,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A206&lt;&gt;"",OR($G206="",$G206="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M206:$U206)+($M206:$U206="DNA")),$M206:$U206),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M206:$U206)+($M206:$U206="DNA")),$M206:$U206),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M206:$U206)+($M206:$U206="DNA")),$M206:$U206),"")&lt;TODAY())),1,0)+COUNTIF($V206:$Z206,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J206" s="32">
@@ -10538,7 +10549,7 @@
         <v/>
       </c>
       <c r="K206" s="32">
-        <f>IF(NOT(AND($A206&lt;&gt;"",OR($G206="",$G206="Active"))),"",IF($L206&lt;&gt;"",IF($L206=$M206,"Booking",INDEX($N$4:$U$4,MATCH($L206,$N206:$U206,0))),IF(COUNTIF($N206:$U206,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N206:$U206)=0,"All done",IF(MAX($M206:$U206)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A206&lt;&gt;"",OR($G206="",$G206="Active"))),"",IF($L206&lt;&gt;"",IF($L206=$M206,"Booking",INDEX($N$4:$U$4,MATCH($L206,$N206:$U206,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M206:$U206)+($M206:$U206="DNA")),$M206:$U206),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M206:$U206)+($M206:$U206="DNA")),$M206:$U206),"")),IF(ISNUMBER($U206),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L206" s="33">
@@ -10576,7 +10587,7 @@
         <v/>
       </c>
       <c r="I207" s="32">
-        <f>IF(NOT(AND($A207&lt;&gt;"",OR($G207="",$G207="Active"))),"",IF(AND(MAX($M207:$U207)&gt;0,MAX($M207:$U207)&lt;TODAY(),COUNTBLANK($N207:$U207)&gt;0,COUNTIF($N207:$U207,"DNA")=0),1,0)+COUNTIF($N207:$U207,"DNA")+COUNTIF($V207:$Z207,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A207&lt;&gt;"",OR($G207="",$G207="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M207:$U207)+($M207:$U207="DNA")),$M207:$U207),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M207:$U207)+($M207:$U207="DNA")),$M207:$U207),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M207:$U207)+($M207:$U207="DNA")),$M207:$U207),"")&lt;TODAY())),1,0)+COUNTIF($V207:$Z207,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J207" s="32">
@@ -10584,7 +10595,7 @@
         <v/>
       </c>
       <c r="K207" s="32">
-        <f>IF(NOT(AND($A207&lt;&gt;"",OR($G207="",$G207="Active"))),"",IF($L207&lt;&gt;"",IF($L207=$M207,"Booking",INDEX($N$4:$U$4,MATCH($L207,$N207:$U207,0))),IF(COUNTIF($N207:$U207,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N207:$U207)=0,"All done",IF(MAX($M207:$U207)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A207&lt;&gt;"",OR($G207="",$G207="Active"))),"",IF($L207&lt;&gt;"",IF($L207=$M207,"Booking",INDEX($N$4:$U$4,MATCH($L207,$N207:$U207,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M207:$U207)+($M207:$U207="DNA")),$M207:$U207),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M207:$U207)+($M207:$U207="DNA")),$M207:$U207),"")),IF(ISNUMBER($U207),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L207" s="33">
@@ -10622,7 +10633,7 @@
         <v/>
       </c>
       <c r="I208" s="32">
-        <f>IF(NOT(AND($A208&lt;&gt;"",OR($G208="",$G208="Active"))),"",IF(AND(MAX($M208:$U208)&gt;0,MAX($M208:$U208)&lt;TODAY(),COUNTBLANK($N208:$U208)&gt;0,COUNTIF($N208:$U208,"DNA")=0),1,0)+COUNTIF($N208:$U208,"DNA")+COUNTIF($V208:$Z208,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A208&lt;&gt;"",OR($G208="",$G208="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M208:$U208)+($M208:$U208="DNA")),$M208:$U208),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M208:$U208)+($M208:$U208="DNA")),$M208:$U208),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M208:$U208)+($M208:$U208="DNA")),$M208:$U208),"")&lt;TODAY())),1,0)+COUNTIF($V208:$Z208,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J208" s="32">
@@ -10630,7 +10641,7 @@
         <v/>
       </c>
       <c r="K208" s="32">
-        <f>IF(NOT(AND($A208&lt;&gt;"",OR($G208="",$G208="Active"))),"",IF($L208&lt;&gt;"",IF($L208=$M208,"Booking",INDEX($N$4:$U$4,MATCH($L208,$N208:$U208,0))),IF(COUNTIF($N208:$U208,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N208:$U208)=0,"All done",IF(MAX($M208:$U208)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A208&lt;&gt;"",OR($G208="",$G208="Active"))),"",IF($L208&lt;&gt;"",IF($L208=$M208,"Booking",INDEX($N$4:$U$4,MATCH($L208,$N208:$U208,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M208:$U208)+($M208:$U208="DNA")),$M208:$U208),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M208:$U208)+($M208:$U208="DNA")),$M208:$U208),"")),IF(ISNUMBER($U208),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L208" s="33">
@@ -10668,7 +10679,7 @@
         <v/>
       </c>
       <c r="I209" s="32">
-        <f>IF(NOT(AND($A209&lt;&gt;"",OR($G209="",$G209="Active"))),"",IF(AND(MAX($M209:$U209)&gt;0,MAX($M209:$U209)&lt;TODAY(),COUNTBLANK($N209:$U209)&gt;0,COUNTIF($N209:$U209,"DNA")=0),1,0)+COUNTIF($N209:$U209,"DNA")+COUNTIF($V209:$Z209,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A209&lt;&gt;"",OR($G209="",$G209="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M209:$U209)+($M209:$U209="DNA")),$M209:$U209),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M209:$U209)+($M209:$U209="DNA")),$M209:$U209),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M209:$U209)+($M209:$U209="DNA")),$M209:$U209),"")&lt;TODAY())),1,0)+COUNTIF($V209:$Z209,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J209" s="32">
@@ -10676,7 +10687,7 @@
         <v/>
       </c>
       <c r="K209" s="32">
-        <f>IF(NOT(AND($A209&lt;&gt;"",OR($G209="",$G209="Active"))),"",IF($L209&lt;&gt;"",IF($L209=$M209,"Booking",INDEX($N$4:$U$4,MATCH($L209,$N209:$U209,0))),IF(COUNTIF($N209:$U209,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N209:$U209)=0,"All done",IF(MAX($M209:$U209)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A209&lt;&gt;"",OR($G209="",$G209="Active"))),"",IF($L209&lt;&gt;"",IF($L209=$M209,"Booking",INDEX($N$4:$U$4,MATCH($L209,$N209:$U209,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M209:$U209)+($M209:$U209="DNA")),$M209:$U209),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M209:$U209)+($M209:$U209="DNA")),$M209:$U209),"")),IF(ISNUMBER($U209),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L209" s="33">
@@ -10714,7 +10725,7 @@
         <v/>
       </c>
       <c r="I210" s="32">
-        <f>IF(NOT(AND($A210&lt;&gt;"",OR($G210="",$G210="Active"))),"",IF(AND(MAX($M210:$U210)&gt;0,MAX($M210:$U210)&lt;TODAY(),COUNTBLANK($N210:$U210)&gt;0,COUNTIF($N210:$U210,"DNA")=0),1,0)+COUNTIF($N210:$U210,"DNA")+COUNTIF($V210:$Z210,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A210&lt;&gt;"",OR($G210="",$G210="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M210:$U210)+($M210:$U210="DNA")),$M210:$U210),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M210:$U210)+($M210:$U210="DNA")),$M210:$U210),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M210:$U210)+($M210:$U210="DNA")),$M210:$U210),"")&lt;TODAY())),1,0)+COUNTIF($V210:$Z210,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J210" s="32">
@@ -10722,7 +10733,7 @@
         <v/>
       </c>
       <c r="K210" s="32">
-        <f>IF(NOT(AND($A210&lt;&gt;"",OR($G210="",$G210="Active"))),"",IF($L210&lt;&gt;"",IF($L210=$M210,"Booking",INDEX($N$4:$U$4,MATCH($L210,$N210:$U210,0))),IF(COUNTIF($N210:$U210,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N210:$U210)=0,"All done",IF(MAX($M210:$U210)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A210&lt;&gt;"",OR($G210="",$G210="Active"))),"",IF($L210&lt;&gt;"",IF($L210=$M210,"Booking",INDEX($N$4:$U$4,MATCH($L210,$N210:$U210,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M210:$U210)+($M210:$U210="DNA")),$M210:$U210),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M210:$U210)+($M210:$U210="DNA")),$M210:$U210),"")),IF(ISNUMBER($U210),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L210" s="33">
@@ -10760,7 +10771,7 @@
         <v/>
       </c>
       <c r="I211" s="32">
-        <f>IF(NOT(AND($A211&lt;&gt;"",OR($G211="",$G211="Active"))),"",IF(AND(MAX($M211:$U211)&gt;0,MAX($M211:$U211)&lt;TODAY(),COUNTBLANK($N211:$U211)&gt;0,COUNTIF($N211:$U211,"DNA")=0),1,0)+COUNTIF($N211:$U211,"DNA")+COUNTIF($V211:$Z211,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A211&lt;&gt;"",OR($G211="",$G211="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M211:$U211)+($M211:$U211="DNA")),$M211:$U211),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M211:$U211)+($M211:$U211="DNA")),$M211:$U211),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M211:$U211)+($M211:$U211="DNA")),$M211:$U211),"")&lt;TODAY())),1,0)+COUNTIF($V211:$Z211,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J211" s="32">
@@ -10768,7 +10779,7 @@
         <v/>
       </c>
       <c r="K211" s="32">
-        <f>IF(NOT(AND($A211&lt;&gt;"",OR($G211="",$G211="Active"))),"",IF($L211&lt;&gt;"",IF($L211=$M211,"Booking",INDEX($N$4:$U$4,MATCH($L211,$N211:$U211,0))),IF(COUNTIF($N211:$U211,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N211:$U211)=0,"All done",IF(MAX($M211:$U211)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A211&lt;&gt;"",OR($G211="",$G211="Active"))),"",IF($L211&lt;&gt;"",IF($L211=$M211,"Booking",INDEX($N$4:$U$4,MATCH($L211,$N211:$U211,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M211:$U211)+($M211:$U211="DNA")),$M211:$U211),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M211:$U211)+($M211:$U211="DNA")),$M211:$U211),"")),IF(ISNUMBER($U211),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L211" s="33">
@@ -10806,7 +10817,7 @@
         <v/>
       </c>
       <c r="I212" s="32">
-        <f>IF(NOT(AND($A212&lt;&gt;"",OR($G212="",$G212="Active"))),"",IF(AND(MAX($M212:$U212)&gt;0,MAX($M212:$U212)&lt;TODAY(),COUNTBLANK($N212:$U212)&gt;0,COUNTIF($N212:$U212,"DNA")=0),1,0)+COUNTIF($N212:$U212,"DNA")+COUNTIF($V212:$Z212,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A212&lt;&gt;"",OR($G212="",$G212="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M212:$U212)+($M212:$U212="DNA")),$M212:$U212),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M212:$U212)+($M212:$U212="DNA")),$M212:$U212),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M212:$U212)+($M212:$U212="DNA")),$M212:$U212),"")&lt;TODAY())),1,0)+COUNTIF($V212:$Z212,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J212" s="32">
@@ -10814,7 +10825,7 @@
         <v/>
       </c>
       <c r="K212" s="32">
-        <f>IF(NOT(AND($A212&lt;&gt;"",OR($G212="",$G212="Active"))),"",IF($L212&lt;&gt;"",IF($L212=$M212,"Booking",INDEX($N$4:$U$4,MATCH($L212,$N212:$U212,0))),IF(COUNTIF($N212:$U212,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N212:$U212)=0,"All done",IF(MAX($M212:$U212)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A212&lt;&gt;"",OR($G212="",$G212="Active"))),"",IF($L212&lt;&gt;"",IF($L212=$M212,"Booking",INDEX($N$4:$U$4,MATCH($L212,$N212:$U212,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M212:$U212)+($M212:$U212="DNA")),$M212:$U212),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M212:$U212)+($M212:$U212="DNA")),$M212:$U212),"")),IF(ISNUMBER($U212),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L212" s="33">
@@ -10852,7 +10863,7 @@
         <v/>
       </c>
       <c r="I213" s="32">
-        <f>IF(NOT(AND($A213&lt;&gt;"",OR($G213="",$G213="Active"))),"",IF(AND(MAX($M213:$U213)&gt;0,MAX($M213:$U213)&lt;TODAY(),COUNTBLANK($N213:$U213)&gt;0,COUNTIF($N213:$U213,"DNA")=0),1,0)+COUNTIF($N213:$U213,"DNA")+COUNTIF($V213:$Z213,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A213&lt;&gt;"",OR($G213="",$G213="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M213:$U213)+($M213:$U213="DNA")),$M213:$U213),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M213:$U213)+($M213:$U213="DNA")),$M213:$U213),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M213:$U213)+($M213:$U213="DNA")),$M213:$U213),"")&lt;TODAY())),1,0)+COUNTIF($V213:$Z213,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J213" s="32">
@@ -10860,7 +10871,7 @@
         <v/>
       </c>
       <c r="K213" s="32">
-        <f>IF(NOT(AND($A213&lt;&gt;"",OR($G213="",$G213="Active"))),"",IF($L213&lt;&gt;"",IF($L213=$M213,"Booking",INDEX($N$4:$U$4,MATCH($L213,$N213:$U213,0))),IF(COUNTIF($N213:$U213,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N213:$U213)=0,"All done",IF(MAX($M213:$U213)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A213&lt;&gt;"",OR($G213="",$G213="Active"))),"",IF($L213&lt;&gt;"",IF($L213=$M213,"Booking",INDEX($N$4:$U$4,MATCH($L213,$N213:$U213,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M213:$U213)+($M213:$U213="DNA")),$M213:$U213),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M213:$U213)+($M213:$U213="DNA")),$M213:$U213),"")),IF(ISNUMBER($U213),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L213" s="33">
@@ -10898,7 +10909,7 @@
         <v/>
       </c>
       <c r="I214" s="32">
-        <f>IF(NOT(AND($A214&lt;&gt;"",OR($G214="",$G214="Active"))),"",IF(AND(MAX($M214:$U214)&gt;0,MAX($M214:$U214)&lt;TODAY(),COUNTBLANK($N214:$U214)&gt;0,COUNTIF($N214:$U214,"DNA")=0),1,0)+COUNTIF($N214:$U214,"DNA")+COUNTIF($V214:$Z214,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A214&lt;&gt;"",OR($G214="",$G214="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M214:$U214)+($M214:$U214="DNA")),$M214:$U214),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M214:$U214)+($M214:$U214="DNA")),$M214:$U214),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M214:$U214)+($M214:$U214="DNA")),$M214:$U214),"")&lt;TODAY())),1,0)+COUNTIF($V214:$Z214,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J214" s="32">
@@ -10906,7 +10917,7 @@
         <v/>
       </c>
       <c r="K214" s="32">
-        <f>IF(NOT(AND($A214&lt;&gt;"",OR($G214="",$G214="Active"))),"",IF($L214&lt;&gt;"",IF($L214=$M214,"Booking",INDEX($N$4:$U$4,MATCH($L214,$N214:$U214,0))),IF(COUNTIF($N214:$U214,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N214:$U214)=0,"All done",IF(MAX($M214:$U214)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A214&lt;&gt;"",OR($G214="",$G214="Active"))),"",IF($L214&lt;&gt;"",IF($L214=$M214,"Booking",INDEX($N$4:$U$4,MATCH($L214,$N214:$U214,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M214:$U214)+($M214:$U214="DNA")),$M214:$U214),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M214:$U214)+($M214:$U214="DNA")),$M214:$U214),"")),IF(ISNUMBER($U214),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L214" s="33">
@@ -10944,7 +10955,7 @@
         <v/>
       </c>
       <c r="I215" s="32">
-        <f>IF(NOT(AND($A215&lt;&gt;"",OR($G215="",$G215="Active"))),"",IF(AND(MAX($M215:$U215)&gt;0,MAX($M215:$U215)&lt;TODAY(),COUNTBLANK($N215:$U215)&gt;0,COUNTIF($N215:$U215,"DNA")=0),1,0)+COUNTIF($N215:$U215,"DNA")+COUNTIF($V215:$Z215,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A215&lt;&gt;"",OR($G215="",$G215="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M215:$U215)+($M215:$U215="DNA")),$M215:$U215),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M215:$U215)+($M215:$U215="DNA")),$M215:$U215),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M215:$U215)+($M215:$U215="DNA")),$M215:$U215),"")&lt;TODAY())),1,0)+COUNTIF($V215:$Z215,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J215" s="32">
@@ -10952,7 +10963,7 @@
         <v/>
       </c>
       <c r="K215" s="32">
-        <f>IF(NOT(AND($A215&lt;&gt;"",OR($G215="",$G215="Active"))),"",IF($L215&lt;&gt;"",IF($L215=$M215,"Booking",INDEX($N$4:$U$4,MATCH($L215,$N215:$U215,0))),IF(COUNTIF($N215:$U215,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N215:$U215)=0,"All done",IF(MAX($M215:$U215)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A215&lt;&gt;"",OR($G215="",$G215="Active"))),"",IF($L215&lt;&gt;"",IF($L215=$M215,"Booking",INDEX($N$4:$U$4,MATCH($L215,$N215:$U215,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M215:$U215)+($M215:$U215="DNA")),$M215:$U215),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M215:$U215)+($M215:$U215="DNA")),$M215:$U215),"")),IF(ISNUMBER($U215),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L215" s="33">
@@ -10990,7 +11001,7 @@
         <v/>
       </c>
       <c r="I216" s="32">
-        <f>IF(NOT(AND($A216&lt;&gt;"",OR($G216="",$G216="Active"))),"",IF(AND(MAX($M216:$U216)&gt;0,MAX($M216:$U216)&lt;TODAY(),COUNTBLANK($N216:$U216)&gt;0,COUNTIF($N216:$U216,"DNA")=0),1,0)+COUNTIF($N216:$U216,"DNA")+COUNTIF($V216:$Z216,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A216&lt;&gt;"",OR($G216="",$G216="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M216:$U216)+($M216:$U216="DNA")),$M216:$U216),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M216:$U216)+($M216:$U216="DNA")),$M216:$U216),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M216:$U216)+($M216:$U216="DNA")),$M216:$U216),"")&lt;TODAY())),1,0)+COUNTIF($V216:$Z216,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J216" s="32">
@@ -10998,7 +11009,7 @@
         <v/>
       </c>
       <c r="K216" s="32">
-        <f>IF(NOT(AND($A216&lt;&gt;"",OR($G216="",$G216="Active"))),"",IF($L216&lt;&gt;"",IF($L216=$M216,"Booking",INDEX($N$4:$U$4,MATCH($L216,$N216:$U216,0))),IF(COUNTIF($N216:$U216,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N216:$U216)=0,"All done",IF(MAX($M216:$U216)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A216&lt;&gt;"",OR($G216="",$G216="Active"))),"",IF($L216&lt;&gt;"",IF($L216=$M216,"Booking",INDEX($N$4:$U$4,MATCH($L216,$N216:$U216,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M216:$U216)+($M216:$U216="DNA")),$M216:$U216),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M216:$U216)+($M216:$U216="DNA")),$M216:$U216),"")),IF(ISNUMBER($U216),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L216" s="33">
@@ -11036,7 +11047,7 @@
         <v/>
       </c>
       <c r="I217" s="32">
-        <f>IF(NOT(AND($A217&lt;&gt;"",OR($G217="",$G217="Active"))),"",IF(AND(MAX($M217:$U217)&gt;0,MAX($M217:$U217)&lt;TODAY(),COUNTBLANK($N217:$U217)&gt;0,COUNTIF($N217:$U217,"DNA")=0),1,0)+COUNTIF($N217:$U217,"DNA")+COUNTIF($V217:$Z217,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A217&lt;&gt;"",OR($G217="",$G217="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M217:$U217)+($M217:$U217="DNA")),$M217:$U217),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M217:$U217)+($M217:$U217="DNA")),$M217:$U217),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M217:$U217)+($M217:$U217="DNA")),$M217:$U217),"")&lt;TODAY())),1,0)+COUNTIF($V217:$Z217,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J217" s="32">
@@ -11044,7 +11055,7 @@
         <v/>
       </c>
       <c r="K217" s="32">
-        <f>IF(NOT(AND($A217&lt;&gt;"",OR($G217="",$G217="Active"))),"",IF($L217&lt;&gt;"",IF($L217=$M217,"Booking",INDEX($N$4:$U$4,MATCH($L217,$N217:$U217,0))),IF(COUNTIF($N217:$U217,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N217:$U217)=0,"All done",IF(MAX($M217:$U217)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A217&lt;&gt;"",OR($G217="",$G217="Active"))),"",IF($L217&lt;&gt;"",IF($L217=$M217,"Booking",INDEX($N$4:$U$4,MATCH($L217,$N217:$U217,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M217:$U217)+($M217:$U217="DNA")),$M217:$U217),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M217:$U217)+($M217:$U217="DNA")),$M217:$U217),"")),IF(ISNUMBER($U217),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L217" s="33">
@@ -11082,7 +11093,7 @@
         <v/>
       </c>
       <c r="I218" s="32">
-        <f>IF(NOT(AND($A218&lt;&gt;"",OR($G218="",$G218="Active"))),"",IF(AND(MAX($M218:$U218)&gt;0,MAX($M218:$U218)&lt;TODAY(),COUNTBLANK($N218:$U218)&gt;0,COUNTIF($N218:$U218,"DNA")=0),1,0)+COUNTIF($N218:$U218,"DNA")+COUNTIF($V218:$Z218,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A218&lt;&gt;"",OR($G218="",$G218="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M218:$U218)+($M218:$U218="DNA")),$M218:$U218),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M218:$U218)+($M218:$U218="DNA")),$M218:$U218),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M218:$U218)+($M218:$U218="DNA")),$M218:$U218),"")&lt;TODAY())),1,0)+COUNTIF($V218:$Z218,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J218" s="32">
@@ -11090,7 +11101,7 @@
         <v/>
       </c>
       <c r="K218" s="32">
-        <f>IF(NOT(AND($A218&lt;&gt;"",OR($G218="",$G218="Active"))),"",IF($L218&lt;&gt;"",IF($L218=$M218,"Booking",INDEX($N$4:$U$4,MATCH($L218,$N218:$U218,0))),IF(COUNTIF($N218:$U218,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N218:$U218)=0,"All done",IF(MAX($M218:$U218)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A218&lt;&gt;"",OR($G218="",$G218="Active"))),"",IF($L218&lt;&gt;"",IF($L218=$M218,"Booking",INDEX($N$4:$U$4,MATCH($L218,$N218:$U218,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M218:$U218)+($M218:$U218="DNA")),$M218:$U218),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M218:$U218)+($M218:$U218="DNA")),$M218:$U218),"")),IF(ISNUMBER($U218),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L218" s="33">
@@ -11128,7 +11139,7 @@
         <v/>
       </c>
       <c r="I219" s="32">
-        <f>IF(NOT(AND($A219&lt;&gt;"",OR($G219="",$G219="Active"))),"",IF(AND(MAX($M219:$U219)&gt;0,MAX($M219:$U219)&lt;TODAY(),COUNTBLANK($N219:$U219)&gt;0,COUNTIF($N219:$U219,"DNA")=0),1,0)+COUNTIF($N219:$U219,"DNA")+COUNTIF($V219:$Z219,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A219&lt;&gt;"",OR($G219="",$G219="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M219:$U219)+($M219:$U219="DNA")),$M219:$U219),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M219:$U219)+($M219:$U219="DNA")),$M219:$U219),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M219:$U219)+($M219:$U219="DNA")),$M219:$U219),"")&lt;TODAY())),1,0)+COUNTIF($V219:$Z219,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J219" s="32">
@@ -11136,7 +11147,7 @@
         <v/>
       </c>
       <c r="K219" s="32">
-        <f>IF(NOT(AND($A219&lt;&gt;"",OR($G219="",$G219="Active"))),"",IF($L219&lt;&gt;"",IF($L219=$M219,"Booking",INDEX($N$4:$U$4,MATCH($L219,$N219:$U219,0))),IF(COUNTIF($N219:$U219,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N219:$U219)=0,"All done",IF(MAX($M219:$U219)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A219&lt;&gt;"",OR($G219="",$G219="Active"))),"",IF($L219&lt;&gt;"",IF($L219=$M219,"Booking",INDEX($N$4:$U$4,MATCH($L219,$N219:$U219,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M219:$U219)+($M219:$U219="DNA")),$M219:$U219),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M219:$U219)+($M219:$U219="DNA")),$M219:$U219),"")),IF(ISNUMBER($U219),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L219" s="33">
@@ -11174,7 +11185,7 @@
         <v/>
       </c>
       <c r="I220" s="32">
-        <f>IF(NOT(AND($A220&lt;&gt;"",OR($G220="",$G220="Active"))),"",IF(AND(MAX($M220:$U220)&gt;0,MAX($M220:$U220)&lt;TODAY(),COUNTBLANK($N220:$U220)&gt;0,COUNTIF($N220:$U220,"DNA")=0),1,0)+COUNTIF($N220:$U220,"DNA")+COUNTIF($V220:$Z220,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A220&lt;&gt;"",OR($G220="",$G220="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M220:$U220)+($M220:$U220="DNA")),$M220:$U220),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M220:$U220)+($M220:$U220="DNA")),$M220:$U220),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M220:$U220)+($M220:$U220="DNA")),$M220:$U220),"")&lt;TODAY())),1,0)+COUNTIF($V220:$Z220,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J220" s="32">
@@ -11182,7 +11193,7 @@
         <v/>
       </c>
       <c r="K220" s="32">
-        <f>IF(NOT(AND($A220&lt;&gt;"",OR($G220="",$G220="Active"))),"",IF($L220&lt;&gt;"",IF($L220=$M220,"Booking",INDEX($N$4:$U$4,MATCH($L220,$N220:$U220,0))),IF(COUNTIF($N220:$U220,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N220:$U220)=0,"All done",IF(MAX($M220:$U220)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A220&lt;&gt;"",OR($G220="",$G220="Active"))),"",IF($L220&lt;&gt;"",IF($L220=$M220,"Booking",INDEX($N$4:$U$4,MATCH($L220,$N220:$U220,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M220:$U220)+($M220:$U220="DNA")),$M220:$U220),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M220:$U220)+($M220:$U220="DNA")),$M220:$U220),"")),IF(ISNUMBER($U220),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L220" s="33">
@@ -11220,7 +11231,7 @@
         <v/>
       </c>
       <c r="I221" s="32">
-        <f>IF(NOT(AND($A221&lt;&gt;"",OR($G221="",$G221="Active"))),"",IF(AND(MAX($M221:$U221)&gt;0,MAX($M221:$U221)&lt;TODAY(),COUNTBLANK($N221:$U221)&gt;0,COUNTIF($N221:$U221,"DNA")=0),1,0)+COUNTIF($N221:$U221,"DNA")+COUNTIF($V221:$Z221,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A221&lt;&gt;"",OR($G221="",$G221="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M221:$U221)+($M221:$U221="DNA")),$M221:$U221),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M221:$U221)+($M221:$U221="DNA")),$M221:$U221),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M221:$U221)+($M221:$U221="DNA")),$M221:$U221),"")&lt;TODAY())),1,0)+COUNTIF($V221:$Z221,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J221" s="32">
@@ -11228,7 +11239,7 @@
         <v/>
       </c>
       <c r="K221" s="32">
-        <f>IF(NOT(AND($A221&lt;&gt;"",OR($G221="",$G221="Active"))),"",IF($L221&lt;&gt;"",IF($L221=$M221,"Booking",INDEX($N$4:$U$4,MATCH($L221,$N221:$U221,0))),IF(COUNTIF($N221:$U221,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N221:$U221)=0,"All done",IF(MAX($M221:$U221)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A221&lt;&gt;"",OR($G221="",$G221="Active"))),"",IF($L221&lt;&gt;"",IF($L221=$M221,"Booking",INDEX($N$4:$U$4,MATCH($L221,$N221:$U221,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M221:$U221)+($M221:$U221="DNA")),$M221:$U221),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M221:$U221)+($M221:$U221="DNA")),$M221:$U221),"")),IF(ISNUMBER($U221),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L221" s="33">
@@ -11266,7 +11277,7 @@
         <v/>
       </c>
       <c r="I222" s="32">
-        <f>IF(NOT(AND($A222&lt;&gt;"",OR($G222="",$G222="Active"))),"",IF(AND(MAX($M222:$U222)&gt;0,MAX($M222:$U222)&lt;TODAY(),COUNTBLANK($N222:$U222)&gt;0,COUNTIF($N222:$U222,"DNA")=0),1,0)+COUNTIF($N222:$U222,"DNA")+COUNTIF($V222:$Z222,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A222&lt;&gt;"",OR($G222="",$G222="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M222:$U222)+($M222:$U222="DNA")),$M222:$U222),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M222:$U222)+($M222:$U222="DNA")),$M222:$U222),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M222:$U222)+($M222:$U222="DNA")),$M222:$U222),"")&lt;TODAY())),1,0)+COUNTIF($V222:$Z222,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J222" s="32">
@@ -11274,7 +11285,7 @@
         <v/>
       </c>
       <c r="K222" s="32">
-        <f>IF(NOT(AND($A222&lt;&gt;"",OR($G222="",$G222="Active"))),"",IF($L222&lt;&gt;"",IF($L222=$M222,"Booking",INDEX($N$4:$U$4,MATCH($L222,$N222:$U222,0))),IF(COUNTIF($N222:$U222,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N222:$U222)=0,"All done",IF(MAX($M222:$U222)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A222&lt;&gt;"",OR($G222="",$G222="Active"))),"",IF($L222&lt;&gt;"",IF($L222=$M222,"Booking",INDEX($N$4:$U$4,MATCH($L222,$N222:$U222,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M222:$U222)+($M222:$U222="DNA")),$M222:$U222),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M222:$U222)+($M222:$U222="DNA")),$M222:$U222),"")),IF(ISNUMBER($U222),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L222" s="33">
@@ -11312,7 +11323,7 @@
         <v/>
       </c>
       <c r="I223" s="32">
-        <f>IF(NOT(AND($A223&lt;&gt;"",OR($G223="",$G223="Active"))),"",IF(AND(MAX($M223:$U223)&gt;0,MAX($M223:$U223)&lt;TODAY(),COUNTBLANK($N223:$U223)&gt;0,COUNTIF($N223:$U223,"DNA")=0),1,0)+COUNTIF($N223:$U223,"DNA")+COUNTIF($V223:$Z223,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A223&lt;&gt;"",OR($G223="",$G223="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M223:$U223)+($M223:$U223="DNA")),$M223:$U223),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M223:$U223)+($M223:$U223="DNA")),$M223:$U223),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M223:$U223)+($M223:$U223="DNA")),$M223:$U223),"")&lt;TODAY())),1,0)+COUNTIF($V223:$Z223,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J223" s="32">
@@ -11320,7 +11331,7 @@
         <v/>
       </c>
       <c r="K223" s="32">
-        <f>IF(NOT(AND($A223&lt;&gt;"",OR($G223="",$G223="Active"))),"",IF($L223&lt;&gt;"",IF($L223=$M223,"Booking",INDEX($N$4:$U$4,MATCH($L223,$N223:$U223,0))),IF(COUNTIF($N223:$U223,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N223:$U223)=0,"All done",IF(MAX($M223:$U223)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A223&lt;&gt;"",OR($G223="",$G223="Active"))),"",IF($L223&lt;&gt;"",IF($L223=$M223,"Booking",INDEX($N$4:$U$4,MATCH($L223,$N223:$U223,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M223:$U223)+($M223:$U223="DNA")),$M223:$U223),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M223:$U223)+($M223:$U223="DNA")),$M223:$U223),"")),IF(ISNUMBER($U223),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L223" s="33">
@@ -11358,7 +11369,7 @@
         <v/>
       </c>
       <c r="I224" s="32">
-        <f>IF(NOT(AND($A224&lt;&gt;"",OR($G224="",$G224="Active"))),"",IF(AND(MAX($M224:$U224)&gt;0,MAX($M224:$U224)&lt;TODAY(),COUNTBLANK($N224:$U224)&gt;0,COUNTIF($N224:$U224,"DNA")=0),1,0)+COUNTIF($N224:$U224,"DNA")+COUNTIF($V224:$Z224,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A224&lt;&gt;"",OR($G224="",$G224="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M224:$U224)+($M224:$U224="DNA")),$M224:$U224),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M224:$U224)+($M224:$U224="DNA")),$M224:$U224),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M224:$U224)+($M224:$U224="DNA")),$M224:$U224),"")&lt;TODAY())),1,0)+COUNTIF($V224:$Z224,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J224" s="32">
@@ -11366,7 +11377,7 @@
         <v/>
       </c>
       <c r="K224" s="32">
-        <f>IF(NOT(AND($A224&lt;&gt;"",OR($G224="",$G224="Active"))),"",IF($L224&lt;&gt;"",IF($L224=$M224,"Booking",INDEX($N$4:$U$4,MATCH($L224,$N224:$U224,0))),IF(COUNTIF($N224:$U224,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N224:$U224)=0,"All done",IF(MAX($M224:$U224)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A224&lt;&gt;"",OR($G224="",$G224="Active"))),"",IF($L224&lt;&gt;"",IF($L224=$M224,"Booking",INDEX($N$4:$U$4,MATCH($L224,$N224:$U224,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M224:$U224)+($M224:$U224="DNA")),$M224:$U224),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M224:$U224)+($M224:$U224="DNA")),$M224:$U224),"")),IF(ISNUMBER($U224),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L224" s="33">
@@ -11404,7 +11415,7 @@
         <v/>
       </c>
       <c r="I225" s="32">
-        <f>IF(NOT(AND($A225&lt;&gt;"",OR($G225="",$G225="Active"))),"",IF(AND(MAX($M225:$U225)&gt;0,MAX($M225:$U225)&lt;TODAY(),COUNTBLANK($N225:$U225)&gt;0,COUNTIF($N225:$U225,"DNA")=0),1,0)+COUNTIF($N225:$U225,"DNA")+COUNTIF($V225:$Z225,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A225&lt;&gt;"",OR($G225="",$G225="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M225:$U225)+($M225:$U225="DNA")),$M225:$U225),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M225:$U225)+($M225:$U225="DNA")),$M225:$U225),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M225:$U225)+($M225:$U225="DNA")),$M225:$U225),"")&lt;TODAY())),1,0)+COUNTIF($V225:$Z225,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J225" s="32">
@@ -11412,7 +11423,7 @@
         <v/>
       </c>
       <c r="K225" s="32">
-        <f>IF(NOT(AND($A225&lt;&gt;"",OR($G225="",$G225="Active"))),"",IF($L225&lt;&gt;"",IF($L225=$M225,"Booking",INDEX($N$4:$U$4,MATCH($L225,$N225:$U225,0))),IF(COUNTIF($N225:$U225,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N225:$U225)=0,"All done",IF(MAX($M225:$U225)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A225&lt;&gt;"",OR($G225="",$G225="Active"))),"",IF($L225&lt;&gt;"",IF($L225=$M225,"Booking",INDEX($N$4:$U$4,MATCH($L225,$N225:$U225,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M225:$U225)+($M225:$U225="DNA")),$M225:$U225),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M225:$U225)+($M225:$U225="DNA")),$M225:$U225),"")),IF(ISNUMBER($U225),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L225" s="33">
@@ -11450,7 +11461,7 @@
         <v/>
       </c>
       <c r="I226" s="32">
-        <f>IF(NOT(AND($A226&lt;&gt;"",OR($G226="",$G226="Active"))),"",IF(AND(MAX($M226:$U226)&gt;0,MAX($M226:$U226)&lt;TODAY(),COUNTBLANK($N226:$U226)&gt;0,COUNTIF($N226:$U226,"DNA")=0),1,0)+COUNTIF($N226:$U226,"DNA")+COUNTIF($V226:$Z226,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A226&lt;&gt;"",OR($G226="",$G226="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M226:$U226)+($M226:$U226="DNA")),$M226:$U226),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M226:$U226)+($M226:$U226="DNA")),$M226:$U226),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M226:$U226)+($M226:$U226="DNA")),$M226:$U226),"")&lt;TODAY())),1,0)+COUNTIF($V226:$Z226,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J226" s="32">
@@ -11458,7 +11469,7 @@
         <v/>
       </c>
       <c r="K226" s="32">
-        <f>IF(NOT(AND($A226&lt;&gt;"",OR($G226="",$G226="Active"))),"",IF($L226&lt;&gt;"",IF($L226=$M226,"Booking",INDEX($N$4:$U$4,MATCH($L226,$N226:$U226,0))),IF(COUNTIF($N226:$U226,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N226:$U226)=0,"All done",IF(MAX($M226:$U226)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A226&lt;&gt;"",OR($G226="",$G226="Active"))),"",IF($L226&lt;&gt;"",IF($L226=$M226,"Booking",INDEX($N$4:$U$4,MATCH($L226,$N226:$U226,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M226:$U226)+($M226:$U226="DNA")),$M226:$U226),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M226:$U226)+($M226:$U226="DNA")),$M226:$U226),"")),IF(ISNUMBER($U226),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L226" s="33">
@@ -11496,7 +11507,7 @@
         <v/>
       </c>
       <c r="I227" s="32">
-        <f>IF(NOT(AND($A227&lt;&gt;"",OR($G227="",$G227="Active"))),"",IF(AND(MAX($M227:$U227)&gt;0,MAX($M227:$U227)&lt;TODAY(),COUNTBLANK($N227:$U227)&gt;0,COUNTIF($N227:$U227,"DNA")=0),1,0)+COUNTIF($N227:$U227,"DNA")+COUNTIF($V227:$Z227,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A227&lt;&gt;"",OR($G227="",$G227="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M227:$U227)+($M227:$U227="DNA")),$M227:$U227),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M227:$U227)+($M227:$U227="DNA")),$M227:$U227),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M227:$U227)+($M227:$U227="DNA")),$M227:$U227),"")&lt;TODAY())),1,0)+COUNTIF($V227:$Z227,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J227" s="32">
@@ -11504,7 +11515,7 @@
         <v/>
       </c>
       <c r="K227" s="32">
-        <f>IF(NOT(AND($A227&lt;&gt;"",OR($G227="",$G227="Active"))),"",IF($L227&lt;&gt;"",IF($L227=$M227,"Booking",INDEX($N$4:$U$4,MATCH($L227,$N227:$U227,0))),IF(COUNTIF($N227:$U227,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N227:$U227)=0,"All done",IF(MAX($M227:$U227)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A227&lt;&gt;"",OR($G227="",$G227="Active"))),"",IF($L227&lt;&gt;"",IF($L227=$M227,"Booking",INDEX($N$4:$U$4,MATCH($L227,$N227:$U227,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M227:$U227)+($M227:$U227="DNA")),$M227:$U227),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M227:$U227)+($M227:$U227="DNA")),$M227:$U227),"")),IF(ISNUMBER($U227),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L227" s="33">
@@ -11542,7 +11553,7 @@
         <v/>
       </c>
       <c r="I228" s="32">
-        <f>IF(NOT(AND($A228&lt;&gt;"",OR($G228="",$G228="Active"))),"",IF(AND(MAX($M228:$U228)&gt;0,MAX($M228:$U228)&lt;TODAY(),COUNTBLANK($N228:$U228)&gt;0,COUNTIF($N228:$U228,"DNA")=0),1,0)+COUNTIF($N228:$U228,"DNA")+COUNTIF($V228:$Z228,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A228&lt;&gt;"",OR($G228="",$G228="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M228:$U228)+($M228:$U228="DNA")),$M228:$U228),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M228:$U228)+($M228:$U228="DNA")),$M228:$U228),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M228:$U228)+($M228:$U228="DNA")),$M228:$U228),"")&lt;TODAY())),1,0)+COUNTIF($V228:$Z228,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J228" s="32">
@@ -11550,7 +11561,7 @@
         <v/>
       </c>
       <c r="K228" s="32">
-        <f>IF(NOT(AND($A228&lt;&gt;"",OR($G228="",$G228="Active"))),"",IF($L228&lt;&gt;"",IF($L228=$M228,"Booking",INDEX($N$4:$U$4,MATCH($L228,$N228:$U228,0))),IF(COUNTIF($N228:$U228,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N228:$U228)=0,"All done",IF(MAX($M228:$U228)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A228&lt;&gt;"",OR($G228="",$G228="Active"))),"",IF($L228&lt;&gt;"",IF($L228=$M228,"Booking",INDEX($N$4:$U$4,MATCH($L228,$N228:$U228,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M228:$U228)+($M228:$U228="DNA")),$M228:$U228),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M228:$U228)+($M228:$U228="DNA")),$M228:$U228),"")),IF(ISNUMBER($U228),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L228" s="33">
@@ -11588,7 +11599,7 @@
         <v/>
       </c>
       <c r="I229" s="32">
-        <f>IF(NOT(AND($A229&lt;&gt;"",OR($G229="",$G229="Active"))),"",IF(AND(MAX($M229:$U229)&gt;0,MAX($M229:$U229)&lt;TODAY(),COUNTBLANK($N229:$U229)&gt;0,COUNTIF($N229:$U229,"DNA")=0),1,0)+COUNTIF($N229:$U229,"DNA")+COUNTIF($V229:$Z229,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A229&lt;&gt;"",OR($G229="",$G229="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M229:$U229)+($M229:$U229="DNA")),$M229:$U229),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M229:$U229)+($M229:$U229="DNA")),$M229:$U229),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M229:$U229)+($M229:$U229="DNA")),$M229:$U229),"")&lt;TODAY())),1,0)+COUNTIF($V229:$Z229,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J229" s="32">
@@ -11596,7 +11607,7 @@
         <v/>
       </c>
       <c r="K229" s="32">
-        <f>IF(NOT(AND($A229&lt;&gt;"",OR($G229="",$G229="Active"))),"",IF($L229&lt;&gt;"",IF($L229=$M229,"Booking",INDEX($N$4:$U$4,MATCH($L229,$N229:$U229,0))),IF(COUNTIF($N229:$U229,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N229:$U229)=0,"All done",IF(MAX($M229:$U229)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A229&lt;&gt;"",OR($G229="",$G229="Active"))),"",IF($L229&lt;&gt;"",IF($L229=$M229,"Booking",INDEX($N$4:$U$4,MATCH($L229,$N229:$U229,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M229:$U229)+($M229:$U229="DNA")),$M229:$U229),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M229:$U229)+($M229:$U229="DNA")),$M229:$U229),"")),IF(ISNUMBER($U229),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L229" s="33">
@@ -11634,7 +11645,7 @@
         <v/>
       </c>
       <c r="I230" s="32">
-        <f>IF(NOT(AND($A230&lt;&gt;"",OR($G230="",$G230="Active"))),"",IF(AND(MAX($M230:$U230)&gt;0,MAX($M230:$U230)&lt;TODAY(),COUNTBLANK($N230:$U230)&gt;0,COUNTIF($N230:$U230,"DNA")=0),1,0)+COUNTIF($N230:$U230,"DNA")+COUNTIF($V230:$Z230,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A230&lt;&gt;"",OR($G230="",$G230="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M230:$U230)+($M230:$U230="DNA")),$M230:$U230),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M230:$U230)+($M230:$U230="DNA")),$M230:$U230),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M230:$U230)+($M230:$U230="DNA")),$M230:$U230),"")&lt;TODAY())),1,0)+COUNTIF($V230:$Z230,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J230" s="32">
@@ -11642,7 +11653,7 @@
         <v/>
       </c>
       <c r="K230" s="32">
-        <f>IF(NOT(AND($A230&lt;&gt;"",OR($G230="",$G230="Active"))),"",IF($L230&lt;&gt;"",IF($L230=$M230,"Booking",INDEX($N$4:$U$4,MATCH($L230,$N230:$U230,0))),IF(COUNTIF($N230:$U230,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N230:$U230)=0,"All done",IF(MAX($M230:$U230)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A230&lt;&gt;"",OR($G230="",$G230="Active"))),"",IF($L230&lt;&gt;"",IF($L230=$M230,"Booking",INDEX($N$4:$U$4,MATCH($L230,$N230:$U230,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M230:$U230)+($M230:$U230="DNA")),$M230:$U230),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M230:$U230)+($M230:$U230="DNA")),$M230:$U230),"")),IF(ISNUMBER($U230),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L230" s="33">
@@ -11680,7 +11691,7 @@
         <v/>
       </c>
       <c r="I231" s="32">
-        <f>IF(NOT(AND($A231&lt;&gt;"",OR($G231="",$G231="Active"))),"",IF(AND(MAX($M231:$U231)&gt;0,MAX($M231:$U231)&lt;TODAY(),COUNTBLANK($N231:$U231)&gt;0,COUNTIF($N231:$U231,"DNA")=0),1,0)+COUNTIF($N231:$U231,"DNA")+COUNTIF($V231:$Z231,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A231&lt;&gt;"",OR($G231="",$G231="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M231:$U231)+($M231:$U231="DNA")),$M231:$U231),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M231:$U231)+($M231:$U231="DNA")),$M231:$U231),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M231:$U231)+($M231:$U231="DNA")),$M231:$U231),"")&lt;TODAY())),1,0)+COUNTIF($V231:$Z231,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J231" s="32">
@@ -11688,7 +11699,7 @@
         <v/>
       </c>
       <c r="K231" s="32">
-        <f>IF(NOT(AND($A231&lt;&gt;"",OR($G231="",$G231="Active"))),"",IF($L231&lt;&gt;"",IF($L231=$M231,"Booking",INDEX($N$4:$U$4,MATCH($L231,$N231:$U231,0))),IF(COUNTIF($N231:$U231,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N231:$U231)=0,"All done",IF(MAX($M231:$U231)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A231&lt;&gt;"",OR($G231="",$G231="Active"))),"",IF($L231&lt;&gt;"",IF($L231=$M231,"Booking",INDEX($N$4:$U$4,MATCH($L231,$N231:$U231,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M231:$U231)+($M231:$U231="DNA")),$M231:$U231),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M231:$U231)+($M231:$U231="DNA")),$M231:$U231),"")),IF(ISNUMBER($U231),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L231" s="33">
@@ -11726,7 +11737,7 @@
         <v/>
       </c>
       <c r="I232" s="32">
-        <f>IF(NOT(AND($A232&lt;&gt;"",OR($G232="",$G232="Active"))),"",IF(AND(MAX($M232:$U232)&gt;0,MAX($M232:$U232)&lt;TODAY(),COUNTBLANK($N232:$U232)&gt;0,COUNTIF($N232:$U232,"DNA")=0),1,0)+COUNTIF($N232:$U232,"DNA")+COUNTIF($V232:$Z232,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A232&lt;&gt;"",OR($G232="",$G232="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M232:$U232)+($M232:$U232="DNA")),$M232:$U232),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M232:$U232)+($M232:$U232="DNA")),$M232:$U232),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M232:$U232)+($M232:$U232="DNA")),$M232:$U232),"")&lt;TODAY())),1,0)+COUNTIF($V232:$Z232,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J232" s="32">
@@ -11734,7 +11745,7 @@
         <v/>
       </c>
       <c r="K232" s="32">
-        <f>IF(NOT(AND($A232&lt;&gt;"",OR($G232="",$G232="Active"))),"",IF($L232&lt;&gt;"",IF($L232=$M232,"Booking",INDEX($N$4:$U$4,MATCH($L232,$N232:$U232,0))),IF(COUNTIF($N232:$U232,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N232:$U232)=0,"All done",IF(MAX($M232:$U232)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A232&lt;&gt;"",OR($G232="",$G232="Active"))),"",IF($L232&lt;&gt;"",IF($L232=$M232,"Booking",INDEX($N$4:$U$4,MATCH($L232,$N232:$U232,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M232:$U232)+($M232:$U232="DNA")),$M232:$U232),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M232:$U232)+($M232:$U232="DNA")),$M232:$U232),"")),IF(ISNUMBER($U232),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L232" s="33">
@@ -11772,7 +11783,7 @@
         <v/>
       </c>
       <c r="I233" s="32">
-        <f>IF(NOT(AND($A233&lt;&gt;"",OR($G233="",$G233="Active"))),"",IF(AND(MAX($M233:$U233)&gt;0,MAX($M233:$U233)&lt;TODAY(),COUNTBLANK($N233:$U233)&gt;0,COUNTIF($N233:$U233,"DNA")=0),1,0)+COUNTIF($N233:$U233,"DNA")+COUNTIF($V233:$Z233,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A233&lt;&gt;"",OR($G233="",$G233="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M233:$U233)+($M233:$U233="DNA")),$M233:$U233),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M233:$U233)+($M233:$U233="DNA")),$M233:$U233),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M233:$U233)+($M233:$U233="DNA")),$M233:$U233),"")&lt;TODAY())),1,0)+COUNTIF($V233:$Z233,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J233" s="32">
@@ -11780,7 +11791,7 @@
         <v/>
       </c>
       <c r="K233" s="32">
-        <f>IF(NOT(AND($A233&lt;&gt;"",OR($G233="",$G233="Active"))),"",IF($L233&lt;&gt;"",IF($L233=$M233,"Booking",INDEX($N$4:$U$4,MATCH($L233,$N233:$U233,0))),IF(COUNTIF($N233:$U233,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N233:$U233)=0,"All done",IF(MAX($M233:$U233)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A233&lt;&gt;"",OR($G233="",$G233="Active"))),"",IF($L233&lt;&gt;"",IF($L233=$M233,"Booking",INDEX($N$4:$U$4,MATCH($L233,$N233:$U233,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M233:$U233)+($M233:$U233="DNA")),$M233:$U233),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M233:$U233)+($M233:$U233="DNA")),$M233:$U233),"")),IF(ISNUMBER($U233),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L233" s="33">
@@ -11818,7 +11829,7 @@
         <v/>
       </c>
       <c r="I234" s="32">
-        <f>IF(NOT(AND($A234&lt;&gt;"",OR($G234="",$G234="Active"))),"",IF(AND(MAX($M234:$U234)&gt;0,MAX($M234:$U234)&lt;TODAY(),COUNTBLANK($N234:$U234)&gt;0,COUNTIF($N234:$U234,"DNA")=0),1,0)+COUNTIF($N234:$U234,"DNA")+COUNTIF($V234:$Z234,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A234&lt;&gt;"",OR($G234="",$G234="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M234:$U234)+($M234:$U234="DNA")),$M234:$U234),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M234:$U234)+($M234:$U234="DNA")),$M234:$U234),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M234:$U234)+($M234:$U234="DNA")),$M234:$U234),"")&lt;TODAY())),1,0)+COUNTIF($V234:$Z234,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J234" s="32">
@@ -11826,7 +11837,7 @@
         <v/>
       </c>
       <c r="K234" s="32">
-        <f>IF(NOT(AND($A234&lt;&gt;"",OR($G234="",$G234="Active"))),"",IF($L234&lt;&gt;"",IF($L234=$M234,"Booking",INDEX($N$4:$U$4,MATCH($L234,$N234:$U234,0))),IF(COUNTIF($N234:$U234,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N234:$U234)=0,"All done",IF(MAX($M234:$U234)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A234&lt;&gt;"",OR($G234="",$G234="Active"))),"",IF($L234&lt;&gt;"",IF($L234=$M234,"Booking",INDEX($N$4:$U$4,MATCH($L234,$N234:$U234,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M234:$U234)+($M234:$U234="DNA")),$M234:$U234),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M234:$U234)+($M234:$U234="DNA")),$M234:$U234),"")),IF(ISNUMBER($U234),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L234" s="33">
@@ -11864,7 +11875,7 @@
         <v/>
       </c>
       <c r="I235" s="32">
-        <f>IF(NOT(AND($A235&lt;&gt;"",OR($G235="",$G235="Active"))),"",IF(AND(MAX($M235:$U235)&gt;0,MAX($M235:$U235)&lt;TODAY(),COUNTBLANK($N235:$U235)&gt;0,COUNTIF($N235:$U235,"DNA")=0),1,0)+COUNTIF($N235:$U235,"DNA")+COUNTIF($V235:$Z235,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A235&lt;&gt;"",OR($G235="",$G235="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M235:$U235)+($M235:$U235="DNA")),$M235:$U235),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M235:$U235)+($M235:$U235="DNA")),$M235:$U235),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M235:$U235)+($M235:$U235="DNA")),$M235:$U235),"")&lt;TODAY())),1,0)+COUNTIF($V235:$Z235,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J235" s="32">
@@ -11872,7 +11883,7 @@
         <v/>
       </c>
       <c r="K235" s="32">
-        <f>IF(NOT(AND($A235&lt;&gt;"",OR($G235="",$G235="Active"))),"",IF($L235&lt;&gt;"",IF($L235=$M235,"Booking",INDEX($N$4:$U$4,MATCH($L235,$N235:$U235,0))),IF(COUNTIF($N235:$U235,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N235:$U235)=0,"All done",IF(MAX($M235:$U235)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A235&lt;&gt;"",OR($G235="",$G235="Active"))),"",IF($L235&lt;&gt;"",IF($L235=$M235,"Booking",INDEX($N$4:$U$4,MATCH($L235,$N235:$U235,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M235:$U235)+($M235:$U235="DNA")),$M235:$U235),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M235:$U235)+($M235:$U235="DNA")),$M235:$U235),"")),IF(ISNUMBER($U235),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L235" s="33">
@@ -11910,7 +11921,7 @@
         <v/>
       </c>
       <c r="I236" s="32">
-        <f>IF(NOT(AND($A236&lt;&gt;"",OR($G236="",$G236="Active"))),"",IF(AND(MAX($M236:$U236)&gt;0,MAX($M236:$U236)&lt;TODAY(),COUNTBLANK($N236:$U236)&gt;0,COUNTIF($N236:$U236,"DNA")=0),1,0)+COUNTIF($N236:$U236,"DNA")+COUNTIF($V236:$Z236,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A236&lt;&gt;"",OR($G236="",$G236="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M236:$U236)+($M236:$U236="DNA")),$M236:$U236),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M236:$U236)+($M236:$U236="DNA")),$M236:$U236),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M236:$U236)+($M236:$U236="DNA")),$M236:$U236),"")&lt;TODAY())),1,0)+COUNTIF($V236:$Z236,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J236" s="32">
@@ -11918,7 +11929,7 @@
         <v/>
       </c>
       <c r="K236" s="32">
-        <f>IF(NOT(AND($A236&lt;&gt;"",OR($G236="",$G236="Active"))),"",IF($L236&lt;&gt;"",IF($L236=$M236,"Booking",INDEX($N$4:$U$4,MATCH($L236,$N236:$U236,0))),IF(COUNTIF($N236:$U236,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N236:$U236)=0,"All done",IF(MAX($M236:$U236)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A236&lt;&gt;"",OR($G236="",$G236="Active"))),"",IF($L236&lt;&gt;"",IF($L236=$M236,"Booking",INDEX($N$4:$U$4,MATCH($L236,$N236:$U236,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M236:$U236)+($M236:$U236="DNA")),$M236:$U236),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M236:$U236)+($M236:$U236="DNA")),$M236:$U236),"")),IF(ISNUMBER($U236),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L236" s="33">
@@ -11956,7 +11967,7 @@
         <v/>
       </c>
       <c r="I237" s="32">
-        <f>IF(NOT(AND($A237&lt;&gt;"",OR($G237="",$G237="Active"))),"",IF(AND(MAX($M237:$U237)&gt;0,MAX($M237:$U237)&lt;TODAY(),COUNTBLANK($N237:$U237)&gt;0,COUNTIF($N237:$U237,"DNA")=0),1,0)+COUNTIF($N237:$U237,"DNA")+COUNTIF($V237:$Z237,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A237&lt;&gt;"",OR($G237="",$G237="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M237:$U237)+($M237:$U237="DNA")),$M237:$U237),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M237:$U237)+($M237:$U237="DNA")),$M237:$U237),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M237:$U237)+($M237:$U237="DNA")),$M237:$U237),"")&lt;TODAY())),1,0)+COUNTIF($V237:$Z237,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J237" s="32">
@@ -11964,7 +11975,7 @@
         <v/>
       </c>
       <c r="K237" s="32">
-        <f>IF(NOT(AND($A237&lt;&gt;"",OR($G237="",$G237="Active"))),"",IF($L237&lt;&gt;"",IF($L237=$M237,"Booking",INDEX($N$4:$U$4,MATCH($L237,$N237:$U237,0))),IF(COUNTIF($N237:$U237,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N237:$U237)=0,"All done",IF(MAX($M237:$U237)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A237&lt;&gt;"",OR($G237="",$G237="Active"))),"",IF($L237&lt;&gt;"",IF($L237=$M237,"Booking",INDEX($N$4:$U$4,MATCH($L237,$N237:$U237,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M237:$U237)+($M237:$U237="DNA")),$M237:$U237),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M237:$U237)+($M237:$U237="DNA")),$M237:$U237),"")),IF(ISNUMBER($U237),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L237" s="33">
@@ -12002,7 +12013,7 @@
         <v/>
       </c>
       <c r="I238" s="32">
-        <f>IF(NOT(AND($A238&lt;&gt;"",OR($G238="",$G238="Active"))),"",IF(AND(MAX($M238:$U238)&gt;0,MAX($M238:$U238)&lt;TODAY(),COUNTBLANK($N238:$U238)&gt;0,COUNTIF($N238:$U238,"DNA")=0),1,0)+COUNTIF($N238:$U238,"DNA")+COUNTIF($V238:$Z238,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A238&lt;&gt;"",OR($G238="",$G238="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M238:$U238)+($M238:$U238="DNA")),$M238:$U238),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M238:$U238)+($M238:$U238="DNA")),$M238:$U238),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M238:$U238)+($M238:$U238="DNA")),$M238:$U238),"")&lt;TODAY())),1,0)+COUNTIF($V238:$Z238,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J238" s="32">
@@ -12010,7 +12021,7 @@
         <v/>
       </c>
       <c r="K238" s="32">
-        <f>IF(NOT(AND($A238&lt;&gt;"",OR($G238="",$G238="Active"))),"",IF($L238&lt;&gt;"",IF($L238=$M238,"Booking",INDEX($N$4:$U$4,MATCH($L238,$N238:$U238,0))),IF(COUNTIF($N238:$U238,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N238:$U238)=0,"All done",IF(MAX($M238:$U238)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A238&lt;&gt;"",OR($G238="",$G238="Active"))),"",IF($L238&lt;&gt;"",IF($L238=$M238,"Booking",INDEX($N$4:$U$4,MATCH($L238,$N238:$U238,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M238:$U238)+($M238:$U238="DNA")),$M238:$U238),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M238:$U238)+($M238:$U238="DNA")),$M238:$U238),"")),IF(ISNUMBER($U238),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L238" s="33">
@@ -12048,7 +12059,7 @@
         <v/>
       </c>
       <c r="I239" s="32">
-        <f>IF(NOT(AND($A239&lt;&gt;"",OR($G239="",$G239="Active"))),"",IF(AND(MAX($M239:$U239)&gt;0,MAX($M239:$U239)&lt;TODAY(),COUNTBLANK($N239:$U239)&gt;0,COUNTIF($N239:$U239,"DNA")=0),1,0)+COUNTIF($N239:$U239,"DNA")+COUNTIF($V239:$Z239,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A239&lt;&gt;"",OR($G239="",$G239="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M239:$U239)+($M239:$U239="DNA")),$M239:$U239),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M239:$U239)+($M239:$U239="DNA")),$M239:$U239),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M239:$U239)+($M239:$U239="DNA")),$M239:$U239),"")&lt;TODAY())),1,0)+COUNTIF($V239:$Z239,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J239" s="32">
@@ -12056,7 +12067,7 @@
         <v/>
       </c>
       <c r="K239" s="32">
-        <f>IF(NOT(AND($A239&lt;&gt;"",OR($G239="",$G239="Active"))),"",IF($L239&lt;&gt;"",IF($L239=$M239,"Booking",INDEX($N$4:$U$4,MATCH($L239,$N239:$U239,0))),IF(COUNTIF($N239:$U239,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N239:$U239)=0,"All done",IF(MAX($M239:$U239)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A239&lt;&gt;"",OR($G239="",$G239="Active"))),"",IF($L239&lt;&gt;"",IF($L239=$M239,"Booking",INDEX($N$4:$U$4,MATCH($L239,$N239:$U239,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M239:$U239)+($M239:$U239="DNA")),$M239:$U239),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M239:$U239)+($M239:$U239="DNA")),$M239:$U239),"")),IF(ISNUMBER($U239),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L239" s="33">
@@ -12094,7 +12105,7 @@
         <v/>
       </c>
       <c r="I240" s="32">
-        <f>IF(NOT(AND($A240&lt;&gt;"",OR($G240="",$G240="Active"))),"",IF(AND(MAX($M240:$U240)&gt;0,MAX($M240:$U240)&lt;TODAY(),COUNTBLANK($N240:$U240)&gt;0,COUNTIF($N240:$U240,"DNA")=0),1,0)+COUNTIF($N240:$U240,"DNA")+COUNTIF($V240:$Z240,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A240&lt;&gt;"",OR($G240="",$G240="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M240:$U240)+($M240:$U240="DNA")),$M240:$U240),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M240:$U240)+($M240:$U240="DNA")),$M240:$U240),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M240:$U240)+($M240:$U240="DNA")),$M240:$U240),"")&lt;TODAY())),1,0)+COUNTIF($V240:$Z240,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J240" s="32">
@@ -12102,7 +12113,7 @@
         <v/>
       </c>
       <c r="K240" s="32">
-        <f>IF(NOT(AND($A240&lt;&gt;"",OR($G240="",$G240="Active"))),"",IF($L240&lt;&gt;"",IF($L240=$M240,"Booking",INDEX($N$4:$U$4,MATCH($L240,$N240:$U240,0))),IF(COUNTIF($N240:$U240,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N240:$U240)=0,"All done",IF(MAX($M240:$U240)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A240&lt;&gt;"",OR($G240="",$G240="Active"))),"",IF($L240&lt;&gt;"",IF($L240=$M240,"Booking",INDEX($N$4:$U$4,MATCH($L240,$N240:$U240,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M240:$U240)+($M240:$U240="DNA")),$M240:$U240),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M240:$U240)+($M240:$U240="DNA")),$M240:$U240),"")),IF(ISNUMBER($U240),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L240" s="33">
@@ -12140,7 +12151,7 @@
         <v/>
       </c>
       <c r="I241" s="32">
-        <f>IF(NOT(AND($A241&lt;&gt;"",OR($G241="",$G241="Active"))),"",IF(AND(MAX($M241:$U241)&gt;0,MAX($M241:$U241)&lt;TODAY(),COUNTBLANK($N241:$U241)&gt;0,COUNTIF($N241:$U241,"DNA")=0),1,0)+COUNTIF($N241:$U241,"DNA")+COUNTIF($V241:$Z241,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A241&lt;&gt;"",OR($G241="",$G241="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M241:$U241)+($M241:$U241="DNA")),$M241:$U241),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M241:$U241)+($M241:$U241="DNA")),$M241:$U241),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M241:$U241)+($M241:$U241="DNA")),$M241:$U241),"")&lt;TODAY())),1,0)+COUNTIF($V241:$Z241,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J241" s="32">
@@ -12148,7 +12159,7 @@
         <v/>
       </c>
       <c r="K241" s="32">
-        <f>IF(NOT(AND($A241&lt;&gt;"",OR($G241="",$G241="Active"))),"",IF($L241&lt;&gt;"",IF($L241=$M241,"Booking",INDEX($N$4:$U$4,MATCH($L241,$N241:$U241,0))),IF(COUNTIF($N241:$U241,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N241:$U241)=0,"All done",IF(MAX($M241:$U241)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A241&lt;&gt;"",OR($G241="",$G241="Active"))),"",IF($L241&lt;&gt;"",IF($L241=$M241,"Booking",INDEX($N$4:$U$4,MATCH($L241,$N241:$U241,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M241:$U241)+($M241:$U241="DNA")),$M241:$U241),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M241:$U241)+($M241:$U241="DNA")),$M241:$U241),"")),IF(ISNUMBER($U241),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L241" s="33">
@@ -12186,7 +12197,7 @@
         <v/>
       </c>
       <c r="I242" s="32">
-        <f>IF(NOT(AND($A242&lt;&gt;"",OR($G242="",$G242="Active"))),"",IF(AND(MAX($M242:$U242)&gt;0,MAX($M242:$U242)&lt;TODAY(),COUNTBLANK($N242:$U242)&gt;0,COUNTIF($N242:$U242,"DNA")=0),1,0)+COUNTIF($N242:$U242,"DNA")+COUNTIF($V242:$Z242,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A242&lt;&gt;"",OR($G242="",$G242="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M242:$U242)+($M242:$U242="DNA")),$M242:$U242),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M242:$U242)+($M242:$U242="DNA")),$M242:$U242),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M242:$U242)+($M242:$U242="DNA")),$M242:$U242),"")&lt;TODAY())),1,0)+COUNTIF($V242:$Z242,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J242" s="32">
@@ -12194,7 +12205,7 @@
         <v/>
       </c>
       <c r="K242" s="32">
-        <f>IF(NOT(AND($A242&lt;&gt;"",OR($G242="",$G242="Active"))),"",IF($L242&lt;&gt;"",IF($L242=$M242,"Booking",INDEX($N$4:$U$4,MATCH($L242,$N242:$U242,0))),IF(COUNTIF($N242:$U242,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N242:$U242)=0,"All done",IF(MAX($M242:$U242)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A242&lt;&gt;"",OR($G242="",$G242="Active"))),"",IF($L242&lt;&gt;"",IF($L242=$M242,"Booking",INDEX($N$4:$U$4,MATCH($L242,$N242:$U242,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M242:$U242)+($M242:$U242="DNA")),$M242:$U242),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M242:$U242)+($M242:$U242="DNA")),$M242:$U242),"")),IF(ISNUMBER($U242),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L242" s="33">
@@ -12232,7 +12243,7 @@
         <v/>
       </c>
       <c r="I243" s="32">
-        <f>IF(NOT(AND($A243&lt;&gt;"",OR($G243="",$G243="Active"))),"",IF(AND(MAX($M243:$U243)&gt;0,MAX($M243:$U243)&lt;TODAY(),COUNTBLANK($N243:$U243)&gt;0,COUNTIF($N243:$U243,"DNA")=0),1,0)+COUNTIF($N243:$U243,"DNA")+COUNTIF($V243:$Z243,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A243&lt;&gt;"",OR($G243="",$G243="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M243:$U243)+($M243:$U243="DNA")),$M243:$U243),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M243:$U243)+($M243:$U243="DNA")),$M243:$U243),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M243:$U243)+($M243:$U243="DNA")),$M243:$U243),"")&lt;TODAY())),1,0)+COUNTIF($V243:$Z243,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J243" s="32">
@@ -12240,7 +12251,7 @@
         <v/>
       </c>
       <c r="K243" s="32">
-        <f>IF(NOT(AND($A243&lt;&gt;"",OR($G243="",$G243="Active"))),"",IF($L243&lt;&gt;"",IF($L243=$M243,"Booking",INDEX($N$4:$U$4,MATCH($L243,$N243:$U243,0))),IF(COUNTIF($N243:$U243,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N243:$U243)=0,"All done",IF(MAX($M243:$U243)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A243&lt;&gt;"",OR($G243="",$G243="Active"))),"",IF($L243&lt;&gt;"",IF($L243=$M243,"Booking",INDEX($N$4:$U$4,MATCH($L243,$N243:$U243,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M243:$U243)+($M243:$U243="DNA")),$M243:$U243),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M243:$U243)+($M243:$U243="DNA")),$M243:$U243),"")),IF(ISNUMBER($U243),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L243" s="33">
@@ -12278,7 +12289,7 @@
         <v/>
       </c>
       <c r="I244" s="32">
-        <f>IF(NOT(AND($A244&lt;&gt;"",OR($G244="",$G244="Active"))),"",IF(AND(MAX($M244:$U244)&gt;0,MAX($M244:$U244)&lt;TODAY(),COUNTBLANK($N244:$U244)&gt;0,COUNTIF($N244:$U244,"DNA")=0),1,0)+COUNTIF($N244:$U244,"DNA")+COUNTIF($V244:$Z244,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A244&lt;&gt;"",OR($G244="",$G244="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M244:$U244)+($M244:$U244="DNA")),$M244:$U244),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M244:$U244)+($M244:$U244="DNA")),$M244:$U244),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M244:$U244)+($M244:$U244="DNA")),$M244:$U244),"")&lt;TODAY())),1,0)+COUNTIF($V244:$Z244,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J244" s="32">
@@ -12286,7 +12297,7 @@
         <v/>
       </c>
       <c r="K244" s="32">
-        <f>IF(NOT(AND($A244&lt;&gt;"",OR($G244="",$G244="Active"))),"",IF($L244&lt;&gt;"",IF($L244=$M244,"Booking",INDEX($N$4:$U$4,MATCH($L244,$N244:$U244,0))),IF(COUNTIF($N244:$U244,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N244:$U244)=0,"All done",IF(MAX($M244:$U244)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A244&lt;&gt;"",OR($G244="",$G244="Active"))),"",IF($L244&lt;&gt;"",IF($L244=$M244,"Booking",INDEX($N$4:$U$4,MATCH($L244,$N244:$U244,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M244:$U244)+($M244:$U244="DNA")),$M244:$U244),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M244:$U244)+($M244:$U244="DNA")),$M244:$U244),"")),IF(ISNUMBER($U244),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L244" s="33">
@@ -12324,7 +12335,7 @@
         <v/>
       </c>
       <c r="I245" s="32">
-        <f>IF(NOT(AND($A245&lt;&gt;"",OR($G245="",$G245="Active"))),"",IF(AND(MAX($M245:$U245)&gt;0,MAX($M245:$U245)&lt;TODAY(),COUNTBLANK($N245:$U245)&gt;0,COUNTIF($N245:$U245,"DNA")=0),1,0)+COUNTIF($N245:$U245,"DNA")+COUNTIF($V245:$Z245,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A245&lt;&gt;"",OR($G245="",$G245="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M245:$U245)+($M245:$U245="DNA")),$M245:$U245),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M245:$U245)+($M245:$U245="DNA")),$M245:$U245),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M245:$U245)+($M245:$U245="DNA")),$M245:$U245),"")&lt;TODAY())),1,0)+COUNTIF($V245:$Z245,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J245" s="32">
@@ -12332,7 +12343,7 @@
         <v/>
       </c>
       <c r="K245" s="32">
-        <f>IF(NOT(AND($A245&lt;&gt;"",OR($G245="",$G245="Active"))),"",IF($L245&lt;&gt;"",IF($L245=$M245,"Booking",INDEX($N$4:$U$4,MATCH($L245,$N245:$U245,0))),IF(COUNTIF($N245:$U245,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N245:$U245)=0,"All done",IF(MAX($M245:$U245)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A245&lt;&gt;"",OR($G245="",$G245="Active"))),"",IF($L245&lt;&gt;"",IF($L245=$M245,"Booking",INDEX($N$4:$U$4,MATCH($L245,$N245:$U245,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M245:$U245)+($M245:$U245="DNA")),$M245:$U245),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M245:$U245)+($M245:$U245="DNA")),$M245:$U245),"")),IF(ISNUMBER($U245),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L245" s="33">
@@ -12370,7 +12381,7 @@
         <v/>
       </c>
       <c r="I246" s="32">
-        <f>IF(NOT(AND($A246&lt;&gt;"",OR($G246="",$G246="Active"))),"",IF(AND(MAX($M246:$U246)&gt;0,MAX($M246:$U246)&lt;TODAY(),COUNTBLANK($N246:$U246)&gt;0,COUNTIF($N246:$U246,"DNA")=0),1,0)+COUNTIF($N246:$U246,"DNA")+COUNTIF($V246:$Z246,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A246&lt;&gt;"",OR($G246="",$G246="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M246:$U246)+($M246:$U246="DNA")),$M246:$U246),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M246:$U246)+($M246:$U246="DNA")),$M246:$U246),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M246:$U246)+($M246:$U246="DNA")),$M246:$U246),"")&lt;TODAY())),1,0)+COUNTIF($V246:$Z246,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J246" s="32">
@@ -12378,7 +12389,7 @@
         <v/>
       </c>
       <c r="K246" s="32">
-        <f>IF(NOT(AND($A246&lt;&gt;"",OR($G246="",$G246="Active"))),"",IF($L246&lt;&gt;"",IF($L246=$M246,"Booking",INDEX($N$4:$U$4,MATCH($L246,$N246:$U246,0))),IF(COUNTIF($N246:$U246,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N246:$U246)=0,"All done",IF(MAX($M246:$U246)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A246&lt;&gt;"",OR($G246="",$G246="Active"))),"",IF($L246&lt;&gt;"",IF($L246=$M246,"Booking",INDEX($N$4:$U$4,MATCH($L246,$N246:$U246,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M246:$U246)+($M246:$U246="DNA")),$M246:$U246),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M246:$U246)+($M246:$U246="DNA")),$M246:$U246),"")),IF(ISNUMBER($U246),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L246" s="33">
@@ -12416,7 +12427,7 @@
         <v/>
       </c>
       <c r="I247" s="32">
-        <f>IF(NOT(AND($A247&lt;&gt;"",OR($G247="",$G247="Active"))),"",IF(AND(MAX($M247:$U247)&gt;0,MAX($M247:$U247)&lt;TODAY(),COUNTBLANK($N247:$U247)&gt;0,COUNTIF($N247:$U247,"DNA")=0),1,0)+COUNTIF($N247:$U247,"DNA")+COUNTIF($V247:$Z247,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A247&lt;&gt;"",OR($G247="",$G247="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M247:$U247)+($M247:$U247="DNA")),$M247:$U247),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M247:$U247)+($M247:$U247="DNA")),$M247:$U247),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M247:$U247)+($M247:$U247="DNA")),$M247:$U247),"")&lt;TODAY())),1,0)+COUNTIF($V247:$Z247,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J247" s="32">
@@ -12424,7 +12435,7 @@
         <v/>
       </c>
       <c r="K247" s="32">
-        <f>IF(NOT(AND($A247&lt;&gt;"",OR($G247="",$G247="Active"))),"",IF($L247&lt;&gt;"",IF($L247=$M247,"Booking",INDEX($N$4:$U$4,MATCH($L247,$N247:$U247,0))),IF(COUNTIF($N247:$U247,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N247:$U247)=0,"All done",IF(MAX($M247:$U247)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A247&lt;&gt;"",OR($G247="",$G247="Active"))),"",IF($L247&lt;&gt;"",IF($L247=$M247,"Booking",INDEX($N$4:$U$4,MATCH($L247,$N247:$U247,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M247:$U247)+($M247:$U247="DNA")),$M247:$U247),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M247:$U247)+($M247:$U247="DNA")),$M247:$U247),"")),IF(ISNUMBER($U247),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L247" s="33">
@@ -12462,7 +12473,7 @@
         <v/>
       </c>
       <c r="I248" s="32">
-        <f>IF(NOT(AND($A248&lt;&gt;"",OR($G248="",$G248="Active"))),"",IF(AND(MAX($M248:$U248)&gt;0,MAX($M248:$U248)&lt;TODAY(),COUNTBLANK($N248:$U248)&gt;0,COUNTIF($N248:$U248,"DNA")=0),1,0)+COUNTIF($N248:$U248,"DNA")+COUNTIF($V248:$Z248,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A248&lt;&gt;"",OR($G248="",$G248="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M248:$U248)+($M248:$U248="DNA")),$M248:$U248),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M248:$U248)+($M248:$U248="DNA")),$M248:$U248),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M248:$U248)+($M248:$U248="DNA")),$M248:$U248),"")&lt;TODAY())),1,0)+COUNTIF($V248:$Z248,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J248" s="32">
@@ -12470,7 +12481,7 @@
         <v/>
       </c>
       <c r="K248" s="32">
-        <f>IF(NOT(AND($A248&lt;&gt;"",OR($G248="",$G248="Active"))),"",IF($L248&lt;&gt;"",IF($L248=$M248,"Booking",INDEX($N$4:$U$4,MATCH($L248,$N248:$U248,0))),IF(COUNTIF($N248:$U248,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N248:$U248)=0,"All done",IF(MAX($M248:$U248)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A248&lt;&gt;"",OR($G248="",$G248="Active"))),"",IF($L248&lt;&gt;"",IF($L248=$M248,"Booking",INDEX($N$4:$U$4,MATCH($L248,$N248:$U248,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M248:$U248)+($M248:$U248="DNA")),$M248:$U248),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M248:$U248)+($M248:$U248="DNA")),$M248:$U248),"")),IF(ISNUMBER($U248),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L248" s="33">
@@ -12508,7 +12519,7 @@
         <v/>
       </c>
       <c r="I249" s="32">
-        <f>IF(NOT(AND($A249&lt;&gt;"",OR($G249="",$G249="Active"))),"",IF(AND(MAX($M249:$U249)&gt;0,MAX($M249:$U249)&lt;TODAY(),COUNTBLANK($N249:$U249)&gt;0,COUNTIF($N249:$U249,"DNA")=0),1,0)+COUNTIF($N249:$U249,"DNA")+COUNTIF($V249:$Z249,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A249&lt;&gt;"",OR($G249="",$G249="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M249:$U249)+($M249:$U249="DNA")),$M249:$U249),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M249:$U249)+($M249:$U249="DNA")),$M249:$U249),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M249:$U249)+($M249:$U249="DNA")),$M249:$U249),"")&lt;TODAY())),1,0)+COUNTIF($V249:$Z249,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J249" s="32">
@@ -12516,7 +12527,7 @@
         <v/>
       </c>
       <c r="K249" s="32">
-        <f>IF(NOT(AND($A249&lt;&gt;"",OR($G249="",$G249="Active"))),"",IF($L249&lt;&gt;"",IF($L249=$M249,"Booking",INDEX($N$4:$U$4,MATCH($L249,$N249:$U249,0))),IF(COUNTIF($N249:$U249,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N249:$U249)=0,"All done",IF(MAX($M249:$U249)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A249&lt;&gt;"",OR($G249="",$G249="Active"))),"",IF($L249&lt;&gt;"",IF($L249=$M249,"Booking",INDEX($N$4:$U$4,MATCH($L249,$N249:$U249,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M249:$U249)+($M249:$U249="DNA")),$M249:$U249),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M249:$U249)+($M249:$U249="DNA")),$M249:$U249),"")),IF(ISNUMBER($U249),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L249" s="33">
@@ -12554,7 +12565,7 @@
         <v/>
       </c>
       <c r="I250" s="32">
-        <f>IF(NOT(AND($A250&lt;&gt;"",OR($G250="",$G250="Active"))),"",IF(AND(MAX($M250:$U250)&gt;0,MAX($M250:$U250)&lt;TODAY(),COUNTBLANK($N250:$U250)&gt;0,COUNTIF($N250:$U250,"DNA")=0),1,0)+COUNTIF($N250:$U250,"DNA")+COUNTIF($V250:$Z250,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A250&lt;&gt;"",OR($G250="",$G250="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M250:$U250)+($M250:$U250="DNA")),$M250:$U250),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M250:$U250)+($M250:$U250="DNA")),$M250:$U250),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M250:$U250)+($M250:$U250="DNA")),$M250:$U250),"")&lt;TODAY())),1,0)+COUNTIF($V250:$Z250,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J250" s="32">
@@ -12562,7 +12573,7 @@
         <v/>
       </c>
       <c r="K250" s="32">
-        <f>IF(NOT(AND($A250&lt;&gt;"",OR($G250="",$G250="Active"))),"",IF($L250&lt;&gt;"",IF($L250=$M250,"Booking",INDEX($N$4:$U$4,MATCH($L250,$N250:$U250,0))),IF(COUNTIF($N250:$U250,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N250:$U250)=0,"All done",IF(MAX($M250:$U250)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A250&lt;&gt;"",OR($G250="",$G250="Active"))),"",IF($L250&lt;&gt;"",IF($L250=$M250,"Booking",INDEX($N$4:$U$4,MATCH($L250,$N250:$U250,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M250:$U250)+($M250:$U250="DNA")),$M250:$U250),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M250:$U250)+($M250:$U250="DNA")),$M250:$U250),"")),IF(ISNUMBER($U250),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L250" s="33">
@@ -12600,7 +12611,7 @@
         <v/>
       </c>
       <c r="I251" s="32">
-        <f>IF(NOT(AND($A251&lt;&gt;"",OR($G251="",$G251="Active"))),"",IF(AND(MAX($M251:$U251)&gt;0,MAX($M251:$U251)&lt;TODAY(),COUNTBLANK($N251:$U251)&gt;0,COUNTIF($N251:$U251,"DNA")=0),1,0)+COUNTIF($N251:$U251,"DNA")+COUNTIF($V251:$Z251,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A251&lt;&gt;"",OR($G251="",$G251="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M251:$U251)+($M251:$U251="DNA")),$M251:$U251),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M251:$U251)+($M251:$U251="DNA")),$M251:$U251),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M251:$U251)+($M251:$U251="DNA")),$M251:$U251),"")&lt;TODAY())),1,0)+COUNTIF($V251:$Z251,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J251" s="32">
@@ -12608,7 +12619,7 @@
         <v/>
       </c>
       <c r="K251" s="32">
-        <f>IF(NOT(AND($A251&lt;&gt;"",OR($G251="",$G251="Active"))),"",IF($L251&lt;&gt;"",IF($L251=$M251,"Booking",INDEX($N$4:$U$4,MATCH($L251,$N251:$U251,0))),IF(COUNTIF($N251:$U251,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N251:$U251)=0,"All done",IF(MAX($M251:$U251)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A251&lt;&gt;"",OR($G251="",$G251="Active"))),"",IF($L251&lt;&gt;"",IF($L251=$M251,"Booking",INDEX($N$4:$U$4,MATCH($L251,$N251:$U251,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M251:$U251)+($M251:$U251="DNA")),$M251:$U251),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M251:$U251)+($M251:$U251="DNA")),$M251:$U251),"")),IF(ISNUMBER($U251),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L251" s="33">
@@ -12646,7 +12657,7 @@
         <v/>
       </c>
       <c r="I252" s="32">
-        <f>IF(NOT(AND($A252&lt;&gt;"",OR($G252="",$G252="Active"))),"",IF(AND(MAX($M252:$U252)&gt;0,MAX($M252:$U252)&lt;TODAY(),COUNTBLANK($N252:$U252)&gt;0,COUNTIF($N252:$U252,"DNA")=0),1,0)+COUNTIF($N252:$U252,"DNA")+COUNTIF($V252:$Z252,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A252&lt;&gt;"",OR($G252="",$G252="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M252:$U252)+($M252:$U252="DNA")),$M252:$U252),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M252:$U252)+($M252:$U252="DNA")),$M252:$U252),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M252:$U252)+($M252:$U252="DNA")),$M252:$U252),"")&lt;TODAY())),1,0)+COUNTIF($V252:$Z252,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J252" s="32">
@@ -12654,7 +12665,7 @@
         <v/>
       </c>
       <c r="K252" s="32">
-        <f>IF(NOT(AND($A252&lt;&gt;"",OR($G252="",$G252="Active"))),"",IF($L252&lt;&gt;"",IF($L252=$M252,"Booking",INDEX($N$4:$U$4,MATCH($L252,$N252:$U252,0))),IF(COUNTIF($N252:$U252,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N252:$U252)=0,"All done",IF(MAX($M252:$U252)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A252&lt;&gt;"",OR($G252="",$G252="Active"))),"",IF($L252&lt;&gt;"",IF($L252=$M252,"Booking",INDEX($N$4:$U$4,MATCH($L252,$N252:$U252,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M252:$U252)+($M252:$U252="DNA")),$M252:$U252),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M252:$U252)+($M252:$U252="DNA")),$M252:$U252),"")),IF(ISNUMBER($U252),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L252" s="33">
@@ -12692,7 +12703,7 @@
         <v/>
       </c>
       <c r="I253" s="32">
-        <f>IF(NOT(AND($A253&lt;&gt;"",OR($G253="",$G253="Active"))),"",IF(AND(MAX($M253:$U253)&gt;0,MAX($M253:$U253)&lt;TODAY(),COUNTBLANK($N253:$U253)&gt;0,COUNTIF($N253:$U253,"DNA")=0),1,0)+COUNTIF($N253:$U253,"DNA")+COUNTIF($V253:$Z253,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A253&lt;&gt;"",OR($G253="",$G253="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M253:$U253)+($M253:$U253="DNA")),$M253:$U253),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M253:$U253)+($M253:$U253="DNA")),$M253:$U253),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M253:$U253)+($M253:$U253="DNA")),$M253:$U253),"")&lt;TODAY())),1,0)+COUNTIF($V253:$Z253,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J253" s="32">
@@ -12700,7 +12711,7 @@
         <v/>
       </c>
       <c r="K253" s="32">
-        <f>IF(NOT(AND($A253&lt;&gt;"",OR($G253="",$G253="Active"))),"",IF($L253&lt;&gt;"",IF($L253=$M253,"Booking",INDEX($N$4:$U$4,MATCH($L253,$N253:$U253,0))),IF(COUNTIF($N253:$U253,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N253:$U253)=0,"All done",IF(MAX($M253:$U253)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A253&lt;&gt;"",OR($G253="",$G253="Active"))),"",IF($L253&lt;&gt;"",IF($L253=$M253,"Booking",INDEX($N$4:$U$4,MATCH($L253,$N253:$U253,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M253:$U253)+($M253:$U253="DNA")),$M253:$U253),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M253:$U253)+($M253:$U253="DNA")),$M253:$U253),"")),IF(ISNUMBER($U253),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L253" s="33">
@@ -12738,7 +12749,7 @@
         <v/>
       </c>
       <c r="I254" s="32">
-        <f>IF(NOT(AND($A254&lt;&gt;"",OR($G254="",$G254="Active"))),"",IF(AND(MAX($M254:$U254)&gt;0,MAX($M254:$U254)&lt;TODAY(),COUNTBLANK($N254:$U254)&gt;0,COUNTIF($N254:$U254,"DNA")=0),1,0)+COUNTIF($N254:$U254,"DNA")+COUNTIF($V254:$Z254,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A254&lt;&gt;"",OR($G254="",$G254="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M254:$U254)+($M254:$U254="DNA")),$M254:$U254),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M254:$U254)+($M254:$U254="DNA")),$M254:$U254),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M254:$U254)+($M254:$U254="DNA")),$M254:$U254),"")&lt;TODAY())),1,0)+COUNTIF($V254:$Z254,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J254" s="32">
@@ -12746,7 +12757,7 @@
         <v/>
       </c>
       <c r="K254" s="32">
-        <f>IF(NOT(AND($A254&lt;&gt;"",OR($G254="",$G254="Active"))),"",IF($L254&lt;&gt;"",IF($L254=$M254,"Booking",INDEX($N$4:$U$4,MATCH($L254,$N254:$U254,0))),IF(COUNTIF($N254:$U254,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N254:$U254)=0,"All done",IF(MAX($M254:$U254)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A254&lt;&gt;"",OR($G254="",$G254="Active"))),"",IF($L254&lt;&gt;"",IF($L254=$M254,"Booking",INDEX($N$4:$U$4,MATCH($L254,$N254:$U254,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M254:$U254)+($M254:$U254="DNA")),$M254:$U254),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M254:$U254)+($M254:$U254="DNA")),$M254:$U254),"")),IF(ISNUMBER($U254),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L254" s="33">
@@ -12784,7 +12795,7 @@
         <v/>
       </c>
       <c r="I255" s="32">
-        <f>IF(NOT(AND($A255&lt;&gt;"",OR($G255="",$G255="Active"))),"",IF(AND(MAX($M255:$U255)&gt;0,MAX($M255:$U255)&lt;TODAY(),COUNTBLANK($N255:$U255)&gt;0,COUNTIF($N255:$U255,"DNA")=0),1,0)+COUNTIF($N255:$U255,"DNA")+COUNTIF($V255:$Z255,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A255&lt;&gt;"",OR($G255="",$G255="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M255:$U255)+($M255:$U255="DNA")),$M255:$U255),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M255:$U255)+($M255:$U255="DNA")),$M255:$U255),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M255:$U255)+($M255:$U255="DNA")),$M255:$U255),"")&lt;TODAY())),1,0)+COUNTIF($V255:$Z255,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J255" s="32">
@@ -12792,7 +12803,7 @@
         <v/>
       </c>
       <c r="K255" s="32">
-        <f>IF(NOT(AND($A255&lt;&gt;"",OR($G255="",$G255="Active"))),"",IF($L255&lt;&gt;"",IF($L255=$M255,"Booking",INDEX($N$4:$U$4,MATCH($L255,$N255:$U255,0))),IF(COUNTIF($N255:$U255,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N255:$U255)=0,"All done",IF(MAX($M255:$U255)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A255&lt;&gt;"",OR($G255="",$G255="Active"))),"",IF($L255&lt;&gt;"",IF($L255=$M255,"Booking",INDEX($N$4:$U$4,MATCH($L255,$N255:$U255,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M255:$U255)+($M255:$U255="DNA")),$M255:$U255),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M255:$U255)+($M255:$U255="DNA")),$M255:$U255),"")),IF(ISNUMBER($U255),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L255" s="33">
@@ -12830,7 +12841,7 @@
         <v/>
       </c>
       <c r="I256" s="32">
-        <f>IF(NOT(AND($A256&lt;&gt;"",OR($G256="",$G256="Active"))),"",IF(AND(MAX($M256:$U256)&gt;0,MAX($M256:$U256)&lt;TODAY(),COUNTBLANK($N256:$U256)&gt;0,COUNTIF($N256:$U256,"DNA")=0),1,0)+COUNTIF($N256:$U256,"DNA")+COUNTIF($V256:$Z256,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A256&lt;&gt;"",OR($G256="",$G256="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M256:$U256)+($M256:$U256="DNA")),$M256:$U256),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M256:$U256)+($M256:$U256="DNA")),$M256:$U256),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M256:$U256)+($M256:$U256="DNA")),$M256:$U256),"")&lt;TODAY())),1,0)+COUNTIF($V256:$Z256,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J256" s="32">
@@ -12838,7 +12849,7 @@
         <v/>
       </c>
       <c r="K256" s="32">
-        <f>IF(NOT(AND($A256&lt;&gt;"",OR($G256="",$G256="Active"))),"",IF($L256&lt;&gt;"",IF($L256=$M256,"Booking",INDEX($N$4:$U$4,MATCH($L256,$N256:$U256,0))),IF(COUNTIF($N256:$U256,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N256:$U256)=0,"All done",IF(MAX($M256:$U256)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A256&lt;&gt;"",OR($G256="",$G256="Active"))),"",IF($L256&lt;&gt;"",IF($L256=$M256,"Booking",INDEX($N$4:$U$4,MATCH($L256,$N256:$U256,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M256:$U256)+($M256:$U256="DNA")),$M256:$U256),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M256:$U256)+($M256:$U256="DNA")),$M256:$U256),"")),IF(ISNUMBER($U256),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L256" s="33">
@@ -12876,7 +12887,7 @@
         <v/>
       </c>
       <c r="I257" s="32">
-        <f>IF(NOT(AND($A257&lt;&gt;"",OR($G257="",$G257="Active"))),"",IF(AND(MAX($M257:$U257)&gt;0,MAX($M257:$U257)&lt;TODAY(),COUNTBLANK($N257:$U257)&gt;0,COUNTIF($N257:$U257,"DNA")=0),1,0)+COUNTIF($N257:$U257,"DNA")+COUNTIF($V257:$Z257,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A257&lt;&gt;"",OR($G257="",$G257="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M257:$U257)+($M257:$U257="DNA")),$M257:$U257),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M257:$U257)+($M257:$U257="DNA")),$M257:$U257),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M257:$U257)+($M257:$U257="DNA")),$M257:$U257),"")&lt;TODAY())),1,0)+COUNTIF($V257:$Z257,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J257" s="32">
@@ -12884,7 +12895,7 @@
         <v/>
       </c>
       <c r="K257" s="32">
-        <f>IF(NOT(AND($A257&lt;&gt;"",OR($G257="",$G257="Active"))),"",IF($L257&lt;&gt;"",IF($L257=$M257,"Booking",INDEX($N$4:$U$4,MATCH($L257,$N257:$U257,0))),IF(COUNTIF($N257:$U257,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N257:$U257)=0,"All done",IF(MAX($M257:$U257)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A257&lt;&gt;"",OR($G257="",$G257="Active"))),"",IF($L257&lt;&gt;"",IF($L257=$M257,"Booking",INDEX($N$4:$U$4,MATCH($L257,$N257:$U257,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M257:$U257)+($M257:$U257="DNA")),$M257:$U257),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M257:$U257)+($M257:$U257="DNA")),$M257:$U257),"")),IF(ISNUMBER($U257),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L257" s="33">
@@ -12922,7 +12933,7 @@
         <v/>
       </c>
       <c r="I258" s="32">
-        <f>IF(NOT(AND($A258&lt;&gt;"",OR($G258="",$G258="Active"))),"",IF(AND(MAX($M258:$U258)&gt;0,MAX($M258:$U258)&lt;TODAY(),COUNTBLANK($N258:$U258)&gt;0,COUNTIF($N258:$U258,"DNA")=0),1,0)+COUNTIF($N258:$U258,"DNA")+COUNTIF($V258:$Z258,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A258&lt;&gt;"",OR($G258="",$G258="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M258:$U258)+($M258:$U258="DNA")),$M258:$U258),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M258:$U258)+($M258:$U258="DNA")),$M258:$U258),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M258:$U258)+($M258:$U258="DNA")),$M258:$U258),"")&lt;TODAY())),1,0)+COUNTIF($V258:$Z258,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J258" s="32">
@@ -12930,7 +12941,7 @@
         <v/>
       </c>
       <c r="K258" s="32">
-        <f>IF(NOT(AND($A258&lt;&gt;"",OR($G258="",$G258="Active"))),"",IF($L258&lt;&gt;"",IF($L258=$M258,"Booking",INDEX($N$4:$U$4,MATCH($L258,$N258:$U258,0))),IF(COUNTIF($N258:$U258,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N258:$U258)=0,"All done",IF(MAX($M258:$U258)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A258&lt;&gt;"",OR($G258="",$G258="Active"))),"",IF($L258&lt;&gt;"",IF($L258=$M258,"Booking",INDEX($N$4:$U$4,MATCH($L258,$N258:$U258,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M258:$U258)+($M258:$U258="DNA")),$M258:$U258),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M258:$U258)+($M258:$U258="DNA")),$M258:$U258),"")),IF(ISNUMBER($U258),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L258" s="33">
@@ -12968,7 +12979,7 @@
         <v/>
       </c>
       <c r="I259" s="32">
-        <f>IF(NOT(AND($A259&lt;&gt;"",OR($G259="",$G259="Active"))),"",IF(AND(MAX($M259:$U259)&gt;0,MAX($M259:$U259)&lt;TODAY(),COUNTBLANK($N259:$U259)&gt;0,COUNTIF($N259:$U259,"DNA")=0),1,0)+COUNTIF($N259:$U259,"DNA")+COUNTIF($V259:$Z259,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A259&lt;&gt;"",OR($G259="",$G259="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M259:$U259)+($M259:$U259="DNA")),$M259:$U259),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M259:$U259)+($M259:$U259="DNA")),$M259:$U259),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M259:$U259)+($M259:$U259="DNA")),$M259:$U259),"")&lt;TODAY())),1,0)+COUNTIF($V259:$Z259,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J259" s="32">
@@ -12976,7 +12987,7 @@
         <v/>
       </c>
       <c r="K259" s="32">
-        <f>IF(NOT(AND($A259&lt;&gt;"",OR($G259="",$G259="Active"))),"",IF($L259&lt;&gt;"",IF($L259=$M259,"Booking",INDEX($N$4:$U$4,MATCH($L259,$N259:$U259,0))),IF(COUNTIF($N259:$U259,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N259:$U259)=0,"All done",IF(MAX($M259:$U259)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A259&lt;&gt;"",OR($G259="",$G259="Active"))),"",IF($L259&lt;&gt;"",IF($L259=$M259,"Booking",INDEX($N$4:$U$4,MATCH($L259,$N259:$U259,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M259:$U259)+($M259:$U259="DNA")),$M259:$U259),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M259:$U259)+($M259:$U259="DNA")),$M259:$U259),"")),IF(ISNUMBER($U259),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L259" s="33">
@@ -13014,7 +13025,7 @@
         <v/>
       </c>
       <c r="I260" s="32">
-        <f>IF(NOT(AND($A260&lt;&gt;"",OR($G260="",$G260="Active"))),"",IF(AND(MAX($M260:$U260)&gt;0,MAX($M260:$U260)&lt;TODAY(),COUNTBLANK($N260:$U260)&gt;0,COUNTIF($N260:$U260,"DNA")=0),1,0)+COUNTIF($N260:$U260,"DNA")+COUNTIF($V260:$Z260,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A260&lt;&gt;"",OR($G260="",$G260="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M260:$U260)+($M260:$U260="DNA")),$M260:$U260),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M260:$U260)+($M260:$U260="DNA")),$M260:$U260),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M260:$U260)+($M260:$U260="DNA")),$M260:$U260),"")&lt;TODAY())),1,0)+COUNTIF($V260:$Z260,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J260" s="32">
@@ -13022,7 +13033,7 @@
         <v/>
       </c>
       <c r="K260" s="32">
-        <f>IF(NOT(AND($A260&lt;&gt;"",OR($G260="",$G260="Active"))),"",IF($L260&lt;&gt;"",IF($L260=$M260,"Booking",INDEX($N$4:$U$4,MATCH($L260,$N260:$U260,0))),IF(COUNTIF($N260:$U260,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N260:$U260)=0,"All done",IF(MAX($M260:$U260)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A260&lt;&gt;"",OR($G260="",$G260="Active"))),"",IF($L260&lt;&gt;"",IF($L260=$M260,"Booking",INDEX($N$4:$U$4,MATCH($L260,$N260:$U260,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M260:$U260)+($M260:$U260="DNA")),$M260:$U260),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M260:$U260)+($M260:$U260="DNA")),$M260:$U260),"")),IF(ISNUMBER($U260),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L260" s="33">
@@ -13060,7 +13071,7 @@
         <v/>
       </c>
       <c r="I261" s="32">
-        <f>IF(NOT(AND($A261&lt;&gt;"",OR($G261="",$G261="Active"))),"",IF(AND(MAX($M261:$U261)&gt;0,MAX($M261:$U261)&lt;TODAY(),COUNTBLANK($N261:$U261)&gt;0,COUNTIF($N261:$U261,"DNA")=0),1,0)+COUNTIF($N261:$U261,"DNA")+COUNTIF($V261:$Z261,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A261&lt;&gt;"",OR($G261="",$G261="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M261:$U261)+($M261:$U261="DNA")),$M261:$U261),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M261:$U261)+($M261:$U261="DNA")),$M261:$U261),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M261:$U261)+($M261:$U261="DNA")),$M261:$U261),"")&lt;TODAY())),1,0)+COUNTIF($V261:$Z261,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J261" s="32">
@@ -13068,7 +13079,7 @@
         <v/>
       </c>
       <c r="K261" s="32">
-        <f>IF(NOT(AND($A261&lt;&gt;"",OR($G261="",$G261="Active"))),"",IF($L261&lt;&gt;"",IF($L261=$M261,"Booking",INDEX($N$4:$U$4,MATCH($L261,$N261:$U261,0))),IF(COUNTIF($N261:$U261,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N261:$U261)=0,"All done",IF(MAX($M261:$U261)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A261&lt;&gt;"",OR($G261="",$G261="Active"))),"",IF($L261&lt;&gt;"",IF($L261=$M261,"Booking",INDEX($N$4:$U$4,MATCH($L261,$N261:$U261,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M261:$U261)+($M261:$U261="DNA")),$M261:$U261),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M261:$U261)+($M261:$U261="DNA")),$M261:$U261),"")),IF(ISNUMBER($U261),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L261" s="33">
@@ -13106,7 +13117,7 @@
         <v/>
       </c>
       <c r="I262" s="32">
-        <f>IF(NOT(AND($A262&lt;&gt;"",OR($G262="",$G262="Active"))),"",IF(AND(MAX($M262:$U262)&gt;0,MAX($M262:$U262)&lt;TODAY(),COUNTBLANK($N262:$U262)&gt;0,COUNTIF($N262:$U262,"DNA")=0),1,0)+COUNTIF($N262:$U262,"DNA")+COUNTIF($V262:$Z262,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A262&lt;&gt;"",OR($G262="",$G262="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M262:$U262)+($M262:$U262="DNA")),$M262:$U262),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M262:$U262)+($M262:$U262="DNA")),$M262:$U262),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M262:$U262)+($M262:$U262="DNA")),$M262:$U262),"")&lt;TODAY())),1,0)+COUNTIF($V262:$Z262,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J262" s="32">
@@ -13114,7 +13125,7 @@
         <v/>
       </c>
       <c r="K262" s="32">
-        <f>IF(NOT(AND($A262&lt;&gt;"",OR($G262="",$G262="Active"))),"",IF($L262&lt;&gt;"",IF($L262=$M262,"Booking",INDEX($N$4:$U$4,MATCH($L262,$N262:$U262,0))),IF(COUNTIF($N262:$U262,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N262:$U262)=0,"All done",IF(MAX($M262:$U262)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A262&lt;&gt;"",OR($G262="",$G262="Active"))),"",IF($L262&lt;&gt;"",IF($L262=$M262,"Booking",INDEX($N$4:$U$4,MATCH($L262,$N262:$U262,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M262:$U262)+($M262:$U262="DNA")),$M262:$U262),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M262:$U262)+($M262:$U262="DNA")),$M262:$U262),"")),IF(ISNUMBER($U262),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L262" s="33">
@@ -13152,7 +13163,7 @@
         <v/>
       </c>
       <c r="I263" s="32">
-        <f>IF(NOT(AND($A263&lt;&gt;"",OR($G263="",$G263="Active"))),"",IF(AND(MAX($M263:$U263)&gt;0,MAX($M263:$U263)&lt;TODAY(),COUNTBLANK($N263:$U263)&gt;0,COUNTIF($N263:$U263,"DNA")=0),1,0)+COUNTIF($N263:$U263,"DNA")+COUNTIF($V263:$Z263,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A263&lt;&gt;"",OR($G263="",$G263="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M263:$U263)+($M263:$U263="DNA")),$M263:$U263),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M263:$U263)+($M263:$U263="DNA")),$M263:$U263),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M263:$U263)+($M263:$U263="DNA")),$M263:$U263),"")&lt;TODAY())),1,0)+COUNTIF($V263:$Z263,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J263" s="32">
@@ -13160,7 +13171,7 @@
         <v/>
       </c>
       <c r="K263" s="32">
-        <f>IF(NOT(AND($A263&lt;&gt;"",OR($G263="",$G263="Active"))),"",IF($L263&lt;&gt;"",IF($L263=$M263,"Booking",INDEX($N$4:$U$4,MATCH($L263,$N263:$U263,0))),IF(COUNTIF($N263:$U263,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N263:$U263)=0,"All done",IF(MAX($M263:$U263)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A263&lt;&gt;"",OR($G263="",$G263="Active"))),"",IF($L263&lt;&gt;"",IF($L263=$M263,"Booking",INDEX($N$4:$U$4,MATCH($L263,$N263:$U263,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M263:$U263)+($M263:$U263="DNA")),$M263:$U263),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M263:$U263)+($M263:$U263="DNA")),$M263:$U263),"")),IF(ISNUMBER($U263),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L263" s="33">
@@ -13198,7 +13209,7 @@
         <v/>
       </c>
       <c r="I264" s="32">
-        <f>IF(NOT(AND($A264&lt;&gt;"",OR($G264="",$G264="Active"))),"",IF(AND(MAX($M264:$U264)&gt;0,MAX($M264:$U264)&lt;TODAY(),COUNTBLANK($N264:$U264)&gt;0,COUNTIF($N264:$U264,"DNA")=0),1,0)+COUNTIF($N264:$U264,"DNA")+COUNTIF($V264:$Z264,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A264&lt;&gt;"",OR($G264="",$G264="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M264:$U264)+($M264:$U264="DNA")),$M264:$U264),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M264:$U264)+($M264:$U264="DNA")),$M264:$U264),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M264:$U264)+($M264:$U264="DNA")),$M264:$U264),"")&lt;TODAY())),1,0)+COUNTIF($V264:$Z264,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J264" s="32">
@@ -13206,7 +13217,7 @@
         <v/>
       </c>
       <c r="K264" s="32">
-        <f>IF(NOT(AND($A264&lt;&gt;"",OR($G264="",$G264="Active"))),"",IF($L264&lt;&gt;"",IF($L264=$M264,"Booking",INDEX($N$4:$U$4,MATCH($L264,$N264:$U264,0))),IF(COUNTIF($N264:$U264,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N264:$U264)=0,"All done",IF(MAX($M264:$U264)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A264&lt;&gt;"",OR($G264="",$G264="Active"))),"",IF($L264&lt;&gt;"",IF($L264=$M264,"Booking",INDEX($N$4:$U$4,MATCH($L264,$N264:$U264,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M264:$U264)+($M264:$U264="DNA")),$M264:$U264),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M264:$U264)+($M264:$U264="DNA")),$M264:$U264),"")),IF(ISNUMBER($U264),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L264" s="33">
@@ -13244,7 +13255,7 @@
         <v/>
       </c>
       <c r="I265" s="32">
-        <f>IF(NOT(AND($A265&lt;&gt;"",OR($G265="",$G265="Active"))),"",IF(AND(MAX($M265:$U265)&gt;0,MAX($M265:$U265)&lt;TODAY(),COUNTBLANK($N265:$U265)&gt;0,COUNTIF($N265:$U265,"DNA")=0),1,0)+COUNTIF($N265:$U265,"DNA")+COUNTIF($V265:$Z265,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A265&lt;&gt;"",OR($G265="",$G265="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M265:$U265)+($M265:$U265="DNA")),$M265:$U265),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M265:$U265)+($M265:$U265="DNA")),$M265:$U265),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M265:$U265)+($M265:$U265="DNA")),$M265:$U265),"")&lt;TODAY())),1,0)+COUNTIF($V265:$Z265,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J265" s="32">
@@ -13252,7 +13263,7 @@
         <v/>
       </c>
       <c r="K265" s="32">
-        <f>IF(NOT(AND($A265&lt;&gt;"",OR($G265="",$G265="Active"))),"",IF($L265&lt;&gt;"",IF($L265=$M265,"Booking",INDEX($N$4:$U$4,MATCH($L265,$N265:$U265,0))),IF(COUNTIF($N265:$U265,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N265:$U265)=0,"All done",IF(MAX($M265:$U265)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A265&lt;&gt;"",OR($G265="",$G265="Active"))),"",IF($L265&lt;&gt;"",IF($L265=$M265,"Booking",INDEX($N$4:$U$4,MATCH($L265,$N265:$U265,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M265:$U265)+($M265:$U265="DNA")),$M265:$U265),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M265:$U265)+($M265:$U265="DNA")),$M265:$U265),"")),IF(ISNUMBER($U265),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L265" s="33">
@@ -13290,7 +13301,7 @@
         <v/>
       </c>
       <c r="I266" s="32">
-        <f>IF(NOT(AND($A266&lt;&gt;"",OR($G266="",$G266="Active"))),"",IF(AND(MAX($M266:$U266)&gt;0,MAX($M266:$U266)&lt;TODAY(),COUNTBLANK($N266:$U266)&gt;0,COUNTIF($N266:$U266,"DNA")=0),1,0)+COUNTIF($N266:$U266,"DNA")+COUNTIF($V266:$Z266,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A266&lt;&gt;"",OR($G266="",$G266="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M266:$U266)+($M266:$U266="DNA")),$M266:$U266),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M266:$U266)+($M266:$U266="DNA")),$M266:$U266),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M266:$U266)+($M266:$U266="DNA")),$M266:$U266),"")&lt;TODAY())),1,0)+COUNTIF($V266:$Z266,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J266" s="32">
@@ -13298,7 +13309,7 @@
         <v/>
       </c>
       <c r="K266" s="32">
-        <f>IF(NOT(AND($A266&lt;&gt;"",OR($G266="",$G266="Active"))),"",IF($L266&lt;&gt;"",IF($L266=$M266,"Booking",INDEX($N$4:$U$4,MATCH($L266,$N266:$U266,0))),IF(COUNTIF($N266:$U266,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N266:$U266)=0,"All done",IF(MAX($M266:$U266)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A266&lt;&gt;"",OR($G266="",$G266="Active"))),"",IF($L266&lt;&gt;"",IF($L266=$M266,"Booking",INDEX($N$4:$U$4,MATCH($L266,$N266:$U266,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M266:$U266)+($M266:$U266="DNA")),$M266:$U266),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M266:$U266)+($M266:$U266="DNA")),$M266:$U266),"")),IF(ISNUMBER($U266),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L266" s="33">
@@ -13336,7 +13347,7 @@
         <v/>
       </c>
       <c r="I267" s="32">
-        <f>IF(NOT(AND($A267&lt;&gt;"",OR($G267="",$G267="Active"))),"",IF(AND(MAX($M267:$U267)&gt;0,MAX($M267:$U267)&lt;TODAY(),COUNTBLANK($N267:$U267)&gt;0,COUNTIF($N267:$U267,"DNA")=0),1,0)+COUNTIF($N267:$U267,"DNA")+COUNTIF($V267:$Z267,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A267&lt;&gt;"",OR($G267="",$G267="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M267:$U267)+($M267:$U267="DNA")),$M267:$U267),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M267:$U267)+($M267:$U267="DNA")),$M267:$U267),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M267:$U267)+($M267:$U267="DNA")),$M267:$U267),"")&lt;TODAY())),1,0)+COUNTIF($V267:$Z267,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J267" s="32">
@@ -13344,7 +13355,7 @@
         <v/>
       </c>
       <c r="K267" s="32">
-        <f>IF(NOT(AND($A267&lt;&gt;"",OR($G267="",$G267="Active"))),"",IF($L267&lt;&gt;"",IF($L267=$M267,"Booking",INDEX($N$4:$U$4,MATCH($L267,$N267:$U267,0))),IF(COUNTIF($N267:$U267,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N267:$U267)=0,"All done",IF(MAX($M267:$U267)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A267&lt;&gt;"",OR($G267="",$G267="Active"))),"",IF($L267&lt;&gt;"",IF($L267=$M267,"Booking",INDEX($N$4:$U$4,MATCH($L267,$N267:$U267,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M267:$U267)+($M267:$U267="DNA")),$M267:$U267),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M267:$U267)+($M267:$U267="DNA")),$M267:$U267),"")),IF(ISNUMBER($U267),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L267" s="33">
@@ -13382,7 +13393,7 @@
         <v/>
       </c>
       <c r="I268" s="32">
-        <f>IF(NOT(AND($A268&lt;&gt;"",OR($G268="",$G268="Active"))),"",IF(AND(MAX($M268:$U268)&gt;0,MAX($M268:$U268)&lt;TODAY(),COUNTBLANK($N268:$U268)&gt;0,COUNTIF($N268:$U268,"DNA")=0),1,0)+COUNTIF($N268:$U268,"DNA")+COUNTIF($V268:$Z268,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A268&lt;&gt;"",OR($G268="",$G268="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M268:$U268)+($M268:$U268="DNA")),$M268:$U268),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M268:$U268)+($M268:$U268="DNA")),$M268:$U268),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M268:$U268)+($M268:$U268="DNA")),$M268:$U268),"")&lt;TODAY())),1,0)+COUNTIF($V268:$Z268,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J268" s="32">
@@ -13390,7 +13401,7 @@
         <v/>
       </c>
       <c r="K268" s="32">
-        <f>IF(NOT(AND($A268&lt;&gt;"",OR($G268="",$G268="Active"))),"",IF($L268&lt;&gt;"",IF($L268=$M268,"Booking",INDEX($N$4:$U$4,MATCH($L268,$N268:$U268,0))),IF(COUNTIF($N268:$U268,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N268:$U268)=0,"All done",IF(MAX($M268:$U268)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A268&lt;&gt;"",OR($G268="",$G268="Active"))),"",IF($L268&lt;&gt;"",IF($L268=$M268,"Booking",INDEX($N$4:$U$4,MATCH($L268,$N268:$U268,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M268:$U268)+($M268:$U268="DNA")),$M268:$U268),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M268:$U268)+($M268:$U268="DNA")),$M268:$U268),"")),IF(ISNUMBER($U268),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L268" s="33">
@@ -13428,7 +13439,7 @@
         <v/>
       </c>
       <c r="I269" s="32">
-        <f>IF(NOT(AND($A269&lt;&gt;"",OR($G269="",$G269="Active"))),"",IF(AND(MAX($M269:$U269)&gt;0,MAX($M269:$U269)&lt;TODAY(),COUNTBLANK($N269:$U269)&gt;0,COUNTIF($N269:$U269,"DNA")=0),1,0)+COUNTIF($N269:$U269,"DNA")+COUNTIF($V269:$Z269,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A269&lt;&gt;"",OR($G269="",$G269="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M269:$U269)+($M269:$U269="DNA")),$M269:$U269),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M269:$U269)+($M269:$U269="DNA")),$M269:$U269),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M269:$U269)+($M269:$U269="DNA")),$M269:$U269),"")&lt;TODAY())),1,0)+COUNTIF($V269:$Z269,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J269" s="32">
@@ -13436,7 +13447,7 @@
         <v/>
       </c>
       <c r="K269" s="32">
-        <f>IF(NOT(AND($A269&lt;&gt;"",OR($G269="",$G269="Active"))),"",IF($L269&lt;&gt;"",IF($L269=$M269,"Booking",INDEX($N$4:$U$4,MATCH($L269,$N269:$U269,0))),IF(COUNTIF($N269:$U269,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N269:$U269)=0,"All done",IF(MAX($M269:$U269)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A269&lt;&gt;"",OR($G269="",$G269="Active"))),"",IF($L269&lt;&gt;"",IF($L269=$M269,"Booking",INDEX($N$4:$U$4,MATCH($L269,$N269:$U269,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M269:$U269)+($M269:$U269="DNA")),$M269:$U269),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M269:$U269)+($M269:$U269="DNA")),$M269:$U269),"")),IF(ISNUMBER($U269),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L269" s="33">
@@ -13474,7 +13485,7 @@
         <v/>
       </c>
       <c r="I270" s="32">
-        <f>IF(NOT(AND($A270&lt;&gt;"",OR($G270="",$G270="Active"))),"",IF(AND(MAX($M270:$U270)&gt;0,MAX($M270:$U270)&lt;TODAY(),COUNTBLANK($N270:$U270)&gt;0,COUNTIF($N270:$U270,"DNA")=0),1,0)+COUNTIF($N270:$U270,"DNA")+COUNTIF($V270:$Z270,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A270&lt;&gt;"",OR($G270="",$G270="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M270:$U270)+($M270:$U270="DNA")),$M270:$U270),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M270:$U270)+($M270:$U270="DNA")),$M270:$U270),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M270:$U270)+($M270:$U270="DNA")),$M270:$U270),"")&lt;TODAY())),1,0)+COUNTIF($V270:$Z270,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J270" s="32">
@@ -13482,7 +13493,7 @@
         <v/>
       </c>
       <c r="K270" s="32">
-        <f>IF(NOT(AND($A270&lt;&gt;"",OR($G270="",$G270="Active"))),"",IF($L270&lt;&gt;"",IF($L270=$M270,"Booking",INDEX($N$4:$U$4,MATCH($L270,$N270:$U270,0))),IF(COUNTIF($N270:$U270,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N270:$U270)=0,"All done",IF(MAX($M270:$U270)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A270&lt;&gt;"",OR($G270="",$G270="Active"))),"",IF($L270&lt;&gt;"",IF($L270=$M270,"Booking",INDEX($N$4:$U$4,MATCH($L270,$N270:$U270,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M270:$U270)+($M270:$U270="DNA")),$M270:$U270),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M270:$U270)+($M270:$U270="DNA")),$M270:$U270),"")),IF(ISNUMBER($U270),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L270" s="33">
@@ -13520,7 +13531,7 @@
         <v/>
       </c>
       <c r="I271" s="32">
-        <f>IF(NOT(AND($A271&lt;&gt;"",OR($G271="",$G271="Active"))),"",IF(AND(MAX($M271:$U271)&gt;0,MAX($M271:$U271)&lt;TODAY(),COUNTBLANK($N271:$U271)&gt;0,COUNTIF($N271:$U271,"DNA")=0),1,0)+COUNTIF($N271:$U271,"DNA")+COUNTIF($V271:$Z271,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A271&lt;&gt;"",OR($G271="",$G271="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M271:$U271)+($M271:$U271="DNA")),$M271:$U271),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M271:$U271)+($M271:$U271="DNA")),$M271:$U271),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M271:$U271)+($M271:$U271="DNA")),$M271:$U271),"")&lt;TODAY())),1,0)+COUNTIF($V271:$Z271,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J271" s="32">
@@ -13528,7 +13539,7 @@
         <v/>
       </c>
       <c r="K271" s="32">
-        <f>IF(NOT(AND($A271&lt;&gt;"",OR($G271="",$G271="Active"))),"",IF($L271&lt;&gt;"",IF($L271=$M271,"Booking",INDEX($N$4:$U$4,MATCH($L271,$N271:$U271,0))),IF(COUNTIF($N271:$U271,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N271:$U271)=0,"All done",IF(MAX($M271:$U271)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A271&lt;&gt;"",OR($G271="",$G271="Active"))),"",IF($L271&lt;&gt;"",IF($L271=$M271,"Booking",INDEX($N$4:$U$4,MATCH($L271,$N271:$U271,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M271:$U271)+($M271:$U271="DNA")),$M271:$U271),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M271:$U271)+($M271:$U271="DNA")),$M271:$U271),"")),IF(ISNUMBER($U271),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L271" s="33">
@@ -13566,7 +13577,7 @@
         <v/>
       </c>
       <c r="I272" s="32">
-        <f>IF(NOT(AND($A272&lt;&gt;"",OR($G272="",$G272="Active"))),"",IF(AND(MAX($M272:$U272)&gt;0,MAX($M272:$U272)&lt;TODAY(),COUNTBLANK($N272:$U272)&gt;0,COUNTIF($N272:$U272,"DNA")=0),1,0)+COUNTIF($N272:$U272,"DNA")+COUNTIF($V272:$Z272,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A272&lt;&gt;"",OR($G272="",$G272="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M272:$U272)+($M272:$U272="DNA")),$M272:$U272),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M272:$U272)+($M272:$U272="DNA")),$M272:$U272),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M272:$U272)+($M272:$U272="DNA")),$M272:$U272),"")&lt;TODAY())),1,0)+COUNTIF($V272:$Z272,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J272" s="32">
@@ -13574,7 +13585,7 @@
         <v/>
       </c>
       <c r="K272" s="32">
-        <f>IF(NOT(AND($A272&lt;&gt;"",OR($G272="",$G272="Active"))),"",IF($L272&lt;&gt;"",IF($L272=$M272,"Booking",INDEX($N$4:$U$4,MATCH($L272,$N272:$U272,0))),IF(COUNTIF($N272:$U272,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N272:$U272)=0,"All done",IF(MAX($M272:$U272)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A272&lt;&gt;"",OR($G272="",$G272="Active"))),"",IF($L272&lt;&gt;"",IF($L272=$M272,"Booking",INDEX($N$4:$U$4,MATCH($L272,$N272:$U272,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M272:$U272)+($M272:$U272="DNA")),$M272:$U272),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M272:$U272)+($M272:$U272="DNA")),$M272:$U272),"")),IF(ISNUMBER($U272),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L272" s="33">
@@ -13612,7 +13623,7 @@
         <v/>
       </c>
       <c r="I273" s="32">
-        <f>IF(NOT(AND($A273&lt;&gt;"",OR($G273="",$G273="Active"))),"",IF(AND(MAX($M273:$U273)&gt;0,MAX($M273:$U273)&lt;TODAY(),COUNTBLANK($N273:$U273)&gt;0,COUNTIF($N273:$U273,"DNA")=0),1,0)+COUNTIF($N273:$U273,"DNA")+COUNTIF($V273:$Z273,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A273&lt;&gt;"",OR($G273="",$G273="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M273:$U273)+($M273:$U273="DNA")),$M273:$U273),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M273:$U273)+($M273:$U273="DNA")),$M273:$U273),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M273:$U273)+($M273:$U273="DNA")),$M273:$U273),"")&lt;TODAY())),1,0)+COUNTIF($V273:$Z273,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J273" s="32">
@@ -13620,7 +13631,7 @@
         <v/>
       </c>
       <c r="K273" s="32">
-        <f>IF(NOT(AND($A273&lt;&gt;"",OR($G273="",$G273="Active"))),"",IF($L273&lt;&gt;"",IF($L273=$M273,"Booking",INDEX($N$4:$U$4,MATCH($L273,$N273:$U273,0))),IF(COUNTIF($N273:$U273,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N273:$U273)=0,"All done",IF(MAX($M273:$U273)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A273&lt;&gt;"",OR($G273="",$G273="Active"))),"",IF($L273&lt;&gt;"",IF($L273=$M273,"Booking",INDEX($N$4:$U$4,MATCH($L273,$N273:$U273,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M273:$U273)+($M273:$U273="DNA")),$M273:$U273),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M273:$U273)+($M273:$U273="DNA")),$M273:$U273),"")),IF(ISNUMBER($U273),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L273" s="33">
@@ -13658,7 +13669,7 @@
         <v/>
       </c>
       <c r="I274" s="32">
-        <f>IF(NOT(AND($A274&lt;&gt;"",OR($G274="",$G274="Active"))),"",IF(AND(MAX($M274:$U274)&gt;0,MAX($M274:$U274)&lt;TODAY(),COUNTBLANK($N274:$U274)&gt;0,COUNTIF($N274:$U274,"DNA")=0),1,0)+COUNTIF($N274:$U274,"DNA")+COUNTIF($V274:$Z274,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A274&lt;&gt;"",OR($G274="",$G274="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M274:$U274)+($M274:$U274="DNA")),$M274:$U274),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M274:$U274)+($M274:$U274="DNA")),$M274:$U274),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M274:$U274)+($M274:$U274="DNA")),$M274:$U274),"")&lt;TODAY())),1,0)+COUNTIF($V274:$Z274,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J274" s="32">
@@ -13666,7 +13677,7 @@
         <v/>
       </c>
       <c r="K274" s="32">
-        <f>IF(NOT(AND($A274&lt;&gt;"",OR($G274="",$G274="Active"))),"",IF($L274&lt;&gt;"",IF($L274=$M274,"Booking",INDEX($N$4:$U$4,MATCH($L274,$N274:$U274,0))),IF(COUNTIF($N274:$U274,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N274:$U274)=0,"All done",IF(MAX($M274:$U274)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A274&lt;&gt;"",OR($G274="",$G274="Active"))),"",IF($L274&lt;&gt;"",IF($L274=$M274,"Booking",INDEX($N$4:$U$4,MATCH($L274,$N274:$U274,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M274:$U274)+($M274:$U274="DNA")),$M274:$U274),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M274:$U274)+($M274:$U274="DNA")),$M274:$U274),"")),IF(ISNUMBER($U274),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L274" s="33">
@@ -13704,7 +13715,7 @@
         <v/>
       </c>
       <c r="I275" s="32">
-        <f>IF(NOT(AND($A275&lt;&gt;"",OR($G275="",$G275="Active"))),"",IF(AND(MAX($M275:$U275)&gt;0,MAX($M275:$U275)&lt;TODAY(),COUNTBLANK($N275:$U275)&gt;0,COUNTIF($N275:$U275,"DNA")=0),1,0)+COUNTIF($N275:$U275,"DNA")+COUNTIF($V275:$Z275,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A275&lt;&gt;"",OR($G275="",$G275="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M275:$U275)+($M275:$U275="DNA")),$M275:$U275),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M275:$U275)+($M275:$U275="DNA")),$M275:$U275),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M275:$U275)+($M275:$U275="DNA")),$M275:$U275),"")&lt;TODAY())),1,0)+COUNTIF($V275:$Z275,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J275" s="32">
@@ -13712,7 +13723,7 @@
         <v/>
       </c>
       <c r="K275" s="32">
-        <f>IF(NOT(AND($A275&lt;&gt;"",OR($G275="",$G275="Active"))),"",IF($L275&lt;&gt;"",IF($L275=$M275,"Booking",INDEX($N$4:$U$4,MATCH($L275,$N275:$U275,0))),IF(COUNTIF($N275:$U275,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N275:$U275)=0,"All done",IF(MAX($M275:$U275)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A275&lt;&gt;"",OR($G275="",$G275="Active"))),"",IF($L275&lt;&gt;"",IF($L275=$M275,"Booking",INDEX($N$4:$U$4,MATCH($L275,$N275:$U275,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M275:$U275)+($M275:$U275="DNA")),$M275:$U275),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M275:$U275)+($M275:$U275="DNA")),$M275:$U275),"")),IF(ISNUMBER($U275),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L275" s="33">
@@ -13750,7 +13761,7 @@
         <v/>
       </c>
       <c r="I276" s="32">
-        <f>IF(NOT(AND($A276&lt;&gt;"",OR($G276="",$G276="Active"))),"",IF(AND(MAX($M276:$U276)&gt;0,MAX($M276:$U276)&lt;TODAY(),COUNTBLANK($N276:$U276)&gt;0,COUNTIF($N276:$U276,"DNA")=0),1,0)+COUNTIF($N276:$U276,"DNA")+COUNTIF($V276:$Z276,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A276&lt;&gt;"",OR($G276="",$G276="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M276:$U276)+($M276:$U276="DNA")),$M276:$U276),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M276:$U276)+($M276:$U276="DNA")),$M276:$U276),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M276:$U276)+($M276:$U276="DNA")),$M276:$U276),"")&lt;TODAY())),1,0)+COUNTIF($V276:$Z276,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J276" s="32">
@@ -13758,7 +13769,7 @@
         <v/>
       </c>
       <c r="K276" s="32">
-        <f>IF(NOT(AND($A276&lt;&gt;"",OR($G276="",$G276="Active"))),"",IF($L276&lt;&gt;"",IF($L276=$M276,"Booking",INDEX($N$4:$U$4,MATCH($L276,$N276:$U276,0))),IF(COUNTIF($N276:$U276,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N276:$U276)=0,"All done",IF(MAX($M276:$U276)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A276&lt;&gt;"",OR($G276="",$G276="Active"))),"",IF($L276&lt;&gt;"",IF($L276=$M276,"Booking",INDEX($N$4:$U$4,MATCH($L276,$N276:$U276,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M276:$U276)+($M276:$U276="DNA")),$M276:$U276),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M276:$U276)+($M276:$U276="DNA")),$M276:$U276),"")),IF(ISNUMBER($U276),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L276" s="33">
@@ -13796,7 +13807,7 @@
         <v/>
       </c>
       <c r="I277" s="32">
-        <f>IF(NOT(AND($A277&lt;&gt;"",OR($G277="",$G277="Active"))),"",IF(AND(MAX($M277:$U277)&gt;0,MAX($M277:$U277)&lt;TODAY(),COUNTBLANK($N277:$U277)&gt;0,COUNTIF($N277:$U277,"DNA")=0),1,0)+COUNTIF($N277:$U277,"DNA")+COUNTIF($V277:$Z277,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A277&lt;&gt;"",OR($G277="",$G277="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M277:$U277)+($M277:$U277="DNA")),$M277:$U277),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M277:$U277)+($M277:$U277="DNA")),$M277:$U277),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M277:$U277)+($M277:$U277="DNA")),$M277:$U277),"")&lt;TODAY())),1,0)+COUNTIF($V277:$Z277,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J277" s="32">
@@ -13804,7 +13815,7 @@
         <v/>
       </c>
       <c r="K277" s="32">
-        <f>IF(NOT(AND($A277&lt;&gt;"",OR($G277="",$G277="Active"))),"",IF($L277&lt;&gt;"",IF($L277=$M277,"Booking",INDEX($N$4:$U$4,MATCH($L277,$N277:$U277,0))),IF(COUNTIF($N277:$U277,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N277:$U277)=0,"All done",IF(MAX($M277:$U277)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A277&lt;&gt;"",OR($G277="",$G277="Active"))),"",IF($L277&lt;&gt;"",IF($L277=$M277,"Booking",INDEX($N$4:$U$4,MATCH($L277,$N277:$U277,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M277:$U277)+($M277:$U277="DNA")),$M277:$U277),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M277:$U277)+($M277:$U277="DNA")),$M277:$U277),"")),IF(ISNUMBER($U277),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L277" s="33">
@@ -13842,7 +13853,7 @@
         <v/>
       </c>
       <c r="I278" s="32">
-        <f>IF(NOT(AND($A278&lt;&gt;"",OR($G278="",$G278="Active"))),"",IF(AND(MAX($M278:$U278)&gt;0,MAX($M278:$U278)&lt;TODAY(),COUNTBLANK($N278:$U278)&gt;0,COUNTIF($N278:$U278,"DNA")=0),1,0)+COUNTIF($N278:$U278,"DNA")+COUNTIF($V278:$Z278,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A278&lt;&gt;"",OR($G278="",$G278="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M278:$U278)+($M278:$U278="DNA")),$M278:$U278),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M278:$U278)+($M278:$U278="DNA")),$M278:$U278),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M278:$U278)+($M278:$U278="DNA")),$M278:$U278),"")&lt;TODAY())),1,0)+COUNTIF($V278:$Z278,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J278" s="32">
@@ -13850,7 +13861,7 @@
         <v/>
       </c>
       <c r="K278" s="32">
-        <f>IF(NOT(AND($A278&lt;&gt;"",OR($G278="",$G278="Active"))),"",IF($L278&lt;&gt;"",IF($L278=$M278,"Booking",INDEX($N$4:$U$4,MATCH($L278,$N278:$U278,0))),IF(COUNTIF($N278:$U278,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N278:$U278)=0,"All done",IF(MAX($M278:$U278)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A278&lt;&gt;"",OR($G278="",$G278="Active"))),"",IF($L278&lt;&gt;"",IF($L278=$M278,"Booking",INDEX($N$4:$U$4,MATCH($L278,$N278:$U278,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M278:$U278)+($M278:$U278="DNA")),$M278:$U278),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M278:$U278)+($M278:$U278="DNA")),$M278:$U278),"")),IF(ISNUMBER($U278),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L278" s="33">
@@ -13888,7 +13899,7 @@
         <v/>
       </c>
       <c r="I279" s="32">
-        <f>IF(NOT(AND($A279&lt;&gt;"",OR($G279="",$G279="Active"))),"",IF(AND(MAX($M279:$U279)&gt;0,MAX($M279:$U279)&lt;TODAY(),COUNTBLANK($N279:$U279)&gt;0,COUNTIF($N279:$U279,"DNA")=0),1,0)+COUNTIF($N279:$U279,"DNA")+COUNTIF($V279:$Z279,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A279&lt;&gt;"",OR($G279="",$G279="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M279:$U279)+($M279:$U279="DNA")),$M279:$U279),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M279:$U279)+($M279:$U279="DNA")),$M279:$U279),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M279:$U279)+($M279:$U279="DNA")),$M279:$U279),"")&lt;TODAY())),1,0)+COUNTIF($V279:$Z279,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J279" s="32">
@@ -13896,7 +13907,7 @@
         <v/>
       </c>
       <c r="K279" s="32">
-        <f>IF(NOT(AND($A279&lt;&gt;"",OR($G279="",$G279="Active"))),"",IF($L279&lt;&gt;"",IF($L279=$M279,"Booking",INDEX($N$4:$U$4,MATCH($L279,$N279:$U279,0))),IF(COUNTIF($N279:$U279,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N279:$U279)=0,"All done",IF(MAX($M279:$U279)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A279&lt;&gt;"",OR($G279="",$G279="Active"))),"",IF($L279&lt;&gt;"",IF($L279=$M279,"Booking",INDEX($N$4:$U$4,MATCH($L279,$N279:$U279,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M279:$U279)+($M279:$U279="DNA")),$M279:$U279),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M279:$U279)+($M279:$U279="DNA")),$M279:$U279),"")),IF(ISNUMBER($U279),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L279" s="33">
@@ -13934,7 +13945,7 @@
         <v/>
       </c>
       <c r="I280" s="32">
-        <f>IF(NOT(AND($A280&lt;&gt;"",OR($G280="",$G280="Active"))),"",IF(AND(MAX($M280:$U280)&gt;0,MAX($M280:$U280)&lt;TODAY(),COUNTBLANK($N280:$U280)&gt;0,COUNTIF($N280:$U280,"DNA")=0),1,0)+COUNTIF($N280:$U280,"DNA")+COUNTIF($V280:$Z280,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A280&lt;&gt;"",OR($G280="",$G280="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M280:$U280)+($M280:$U280="DNA")),$M280:$U280),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M280:$U280)+($M280:$U280="DNA")),$M280:$U280),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M280:$U280)+($M280:$U280="DNA")),$M280:$U280),"")&lt;TODAY())),1,0)+COUNTIF($V280:$Z280,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J280" s="32">
@@ -13942,7 +13953,7 @@
         <v/>
       </c>
       <c r="K280" s="32">
-        <f>IF(NOT(AND($A280&lt;&gt;"",OR($G280="",$G280="Active"))),"",IF($L280&lt;&gt;"",IF($L280=$M280,"Booking",INDEX($N$4:$U$4,MATCH($L280,$N280:$U280,0))),IF(COUNTIF($N280:$U280,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N280:$U280)=0,"All done",IF(MAX($M280:$U280)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A280&lt;&gt;"",OR($G280="",$G280="Active"))),"",IF($L280&lt;&gt;"",IF($L280=$M280,"Booking",INDEX($N$4:$U$4,MATCH($L280,$N280:$U280,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M280:$U280)+($M280:$U280="DNA")),$M280:$U280),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M280:$U280)+($M280:$U280="DNA")),$M280:$U280),"")),IF(ISNUMBER($U280),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L280" s="33">
@@ -13980,7 +13991,7 @@
         <v/>
       </c>
       <c r="I281" s="32">
-        <f>IF(NOT(AND($A281&lt;&gt;"",OR($G281="",$G281="Active"))),"",IF(AND(MAX($M281:$U281)&gt;0,MAX($M281:$U281)&lt;TODAY(),COUNTBLANK($N281:$U281)&gt;0,COUNTIF($N281:$U281,"DNA")=0),1,0)+COUNTIF($N281:$U281,"DNA")+COUNTIF($V281:$Z281,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A281&lt;&gt;"",OR($G281="",$G281="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M281:$U281)+($M281:$U281="DNA")),$M281:$U281),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M281:$U281)+($M281:$U281="DNA")),$M281:$U281),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M281:$U281)+($M281:$U281="DNA")),$M281:$U281),"")&lt;TODAY())),1,0)+COUNTIF($V281:$Z281,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J281" s="32">
@@ -13988,7 +13999,7 @@
         <v/>
       </c>
       <c r="K281" s="32">
-        <f>IF(NOT(AND($A281&lt;&gt;"",OR($G281="",$G281="Active"))),"",IF($L281&lt;&gt;"",IF($L281=$M281,"Booking",INDEX($N$4:$U$4,MATCH($L281,$N281:$U281,0))),IF(COUNTIF($N281:$U281,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N281:$U281)=0,"All done",IF(MAX($M281:$U281)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A281&lt;&gt;"",OR($G281="",$G281="Active"))),"",IF($L281&lt;&gt;"",IF($L281=$M281,"Booking",INDEX($N$4:$U$4,MATCH($L281,$N281:$U281,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M281:$U281)+($M281:$U281="DNA")),$M281:$U281),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M281:$U281)+($M281:$U281="DNA")),$M281:$U281),"")),IF(ISNUMBER($U281),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L281" s="33">
@@ -14026,7 +14037,7 @@
         <v/>
       </c>
       <c r="I282" s="32">
-        <f>IF(NOT(AND($A282&lt;&gt;"",OR($G282="",$G282="Active"))),"",IF(AND(MAX($M282:$U282)&gt;0,MAX($M282:$U282)&lt;TODAY(),COUNTBLANK($N282:$U282)&gt;0,COUNTIF($N282:$U282,"DNA")=0),1,0)+COUNTIF($N282:$U282,"DNA")+COUNTIF($V282:$Z282,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A282&lt;&gt;"",OR($G282="",$G282="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M282:$U282)+($M282:$U282="DNA")),$M282:$U282),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M282:$U282)+($M282:$U282="DNA")),$M282:$U282),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M282:$U282)+($M282:$U282="DNA")),$M282:$U282),"")&lt;TODAY())),1,0)+COUNTIF($V282:$Z282,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J282" s="32">
@@ -14034,7 +14045,7 @@
         <v/>
       </c>
       <c r="K282" s="32">
-        <f>IF(NOT(AND($A282&lt;&gt;"",OR($G282="",$G282="Active"))),"",IF($L282&lt;&gt;"",IF($L282=$M282,"Booking",INDEX($N$4:$U$4,MATCH($L282,$N282:$U282,0))),IF(COUNTIF($N282:$U282,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N282:$U282)=0,"All done",IF(MAX($M282:$U282)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A282&lt;&gt;"",OR($G282="",$G282="Active"))),"",IF($L282&lt;&gt;"",IF($L282=$M282,"Booking",INDEX($N$4:$U$4,MATCH($L282,$N282:$U282,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M282:$U282)+($M282:$U282="DNA")),$M282:$U282),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M282:$U282)+($M282:$U282="DNA")),$M282:$U282),"")),IF(ISNUMBER($U282),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L282" s="33">
@@ -14072,7 +14083,7 @@
         <v/>
       </c>
       <c r="I283" s="32">
-        <f>IF(NOT(AND($A283&lt;&gt;"",OR($G283="",$G283="Active"))),"",IF(AND(MAX($M283:$U283)&gt;0,MAX($M283:$U283)&lt;TODAY(),COUNTBLANK($N283:$U283)&gt;0,COUNTIF($N283:$U283,"DNA")=0),1,0)+COUNTIF($N283:$U283,"DNA")+COUNTIF($V283:$Z283,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A283&lt;&gt;"",OR($G283="",$G283="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M283:$U283)+($M283:$U283="DNA")),$M283:$U283),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M283:$U283)+($M283:$U283="DNA")),$M283:$U283),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M283:$U283)+($M283:$U283="DNA")),$M283:$U283),"")&lt;TODAY())),1,0)+COUNTIF($V283:$Z283,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J283" s="32">
@@ -14080,7 +14091,7 @@
         <v/>
       </c>
       <c r="K283" s="32">
-        <f>IF(NOT(AND($A283&lt;&gt;"",OR($G283="",$G283="Active"))),"",IF($L283&lt;&gt;"",IF($L283=$M283,"Booking",INDEX($N$4:$U$4,MATCH($L283,$N283:$U283,0))),IF(COUNTIF($N283:$U283,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N283:$U283)=0,"All done",IF(MAX($M283:$U283)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A283&lt;&gt;"",OR($G283="",$G283="Active"))),"",IF($L283&lt;&gt;"",IF($L283=$M283,"Booking",INDEX($N$4:$U$4,MATCH($L283,$N283:$U283,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M283:$U283)+($M283:$U283="DNA")),$M283:$U283),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M283:$U283)+($M283:$U283="DNA")),$M283:$U283),"")),IF(ISNUMBER($U283),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L283" s="33">
@@ -14118,7 +14129,7 @@
         <v/>
       </c>
       <c r="I284" s="32">
-        <f>IF(NOT(AND($A284&lt;&gt;"",OR($G284="",$G284="Active"))),"",IF(AND(MAX($M284:$U284)&gt;0,MAX($M284:$U284)&lt;TODAY(),COUNTBLANK($N284:$U284)&gt;0,COUNTIF($N284:$U284,"DNA")=0),1,0)+COUNTIF($N284:$U284,"DNA")+COUNTIF($V284:$Z284,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A284&lt;&gt;"",OR($G284="",$G284="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M284:$U284)+($M284:$U284="DNA")),$M284:$U284),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M284:$U284)+($M284:$U284="DNA")),$M284:$U284),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M284:$U284)+($M284:$U284="DNA")),$M284:$U284),"")&lt;TODAY())),1,0)+COUNTIF($V284:$Z284,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J284" s="32">
@@ -14126,7 +14137,7 @@
         <v/>
       </c>
       <c r="K284" s="32">
-        <f>IF(NOT(AND($A284&lt;&gt;"",OR($G284="",$G284="Active"))),"",IF($L284&lt;&gt;"",IF($L284=$M284,"Booking",INDEX($N$4:$U$4,MATCH($L284,$N284:$U284,0))),IF(COUNTIF($N284:$U284,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N284:$U284)=0,"All done",IF(MAX($M284:$U284)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A284&lt;&gt;"",OR($G284="",$G284="Active"))),"",IF($L284&lt;&gt;"",IF($L284=$M284,"Booking",INDEX($N$4:$U$4,MATCH($L284,$N284:$U284,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M284:$U284)+($M284:$U284="DNA")),$M284:$U284),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M284:$U284)+($M284:$U284="DNA")),$M284:$U284),"")),IF(ISNUMBER($U284),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L284" s="33">
@@ -14164,7 +14175,7 @@
         <v/>
       </c>
       <c r="I285" s="32">
-        <f>IF(NOT(AND($A285&lt;&gt;"",OR($G285="",$G285="Active"))),"",IF(AND(MAX($M285:$U285)&gt;0,MAX($M285:$U285)&lt;TODAY(),COUNTBLANK($N285:$U285)&gt;0,COUNTIF($N285:$U285,"DNA")=0),1,0)+COUNTIF($N285:$U285,"DNA")+COUNTIF($V285:$Z285,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A285&lt;&gt;"",OR($G285="",$G285="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M285:$U285)+($M285:$U285="DNA")),$M285:$U285),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M285:$U285)+($M285:$U285="DNA")),$M285:$U285),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M285:$U285)+($M285:$U285="DNA")),$M285:$U285),"")&lt;TODAY())),1,0)+COUNTIF($V285:$Z285,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J285" s="32">
@@ -14172,7 +14183,7 @@
         <v/>
       </c>
       <c r="K285" s="32">
-        <f>IF(NOT(AND($A285&lt;&gt;"",OR($G285="",$G285="Active"))),"",IF($L285&lt;&gt;"",IF($L285=$M285,"Booking",INDEX($N$4:$U$4,MATCH($L285,$N285:$U285,0))),IF(COUNTIF($N285:$U285,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N285:$U285)=0,"All done",IF(MAX($M285:$U285)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A285&lt;&gt;"",OR($G285="",$G285="Active"))),"",IF($L285&lt;&gt;"",IF($L285=$M285,"Booking",INDEX($N$4:$U$4,MATCH($L285,$N285:$U285,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M285:$U285)+($M285:$U285="DNA")),$M285:$U285),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M285:$U285)+($M285:$U285="DNA")),$M285:$U285),"")),IF(ISNUMBER($U285),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L285" s="33">
@@ -14210,7 +14221,7 @@
         <v/>
       </c>
       <c r="I286" s="32">
-        <f>IF(NOT(AND($A286&lt;&gt;"",OR($G286="",$G286="Active"))),"",IF(AND(MAX($M286:$U286)&gt;0,MAX($M286:$U286)&lt;TODAY(),COUNTBLANK($N286:$U286)&gt;0,COUNTIF($N286:$U286,"DNA")=0),1,0)+COUNTIF($N286:$U286,"DNA")+COUNTIF($V286:$Z286,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A286&lt;&gt;"",OR($G286="",$G286="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M286:$U286)+($M286:$U286="DNA")),$M286:$U286),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M286:$U286)+($M286:$U286="DNA")),$M286:$U286),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M286:$U286)+($M286:$U286="DNA")),$M286:$U286),"")&lt;TODAY())),1,0)+COUNTIF($V286:$Z286,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J286" s="32">
@@ -14218,7 +14229,7 @@
         <v/>
       </c>
       <c r="K286" s="32">
-        <f>IF(NOT(AND($A286&lt;&gt;"",OR($G286="",$G286="Active"))),"",IF($L286&lt;&gt;"",IF($L286=$M286,"Booking",INDEX($N$4:$U$4,MATCH($L286,$N286:$U286,0))),IF(COUNTIF($N286:$U286,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N286:$U286)=0,"All done",IF(MAX($M286:$U286)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A286&lt;&gt;"",OR($G286="",$G286="Active"))),"",IF($L286&lt;&gt;"",IF($L286=$M286,"Booking",INDEX($N$4:$U$4,MATCH($L286,$N286:$U286,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M286:$U286)+($M286:$U286="DNA")),$M286:$U286),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M286:$U286)+($M286:$U286="DNA")),$M286:$U286),"")),IF(ISNUMBER($U286),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L286" s="33">
@@ -14256,7 +14267,7 @@
         <v/>
       </c>
       <c r="I287" s="32">
-        <f>IF(NOT(AND($A287&lt;&gt;"",OR($G287="",$G287="Active"))),"",IF(AND(MAX($M287:$U287)&gt;0,MAX($M287:$U287)&lt;TODAY(),COUNTBLANK($N287:$U287)&gt;0,COUNTIF($N287:$U287,"DNA")=0),1,0)+COUNTIF($N287:$U287,"DNA")+COUNTIF($V287:$Z287,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A287&lt;&gt;"",OR($G287="",$G287="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M287:$U287)+($M287:$U287="DNA")),$M287:$U287),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M287:$U287)+($M287:$U287="DNA")),$M287:$U287),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M287:$U287)+($M287:$U287="DNA")),$M287:$U287),"")&lt;TODAY())),1,0)+COUNTIF($V287:$Z287,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J287" s="32">
@@ -14264,7 +14275,7 @@
         <v/>
       </c>
       <c r="K287" s="32">
-        <f>IF(NOT(AND($A287&lt;&gt;"",OR($G287="",$G287="Active"))),"",IF($L287&lt;&gt;"",IF($L287=$M287,"Booking",INDEX($N$4:$U$4,MATCH($L287,$N287:$U287,0))),IF(COUNTIF($N287:$U287,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N287:$U287)=0,"All done",IF(MAX($M287:$U287)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A287&lt;&gt;"",OR($G287="",$G287="Active"))),"",IF($L287&lt;&gt;"",IF($L287=$M287,"Booking",INDEX($N$4:$U$4,MATCH($L287,$N287:$U287,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M287:$U287)+($M287:$U287="DNA")),$M287:$U287),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M287:$U287)+($M287:$U287="DNA")),$M287:$U287),"")),IF(ISNUMBER($U287),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L287" s="33">
@@ -14302,7 +14313,7 @@
         <v/>
       </c>
       <c r="I288" s="32">
-        <f>IF(NOT(AND($A288&lt;&gt;"",OR($G288="",$G288="Active"))),"",IF(AND(MAX($M288:$U288)&gt;0,MAX($M288:$U288)&lt;TODAY(),COUNTBLANK($N288:$U288)&gt;0,COUNTIF($N288:$U288,"DNA")=0),1,0)+COUNTIF($N288:$U288,"DNA")+COUNTIF($V288:$Z288,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A288&lt;&gt;"",OR($G288="",$G288="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M288:$U288)+($M288:$U288="DNA")),$M288:$U288),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M288:$U288)+($M288:$U288="DNA")),$M288:$U288),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M288:$U288)+($M288:$U288="DNA")),$M288:$U288),"")&lt;TODAY())),1,0)+COUNTIF($V288:$Z288,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J288" s="32">
@@ -14310,7 +14321,7 @@
         <v/>
       </c>
       <c r="K288" s="32">
-        <f>IF(NOT(AND($A288&lt;&gt;"",OR($G288="",$G288="Active"))),"",IF($L288&lt;&gt;"",IF($L288=$M288,"Booking",INDEX($N$4:$U$4,MATCH($L288,$N288:$U288,0))),IF(COUNTIF($N288:$U288,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N288:$U288)=0,"All done",IF(MAX($M288:$U288)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A288&lt;&gt;"",OR($G288="",$G288="Active"))),"",IF($L288&lt;&gt;"",IF($L288=$M288,"Booking",INDEX($N$4:$U$4,MATCH($L288,$N288:$U288,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M288:$U288)+($M288:$U288="DNA")),$M288:$U288),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M288:$U288)+($M288:$U288="DNA")),$M288:$U288),"")),IF(ISNUMBER($U288),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L288" s="33">
@@ -14348,7 +14359,7 @@
         <v/>
       </c>
       <c r="I289" s="32">
-        <f>IF(NOT(AND($A289&lt;&gt;"",OR($G289="",$G289="Active"))),"",IF(AND(MAX($M289:$U289)&gt;0,MAX($M289:$U289)&lt;TODAY(),COUNTBLANK($N289:$U289)&gt;0,COUNTIF($N289:$U289,"DNA")=0),1,0)+COUNTIF($N289:$U289,"DNA")+COUNTIF($V289:$Z289,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A289&lt;&gt;"",OR($G289="",$G289="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M289:$U289)+($M289:$U289="DNA")),$M289:$U289),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M289:$U289)+($M289:$U289="DNA")),$M289:$U289),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M289:$U289)+($M289:$U289="DNA")),$M289:$U289),"")&lt;TODAY())),1,0)+COUNTIF($V289:$Z289,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J289" s="32">
@@ -14356,7 +14367,7 @@
         <v/>
       </c>
       <c r="K289" s="32">
-        <f>IF(NOT(AND($A289&lt;&gt;"",OR($G289="",$G289="Active"))),"",IF($L289&lt;&gt;"",IF($L289=$M289,"Booking",INDEX($N$4:$U$4,MATCH($L289,$N289:$U289,0))),IF(COUNTIF($N289:$U289,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N289:$U289)=0,"All done",IF(MAX($M289:$U289)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A289&lt;&gt;"",OR($G289="",$G289="Active"))),"",IF($L289&lt;&gt;"",IF($L289=$M289,"Booking",INDEX($N$4:$U$4,MATCH($L289,$N289:$U289,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M289:$U289)+($M289:$U289="DNA")),$M289:$U289),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M289:$U289)+($M289:$U289="DNA")),$M289:$U289),"")),IF(ISNUMBER($U289),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L289" s="33">
@@ -14394,7 +14405,7 @@
         <v/>
       </c>
       <c r="I290" s="32">
-        <f>IF(NOT(AND($A290&lt;&gt;"",OR($G290="",$G290="Active"))),"",IF(AND(MAX($M290:$U290)&gt;0,MAX($M290:$U290)&lt;TODAY(),COUNTBLANK($N290:$U290)&gt;0,COUNTIF($N290:$U290,"DNA")=0),1,0)+COUNTIF($N290:$U290,"DNA")+COUNTIF($V290:$Z290,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A290&lt;&gt;"",OR($G290="",$G290="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M290:$U290)+($M290:$U290="DNA")),$M290:$U290),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M290:$U290)+($M290:$U290="DNA")),$M290:$U290),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M290:$U290)+($M290:$U290="DNA")),$M290:$U290),"")&lt;TODAY())),1,0)+COUNTIF($V290:$Z290,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J290" s="32">
@@ -14402,7 +14413,7 @@
         <v/>
       </c>
       <c r="K290" s="32">
-        <f>IF(NOT(AND($A290&lt;&gt;"",OR($G290="",$G290="Active"))),"",IF($L290&lt;&gt;"",IF($L290=$M290,"Booking",INDEX($N$4:$U$4,MATCH($L290,$N290:$U290,0))),IF(COUNTIF($N290:$U290,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N290:$U290)=0,"All done",IF(MAX($M290:$U290)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A290&lt;&gt;"",OR($G290="",$G290="Active"))),"",IF($L290&lt;&gt;"",IF($L290=$M290,"Booking",INDEX($N$4:$U$4,MATCH($L290,$N290:$U290,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M290:$U290)+($M290:$U290="DNA")),$M290:$U290),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M290:$U290)+($M290:$U290="DNA")),$M290:$U290),"")),IF(ISNUMBER($U290),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L290" s="33">
@@ -14440,7 +14451,7 @@
         <v/>
       </c>
       <c r="I291" s="32">
-        <f>IF(NOT(AND($A291&lt;&gt;"",OR($G291="",$G291="Active"))),"",IF(AND(MAX($M291:$U291)&gt;0,MAX($M291:$U291)&lt;TODAY(),COUNTBLANK($N291:$U291)&gt;0,COUNTIF($N291:$U291,"DNA")=0),1,0)+COUNTIF($N291:$U291,"DNA")+COUNTIF($V291:$Z291,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A291&lt;&gt;"",OR($G291="",$G291="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M291:$U291)+($M291:$U291="DNA")),$M291:$U291),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M291:$U291)+($M291:$U291="DNA")),$M291:$U291),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M291:$U291)+($M291:$U291="DNA")),$M291:$U291),"")&lt;TODAY())),1,0)+COUNTIF($V291:$Z291,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J291" s="32">
@@ -14448,7 +14459,7 @@
         <v/>
       </c>
       <c r="K291" s="32">
-        <f>IF(NOT(AND($A291&lt;&gt;"",OR($G291="",$G291="Active"))),"",IF($L291&lt;&gt;"",IF($L291=$M291,"Booking",INDEX($N$4:$U$4,MATCH($L291,$N291:$U291,0))),IF(COUNTIF($N291:$U291,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N291:$U291)=0,"All done",IF(MAX($M291:$U291)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A291&lt;&gt;"",OR($G291="",$G291="Active"))),"",IF($L291&lt;&gt;"",IF($L291=$M291,"Booking",INDEX($N$4:$U$4,MATCH($L291,$N291:$U291,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M291:$U291)+($M291:$U291="DNA")),$M291:$U291),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M291:$U291)+($M291:$U291="DNA")),$M291:$U291),"")),IF(ISNUMBER($U291),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L291" s="33">
@@ -14486,7 +14497,7 @@
         <v/>
       </c>
       <c r="I292" s="32">
-        <f>IF(NOT(AND($A292&lt;&gt;"",OR($G292="",$G292="Active"))),"",IF(AND(MAX($M292:$U292)&gt;0,MAX($M292:$U292)&lt;TODAY(),COUNTBLANK($N292:$U292)&gt;0,COUNTIF($N292:$U292,"DNA")=0),1,0)+COUNTIF($N292:$U292,"DNA")+COUNTIF($V292:$Z292,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A292&lt;&gt;"",OR($G292="",$G292="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M292:$U292)+($M292:$U292="DNA")),$M292:$U292),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M292:$U292)+($M292:$U292="DNA")),$M292:$U292),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M292:$U292)+($M292:$U292="DNA")),$M292:$U292),"")&lt;TODAY())),1,0)+COUNTIF($V292:$Z292,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J292" s="32">
@@ -14494,7 +14505,7 @@
         <v/>
       </c>
       <c r="K292" s="32">
-        <f>IF(NOT(AND($A292&lt;&gt;"",OR($G292="",$G292="Active"))),"",IF($L292&lt;&gt;"",IF($L292=$M292,"Booking",INDEX($N$4:$U$4,MATCH($L292,$N292:$U292,0))),IF(COUNTIF($N292:$U292,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N292:$U292)=0,"All done",IF(MAX($M292:$U292)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A292&lt;&gt;"",OR($G292="",$G292="Active"))),"",IF($L292&lt;&gt;"",IF($L292=$M292,"Booking",INDEX($N$4:$U$4,MATCH($L292,$N292:$U292,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M292:$U292)+($M292:$U292="DNA")),$M292:$U292),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M292:$U292)+($M292:$U292="DNA")),$M292:$U292),"")),IF(ISNUMBER($U292),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L292" s="33">
@@ -14532,7 +14543,7 @@
         <v/>
       </c>
       <c r="I293" s="32">
-        <f>IF(NOT(AND($A293&lt;&gt;"",OR($G293="",$G293="Active"))),"",IF(AND(MAX($M293:$U293)&gt;0,MAX($M293:$U293)&lt;TODAY(),COUNTBLANK($N293:$U293)&gt;0,COUNTIF($N293:$U293,"DNA")=0),1,0)+COUNTIF($N293:$U293,"DNA")+COUNTIF($V293:$Z293,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A293&lt;&gt;"",OR($G293="",$G293="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M293:$U293)+($M293:$U293="DNA")),$M293:$U293),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M293:$U293)+($M293:$U293="DNA")),$M293:$U293),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M293:$U293)+($M293:$U293="DNA")),$M293:$U293),"")&lt;TODAY())),1,0)+COUNTIF($V293:$Z293,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J293" s="32">
@@ -14540,7 +14551,7 @@
         <v/>
       </c>
       <c r="K293" s="32">
-        <f>IF(NOT(AND($A293&lt;&gt;"",OR($G293="",$G293="Active"))),"",IF($L293&lt;&gt;"",IF($L293=$M293,"Booking",INDEX($N$4:$U$4,MATCH($L293,$N293:$U293,0))),IF(COUNTIF($N293:$U293,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N293:$U293)=0,"All done",IF(MAX($M293:$U293)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A293&lt;&gt;"",OR($G293="",$G293="Active"))),"",IF($L293&lt;&gt;"",IF($L293=$M293,"Booking",INDEX($N$4:$U$4,MATCH($L293,$N293:$U293,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M293:$U293)+($M293:$U293="DNA")),$M293:$U293),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M293:$U293)+($M293:$U293="DNA")),$M293:$U293),"")),IF(ISNUMBER($U293),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L293" s="33">
@@ -14578,7 +14589,7 @@
         <v/>
       </c>
       <c r="I294" s="32">
-        <f>IF(NOT(AND($A294&lt;&gt;"",OR($G294="",$G294="Active"))),"",IF(AND(MAX($M294:$U294)&gt;0,MAX($M294:$U294)&lt;TODAY(),COUNTBLANK($N294:$U294)&gt;0,COUNTIF($N294:$U294,"DNA")=0),1,0)+COUNTIF($N294:$U294,"DNA")+COUNTIF($V294:$Z294,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A294&lt;&gt;"",OR($G294="",$G294="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M294:$U294)+($M294:$U294="DNA")),$M294:$U294),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M294:$U294)+($M294:$U294="DNA")),$M294:$U294),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M294:$U294)+($M294:$U294="DNA")),$M294:$U294),"")&lt;TODAY())),1,0)+COUNTIF($V294:$Z294,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J294" s="32">
@@ -14586,7 +14597,7 @@
         <v/>
       </c>
       <c r="K294" s="32">
-        <f>IF(NOT(AND($A294&lt;&gt;"",OR($G294="",$G294="Active"))),"",IF($L294&lt;&gt;"",IF($L294=$M294,"Booking",INDEX($N$4:$U$4,MATCH($L294,$N294:$U294,0))),IF(COUNTIF($N294:$U294,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N294:$U294)=0,"All done",IF(MAX($M294:$U294)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A294&lt;&gt;"",OR($G294="",$G294="Active"))),"",IF($L294&lt;&gt;"",IF($L294=$M294,"Booking",INDEX($N$4:$U$4,MATCH($L294,$N294:$U294,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M294:$U294)+($M294:$U294="DNA")),$M294:$U294),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M294:$U294)+($M294:$U294="DNA")),$M294:$U294),"")),IF(ISNUMBER($U294),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L294" s="33">
@@ -14624,7 +14635,7 @@
         <v/>
       </c>
       <c r="I295" s="32">
-        <f>IF(NOT(AND($A295&lt;&gt;"",OR($G295="",$G295="Active"))),"",IF(AND(MAX($M295:$U295)&gt;0,MAX($M295:$U295)&lt;TODAY(),COUNTBLANK($N295:$U295)&gt;0,COUNTIF($N295:$U295,"DNA")=0),1,0)+COUNTIF($N295:$U295,"DNA")+COUNTIF($V295:$Z295,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A295&lt;&gt;"",OR($G295="",$G295="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M295:$U295)+($M295:$U295="DNA")),$M295:$U295),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M295:$U295)+($M295:$U295="DNA")),$M295:$U295),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M295:$U295)+($M295:$U295="DNA")),$M295:$U295),"")&lt;TODAY())),1,0)+COUNTIF($V295:$Z295,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J295" s="32">
@@ -14632,7 +14643,7 @@
         <v/>
       </c>
       <c r="K295" s="32">
-        <f>IF(NOT(AND($A295&lt;&gt;"",OR($G295="",$G295="Active"))),"",IF($L295&lt;&gt;"",IF($L295=$M295,"Booking",INDEX($N$4:$U$4,MATCH($L295,$N295:$U295,0))),IF(COUNTIF($N295:$U295,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N295:$U295)=0,"All done",IF(MAX($M295:$U295)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A295&lt;&gt;"",OR($G295="",$G295="Active"))),"",IF($L295&lt;&gt;"",IF($L295=$M295,"Booking",INDEX($N$4:$U$4,MATCH($L295,$N295:$U295,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M295:$U295)+($M295:$U295="DNA")),$M295:$U295),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M295:$U295)+($M295:$U295="DNA")),$M295:$U295),"")),IF(ISNUMBER($U295),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L295" s="33">
@@ -14670,7 +14681,7 @@
         <v/>
       </c>
       <c r="I296" s="32">
-        <f>IF(NOT(AND($A296&lt;&gt;"",OR($G296="",$G296="Active"))),"",IF(AND(MAX($M296:$U296)&gt;0,MAX($M296:$U296)&lt;TODAY(),COUNTBLANK($N296:$U296)&gt;0,COUNTIF($N296:$U296,"DNA")=0),1,0)+COUNTIF($N296:$U296,"DNA")+COUNTIF($V296:$Z296,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A296&lt;&gt;"",OR($G296="",$G296="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M296:$U296)+($M296:$U296="DNA")),$M296:$U296),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M296:$U296)+($M296:$U296="DNA")),$M296:$U296),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M296:$U296)+($M296:$U296="DNA")),$M296:$U296),"")&lt;TODAY())),1,0)+COUNTIF($V296:$Z296,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J296" s="32">
@@ -14678,7 +14689,7 @@
         <v/>
       </c>
       <c r="K296" s="32">
-        <f>IF(NOT(AND($A296&lt;&gt;"",OR($G296="",$G296="Active"))),"",IF($L296&lt;&gt;"",IF($L296=$M296,"Booking",INDEX($N$4:$U$4,MATCH($L296,$N296:$U296,0))),IF(COUNTIF($N296:$U296,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N296:$U296)=0,"All done",IF(MAX($M296:$U296)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A296&lt;&gt;"",OR($G296="",$G296="Active"))),"",IF($L296&lt;&gt;"",IF($L296=$M296,"Booking",INDEX($N$4:$U$4,MATCH($L296,$N296:$U296,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M296:$U296)+($M296:$U296="DNA")),$M296:$U296),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M296:$U296)+($M296:$U296="DNA")),$M296:$U296),"")),IF(ISNUMBER($U296),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L296" s="33">
@@ -14716,7 +14727,7 @@
         <v/>
       </c>
       <c r="I297" s="32">
-        <f>IF(NOT(AND($A297&lt;&gt;"",OR($G297="",$G297="Active"))),"",IF(AND(MAX($M297:$U297)&gt;0,MAX($M297:$U297)&lt;TODAY(),COUNTBLANK($N297:$U297)&gt;0,COUNTIF($N297:$U297,"DNA")=0),1,0)+COUNTIF($N297:$U297,"DNA")+COUNTIF($V297:$Z297,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A297&lt;&gt;"",OR($G297="",$G297="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M297:$U297)+($M297:$U297="DNA")),$M297:$U297),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M297:$U297)+($M297:$U297="DNA")),$M297:$U297),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M297:$U297)+($M297:$U297="DNA")),$M297:$U297),"")&lt;TODAY())),1,0)+COUNTIF($V297:$Z297,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J297" s="32">
@@ -14724,7 +14735,7 @@
         <v/>
       </c>
       <c r="K297" s="32">
-        <f>IF(NOT(AND($A297&lt;&gt;"",OR($G297="",$G297="Active"))),"",IF($L297&lt;&gt;"",IF($L297=$M297,"Booking",INDEX($N$4:$U$4,MATCH($L297,$N297:$U297,0))),IF(COUNTIF($N297:$U297,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N297:$U297)=0,"All done",IF(MAX($M297:$U297)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A297&lt;&gt;"",OR($G297="",$G297="Active"))),"",IF($L297&lt;&gt;"",IF($L297=$M297,"Booking",INDEX($N$4:$U$4,MATCH($L297,$N297:$U297,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M297:$U297)+($M297:$U297="DNA")),$M297:$U297),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M297:$U297)+($M297:$U297="DNA")),$M297:$U297),"")),IF(ISNUMBER($U297),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L297" s="33">
@@ -14762,7 +14773,7 @@
         <v/>
       </c>
       <c r="I298" s="32">
-        <f>IF(NOT(AND($A298&lt;&gt;"",OR($G298="",$G298="Active"))),"",IF(AND(MAX($M298:$U298)&gt;0,MAX($M298:$U298)&lt;TODAY(),COUNTBLANK($N298:$U298)&gt;0,COUNTIF($N298:$U298,"DNA")=0),1,0)+COUNTIF($N298:$U298,"DNA")+COUNTIF($V298:$Z298,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A298&lt;&gt;"",OR($G298="",$G298="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M298:$U298)+($M298:$U298="DNA")),$M298:$U298),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M298:$U298)+($M298:$U298="DNA")),$M298:$U298),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M298:$U298)+($M298:$U298="DNA")),$M298:$U298),"")&lt;TODAY())),1,0)+COUNTIF($V298:$Z298,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J298" s="32">
@@ -14770,7 +14781,7 @@
         <v/>
       </c>
       <c r="K298" s="32">
-        <f>IF(NOT(AND($A298&lt;&gt;"",OR($G298="",$G298="Active"))),"",IF($L298&lt;&gt;"",IF($L298=$M298,"Booking",INDEX($N$4:$U$4,MATCH($L298,$N298:$U298,0))),IF(COUNTIF($N298:$U298,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N298:$U298)=0,"All done",IF(MAX($M298:$U298)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A298&lt;&gt;"",OR($G298="",$G298="Active"))),"",IF($L298&lt;&gt;"",IF($L298=$M298,"Booking",INDEX($N$4:$U$4,MATCH($L298,$N298:$U298,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M298:$U298)+($M298:$U298="DNA")),$M298:$U298),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M298:$U298)+($M298:$U298="DNA")),$M298:$U298),"")),IF(ISNUMBER($U298),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L298" s="33">
@@ -14808,7 +14819,7 @@
         <v/>
       </c>
       <c r="I299" s="32">
-        <f>IF(NOT(AND($A299&lt;&gt;"",OR($G299="",$G299="Active"))),"",IF(AND(MAX($M299:$U299)&gt;0,MAX($M299:$U299)&lt;TODAY(),COUNTBLANK($N299:$U299)&gt;0,COUNTIF($N299:$U299,"DNA")=0),1,0)+COUNTIF($N299:$U299,"DNA")+COUNTIF($V299:$Z299,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A299&lt;&gt;"",OR($G299="",$G299="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M299:$U299)+($M299:$U299="DNA")),$M299:$U299),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M299:$U299)+($M299:$U299="DNA")),$M299:$U299),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M299:$U299)+($M299:$U299="DNA")),$M299:$U299),"")&lt;TODAY())),1,0)+COUNTIF($V299:$Z299,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J299" s="32">
@@ -14816,7 +14827,7 @@
         <v/>
       </c>
       <c r="K299" s="32">
-        <f>IF(NOT(AND($A299&lt;&gt;"",OR($G299="",$G299="Active"))),"",IF($L299&lt;&gt;"",IF($L299=$M299,"Booking",INDEX($N$4:$U$4,MATCH($L299,$N299:$U299,0))),IF(COUNTIF($N299:$U299,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N299:$U299)=0,"All done",IF(MAX($M299:$U299)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A299&lt;&gt;"",OR($G299="",$G299="Active"))),"",IF($L299&lt;&gt;"",IF($L299=$M299,"Booking",INDEX($N$4:$U$4,MATCH($L299,$N299:$U299,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M299:$U299)+($M299:$U299="DNA")),$M299:$U299),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M299:$U299)+($M299:$U299="DNA")),$M299:$U299),"")),IF(ISNUMBER($U299),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L299" s="33">
@@ -14854,7 +14865,7 @@
         <v/>
       </c>
       <c r="I300" s="32">
-        <f>IF(NOT(AND($A300&lt;&gt;"",OR($G300="",$G300="Active"))),"",IF(AND(MAX($M300:$U300)&gt;0,MAX($M300:$U300)&lt;TODAY(),COUNTBLANK($N300:$U300)&gt;0,COUNTIF($N300:$U300,"DNA")=0),1,0)+COUNTIF($N300:$U300,"DNA")+COUNTIF($V300:$Z300,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A300&lt;&gt;"",OR($G300="",$G300="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M300:$U300)+($M300:$U300="DNA")),$M300:$U300),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M300:$U300)+($M300:$U300="DNA")),$M300:$U300),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M300:$U300)+($M300:$U300="DNA")),$M300:$U300),"")&lt;TODAY())),1,0)+COUNTIF($V300:$Z300,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J300" s="32">
@@ -14862,7 +14873,7 @@
         <v/>
       </c>
       <c r="K300" s="32">
-        <f>IF(NOT(AND($A300&lt;&gt;"",OR($G300="",$G300="Active"))),"",IF($L300&lt;&gt;"",IF($L300=$M300,"Booking",INDEX($N$4:$U$4,MATCH($L300,$N300:$U300,0))),IF(COUNTIF($N300:$U300,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N300:$U300)=0,"All done",IF(MAX($M300:$U300)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A300&lt;&gt;"",OR($G300="",$G300="Active"))),"",IF($L300&lt;&gt;"",IF($L300=$M300,"Booking",INDEX($N$4:$U$4,MATCH($L300,$N300:$U300,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M300:$U300)+($M300:$U300="DNA")),$M300:$U300),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M300:$U300)+($M300:$U300="DNA")),$M300:$U300),"")),IF(ISNUMBER($U300),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L300" s="33">
@@ -14900,7 +14911,7 @@
         <v/>
       </c>
       <c r="I301" s="32">
-        <f>IF(NOT(AND($A301&lt;&gt;"",OR($G301="",$G301="Active"))),"",IF(AND(MAX($M301:$U301)&gt;0,MAX($M301:$U301)&lt;TODAY(),COUNTBLANK($N301:$U301)&gt;0,COUNTIF($N301:$U301,"DNA")=0),1,0)+COUNTIF($N301:$U301,"DNA")+COUNTIF($V301:$Z301,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A301&lt;&gt;"",OR($G301="",$G301="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M301:$U301)+($M301:$U301="DNA")),$M301:$U301),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M301:$U301)+($M301:$U301="DNA")),$M301:$U301),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M301:$U301)+($M301:$U301="DNA")),$M301:$U301),"")&lt;TODAY())),1,0)+COUNTIF($V301:$Z301,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J301" s="32">
@@ -14908,7 +14919,7 @@
         <v/>
       </c>
       <c r="K301" s="32">
-        <f>IF(NOT(AND($A301&lt;&gt;"",OR($G301="",$G301="Active"))),"",IF($L301&lt;&gt;"",IF($L301=$M301,"Booking",INDEX($N$4:$U$4,MATCH($L301,$N301:$U301,0))),IF(COUNTIF($N301:$U301,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N301:$U301)=0,"All done",IF(MAX($M301:$U301)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A301&lt;&gt;"",OR($G301="",$G301="Active"))),"",IF($L301&lt;&gt;"",IF($L301=$M301,"Booking",INDEX($N$4:$U$4,MATCH($L301,$N301:$U301,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M301:$U301)+($M301:$U301="DNA")),$M301:$U301),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M301:$U301)+($M301:$U301="DNA")),$M301:$U301),"")),IF(ISNUMBER($U301),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L301" s="33">
@@ -14946,7 +14957,7 @@
         <v/>
       </c>
       <c r="I302" s="32">
-        <f>IF(NOT(AND($A302&lt;&gt;"",OR($G302="",$G302="Active"))),"",IF(AND(MAX($M302:$U302)&gt;0,MAX($M302:$U302)&lt;TODAY(),COUNTBLANK($N302:$U302)&gt;0,COUNTIF($N302:$U302,"DNA")=0),1,0)+COUNTIF($N302:$U302,"DNA")+COUNTIF($V302:$Z302,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A302&lt;&gt;"",OR($G302="",$G302="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M302:$U302)+($M302:$U302="DNA")),$M302:$U302),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M302:$U302)+($M302:$U302="DNA")),$M302:$U302),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M302:$U302)+($M302:$U302="DNA")),$M302:$U302),"")&lt;TODAY())),1,0)+COUNTIF($V302:$Z302,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J302" s="32">
@@ -14954,7 +14965,7 @@
         <v/>
       </c>
       <c r="K302" s="32">
-        <f>IF(NOT(AND($A302&lt;&gt;"",OR($G302="",$G302="Active"))),"",IF($L302&lt;&gt;"",IF($L302=$M302,"Booking",INDEX($N$4:$U$4,MATCH($L302,$N302:$U302,0))),IF(COUNTIF($N302:$U302,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N302:$U302)=0,"All done",IF(MAX($M302:$U302)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A302&lt;&gt;"",OR($G302="",$G302="Active"))),"",IF($L302&lt;&gt;"",IF($L302=$M302,"Booking",INDEX($N$4:$U$4,MATCH($L302,$N302:$U302,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M302:$U302)+($M302:$U302="DNA")),$M302:$U302),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M302:$U302)+($M302:$U302="DNA")),$M302:$U302),"")),IF(ISNUMBER($U302),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L302" s="33">
@@ -14992,7 +15003,7 @@
         <v/>
       </c>
       <c r="I303" s="32">
-        <f>IF(NOT(AND($A303&lt;&gt;"",OR($G303="",$G303="Active"))),"",IF(AND(MAX($M303:$U303)&gt;0,MAX($M303:$U303)&lt;TODAY(),COUNTBLANK($N303:$U303)&gt;0,COUNTIF($N303:$U303,"DNA")=0),1,0)+COUNTIF($N303:$U303,"DNA")+COUNTIF($V303:$Z303,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A303&lt;&gt;"",OR($G303="",$G303="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M303:$U303)+($M303:$U303="DNA")),$M303:$U303),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M303:$U303)+($M303:$U303="DNA")),$M303:$U303),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M303:$U303)+($M303:$U303="DNA")),$M303:$U303),"")&lt;TODAY())),1,0)+COUNTIF($V303:$Z303,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J303" s="32">
@@ -15000,7 +15011,7 @@
         <v/>
       </c>
       <c r="K303" s="32">
-        <f>IF(NOT(AND($A303&lt;&gt;"",OR($G303="",$G303="Active"))),"",IF($L303&lt;&gt;"",IF($L303=$M303,"Booking",INDEX($N$4:$U$4,MATCH($L303,$N303:$U303,0))),IF(COUNTIF($N303:$U303,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N303:$U303)=0,"All done",IF(MAX($M303:$U303)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A303&lt;&gt;"",OR($G303="",$G303="Active"))),"",IF($L303&lt;&gt;"",IF($L303=$M303,"Booking",INDEX($N$4:$U$4,MATCH($L303,$N303:$U303,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M303:$U303)+($M303:$U303="DNA")),$M303:$U303),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M303:$U303)+($M303:$U303="DNA")),$M303:$U303),"")),IF(ISNUMBER($U303),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L303" s="33">
@@ -15038,7 +15049,7 @@
         <v/>
       </c>
       <c r="I304" s="32">
-        <f>IF(NOT(AND($A304&lt;&gt;"",OR($G304="",$G304="Active"))),"",IF(AND(MAX($M304:$U304)&gt;0,MAX($M304:$U304)&lt;TODAY(),COUNTBLANK($N304:$U304)&gt;0,COUNTIF($N304:$U304,"DNA")=0),1,0)+COUNTIF($N304:$U304,"DNA")+COUNTIF($V304:$Z304,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A304&lt;&gt;"",OR($G304="",$G304="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M304:$U304)+($M304:$U304="DNA")),$M304:$U304),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M304:$U304)+($M304:$U304="DNA")),$M304:$U304),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M304:$U304)+($M304:$U304="DNA")),$M304:$U304),"")&lt;TODAY())),1,0)+COUNTIF($V304:$Z304,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J304" s="32">
@@ -15046,7 +15057,7 @@
         <v/>
       </c>
       <c r="K304" s="32">
-        <f>IF(NOT(AND($A304&lt;&gt;"",OR($G304="",$G304="Active"))),"",IF($L304&lt;&gt;"",IF($L304=$M304,"Booking",INDEX($N$4:$U$4,MATCH($L304,$N304:$U304,0))),IF(COUNTIF($N304:$U304,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N304:$U304)=0,"All done",IF(MAX($M304:$U304)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A304&lt;&gt;"",OR($G304="",$G304="Active"))),"",IF($L304&lt;&gt;"",IF($L304=$M304,"Booking",INDEX($N$4:$U$4,MATCH($L304,$N304:$U304,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M304:$U304)+($M304:$U304="DNA")),$M304:$U304),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M304:$U304)+($M304:$U304="DNA")),$M304:$U304),"")),IF(ISNUMBER($U304),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L304" s="33">
@@ -15084,7 +15095,7 @@
         <v/>
       </c>
       <c r="I305" s="32">
-        <f>IF(NOT(AND($A305&lt;&gt;"",OR($G305="",$G305="Active"))),"",IF(AND(MAX($M305:$U305)&gt;0,MAX($M305:$U305)&lt;TODAY(),COUNTBLANK($N305:$U305)&gt;0,COUNTIF($N305:$U305,"DNA")=0),1,0)+COUNTIF($N305:$U305,"DNA")+COUNTIF($V305:$Z305,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A305&lt;&gt;"",OR($G305="",$G305="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M305:$U305)+($M305:$U305="DNA")),$M305:$U305),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M305:$U305)+($M305:$U305="DNA")),$M305:$U305),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M305:$U305)+($M305:$U305="DNA")),$M305:$U305),"")&lt;TODAY())),1,0)+COUNTIF($V305:$Z305,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J305" s="32">
@@ -15092,7 +15103,7 @@
         <v/>
       </c>
       <c r="K305" s="32">
-        <f>IF(NOT(AND($A305&lt;&gt;"",OR($G305="",$G305="Active"))),"",IF($L305&lt;&gt;"",IF($L305=$M305,"Booking",INDEX($N$4:$U$4,MATCH($L305,$N305:$U305,0))),IF(COUNTIF($N305:$U305,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N305:$U305)=0,"All done",IF(MAX($M305:$U305)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A305&lt;&gt;"",OR($G305="",$G305="Active"))),"",IF($L305&lt;&gt;"",IF($L305=$M305,"Booking",INDEX($N$4:$U$4,MATCH($L305,$N305:$U305,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M305:$U305)+($M305:$U305="DNA")),$M305:$U305),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M305:$U305)+($M305:$U305="DNA")),$M305:$U305),"")),IF(ISNUMBER($U305),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L305" s="33">
@@ -15130,7 +15141,7 @@
         <v/>
       </c>
       <c r="I306" s="32">
-        <f>IF(NOT(AND($A306&lt;&gt;"",OR($G306="",$G306="Active"))),"",IF(AND(MAX($M306:$U306)&gt;0,MAX($M306:$U306)&lt;TODAY(),COUNTBLANK($N306:$U306)&gt;0,COUNTIF($N306:$U306,"DNA")=0),1,0)+COUNTIF($N306:$U306,"DNA")+COUNTIF($V306:$Z306,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A306&lt;&gt;"",OR($G306="",$G306="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M306:$U306)+($M306:$U306="DNA")),$M306:$U306),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M306:$U306)+($M306:$U306="DNA")),$M306:$U306),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M306:$U306)+($M306:$U306="DNA")),$M306:$U306),"")&lt;TODAY())),1,0)+COUNTIF($V306:$Z306,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J306" s="32">
@@ -15138,7 +15149,7 @@
         <v/>
       </c>
       <c r="K306" s="32">
-        <f>IF(NOT(AND($A306&lt;&gt;"",OR($G306="",$G306="Active"))),"",IF($L306&lt;&gt;"",IF($L306=$M306,"Booking",INDEX($N$4:$U$4,MATCH($L306,$N306:$U306,0))),IF(COUNTIF($N306:$U306,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N306:$U306)=0,"All done",IF(MAX($M306:$U306)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A306&lt;&gt;"",OR($G306="",$G306="Active"))),"",IF($L306&lt;&gt;"",IF($L306=$M306,"Booking",INDEX($N$4:$U$4,MATCH($L306,$N306:$U306,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M306:$U306)+($M306:$U306="DNA")),$M306:$U306),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M306:$U306)+($M306:$U306="DNA")),$M306:$U306),"")),IF(ISNUMBER($U306),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L306" s="33">
@@ -15176,7 +15187,7 @@
         <v/>
       </c>
       <c r="I307" s="32">
-        <f>IF(NOT(AND($A307&lt;&gt;"",OR($G307="",$G307="Active"))),"",IF(AND(MAX($M307:$U307)&gt;0,MAX($M307:$U307)&lt;TODAY(),COUNTBLANK($N307:$U307)&gt;0,COUNTIF($N307:$U307,"DNA")=0),1,0)+COUNTIF($N307:$U307,"DNA")+COUNTIF($V307:$Z307,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A307&lt;&gt;"",OR($G307="",$G307="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M307:$U307)+($M307:$U307="DNA")),$M307:$U307),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M307:$U307)+($M307:$U307="DNA")),$M307:$U307),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M307:$U307)+($M307:$U307="DNA")),$M307:$U307),"")&lt;TODAY())),1,0)+COUNTIF($V307:$Z307,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J307" s="32">
@@ -15184,7 +15195,7 @@
         <v/>
       </c>
       <c r="K307" s="32">
-        <f>IF(NOT(AND($A307&lt;&gt;"",OR($G307="",$G307="Active"))),"",IF($L307&lt;&gt;"",IF($L307=$M307,"Booking",INDEX($N$4:$U$4,MATCH($L307,$N307:$U307,0))),IF(COUNTIF($N307:$U307,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N307:$U307)=0,"All done",IF(MAX($M307:$U307)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A307&lt;&gt;"",OR($G307="",$G307="Active"))),"",IF($L307&lt;&gt;"",IF($L307=$M307,"Booking",INDEX($N$4:$U$4,MATCH($L307,$N307:$U307,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M307:$U307)+($M307:$U307="DNA")),$M307:$U307),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M307:$U307)+($M307:$U307="DNA")),$M307:$U307),"")),IF(ISNUMBER($U307),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L307" s="33">
@@ -15222,7 +15233,7 @@
         <v/>
       </c>
       <c r="I308" s="32">
-        <f>IF(NOT(AND($A308&lt;&gt;"",OR($G308="",$G308="Active"))),"",IF(AND(MAX($M308:$U308)&gt;0,MAX($M308:$U308)&lt;TODAY(),COUNTBLANK($N308:$U308)&gt;0,COUNTIF($N308:$U308,"DNA")=0),1,0)+COUNTIF($N308:$U308,"DNA")+COUNTIF($V308:$Z308,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A308&lt;&gt;"",OR($G308="",$G308="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M308:$U308)+($M308:$U308="DNA")),$M308:$U308),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M308:$U308)+($M308:$U308="DNA")),$M308:$U308),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M308:$U308)+($M308:$U308="DNA")),$M308:$U308),"")&lt;TODAY())),1,0)+COUNTIF($V308:$Z308,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J308" s="32">
@@ -15230,7 +15241,7 @@
         <v/>
       </c>
       <c r="K308" s="32">
-        <f>IF(NOT(AND($A308&lt;&gt;"",OR($G308="",$G308="Active"))),"",IF($L308&lt;&gt;"",IF($L308=$M308,"Booking",INDEX($N$4:$U$4,MATCH($L308,$N308:$U308,0))),IF(COUNTIF($N308:$U308,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N308:$U308)=0,"All done",IF(MAX($M308:$U308)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A308&lt;&gt;"",OR($G308="",$G308="Active"))),"",IF($L308&lt;&gt;"",IF($L308=$M308,"Booking",INDEX($N$4:$U$4,MATCH($L308,$N308:$U308,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M308:$U308)+($M308:$U308="DNA")),$M308:$U308),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M308:$U308)+($M308:$U308="DNA")),$M308:$U308),"")),IF(ISNUMBER($U308),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L308" s="33">
@@ -15268,7 +15279,7 @@
         <v/>
       </c>
       <c r="I309" s="32">
-        <f>IF(NOT(AND($A309&lt;&gt;"",OR($G309="",$G309="Active"))),"",IF(AND(MAX($M309:$U309)&gt;0,MAX($M309:$U309)&lt;TODAY(),COUNTBLANK($N309:$U309)&gt;0,COUNTIF($N309:$U309,"DNA")=0),1,0)+COUNTIF($N309:$U309,"DNA")+COUNTIF($V309:$Z309,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A309&lt;&gt;"",OR($G309="",$G309="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M309:$U309)+($M309:$U309="DNA")),$M309:$U309),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M309:$U309)+($M309:$U309="DNA")),$M309:$U309),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M309:$U309)+($M309:$U309="DNA")),$M309:$U309),"")&lt;TODAY())),1,0)+COUNTIF($V309:$Z309,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J309" s="32">
@@ -15276,7 +15287,7 @@
         <v/>
       </c>
       <c r="K309" s="32">
-        <f>IF(NOT(AND($A309&lt;&gt;"",OR($G309="",$G309="Active"))),"",IF($L309&lt;&gt;"",IF($L309=$M309,"Booking",INDEX($N$4:$U$4,MATCH($L309,$N309:$U309,0))),IF(COUNTIF($N309:$U309,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N309:$U309)=0,"All done",IF(MAX($M309:$U309)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A309&lt;&gt;"",OR($G309="",$G309="Active"))),"",IF($L309&lt;&gt;"",IF($L309=$M309,"Booking",INDEX($N$4:$U$4,MATCH($L309,$N309:$U309,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M309:$U309)+($M309:$U309="DNA")),$M309:$U309),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M309:$U309)+($M309:$U309="DNA")),$M309:$U309),"")),IF(ISNUMBER($U309),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L309" s="33">
@@ -15314,7 +15325,7 @@
         <v/>
       </c>
       <c r="I310" s="32">
-        <f>IF(NOT(AND($A310&lt;&gt;"",OR($G310="",$G310="Active"))),"",IF(AND(MAX($M310:$U310)&gt;0,MAX($M310:$U310)&lt;TODAY(),COUNTBLANK($N310:$U310)&gt;0,COUNTIF($N310:$U310,"DNA")=0),1,0)+COUNTIF($N310:$U310,"DNA")+COUNTIF($V310:$Z310,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A310&lt;&gt;"",OR($G310="",$G310="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M310:$U310)+($M310:$U310="DNA")),$M310:$U310),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M310:$U310)+($M310:$U310="DNA")),$M310:$U310),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M310:$U310)+($M310:$U310="DNA")),$M310:$U310),"")&lt;TODAY())),1,0)+COUNTIF($V310:$Z310,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J310" s="32">
@@ -15322,7 +15333,7 @@
         <v/>
       </c>
       <c r="K310" s="32">
-        <f>IF(NOT(AND($A310&lt;&gt;"",OR($G310="",$G310="Active"))),"",IF($L310&lt;&gt;"",IF($L310=$M310,"Booking",INDEX($N$4:$U$4,MATCH($L310,$N310:$U310,0))),IF(COUNTIF($N310:$U310,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N310:$U310)=0,"All done",IF(MAX($M310:$U310)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A310&lt;&gt;"",OR($G310="",$G310="Active"))),"",IF($L310&lt;&gt;"",IF($L310=$M310,"Booking",INDEX($N$4:$U$4,MATCH($L310,$N310:$U310,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M310:$U310)+($M310:$U310="DNA")),$M310:$U310),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M310:$U310)+($M310:$U310="DNA")),$M310:$U310),"")),IF(ISNUMBER($U310),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L310" s="33">
@@ -15360,7 +15371,7 @@
         <v/>
       </c>
       <c r="I311" s="32">
-        <f>IF(NOT(AND($A311&lt;&gt;"",OR($G311="",$G311="Active"))),"",IF(AND(MAX($M311:$U311)&gt;0,MAX($M311:$U311)&lt;TODAY(),COUNTBLANK($N311:$U311)&gt;0,COUNTIF($N311:$U311,"DNA")=0),1,0)+COUNTIF($N311:$U311,"DNA")+COUNTIF($V311:$Z311,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A311&lt;&gt;"",OR($G311="",$G311="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M311:$U311)+($M311:$U311="DNA")),$M311:$U311),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M311:$U311)+($M311:$U311="DNA")),$M311:$U311),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M311:$U311)+($M311:$U311="DNA")),$M311:$U311),"")&lt;TODAY())),1,0)+COUNTIF($V311:$Z311,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J311" s="32">
@@ -15368,7 +15379,7 @@
         <v/>
       </c>
       <c r="K311" s="32">
-        <f>IF(NOT(AND($A311&lt;&gt;"",OR($G311="",$G311="Active"))),"",IF($L311&lt;&gt;"",IF($L311=$M311,"Booking",INDEX($N$4:$U$4,MATCH($L311,$N311:$U311,0))),IF(COUNTIF($N311:$U311,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N311:$U311)=0,"All done",IF(MAX($M311:$U311)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A311&lt;&gt;"",OR($G311="",$G311="Active"))),"",IF($L311&lt;&gt;"",IF($L311=$M311,"Booking",INDEX($N$4:$U$4,MATCH($L311,$N311:$U311,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M311:$U311)+($M311:$U311="DNA")),$M311:$U311),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M311:$U311)+($M311:$U311="DNA")),$M311:$U311),"")),IF(ISNUMBER($U311),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L311" s="33">
@@ -15406,7 +15417,7 @@
         <v/>
       </c>
       <c r="I312" s="32">
-        <f>IF(NOT(AND($A312&lt;&gt;"",OR($G312="",$G312="Active"))),"",IF(AND(MAX($M312:$U312)&gt;0,MAX($M312:$U312)&lt;TODAY(),COUNTBLANK($N312:$U312)&gt;0,COUNTIF($N312:$U312,"DNA")=0),1,0)+COUNTIF($N312:$U312,"DNA")+COUNTIF($V312:$Z312,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A312&lt;&gt;"",OR($G312="",$G312="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M312:$U312)+($M312:$U312="DNA")),$M312:$U312),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M312:$U312)+($M312:$U312="DNA")),$M312:$U312),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M312:$U312)+($M312:$U312="DNA")),$M312:$U312),"")&lt;TODAY())),1,0)+COUNTIF($V312:$Z312,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J312" s="32">
@@ -15414,7 +15425,7 @@
         <v/>
       </c>
       <c r="K312" s="32">
-        <f>IF(NOT(AND($A312&lt;&gt;"",OR($G312="",$G312="Active"))),"",IF($L312&lt;&gt;"",IF($L312=$M312,"Booking",INDEX($N$4:$U$4,MATCH($L312,$N312:$U312,0))),IF(COUNTIF($N312:$U312,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N312:$U312)=0,"All done",IF(MAX($M312:$U312)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A312&lt;&gt;"",OR($G312="",$G312="Active"))),"",IF($L312&lt;&gt;"",IF($L312=$M312,"Booking",INDEX($N$4:$U$4,MATCH($L312,$N312:$U312,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M312:$U312)+($M312:$U312="DNA")),$M312:$U312),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M312:$U312)+($M312:$U312="DNA")),$M312:$U312),"")),IF(ISNUMBER($U312),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L312" s="33">
@@ -15452,7 +15463,7 @@
         <v/>
       </c>
       <c r="I313" s="32">
-        <f>IF(NOT(AND($A313&lt;&gt;"",OR($G313="",$G313="Active"))),"",IF(AND(MAX($M313:$U313)&gt;0,MAX($M313:$U313)&lt;TODAY(),COUNTBLANK($N313:$U313)&gt;0,COUNTIF($N313:$U313,"DNA")=0),1,0)+COUNTIF($N313:$U313,"DNA")+COUNTIF($V313:$Z313,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A313&lt;&gt;"",OR($G313="",$G313="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M313:$U313)+($M313:$U313="DNA")),$M313:$U313),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M313:$U313)+($M313:$U313="DNA")),$M313:$U313),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M313:$U313)+($M313:$U313="DNA")),$M313:$U313),"")&lt;TODAY())),1,0)+COUNTIF($V313:$Z313,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J313" s="32">
@@ -15460,7 +15471,7 @@
         <v/>
       </c>
       <c r="K313" s="32">
-        <f>IF(NOT(AND($A313&lt;&gt;"",OR($G313="",$G313="Active"))),"",IF($L313&lt;&gt;"",IF($L313=$M313,"Booking",INDEX($N$4:$U$4,MATCH($L313,$N313:$U313,0))),IF(COUNTIF($N313:$U313,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N313:$U313)=0,"All done",IF(MAX($M313:$U313)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A313&lt;&gt;"",OR($G313="",$G313="Active"))),"",IF($L313&lt;&gt;"",IF($L313=$M313,"Booking",INDEX($N$4:$U$4,MATCH($L313,$N313:$U313,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M313:$U313)+($M313:$U313="DNA")),$M313:$U313),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M313:$U313)+($M313:$U313="DNA")),$M313:$U313),"")),IF(ISNUMBER($U313),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L313" s="33">
@@ -15498,7 +15509,7 @@
         <v/>
       </c>
       <c r="I314" s="32">
-        <f>IF(NOT(AND($A314&lt;&gt;"",OR($G314="",$G314="Active"))),"",IF(AND(MAX($M314:$U314)&gt;0,MAX($M314:$U314)&lt;TODAY(),COUNTBLANK($N314:$U314)&gt;0,COUNTIF($N314:$U314,"DNA")=0),1,0)+COUNTIF($N314:$U314,"DNA")+COUNTIF($V314:$Z314,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A314&lt;&gt;"",OR($G314="",$G314="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M314:$U314)+($M314:$U314="DNA")),$M314:$U314),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M314:$U314)+($M314:$U314="DNA")),$M314:$U314),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M314:$U314)+($M314:$U314="DNA")),$M314:$U314),"")&lt;TODAY())),1,0)+COUNTIF($V314:$Z314,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J314" s="32">
@@ -15506,7 +15517,7 @@
         <v/>
       </c>
       <c r="K314" s="32">
-        <f>IF(NOT(AND($A314&lt;&gt;"",OR($G314="",$G314="Active"))),"",IF($L314&lt;&gt;"",IF($L314=$M314,"Booking",INDEX($N$4:$U$4,MATCH($L314,$N314:$U314,0))),IF(COUNTIF($N314:$U314,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N314:$U314)=0,"All done",IF(MAX($M314:$U314)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A314&lt;&gt;"",OR($G314="",$G314="Active"))),"",IF($L314&lt;&gt;"",IF($L314=$M314,"Booking",INDEX($N$4:$U$4,MATCH($L314,$N314:$U314,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M314:$U314)+($M314:$U314="DNA")),$M314:$U314),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M314:$U314)+($M314:$U314="DNA")),$M314:$U314),"")),IF(ISNUMBER($U314),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L314" s="33">
@@ -15544,7 +15555,7 @@
         <v/>
       </c>
       <c r="I315" s="32">
-        <f>IF(NOT(AND($A315&lt;&gt;"",OR($G315="",$G315="Active"))),"",IF(AND(MAX($M315:$U315)&gt;0,MAX($M315:$U315)&lt;TODAY(),COUNTBLANK($N315:$U315)&gt;0,COUNTIF($N315:$U315,"DNA")=0),1,0)+COUNTIF($N315:$U315,"DNA")+COUNTIF($V315:$Z315,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A315&lt;&gt;"",OR($G315="",$G315="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M315:$U315)+($M315:$U315="DNA")),$M315:$U315),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M315:$U315)+($M315:$U315="DNA")),$M315:$U315),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M315:$U315)+($M315:$U315="DNA")),$M315:$U315),"")&lt;TODAY())),1,0)+COUNTIF($V315:$Z315,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J315" s="32">
@@ -15552,7 +15563,7 @@
         <v/>
       </c>
       <c r="K315" s="32">
-        <f>IF(NOT(AND($A315&lt;&gt;"",OR($G315="",$G315="Active"))),"",IF($L315&lt;&gt;"",IF($L315=$M315,"Booking",INDEX($N$4:$U$4,MATCH($L315,$N315:$U315,0))),IF(COUNTIF($N315:$U315,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N315:$U315)=0,"All done",IF(MAX($M315:$U315)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A315&lt;&gt;"",OR($G315="",$G315="Active"))),"",IF($L315&lt;&gt;"",IF($L315=$M315,"Booking",INDEX($N$4:$U$4,MATCH($L315,$N315:$U315,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M315:$U315)+($M315:$U315="DNA")),$M315:$U315),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M315:$U315)+($M315:$U315="DNA")),$M315:$U315),"")),IF(ISNUMBER($U315),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L315" s="33">
@@ -15590,7 +15601,7 @@
         <v/>
       </c>
       <c r="I316" s="32">
-        <f>IF(NOT(AND($A316&lt;&gt;"",OR($G316="",$G316="Active"))),"",IF(AND(MAX($M316:$U316)&gt;0,MAX($M316:$U316)&lt;TODAY(),COUNTBLANK($N316:$U316)&gt;0,COUNTIF($N316:$U316,"DNA")=0),1,0)+COUNTIF($N316:$U316,"DNA")+COUNTIF($V316:$Z316,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A316&lt;&gt;"",OR($G316="",$G316="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M316:$U316)+($M316:$U316="DNA")),$M316:$U316),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M316:$U316)+($M316:$U316="DNA")),$M316:$U316),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M316:$U316)+($M316:$U316="DNA")),$M316:$U316),"")&lt;TODAY())),1,0)+COUNTIF($V316:$Z316,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J316" s="32">
@@ -15598,7 +15609,7 @@
         <v/>
       </c>
       <c r="K316" s="32">
-        <f>IF(NOT(AND($A316&lt;&gt;"",OR($G316="",$G316="Active"))),"",IF($L316&lt;&gt;"",IF($L316=$M316,"Booking",INDEX($N$4:$U$4,MATCH($L316,$N316:$U316,0))),IF(COUNTIF($N316:$U316,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N316:$U316)=0,"All done",IF(MAX($M316:$U316)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A316&lt;&gt;"",OR($G316="",$G316="Active"))),"",IF($L316&lt;&gt;"",IF($L316=$M316,"Booking",INDEX($N$4:$U$4,MATCH($L316,$N316:$U316,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M316:$U316)+($M316:$U316="DNA")),$M316:$U316),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M316:$U316)+($M316:$U316="DNA")),$M316:$U316),"")),IF(ISNUMBER($U316),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L316" s="33">
@@ -15636,7 +15647,7 @@
         <v/>
       </c>
       <c r="I317" s="32">
-        <f>IF(NOT(AND($A317&lt;&gt;"",OR($G317="",$G317="Active"))),"",IF(AND(MAX($M317:$U317)&gt;0,MAX($M317:$U317)&lt;TODAY(),COUNTBLANK($N317:$U317)&gt;0,COUNTIF($N317:$U317,"DNA")=0),1,0)+COUNTIF($N317:$U317,"DNA")+COUNTIF($V317:$Z317,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A317&lt;&gt;"",OR($G317="",$G317="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M317:$U317)+($M317:$U317="DNA")),$M317:$U317),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M317:$U317)+($M317:$U317="DNA")),$M317:$U317),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M317:$U317)+($M317:$U317="DNA")),$M317:$U317),"")&lt;TODAY())),1,0)+COUNTIF($V317:$Z317,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J317" s="32">
@@ -15644,7 +15655,7 @@
         <v/>
       </c>
       <c r="K317" s="32">
-        <f>IF(NOT(AND($A317&lt;&gt;"",OR($G317="",$G317="Active"))),"",IF($L317&lt;&gt;"",IF($L317=$M317,"Booking",INDEX($N$4:$U$4,MATCH($L317,$N317:$U317,0))),IF(COUNTIF($N317:$U317,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N317:$U317)=0,"All done",IF(MAX($M317:$U317)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A317&lt;&gt;"",OR($G317="",$G317="Active"))),"",IF($L317&lt;&gt;"",IF($L317=$M317,"Booking",INDEX($N$4:$U$4,MATCH($L317,$N317:$U317,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M317:$U317)+($M317:$U317="DNA")),$M317:$U317),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M317:$U317)+($M317:$U317="DNA")),$M317:$U317),"")),IF(ISNUMBER($U317),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L317" s="33">
@@ -15682,7 +15693,7 @@
         <v/>
       </c>
       <c r="I318" s="32">
-        <f>IF(NOT(AND($A318&lt;&gt;"",OR($G318="",$G318="Active"))),"",IF(AND(MAX($M318:$U318)&gt;0,MAX($M318:$U318)&lt;TODAY(),COUNTBLANK($N318:$U318)&gt;0,COUNTIF($N318:$U318,"DNA")=0),1,0)+COUNTIF($N318:$U318,"DNA")+COUNTIF($V318:$Z318,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A318&lt;&gt;"",OR($G318="",$G318="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M318:$U318)+($M318:$U318="DNA")),$M318:$U318),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M318:$U318)+($M318:$U318="DNA")),$M318:$U318),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M318:$U318)+($M318:$U318="DNA")),$M318:$U318),"")&lt;TODAY())),1,0)+COUNTIF($V318:$Z318,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J318" s="32">
@@ -15690,7 +15701,7 @@
         <v/>
       </c>
       <c r="K318" s="32">
-        <f>IF(NOT(AND($A318&lt;&gt;"",OR($G318="",$G318="Active"))),"",IF($L318&lt;&gt;"",IF($L318=$M318,"Booking",INDEX($N$4:$U$4,MATCH($L318,$N318:$U318,0))),IF(COUNTIF($N318:$U318,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N318:$U318)=0,"All done",IF(MAX($M318:$U318)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A318&lt;&gt;"",OR($G318="",$G318="Active"))),"",IF($L318&lt;&gt;"",IF($L318=$M318,"Booking",INDEX($N$4:$U$4,MATCH($L318,$N318:$U318,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M318:$U318)+($M318:$U318="DNA")),$M318:$U318),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M318:$U318)+($M318:$U318="DNA")),$M318:$U318),"")),IF(ISNUMBER($U318),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L318" s="33">
@@ -15728,7 +15739,7 @@
         <v/>
       </c>
       <c r="I319" s="32">
-        <f>IF(NOT(AND($A319&lt;&gt;"",OR($G319="",$G319="Active"))),"",IF(AND(MAX($M319:$U319)&gt;0,MAX($M319:$U319)&lt;TODAY(),COUNTBLANK($N319:$U319)&gt;0,COUNTIF($N319:$U319,"DNA")=0),1,0)+COUNTIF($N319:$U319,"DNA")+COUNTIF($V319:$Z319,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A319&lt;&gt;"",OR($G319="",$G319="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M319:$U319)+($M319:$U319="DNA")),$M319:$U319),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M319:$U319)+($M319:$U319="DNA")),$M319:$U319),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M319:$U319)+($M319:$U319="DNA")),$M319:$U319),"")&lt;TODAY())),1,0)+COUNTIF($V319:$Z319,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J319" s="32">
@@ -15736,7 +15747,7 @@
         <v/>
       </c>
       <c r="K319" s="32">
-        <f>IF(NOT(AND($A319&lt;&gt;"",OR($G319="",$G319="Active"))),"",IF($L319&lt;&gt;"",IF($L319=$M319,"Booking",INDEX($N$4:$U$4,MATCH($L319,$N319:$U319,0))),IF(COUNTIF($N319:$U319,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N319:$U319)=0,"All done",IF(MAX($M319:$U319)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A319&lt;&gt;"",OR($G319="",$G319="Active"))),"",IF($L319&lt;&gt;"",IF($L319=$M319,"Booking",INDEX($N$4:$U$4,MATCH($L319,$N319:$U319,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M319:$U319)+($M319:$U319="DNA")),$M319:$U319),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M319:$U319)+($M319:$U319="DNA")),$M319:$U319),"")),IF(ISNUMBER($U319),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L319" s="33">
@@ -15774,7 +15785,7 @@
         <v/>
       </c>
       <c r="I320" s="32">
-        <f>IF(NOT(AND($A320&lt;&gt;"",OR($G320="",$G320="Active"))),"",IF(AND(MAX($M320:$U320)&gt;0,MAX($M320:$U320)&lt;TODAY(),COUNTBLANK($N320:$U320)&gt;0,COUNTIF($N320:$U320,"DNA")=0),1,0)+COUNTIF($N320:$U320,"DNA")+COUNTIF($V320:$Z320,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A320&lt;&gt;"",OR($G320="",$G320="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M320:$U320)+($M320:$U320="DNA")),$M320:$U320),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M320:$U320)+($M320:$U320="DNA")),$M320:$U320),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M320:$U320)+($M320:$U320="DNA")),$M320:$U320),"")&lt;TODAY())),1,0)+COUNTIF($V320:$Z320,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J320" s="32">
@@ -15782,7 +15793,7 @@
         <v/>
       </c>
       <c r="K320" s="32">
-        <f>IF(NOT(AND($A320&lt;&gt;"",OR($G320="",$G320="Active"))),"",IF($L320&lt;&gt;"",IF($L320=$M320,"Booking",INDEX($N$4:$U$4,MATCH($L320,$N320:$U320,0))),IF(COUNTIF($N320:$U320,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N320:$U320)=0,"All done",IF(MAX($M320:$U320)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A320&lt;&gt;"",OR($G320="",$G320="Active"))),"",IF($L320&lt;&gt;"",IF($L320=$M320,"Booking",INDEX($N$4:$U$4,MATCH($L320,$N320:$U320,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M320:$U320)+($M320:$U320="DNA")),$M320:$U320),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M320:$U320)+($M320:$U320="DNA")),$M320:$U320),"")),IF(ISNUMBER($U320),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L320" s="33">
@@ -15820,7 +15831,7 @@
         <v/>
       </c>
       <c r="I321" s="32">
-        <f>IF(NOT(AND($A321&lt;&gt;"",OR($G321="",$G321="Active"))),"",IF(AND(MAX($M321:$U321)&gt;0,MAX($M321:$U321)&lt;TODAY(),COUNTBLANK($N321:$U321)&gt;0,COUNTIF($N321:$U321,"DNA")=0),1,0)+COUNTIF($N321:$U321,"DNA")+COUNTIF($V321:$Z321,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A321&lt;&gt;"",OR($G321="",$G321="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M321:$U321)+($M321:$U321="DNA")),$M321:$U321),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M321:$U321)+($M321:$U321="DNA")),$M321:$U321),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M321:$U321)+($M321:$U321="DNA")),$M321:$U321),"")&lt;TODAY())),1,0)+COUNTIF($V321:$Z321,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J321" s="32">
@@ -15828,7 +15839,7 @@
         <v/>
       </c>
       <c r="K321" s="32">
-        <f>IF(NOT(AND($A321&lt;&gt;"",OR($G321="",$G321="Active"))),"",IF($L321&lt;&gt;"",IF($L321=$M321,"Booking",INDEX($N$4:$U$4,MATCH($L321,$N321:$U321,0))),IF(COUNTIF($N321:$U321,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N321:$U321)=0,"All done",IF(MAX($M321:$U321)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A321&lt;&gt;"",OR($G321="",$G321="Active"))),"",IF($L321&lt;&gt;"",IF($L321=$M321,"Booking",INDEX($N$4:$U$4,MATCH($L321,$N321:$U321,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M321:$U321)+($M321:$U321="DNA")),$M321:$U321),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M321:$U321)+($M321:$U321="DNA")),$M321:$U321),"")),IF(ISNUMBER($U321),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L321" s="33">
@@ -15866,7 +15877,7 @@
         <v/>
       </c>
       <c r="I322" s="32">
-        <f>IF(NOT(AND($A322&lt;&gt;"",OR($G322="",$G322="Active"))),"",IF(AND(MAX($M322:$U322)&gt;0,MAX($M322:$U322)&lt;TODAY(),COUNTBLANK($N322:$U322)&gt;0,COUNTIF($N322:$U322,"DNA")=0),1,0)+COUNTIF($N322:$U322,"DNA")+COUNTIF($V322:$Z322,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A322&lt;&gt;"",OR($G322="",$G322="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M322:$U322)+($M322:$U322="DNA")),$M322:$U322),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M322:$U322)+($M322:$U322="DNA")),$M322:$U322),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M322:$U322)+($M322:$U322="DNA")),$M322:$U322),"")&lt;TODAY())),1,0)+COUNTIF($V322:$Z322,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J322" s="32">
@@ -15874,7 +15885,7 @@
         <v/>
       </c>
       <c r="K322" s="32">
-        <f>IF(NOT(AND($A322&lt;&gt;"",OR($G322="",$G322="Active"))),"",IF($L322&lt;&gt;"",IF($L322=$M322,"Booking",INDEX($N$4:$U$4,MATCH($L322,$N322:$U322,0))),IF(COUNTIF($N322:$U322,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N322:$U322)=0,"All done",IF(MAX($M322:$U322)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A322&lt;&gt;"",OR($G322="",$G322="Active"))),"",IF($L322&lt;&gt;"",IF($L322=$M322,"Booking",INDEX($N$4:$U$4,MATCH($L322,$N322:$U322,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M322:$U322)+($M322:$U322="DNA")),$M322:$U322),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M322:$U322)+($M322:$U322="DNA")),$M322:$U322),"")),IF(ISNUMBER($U322),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L322" s="33">
@@ -15912,7 +15923,7 @@
         <v/>
       </c>
       <c r="I323" s="32">
-        <f>IF(NOT(AND($A323&lt;&gt;"",OR($G323="",$G323="Active"))),"",IF(AND(MAX($M323:$U323)&gt;0,MAX($M323:$U323)&lt;TODAY(),COUNTBLANK($N323:$U323)&gt;0,COUNTIF($N323:$U323,"DNA")=0),1,0)+COUNTIF($N323:$U323,"DNA")+COUNTIF($V323:$Z323,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A323&lt;&gt;"",OR($G323="",$G323="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M323:$U323)+($M323:$U323="DNA")),$M323:$U323),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M323:$U323)+($M323:$U323="DNA")),$M323:$U323),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M323:$U323)+($M323:$U323="DNA")),$M323:$U323),"")&lt;TODAY())),1,0)+COUNTIF($V323:$Z323,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J323" s="32">
@@ -15920,7 +15931,7 @@
         <v/>
       </c>
       <c r="K323" s="32">
-        <f>IF(NOT(AND($A323&lt;&gt;"",OR($G323="",$G323="Active"))),"",IF($L323&lt;&gt;"",IF($L323=$M323,"Booking",INDEX($N$4:$U$4,MATCH($L323,$N323:$U323,0))),IF(COUNTIF($N323:$U323,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N323:$U323)=0,"All done",IF(MAX($M323:$U323)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A323&lt;&gt;"",OR($G323="",$G323="Active"))),"",IF($L323&lt;&gt;"",IF($L323=$M323,"Booking",INDEX($N$4:$U$4,MATCH($L323,$N323:$U323,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M323:$U323)+($M323:$U323="DNA")),$M323:$U323),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M323:$U323)+($M323:$U323="DNA")),$M323:$U323),"")),IF(ISNUMBER($U323),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L323" s="33">
@@ -15958,7 +15969,7 @@
         <v/>
       </c>
       <c r="I324" s="32">
-        <f>IF(NOT(AND($A324&lt;&gt;"",OR($G324="",$G324="Active"))),"",IF(AND(MAX($M324:$U324)&gt;0,MAX($M324:$U324)&lt;TODAY(),COUNTBLANK($N324:$U324)&gt;0,COUNTIF($N324:$U324,"DNA")=0),1,0)+COUNTIF($N324:$U324,"DNA")+COUNTIF($V324:$Z324,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A324&lt;&gt;"",OR($G324="",$G324="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M324:$U324)+($M324:$U324="DNA")),$M324:$U324),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M324:$U324)+($M324:$U324="DNA")),$M324:$U324),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M324:$U324)+($M324:$U324="DNA")),$M324:$U324),"")&lt;TODAY())),1,0)+COUNTIF($V324:$Z324,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J324" s="32">
@@ -15966,7 +15977,7 @@
         <v/>
       </c>
       <c r="K324" s="32">
-        <f>IF(NOT(AND($A324&lt;&gt;"",OR($G324="",$G324="Active"))),"",IF($L324&lt;&gt;"",IF($L324=$M324,"Booking",INDEX($N$4:$U$4,MATCH($L324,$N324:$U324,0))),IF(COUNTIF($N324:$U324,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N324:$U324)=0,"All done",IF(MAX($M324:$U324)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A324&lt;&gt;"",OR($G324="",$G324="Active"))),"",IF($L324&lt;&gt;"",IF($L324=$M324,"Booking",INDEX($N$4:$U$4,MATCH($L324,$N324:$U324,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M324:$U324)+($M324:$U324="DNA")),$M324:$U324),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M324:$U324)+($M324:$U324="DNA")),$M324:$U324),"")),IF(ISNUMBER($U324),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L324" s="33">
@@ -16004,7 +16015,7 @@
         <v/>
       </c>
       <c r="I325" s="32">
-        <f>IF(NOT(AND($A325&lt;&gt;"",OR($G325="",$G325="Active"))),"",IF(AND(MAX($M325:$U325)&gt;0,MAX($M325:$U325)&lt;TODAY(),COUNTBLANK($N325:$U325)&gt;0,COUNTIF($N325:$U325,"DNA")=0),1,0)+COUNTIF($N325:$U325,"DNA")+COUNTIF($V325:$Z325,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A325&lt;&gt;"",OR($G325="",$G325="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M325:$U325)+($M325:$U325="DNA")),$M325:$U325),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M325:$U325)+($M325:$U325="DNA")),$M325:$U325),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M325:$U325)+($M325:$U325="DNA")),$M325:$U325),"")&lt;TODAY())),1,0)+COUNTIF($V325:$Z325,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J325" s="32">
@@ -16012,7 +16023,7 @@
         <v/>
       </c>
       <c r="K325" s="32">
-        <f>IF(NOT(AND($A325&lt;&gt;"",OR($G325="",$G325="Active"))),"",IF($L325&lt;&gt;"",IF($L325=$M325,"Booking",INDEX($N$4:$U$4,MATCH($L325,$N325:$U325,0))),IF(COUNTIF($N325:$U325,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N325:$U325)=0,"All done",IF(MAX($M325:$U325)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A325&lt;&gt;"",OR($G325="",$G325="Active"))),"",IF($L325&lt;&gt;"",IF($L325=$M325,"Booking",INDEX($N$4:$U$4,MATCH($L325,$N325:$U325,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M325:$U325)+($M325:$U325="DNA")),$M325:$U325),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M325:$U325)+($M325:$U325="DNA")),$M325:$U325),"")),IF(ISNUMBER($U325),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L325" s="33">
@@ -16050,7 +16061,7 @@
         <v/>
       </c>
       <c r="I326" s="32">
-        <f>IF(NOT(AND($A326&lt;&gt;"",OR($G326="",$G326="Active"))),"",IF(AND(MAX($M326:$U326)&gt;0,MAX($M326:$U326)&lt;TODAY(),COUNTBLANK($N326:$U326)&gt;0,COUNTIF($N326:$U326,"DNA")=0),1,0)+COUNTIF($N326:$U326,"DNA")+COUNTIF($V326:$Z326,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A326&lt;&gt;"",OR($G326="",$G326="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M326:$U326)+($M326:$U326="DNA")),$M326:$U326),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M326:$U326)+($M326:$U326="DNA")),$M326:$U326),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M326:$U326)+($M326:$U326="DNA")),$M326:$U326),"")&lt;TODAY())),1,0)+COUNTIF($V326:$Z326,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J326" s="32">
@@ -16058,7 +16069,7 @@
         <v/>
       </c>
       <c r="K326" s="32">
-        <f>IF(NOT(AND($A326&lt;&gt;"",OR($G326="",$G326="Active"))),"",IF($L326&lt;&gt;"",IF($L326=$M326,"Booking",INDEX($N$4:$U$4,MATCH($L326,$N326:$U326,0))),IF(COUNTIF($N326:$U326,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N326:$U326)=0,"All done",IF(MAX($M326:$U326)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A326&lt;&gt;"",OR($G326="",$G326="Active"))),"",IF($L326&lt;&gt;"",IF($L326=$M326,"Booking",INDEX($N$4:$U$4,MATCH($L326,$N326:$U326,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M326:$U326)+($M326:$U326="DNA")),$M326:$U326),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M326:$U326)+($M326:$U326="DNA")),$M326:$U326),"")),IF(ISNUMBER($U326),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L326" s="33">
@@ -16096,7 +16107,7 @@
         <v/>
       </c>
       <c r="I327" s="32">
-        <f>IF(NOT(AND($A327&lt;&gt;"",OR($G327="",$G327="Active"))),"",IF(AND(MAX($M327:$U327)&gt;0,MAX($M327:$U327)&lt;TODAY(),COUNTBLANK($N327:$U327)&gt;0,COUNTIF($N327:$U327,"DNA")=0),1,0)+COUNTIF($N327:$U327,"DNA")+COUNTIF($V327:$Z327,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A327&lt;&gt;"",OR($G327="",$G327="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M327:$U327)+($M327:$U327="DNA")),$M327:$U327),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M327:$U327)+($M327:$U327="DNA")),$M327:$U327),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M327:$U327)+($M327:$U327="DNA")),$M327:$U327),"")&lt;TODAY())),1,0)+COUNTIF($V327:$Z327,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J327" s="32">
@@ -16104,7 +16115,7 @@
         <v/>
       </c>
       <c r="K327" s="32">
-        <f>IF(NOT(AND($A327&lt;&gt;"",OR($G327="",$G327="Active"))),"",IF($L327&lt;&gt;"",IF($L327=$M327,"Booking",INDEX($N$4:$U$4,MATCH($L327,$N327:$U327,0))),IF(COUNTIF($N327:$U327,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N327:$U327)=0,"All done",IF(MAX($M327:$U327)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A327&lt;&gt;"",OR($G327="",$G327="Active"))),"",IF($L327&lt;&gt;"",IF($L327=$M327,"Booking",INDEX($N$4:$U$4,MATCH($L327,$N327:$U327,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M327:$U327)+($M327:$U327="DNA")),$M327:$U327),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M327:$U327)+($M327:$U327="DNA")),$M327:$U327),"")),IF(ISNUMBER($U327),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L327" s="33">
@@ -16142,7 +16153,7 @@
         <v/>
       </c>
       <c r="I328" s="32">
-        <f>IF(NOT(AND($A328&lt;&gt;"",OR($G328="",$G328="Active"))),"",IF(AND(MAX($M328:$U328)&gt;0,MAX($M328:$U328)&lt;TODAY(),COUNTBLANK($N328:$U328)&gt;0,COUNTIF($N328:$U328,"DNA")=0),1,0)+COUNTIF($N328:$U328,"DNA")+COUNTIF($V328:$Z328,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A328&lt;&gt;"",OR($G328="",$G328="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M328:$U328)+($M328:$U328="DNA")),$M328:$U328),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M328:$U328)+($M328:$U328="DNA")),$M328:$U328),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M328:$U328)+($M328:$U328="DNA")),$M328:$U328),"")&lt;TODAY())),1,0)+COUNTIF($V328:$Z328,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J328" s="32">
@@ -16150,7 +16161,7 @@
         <v/>
       </c>
       <c r="K328" s="32">
-        <f>IF(NOT(AND($A328&lt;&gt;"",OR($G328="",$G328="Active"))),"",IF($L328&lt;&gt;"",IF($L328=$M328,"Booking",INDEX($N$4:$U$4,MATCH($L328,$N328:$U328,0))),IF(COUNTIF($N328:$U328,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N328:$U328)=0,"All done",IF(MAX($M328:$U328)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A328&lt;&gt;"",OR($G328="",$G328="Active"))),"",IF($L328&lt;&gt;"",IF($L328=$M328,"Booking",INDEX($N$4:$U$4,MATCH($L328,$N328:$U328,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M328:$U328)+($M328:$U328="DNA")),$M328:$U328),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M328:$U328)+($M328:$U328="DNA")),$M328:$U328),"")),IF(ISNUMBER($U328),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L328" s="33">
@@ -16188,7 +16199,7 @@
         <v/>
       </c>
       <c r="I329" s="32">
-        <f>IF(NOT(AND($A329&lt;&gt;"",OR($G329="",$G329="Active"))),"",IF(AND(MAX($M329:$U329)&gt;0,MAX($M329:$U329)&lt;TODAY(),COUNTBLANK($N329:$U329)&gt;0,COUNTIF($N329:$U329,"DNA")=0),1,0)+COUNTIF($N329:$U329,"DNA")+COUNTIF($V329:$Z329,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A329&lt;&gt;"",OR($G329="",$G329="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M329:$U329)+($M329:$U329="DNA")),$M329:$U329),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M329:$U329)+($M329:$U329="DNA")),$M329:$U329),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M329:$U329)+($M329:$U329="DNA")),$M329:$U329),"")&lt;TODAY())),1,0)+COUNTIF($V329:$Z329,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J329" s="32">
@@ -16196,7 +16207,7 @@
         <v/>
       </c>
       <c r="K329" s="32">
-        <f>IF(NOT(AND($A329&lt;&gt;"",OR($G329="",$G329="Active"))),"",IF($L329&lt;&gt;"",IF($L329=$M329,"Booking",INDEX($N$4:$U$4,MATCH($L329,$N329:$U329,0))),IF(COUNTIF($N329:$U329,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N329:$U329)=0,"All done",IF(MAX($M329:$U329)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A329&lt;&gt;"",OR($G329="",$G329="Active"))),"",IF($L329&lt;&gt;"",IF($L329=$M329,"Booking",INDEX($N$4:$U$4,MATCH($L329,$N329:$U329,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M329:$U329)+($M329:$U329="DNA")),$M329:$U329),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M329:$U329)+($M329:$U329="DNA")),$M329:$U329),"")),IF(ISNUMBER($U329),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L329" s="33">
@@ -16234,7 +16245,7 @@
         <v/>
       </c>
       <c r="I330" s="32">
-        <f>IF(NOT(AND($A330&lt;&gt;"",OR($G330="",$G330="Active"))),"",IF(AND(MAX($M330:$U330)&gt;0,MAX($M330:$U330)&lt;TODAY(),COUNTBLANK($N330:$U330)&gt;0,COUNTIF($N330:$U330,"DNA")=0),1,0)+COUNTIF($N330:$U330,"DNA")+COUNTIF($V330:$Z330,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A330&lt;&gt;"",OR($G330="",$G330="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M330:$U330)+($M330:$U330="DNA")),$M330:$U330),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M330:$U330)+($M330:$U330="DNA")),$M330:$U330),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M330:$U330)+($M330:$U330="DNA")),$M330:$U330),"")&lt;TODAY())),1,0)+COUNTIF($V330:$Z330,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J330" s="32">
@@ -16242,7 +16253,7 @@
         <v/>
       </c>
       <c r="K330" s="32">
-        <f>IF(NOT(AND($A330&lt;&gt;"",OR($G330="",$G330="Active"))),"",IF($L330&lt;&gt;"",IF($L330=$M330,"Booking",INDEX($N$4:$U$4,MATCH($L330,$N330:$U330,0))),IF(COUNTIF($N330:$U330,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N330:$U330)=0,"All done",IF(MAX($M330:$U330)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A330&lt;&gt;"",OR($G330="",$G330="Active"))),"",IF($L330&lt;&gt;"",IF($L330=$M330,"Booking",INDEX($N$4:$U$4,MATCH($L330,$N330:$U330,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M330:$U330)+($M330:$U330="DNA")),$M330:$U330),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M330:$U330)+($M330:$U330="DNA")),$M330:$U330),"")),IF(ISNUMBER($U330),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L330" s="33">
@@ -16280,7 +16291,7 @@
         <v/>
       </c>
       <c r="I331" s="32">
-        <f>IF(NOT(AND($A331&lt;&gt;"",OR($G331="",$G331="Active"))),"",IF(AND(MAX($M331:$U331)&gt;0,MAX($M331:$U331)&lt;TODAY(),COUNTBLANK($N331:$U331)&gt;0,COUNTIF($N331:$U331,"DNA")=0),1,0)+COUNTIF($N331:$U331,"DNA")+COUNTIF($V331:$Z331,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A331&lt;&gt;"",OR($G331="",$G331="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M331:$U331)+($M331:$U331="DNA")),$M331:$U331),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M331:$U331)+($M331:$U331="DNA")),$M331:$U331),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M331:$U331)+($M331:$U331="DNA")),$M331:$U331),"")&lt;TODAY())),1,0)+COUNTIF($V331:$Z331,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J331" s="32">
@@ -16288,7 +16299,7 @@
         <v/>
       </c>
       <c r="K331" s="32">
-        <f>IF(NOT(AND($A331&lt;&gt;"",OR($G331="",$G331="Active"))),"",IF($L331&lt;&gt;"",IF($L331=$M331,"Booking",INDEX($N$4:$U$4,MATCH($L331,$N331:$U331,0))),IF(COUNTIF($N331:$U331,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N331:$U331)=0,"All done",IF(MAX($M331:$U331)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A331&lt;&gt;"",OR($G331="",$G331="Active"))),"",IF($L331&lt;&gt;"",IF($L331=$M331,"Booking",INDEX($N$4:$U$4,MATCH($L331,$N331:$U331,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M331:$U331)+($M331:$U331="DNA")),$M331:$U331),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M331:$U331)+($M331:$U331="DNA")),$M331:$U331),"")),IF(ISNUMBER($U331),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L331" s="33">
@@ -16326,7 +16337,7 @@
         <v/>
       </c>
       <c r="I332" s="32">
-        <f>IF(NOT(AND($A332&lt;&gt;"",OR($G332="",$G332="Active"))),"",IF(AND(MAX($M332:$U332)&gt;0,MAX($M332:$U332)&lt;TODAY(),COUNTBLANK($N332:$U332)&gt;0,COUNTIF($N332:$U332,"DNA")=0),1,0)+COUNTIF($N332:$U332,"DNA")+COUNTIF($V332:$Z332,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A332&lt;&gt;"",OR($G332="",$G332="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M332:$U332)+($M332:$U332="DNA")),$M332:$U332),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M332:$U332)+($M332:$U332="DNA")),$M332:$U332),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M332:$U332)+($M332:$U332="DNA")),$M332:$U332),"")&lt;TODAY())),1,0)+COUNTIF($V332:$Z332,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J332" s="32">
@@ -16334,7 +16345,7 @@
         <v/>
       </c>
       <c r="K332" s="32">
-        <f>IF(NOT(AND($A332&lt;&gt;"",OR($G332="",$G332="Active"))),"",IF($L332&lt;&gt;"",IF($L332=$M332,"Booking",INDEX($N$4:$U$4,MATCH($L332,$N332:$U332,0))),IF(COUNTIF($N332:$U332,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N332:$U332)=0,"All done",IF(MAX($M332:$U332)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A332&lt;&gt;"",OR($G332="",$G332="Active"))),"",IF($L332&lt;&gt;"",IF($L332=$M332,"Booking",INDEX($N$4:$U$4,MATCH($L332,$N332:$U332,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M332:$U332)+($M332:$U332="DNA")),$M332:$U332),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M332:$U332)+($M332:$U332="DNA")),$M332:$U332),"")),IF(ISNUMBER($U332),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L332" s="33">
@@ -16372,7 +16383,7 @@
         <v/>
       </c>
       <c r="I333" s="32">
-        <f>IF(NOT(AND($A333&lt;&gt;"",OR($G333="",$G333="Active"))),"",IF(AND(MAX($M333:$U333)&gt;0,MAX($M333:$U333)&lt;TODAY(),COUNTBLANK($N333:$U333)&gt;0,COUNTIF($N333:$U333,"DNA")=0),1,0)+COUNTIF($N333:$U333,"DNA")+COUNTIF($V333:$Z333,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A333&lt;&gt;"",OR($G333="",$G333="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M333:$U333)+($M333:$U333="DNA")),$M333:$U333),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M333:$U333)+($M333:$U333="DNA")),$M333:$U333),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M333:$U333)+($M333:$U333="DNA")),$M333:$U333),"")&lt;TODAY())),1,0)+COUNTIF($V333:$Z333,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J333" s="32">
@@ -16380,7 +16391,7 @@
         <v/>
       </c>
       <c r="K333" s="32">
-        <f>IF(NOT(AND($A333&lt;&gt;"",OR($G333="",$G333="Active"))),"",IF($L333&lt;&gt;"",IF($L333=$M333,"Booking",INDEX($N$4:$U$4,MATCH($L333,$N333:$U333,0))),IF(COUNTIF($N333:$U333,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N333:$U333)=0,"All done",IF(MAX($M333:$U333)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A333&lt;&gt;"",OR($G333="",$G333="Active"))),"",IF($L333&lt;&gt;"",IF($L333=$M333,"Booking",INDEX($N$4:$U$4,MATCH($L333,$N333:$U333,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M333:$U333)+($M333:$U333="DNA")),$M333:$U333),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M333:$U333)+($M333:$U333="DNA")),$M333:$U333),"")),IF(ISNUMBER($U333),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L333" s="33">
@@ -16418,7 +16429,7 @@
         <v/>
       </c>
       <c r="I334" s="32">
-        <f>IF(NOT(AND($A334&lt;&gt;"",OR($G334="",$G334="Active"))),"",IF(AND(MAX($M334:$U334)&gt;0,MAX($M334:$U334)&lt;TODAY(),COUNTBLANK($N334:$U334)&gt;0,COUNTIF($N334:$U334,"DNA")=0),1,0)+COUNTIF($N334:$U334,"DNA")+COUNTIF($V334:$Z334,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A334&lt;&gt;"",OR($G334="",$G334="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M334:$U334)+($M334:$U334="DNA")),$M334:$U334),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M334:$U334)+($M334:$U334="DNA")),$M334:$U334),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M334:$U334)+($M334:$U334="DNA")),$M334:$U334),"")&lt;TODAY())),1,0)+COUNTIF($V334:$Z334,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J334" s="32">
@@ -16426,7 +16437,7 @@
         <v/>
       </c>
       <c r="K334" s="32">
-        <f>IF(NOT(AND($A334&lt;&gt;"",OR($G334="",$G334="Active"))),"",IF($L334&lt;&gt;"",IF($L334=$M334,"Booking",INDEX($N$4:$U$4,MATCH($L334,$N334:$U334,0))),IF(COUNTIF($N334:$U334,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N334:$U334)=0,"All done",IF(MAX($M334:$U334)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A334&lt;&gt;"",OR($G334="",$G334="Active"))),"",IF($L334&lt;&gt;"",IF($L334=$M334,"Booking",INDEX($N$4:$U$4,MATCH($L334,$N334:$U334,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M334:$U334)+($M334:$U334="DNA")),$M334:$U334),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M334:$U334)+($M334:$U334="DNA")),$M334:$U334),"")),IF(ISNUMBER($U334),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L334" s="33">
@@ -16464,7 +16475,7 @@
         <v/>
       </c>
       <c r="I335" s="32">
-        <f>IF(NOT(AND($A335&lt;&gt;"",OR($G335="",$G335="Active"))),"",IF(AND(MAX($M335:$U335)&gt;0,MAX($M335:$U335)&lt;TODAY(),COUNTBLANK($N335:$U335)&gt;0,COUNTIF($N335:$U335,"DNA")=0),1,0)+COUNTIF($N335:$U335,"DNA")+COUNTIF($V335:$Z335,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A335&lt;&gt;"",OR($G335="",$G335="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M335:$U335)+($M335:$U335="DNA")),$M335:$U335),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M335:$U335)+($M335:$U335="DNA")),$M335:$U335),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M335:$U335)+($M335:$U335="DNA")),$M335:$U335),"")&lt;TODAY())),1,0)+COUNTIF($V335:$Z335,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J335" s="32">
@@ -16472,7 +16483,7 @@
         <v/>
       </c>
       <c r="K335" s="32">
-        <f>IF(NOT(AND($A335&lt;&gt;"",OR($G335="",$G335="Active"))),"",IF($L335&lt;&gt;"",IF($L335=$M335,"Booking",INDEX($N$4:$U$4,MATCH($L335,$N335:$U335,0))),IF(COUNTIF($N335:$U335,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N335:$U335)=0,"All done",IF(MAX($M335:$U335)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A335&lt;&gt;"",OR($G335="",$G335="Active"))),"",IF($L335&lt;&gt;"",IF($L335=$M335,"Booking",INDEX($N$4:$U$4,MATCH($L335,$N335:$U335,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M335:$U335)+($M335:$U335="DNA")),$M335:$U335),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M335:$U335)+($M335:$U335="DNA")),$M335:$U335),"")),IF(ISNUMBER($U335),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L335" s="33">
@@ -16510,7 +16521,7 @@
         <v/>
       </c>
       <c r="I336" s="32">
-        <f>IF(NOT(AND($A336&lt;&gt;"",OR($G336="",$G336="Active"))),"",IF(AND(MAX($M336:$U336)&gt;0,MAX($M336:$U336)&lt;TODAY(),COUNTBLANK($N336:$U336)&gt;0,COUNTIF($N336:$U336,"DNA")=0),1,0)+COUNTIF($N336:$U336,"DNA")+COUNTIF($V336:$Z336,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A336&lt;&gt;"",OR($G336="",$G336="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M336:$U336)+($M336:$U336="DNA")),$M336:$U336),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M336:$U336)+($M336:$U336="DNA")),$M336:$U336),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M336:$U336)+($M336:$U336="DNA")),$M336:$U336),"")&lt;TODAY())),1,0)+COUNTIF($V336:$Z336,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J336" s="32">
@@ -16518,7 +16529,7 @@
         <v/>
       </c>
       <c r="K336" s="32">
-        <f>IF(NOT(AND($A336&lt;&gt;"",OR($G336="",$G336="Active"))),"",IF($L336&lt;&gt;"",IF($L336=$M336,"Booking",INDEX($N$4:$U$4,MATCH($L336,$N336:$U336,0))),IF(COUNTIF($N336:$U336,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N336:$U336)=0,"All done",IF(MAX($M336:$U336)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A336&lt;&gt;"",OR($G336="",$G336="Active"))),"",IF($L336&lt;&gt;"",IF($L336=$M336,"Booking",INDEX($N$4:$U$4,MATCH($L336,$N336:$U336,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M336:$U336)+($M336:$U336="DNA")),$M336:$U336),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M336:$U336)+($M336:$U336="DNA")),$M336:$U336),"")),IF(ISNUMBER($U336),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L336" s="33">
@@ -16556,7 +16567,7 @@
         <v/>
       </c>
       <c r="I337" s="32">
-        <f>IF(NOT(AND($A337&lt;&gt;"",OR($G337="",$G337="Active"))),"",IF(AND(MAX($M337:$U337)&gt;0,MAX($M337:$U337)&lt;TODAY(),COUNTBLANK($N337:$U337)&gt;0,COUNTIF($N337:$U337,"DNA")=0),1,0)+COUNTIF($N337:$U337,"DNA")+COUNTIF($V337:$Z337,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A337&lt;&gt;"",OR($G337="",$G337="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M337:$U337)+($M337:$U337="DNA")),$M337:$U337),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M337:$U337)+($M337:$U337="DNA")),$M337:$U337),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M337:$U337)+($M337:$U337="DNA")),$M337:$U337),"")&lt;TODAY())),1,0)+COUNTIF($V337:$Z337,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J337" s="32">
@@ -16564,7 +16575,7 @@
         <v/>
       </c>
       <c r="K337" s="32">
-        <f>IF(NOT(AND($A337&lt;&gt;"",OR($G337="",$G337="Active"))),"",IF($L337&lt;&gt;"",IF($L337=$M337,"Booking",INDEX($N$4:$U$4,MATCH($L337,$N337:$U337,0))),IF(COUNTIF($N337:$U337,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N337:$U337)=0,"All done",IF(MAX($M337:$U337)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A337&lt;&gt;"",OR($G337="",$G337="Active"))),"",IF($L337&lt;&gt;"",IF($L337=$M337,"Booking",INDEX($N$4:$U$4,MATCH($L337,$N337:$U337,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M337:$U337)+($M337:$U337="DNA")),$M337:$U337),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M337:$U337)+($M337:$U337="DNA")),$M337:$U337),"")),IF(ISNUMBER($U337),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L337" s="33">
@@ -16602,7 +16613,7 @@
         <v/>
       </c>
       <c r="I338" s="32">
-        <f>IF(NOT(AND($A338&lt;&gt;"",OR($G338="",$G338="Active"))),"",IF(AND(MAX($M338:$U338)&gt;0,MAX($M338:$U338)&lt;TODAY(),COUNTBLANK($N338:$U338)&gt;0,COUNTIF($N338:$U338,"DNA")=0),1,0)+COUNTIF($N338:$U338,"DNA")+COUNTIF($V338:$Z338,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A338&lt;&gt;"",OR($G338="",$G338="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M338:$U338)+($M338:$U338="DNA")),$M338:$U338),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M338:$U338)+($M338:$U338="DNA")),$M338:$U338),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M338:$U338)+($M338:$U338="DNA")),$M338:$U338),"")&lt;TODAY())),1,0)+COUNTIF($V338:$Z338,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J338" s="32">
@@ -16610,7 +16621,7 @@
         <v/>
       </c>
       <c r="K338" s="32">
-        <f>IF(NOT(AND($A338&lt;&gt;"",OR($G338="",$G338="Active"))),"",IF($L338&lt;&gt;"",IF($L338=$M338,"Booking",INDEX($N$4:$U$4,MATCH($L338,$N338:$U338,0))),IF(COUNTIF($N338:$U338,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N338:$U338)=0,"All done",IF(MAX($M338:$U338)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A338&lt;&gt;"",OR($G338="",$G338="Active"))),"",IF($L338&lt;&gt;"",IF($L338=$M338,"Booking",INDEX($N$4:$U$4,MATCH($L338,$N338:$U338,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M338:$U338)+($M338:$U338="DNA")),$M338:$U338),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M338:$U338)+($M338:$U338="DNA")),$M338:$U338),"")),IF(ISNUMBER($U338),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L338" s="33">
@@ -16648,7 +16659,7 @@
         <v/>
       </c>
       <c r="I339" s="32">
-        <f>IF(NOT(AND($A339&lt;&gt;"",OR($G339="",$G339="Active"))),"",IF(AND(MAX($M339:$U339)&gt;0,MAX($M339:$U339)&lt;TODAY(),COUNTBLANK($N339:$U339)&gt;0,COUNTIF($N339:$U339,"DNA")=0),1,0)+COUNTIF($N339:$U339,"DNA")+COUNTIF($V339:$Z339,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A339&lt;&gt;"",OR($G339="",$G339="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M339:$U339)+($M339:$U339="DNA")),$M339:$U339),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M339:$U339)+($M339:$U339="DNA")),$M339:$U339),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M339:$U339)+($M339:$U339="DNA")),$M339:$U339),"")&lt;TODAY())),1,0)+COUNTIF($V339:$Z339,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J339" s="32">
@@ -16656,7 +16667,7 @@
         <v/>
       </c>
       <c r="K339" s="32">
-        <f>IF(NOT(AND($A339&lt;&gt;"",OR($G339="",$G339="Active"))),"",IF($L339&lt;&gt;"",IF($L339=$M339,"Booking",INDEX($N$4:$U$4,MATCH($L339,$N339:$U339,0))),IF(COUNTIF($N339:$U339,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N339:$U339)=0,"All done",IF(MAX($M339:$U339)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A339&lt;&gt;"",OR($G339="",$G339="Active"))),"",IF($L339&lt;&gt;"",IF($L339=$M339,"Booking",INDEX($N$4:$U$4,MATCH($L339,$N339:$U339,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M339:$U339)+($M339:$U339="DNA")),$M339:$U339),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M339:$U339)+($M339:$U339="DNA")),$M339:$U339),"")),IF(ISNUMBER($U339),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L339" s="33">
@@ -16694,7 +16705,7 @@
         <v/>
       </c>
       <c r="I340" s="32">
-        <f>IF(NOT(AND($A340&lt;&gt;"",OR($G340="",$G340="Active"))),"",IF(AND(MAX($M340:$U340)&gt;0,MAX($M340:$U340)&lt;TODAY(),COUNTBLANK($N340:$U340)&gt;0,COUNTIF($N340:$U340,"DNA")=0),1,0)+COUNTIF($N340:$U340,"DNA")+COUNTIF($V340:$Z340,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A340&lt;&gt;"",OR($G340="",$G340="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M340:$U340)+($M340:$U340="DNA")),$M340:$U340),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M340:$U340)+($M340:$U340="DNA")),$M340:$U340),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M340:$U340)+($M340:$U340="DNA")),$M340:$U340),"")&lt;TODAY())),1,0)+COUNTIF($V340:$Z340,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J340" s="32">
@@ -16702,7 +16713,7 @@
         <v/>
       </c>
       <c r="K340" s="32">
-        <f>IF(NOT(AND($A340&lt;&gt;"",OR($G340="",$G340="Active"))),"",IF($L340&lt;&gt;"",IF($L340=$M340,"Booking",INDEX($N$4:$U$4,MATCH($L340,$N340:$U340,0))),IF(COUNTIF($N340:$U340,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N340:$U340)=0,"All done",IF(MAX($M340:$U340)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A340&lt;&gt;"",OR($G340="",$G340="Active"))),"",IF($L340&lt;&gt;"",IF($L340=$M340,"Booking",INDEX($N$4:$U$4,MATCH($L340,$N340:$U340,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M340:$U340)+($M340:$U340="DNA")),$M340:$U340),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M340:$U340)+($M340:$U340="DNA")),$M340:$U340),"")),IF(ISNUMBER($U340),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L340" s="33">
@@ -16740,7 +16751,7 @@
         <v/>
       </c>
       <c r="I341" s="32">
-        <f>IF(NOT(AND($A341&lt;&gt;"",OR($G341="",$G341="Active"))),"",IF(AND(MAX($M341:$U341)&gt;0,MAX($M341:$U341)&lt;TODAY(),COUNTBLANK($N341:$U341)&gt;0,COUNTIF($N341:$U341,"DNA")=0),1,0)+COUNTIF($N341:$U341,"DNA")+COUNTIF($V341:$Z341,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A341&lt;&gt;"",OR($G341="",$G341="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M341:$U341)+($M341:$U341="DNA")),$M341:$U341),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M341:$U341)+($M341:$U341="DNA")),$M341:$U341),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M341:$U341)+($M341:$U341="DNA")),$M341:$U341),"")&lt;TODAY())),1,0)+COUNTIF($V341:$Z341,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J341" s="32">
@@ -16748,7 +16759,7 @@
         <v/>
       </c>
       <c r="K341" s="32">
-        <f>IF(NOT(AND($A341&lt;&gt;"",OR($G341="",$G341="Active"))),"",IF($L341&lt;&gt;"",IF($L341=$M341,"Booking",INDEX($N$4:$U$4,MATCH($L341,$N341:$U341,0))),IF(COUNTIF($N341:$U341,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N341:$U341)=0,"All done",IF(MAX($M341:$U341)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A341&lt;&gt;"",OR($G341="",$G341="Active"))),"",IF($L341&lt;&gt;"",IF($L341=$M341,"Booking",INDEX($N$4:$U$4,MATCH($L341,$N341:$U341,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M341:$U341)+($M341:$U341="DNA")),$M341:$U341),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M341:$U341)+($M341:$U341="DNA")),$M341:$U341),"")),IF(ISNUMBER($U341),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L341" s="33">
@@ -16786,7 +16797,7 @@
         <v/>
       </c>
       <c r="I342" s="32">
-        <f>IF(NOT(AND($A342&lt;&gt;"",OR($G342="",$G342="Active"))),"",IF(AND(MAX($M342:$U342)&gt;0,MAX($M342:$U342)&lt;TODAY(),COUNTBLANK($N342:$U342)&gt;0,COUNTIF($N342:$U342,"DNA")=0),1,0)+COUNTIF($N342:$U342,"DNA")+COUNTIF($V342:$Z342,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A342&lt;&gt;"",OR($G342="",$G342="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M342:$U342)+($M342:$U342="DNA")),$M342:$U342),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M342:$U342)+($M342:$U342="DNA")),$M342:$U342),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M342:$U342)+($M342:$U342="DNA")),$M342:$U342),"")&lt;TODAY())),1,0)+COUNTIF($V342:$Z342,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J342" s="32">
@@ -16794,7 +16805,7 @@
         <v/>
       </c>
       <c r="K342" s="32">
-        <f>IF(NOT(AND($A342&lt;&gt;"",OR($G342="",$G342="Active"))),"",IF($L342&lt;&gt;"",IF($L342=$M342,"Booking",INDEX($N$4:$U$4,MATCH($L342,$N342:$U342,0))),IF(COUNTIF($N342:$U342,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N342:$U342)=0,"All done",IF(MAX($M342:$U342)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A342&lt;&gt;"",OR($G342="",$G342="Active"))),"",IF($L342&lt;&gt;"",IF($L342=$M342,"Booking",INDEX($N$4:$U$4,MATCH($L342,$N342:$U342,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M342:$U342)+($M342:$U342="DNA")),$M342:$U342),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M342:$U342)+($M342:$U342="DNA")),$M342:$U342),"")),IF(ISNUMBER($U342),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L342" s="33">
@@ -16832,7 +16843,7 @@
         <v/>
       </c>
       <c r="I343" s="32">
-        <f>IF(NOT(AND($A343&lt;&gt;"",OR($G343="",$G343="Active"))),"",IF(AND(MAX($M343:$U343)&gt;0,MAX($M343:$U343)&lt;TODAY(),COUNTBLANK($N343:$U343)&gt;0,COUNTIF($N343:$U343,"DNA")=0),1,0)+COUNTIF($N343:$U343,"DNA")+COUNTIF($V343:$Z343,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A343&lt;&gt;"",OR($G343="",$G343="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M343:$U343)+($M343:$U343="DNA")),$M343:$U343),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M343:$U343)+($M343:$U343="DNA")),$M343:$U343),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M343:$U343)+($M343:$U343="DNA")),$M343:$U343),"")&lt;TODAY())),1,0)+COUNTIF($V343:$Z343,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J343" s="32">
@@ -16840,7 +16851,7 @@
         <v/>
       </c>
       <c r="K343" s="32">
-        <f>IF(NOT(AND($A343&lt;&gt;"",OR($G343="",$G343="Active"))),"",IF($L343&lt;&gt;"",IF($L343=$M343,"Booking",INDEX($N$4:$U$4,MATCH($L343,$N343:$U343,0))),IF(COUNTIF($N343:$U343,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N343:$U343)=0,"All done",IF(MAX($M343:$U343)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A343&lt;&gt;"",OR($G343="",$G343="Active"))),"",IF($L343&lt;&gt;"",IF($L343=$M343,"Booking",INDEX($N$4:$U$4,MATCH($L343,$N343:$U343,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M343:$U343)+($M343:$U343="DNA")),$M343:$U343),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M343:$U343)+($M343:$U343="DNA")),$M343:$U343),"")),IF(ISNUMBER($U343),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L343" s="33">
@@ -16878,7 +16889,7 @@
         <v/>
       </c>
       <c r="I344" s="32">
-        <f>IF(NOT(AND($A344&lt;&gt;"",OR($G344="",$G344="Active"))),"",IF(AND(MAX($M344:$U344)&gt;0,MAX($M344:$U344)&lt;TODAY(),COUNTBLANK($N344:$U344)&gt;0,COUNTIF($N344:$U344,"DNA")=0),1,0)+COUNTIF($N344:$U344,"DNA")+COUNTIF($V344:$Z344,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A344&lt;&gt;"",OR($G344="",$G344="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M344:$U344)+($M344:$U344="DNA")),$M344:$U344),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M344:$U344)+($M344:$U344="DNA")),$M344:$U344),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M344:$U344)+($M344:$U344="DNA")),$M344:$U344),"")&lt;TODAY())),1,0)+COUNTIF($V344:$Z344,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J344" s="32">
@@ -16886,7 +16897,7 @@
         <v/>
       </c>
       <c r="K344" s="32">
-        <f>IF(NOT(AND($A344&lt;&gt;"",OR($G344="",$G344="Active"))),"",IF($L344&lt;&gt;"",IF($L344=$M344,"Booking",INDEX($N$4:$U$4,MATCH($L344,$N344:$U344,0))),IF(COUNTIF($N344:$U344,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N344:$U344)=0,"All done",IF(MAX($M344:$U344)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A344&lt;&gt;"",OR($G344="",$G344="Active"))),"",IF($L344&lt;&gt;"",IF($L344=$M344,"Booking",INDEX($N$4:$U$4,MATCH($L344,$N344:$U344,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M344:$U344)+($M344:$U344="DNA")),$M344:$U344),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M344:$U344)+($M344:$U344="DNA")),$M344:$U344),"")),IF(ISNUMBER($U344),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L344" s="33">
@@ -16924,7 +16935,7 @@
         <v/>
       </c>
       <c r="I345" s="32">
-        <f>IF(NOT(AND($A345&lt;&gt;"",OR($G345="",$G345="Active"))),"",IF(AND(MAX($M345:$U345)&gt;0,MAX($M345:$U345)&lt;TODAY(),COUNTBLANK($N345:$U345)&gt;0,COUNTIF($N345:$U345,"DNA")=0),1,0)+COUNTIF($N345:$U345,"DNA")+COUNTIF($V345:$Z345,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A345&lt;&gt;"",OR($G345="",$G345="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M345:$U345)+($M345:$U345="DNA")),$M345:$U345),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M345:$U345)+($M345:$U345="DNA")),$M345:$U345),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M345:$U345)+($M345:$U345="DNA")),$M345:$U345),"")&lt;TODAY())),1,0)+COUNTIF($V345:$Z345,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J345" s="32">
@@ -16932,7 +16943,7 @@
         <v/>
       </c>
       <c r="K345" s="32">
-        <f>IF(NOT(AND($A345&lt;&gt;"",OR($G345="",$G345="Active"))),"",IF($L345&lt;&gt;"",IF($L345=$M345,"Booking",INDEX($N$4:$U$4,MATCH($L345,$N345:$U345,0))),IF(COUNTIF($N345:$U345,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N345:$U345)=0,"All done",IF(MAX($M345:$U345)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A345&lt;&gt;"",OR($G345="",$G345="Active"))),"",IF($L345&lt;&gt;"",IF($L345=$M345,"Booking",INDEX($N$4:$U$4,MATCH($L345,$N345:$U345,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M345:$U345)+($M345:$U345="DNA")),$M345:$U345),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M345:$U345)+($M345:$U345="DNA")),$M345:$U345),"")),IF(ISNUMBER($U345),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L345" s="33">
@@ -16970,7 +16981,7 @@
         <v/>
       </c>
       <c r="I346" s="32">
-        <f>IF(NOT(AND($A346&lt;&gt;"",OR($G346="",$G346="Active"))),"",IF(AND(MAX($M346:$U346)&gt;0,MAX($M346:$U346)&lt;TODAY(),COUNTBLANK($N346:$U346)&gt;0,COUNTIF($N346:$U346,"DNA")=0),1,0)+COUNTIF($N346:$U346,"DNA")+COUNTIF($V346:$Z346,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A346&lt;&gt;"",OR($G346="",$G346="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M346:$U346)+($M346:$U346="DNA")),$M346:$U346),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M346:$U346)+($M346:$U346="DNA")),$M346:$U346),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M346:$U346)+($M346:$U346="DNA")),$M346:$U346),"")&lt;TODAY())),1,0)+COUNTIF($V346:$Z346,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J346" s="32">
@@ -16978,7 +16989,7 @@
         <v/>
       </c>
       <c r="K346" s="32">
-        <f>IF(NOT(AND($A346&lt;&gt;"",OR($G346="",$G346="Active"))),"",IF($L346&lt;&gt;"",IF($L346=$M346,"Booking",INDEX($N$4:$U$4,MATCH($L346,$N346:$U346,0))),IF(COUNTIF($N346:$U346,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N346:$U346)=0,"All done",IF(MAX($M346:$U346)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A346&lt;&gt;"",OR($G346="",$G346="Active"))),"",IF($L346&lt;&gt;"",IF($L346=$M346,"Booking",INDEX($N$4:$U$4,MATCH($L346,$N346:$U346,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M346:$U346)+($M346:$U346="DNA")),$M346:$U346),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M346:$U346)+($M346:$U346="DNA")),$M346:$U346),"")),IF(ISNUMBER($U346),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L346" s="33">
@@ -17016,7 +17027,7 @@
         <v/>
       </c>
       <c r="I347" s="32">
-        <f>IF(NOT(AND($A347&lt;&gt;"",OR($G347="",$G347="Active"))),"",IF(AND(MAX($M347:$U347)&gt;0,MAX($M347:$U347)&lt;TODAY(),COUNTBLANK($N347:$U347)&gt;0,COUNTIF($N347:$U347,"DNA")=0),1,0)+COUNTIF($N347:$U347,"DNA")+COUNTIF($V347:$Z347,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A347&lt;&gt;"",OR($G347="",$G347="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M347:$U347)+($M347:$U347="DNA")),$M347:$U347),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M347:$U347)+($M347:$U347="DNA")),$M347:$U347),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M347:$U347)+($M347:$U347="DNA")),$M347:$U347),"")&lt;TODAY())),1,0)+COUNTIF($V347:$Z347,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J347" s="32">
@@ -17024,7 +17035,7 @@
         <v/>
       </c>
       <c r="K347" s="32">
-        <f>IF(NOT(AND($A347&lt;&gt;"",OR($G347="",$G347="Active"))),"",IF($L347&lt;&gt;"",IF($L347=$M347,"Booking",INDEX($N$4:$U$4,MATCH($L347,$N347:$U347,0))),IF(COUNTIF($N347:$U347,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N347:$U347)=0,"All done",IF(MAX($M347:$U347)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A347&lt;&gt;"",OR($G347="",$G347="Active"))),"",IF($L347&lt;&gt;"",IF($L347=$M347,"Booking",INDEX($N$4:$U$4,MATCH($L347,$N347:$U347,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M347:$U347)+($M347:$U347="DNA")),$M347:$U347),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M347:$U347)+($M347:$U347="DNA")),$M347:$U347),"")),IF(ISNUMBER($U347),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L347" s="33">
@@ -17062,7 +17073,7 @@
         <v/>
       </c>
       <c r="I348" s="32">
-        <f>IF(NOT(AND($A348&lt;&gt;"",OR($G348="",$G348="Active"))),"",IF(AND(MAX($M348:$U348)&gt;0,MAX($M348:$U348)&lt;TODAY(),COUNTBLANK($N348:$U348)&gt;0,COUNTIF($N348:$U348,"DNA")=0),1,0)+COUNTIF($N348:$U348,"DNA")+COUNTIF($V348:$Z348,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A348&lt;&gt;"",OR($G348="",$G348="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M348:$U348)+($M348:$U348="DNA")),$M348:$U348),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M348:$U348)+($M348:$U348="DNA")),$M348:$U348),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M348:$U348)+($M348:$U348="DNA")),$M348:$U348),"")&lt;TODAY())),1,0)+COUNTIF($V348:$Z348,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J348" s="32">
@@ -17070,7 +17081,7 @@
         <v/>
       </c>
       <c r="K348" s="32">
-        <f>IF(NOT(AND($A348&lt;&gt;"",OR($G348="",$G348="Active"))),"",IF($L348&lt;&gt;"",IF($L348=$M348,"Booking",INDEX($N$4:$U$4,MATCH($L348,$N348:$U348,0))),IF(COUNTIF($N348:$U348,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N348:$U348)=0,"All done",IF(MAX($M348:$U348)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A348&lt;&gt;"",OR($G348="",$G348="Active"))),"",IF($L348&lt;&gt;"",IF($L348=$M348,"Booking",INDEX($N$4:$U$4,MATCH($L348,$N348:$U348,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M348:$U348)+($M348:$U348="DNA")),$M348:$U348),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M348:$U348)+($M348:$U348="DNA")),$M348:$U348),"")),IF(ISNUMBER($U348),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L348" s="33">
@@ -17108,7 +17119,7 @@
         <v/>
       </c>
       <c r="I349" s="32">
-        <f>IF(NOT(AND($A349&lt;&gt;"",OR($G349="",$G349="Active"))),"",IF(AND(MAX($M349:$U349)&gt;0,MAX($M349:$U349)&lt;TODAY(),COUNTBLANK($N349:$U349)&gt;0,COUNTIF($N349:$U349,"DNA")=0),1,0)+COUNTIF($N349:$U349,"DNA")+COUNTIF($V349:$Z349,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A349&lt;&gt;"",OR($G349="",$G349="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M349:$U349)+($M349:$U349="DNA")),$M349:$U349),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M349:$U349)+($M349:$U349="DNA")),$M349:$U349),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M349:$U349)+($M349:$U349="DNA")),$M349:$U349),"")&lt;TODAY())),1,0)+COUNTIF($V349:$Z349,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J349" s="32">
@@ -17116,7 +17127,7 @@
         <v/>
       </c>
       <c r="K349" s="32">
-        <f>IF(NOT(AND($A349&lt;&gt;"",OR($G349="",$G349="Active"))),"",IF($L349&lt;&gt;"",IF($L349=$M349,"Booking",INDEX($N$4:$U$4,MATCH($L349,$N349:$U349,0))),IF(COUNTIF($N349:$U349,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N349:$U349)=0,"All done",IF(MAX($M349:$U349)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A349&lt;&gt;"",OR($G349="",$G349="Active"))),"",IF($L349&lt;&gt;"",IF($L349=$M349,"Booking",INDEX($N$4:$U$4,MATCH($L349,$N349:$U349,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M349:$U349)+($M349:$U349="DNA")),$M349:$U349),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M349:$U349)+($M349:$U349="DNA")),$M349:$U349),"")),IF(ISNUMBER($U349),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L349" s="33">
@@ -17154,7 +17165,7 @@
         <v/>
       </c>
       <c r="I350" s="32">
-        <f>IF(NOT(AND($A350&lt;&gt;"",OR($G350="",$G350="Active"))),"",IF(AND(MAX($M350:$U350)&gt;0,MAX($M350:$U350)&lt;TODAY(),COUNTBLANK($N350:$U350)&gt;0,COUNTIF($N350:$U350,"DNA")=0),1,0)+COUNTIF($N350:$U350,"DNA")+COUNTIF($V350:$Z350,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A350&lt;&gt;"",OR($G350="",$G350="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M350:$U350)+($M350:$U350="DNA")),$M350:$U350),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M350:$U350)+($M350:$U350="DNA")),$M350:$U350),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M350:$U350)+($M350:$U350="DNA")),$M350:$U350),"")&lt;TODAY())),1,0)+COUNTIF($V350:$Z350,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J350" s="32">
@@ -17162,7 +17173,7 @@
         <v/>
       </c>
       <c r="K350" s="32">
-        <f>IF(NOT(AND($A350&lt;&gt;"",OR($G350="",$G350="Active"))),"",IF($L350&lt;&gt;"",IF($L350=$M350,"Booking",INDEX($N$4:$U$4,MATCH($L350,$N350:$U350,0))),IF(COUNTIF($N350:$U350,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N350:$U350)=0,"All done",IF(MAX($M350:$U350)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A350&lt;&gt;"",OR($G350="",$G350="Active"))),"",IF($L350&lt;&gt;"",IF($L350=$M350,"Booking",INDEX($N$4:$U$4,MATCH($L350,$N350:$U350,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M350:$U350)+($M350:$U350="DNA")),$M350:$U350),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M350:$U350)+($M350:$U350="DNA")),$M350:$U350),"")),IF(ISNUMBER($U350),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L350" s="33">
@@ -17200,7 +17211,7 @@
         <v/>
       </c>
       <c r="I351" s="32">
-        <f>IF(NOT(AND($A351&lt;&gt;"",OR($G351="",$G351="Active"))),"",IF(AND(MAX($M351:$U351)&gt;0,MAX($M351:$U351)&lt;TODAY(),COUNTBLANK($N351:$U351)&gt;0,COUNTIF($N351:$U351,"DNA")=0),1,0)+COUNTIF($N351:$U351,"DNA")+COUNTIF($V351:$Z351,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A351&lt;&gt;"",OR($G351="",$G351="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M351:$U351)+($M351:$U351="DNA")),$M351:$U351),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M351:$U351)+($M351:$U351="DNA")),$M351:$U351),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M351:$U351)+($M351:$U351="DNA")),$M351:$U351),"")&lt;TODAY())),1,0)+COUNTIF($V351:$Z351,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J351" s="32">
@@ -17208,7 +17219,7 @@
         <v/>
       </c>
       <c r="K351" s="32">
-        <f>IF(NOT(AND($A351&lt;&gt;"",OR($G351="",$G351="Active"))),"",IF($L351&lt;&gt;"",IF($L351=$M351,"Booking",INDEX($N$4:$U$4,MATCH($L351,$N351:$U351,0))),IF(COUNTIF($N351:$U351,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N351:$U351)=0,"All done",IF(MAX($M351:$U351)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A351&lt;&gt;"",OR($G351="",$G351="Active"))),"",IF($L351&lt;&gt;"",IF($L351=$M351,"Booking",INDEX($N$4:$U$4,MATCH($L351,$N351:$U351,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M351:$U351)+($M351:$U351="DNA")),$M351:$U351),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M351:$U351)+($M351:$U351="DNA")),$M351:$U351),"")),IF(ISNUMBER($U351),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L351" s="33">
@@ -17246,7 +17257,7 @@
         <v/>
       </c>
       <c r="I352" s="32">
-        <f>IF(NOT(AND($A352&lt;&gt;"",OR($G352="",$G352="Active"))),"",IF(AND(MAX($M352:$U352)&gt;0,MAX($M352:$U352)&lt;TODAY(),COUNTBLANK($N352:$U352)&gt;0,COUNTIF($N352:$U352,"DNA")=0),1,0)+COUNTIF($N352:$U352,"DNA")+COUNTIF($V352:$Z352,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A352&lt;&gt;"",OR($G352="",$G352="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M352:$U352)+($M352:$U352="DNA")),$M352:$U352),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M352:$U352)+($M352:$U352="DNA")),$M352:$U352),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M352:$U352)+($M352:$U352="DNA")),$M352:$U352),"")&lt;TODAY())),1,0)+COUNTIF($V352:$Z352,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J352" s="32">
@@ -17254,7 +17265,7 @@
         <v/>
       </c>
       <c r="K352" s="32">
-        <f>IF(NOT(AND($A352&lt;&gt;"",OR($G352="",$G352="Active"))),"",IF($L352&lt;&gt;"",IF($L352=$M352,"Booking",INDEX($N$4:$U$4,MATCH($L352,$N352:$U352,0))),IF(COUNTIF($N352:$U352,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N352:$U352)=0,"All done",IF(MAX($M352:$U352)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A352&lt;&gt;"",OR($G352="",$G352="Active"))),"",IF($L352&lt;&gt;"",IF($L352=$M352,"Booking",INDEX($N$4:$U$4,MATCH($L352,$N352:$U352,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M352:$U352)+($M352:$U352="DNA")),$M352:$U352),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M352:$U352)+($M352:$U352="DNA")),$M352:$U352),"")),IF(ISNUMBER($U352),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L352" s="33">
@@ -17292,7 +17303,7 @@
         <v/>
       </c>
       <c r="I353" s="32">
-        <f>IF(NOT(AND($A353&lt;&gt;"",OR($G353="",$G353="Active"))),"",IF(AND(MAX($M353:$U353)&gt;0,MAX($M353:$U353)&lt;TODAY(),COUNTBLANK($N353:$U353)&gt;0,COUNTIF($N353:$U353,"DNA")=0),1,0)+COUNTIF($N353:$U353,"DNA")+COUNTIF($V353:$Z353,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A353&lt;&gt;"",OR($G353="",$G353="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M353:$U353)+($M353:$U353="DNA")),$M353:$U353),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M353:$U353)+($M353:$U353="DNA")),$M353:$U353),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M353:$U353)+($M353:$U353="DNA")),$M353:$U353),"")&lt;TODAY())),1,0)+COUNTIF($V353:$Z353,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J353" s="32">
@@ -17300,7 +17311,7 @@
         <v/>
       </c>
       <c r="K353" s="32">
-        <f>IF(NOT(AND($A353&lt;&gt;"",OR($G353="",$G353="Active"))),"",IF($L353&lt;&gt;"",IF($L353=$M353,"Booking",INDEX($N$4:$U$4,MATCH($L353,$N353:$U353,0))),IF(COUNTIF($N353:$U353,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N353:$U353)=0,"All done",IF(MAX($M353:$U353)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A353&lt;&gt;"",OR($G353="",$G353="Active"))),"",IF($L353&lt;&gt;"",IF($L353=$M353,"Booking",INDEX($N$4:$U$4,MATCH($L353,$N353:$U353,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M353:$U353)+($M353:$U353="DNA")),$M353:$U353),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M353:$U353)+($M353:$U353="DNA")),$M353:$U353),"")),IF(ISNUMBER($U353),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L353" s="33">
@@ -17338,7 +17349,7 @@
         <v/>
       </c>
       <c r="I354" s="32">
-        <f>IF(NOT(AND($A354&lt;&gt;"",OR($G354="",$G354="Active"))),"",IF(AND(MAX($M354:$U354)&gt;0,MAX($M354:$U354)&lt;TODAY(),COUNTBLANK($N354:$U354)&gt;0,COUNTIF($N354:$U354,"DNA")=0),1,0)+COUNTIF($N354:$U354,"DNA")+COUNTIF($V354:$Z354,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A354&lt;&gt;"",OR($G354="",$G354="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M354:$U354)+($M354:$U354="DNA")),$M354:$U354),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M354:$U354)+($M354:$U354="DNA")),$M354:$U354),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M354:$U354)+($M354:$U354="DNA")),$M354:$U354),"")&lt;TODAY())),1,0)+COUNTIF($V354:$Z354,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J354" s="32">
@@ -17346,7 +17357,7 @@
         <v/>
       </c>
       <c r="K354" s="32">
-        <f>IF(NOT(AND($A354&lt;&gt;"",OR($G354="",$G354="Active"))),"",IF($L354&lt;&gt;"",IF($L354=$M354,"Booking",INDEX($N$4:$U$4,MATCH($L354,$N354:$U354,0))),IF(COUNTIF($N354:$U354,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N354:$U354)=0,"All done",IF(MAX($M354:$U354)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A354&lt;&gt;"",OR($G354="",$G354="Active"))),"",IF($L354&lt;&gt;"",IF($L354=$M354,"Booking",INDEX($N$4:$U$4,MATCH($L354,$N354:$U354,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M354:$U354)+($M354:$U354="DNA")),$M354:$U354),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M354:$U354)+($M354:$U354="DNA")),$M354:$U354),"")),IF(ISNUMBER($U354),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L354" s="33">
@@ -17384,7 +17395,7 @@
         <v/>
       </c>
       <c r="I355" s="32">
-        <f>IF(NOT(AND($A355&lt;&gt;"",OR($G355="",$G355="Active"))),"",IF(AND(MAX($M355:$U355)&gt;0,MAX($M355:$U355)&lt;TODAY(),COUNTBLANK($N355:$U355)&gt;0,COUNTIF($N355:$U355,"DNA")=0),1,0)+COUNTIF($N355:$U355,"DNA")+COUNTIF($V355:$Z355,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A355&lt;&gt;"",OR($G355="",$G355="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M355:$U355)+($M355:$U355="DNA")),$M355:$U355),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M355:$U355)+($M355:$U355="DNA")),$M355:$U355),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M355:$U355)+($M355:$U355="DNA")),$M355:$U355),"")&lt;TODAY())),1,0)+COUNTIF($V355:$Z355,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J355" s="32">
@@ -17392,7 +17403,7 @@
         <v/>
       </c>
       <c r="K355" s="32">
-        <f>IF(NOT(AND($A355&lt;&gt;"",OR($G355="",$G355="Active"))),"",IF($L355&lt;&gt;"",IF($L355=$M355,"Booking",INDEX($N$4:$U$4,MATCH($L355,$N355:$U355,0))),IF(COUNTIF($N355:$U355,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N355:$U355)=0,"All done",IF(MAX($M355:$U355)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A355&lt;&gt;"",OR($G355="",$G355="Active"))),"",IF($L355&lt;&gt;"",IF($L355=$M355,"Booking",INDEX($N$4:$U$4,MATCH($L355,$N355:$U355,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M355:$U355)+($M355:$U355="DNA")),$M355:$U355),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M355:$U355)+($M355:$U355="DNA")),$M355:$U355),"")),IF(ISNUMBER($U355),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L355" s="33">
@@ -17430,7 +17441,7 @@
         <v/>
       </c>
       <c r="I356" s="32">
-        <f>IF(NOT(AND($A356&lt;&gt;"",OR($G356="",$G356="Active"))),"",IF(AND(MAX($M356:$U356)&gt;0,MAX($M356:$U356)&lt;TODAY(),COUNTBLANK($N356:$U356)&gt;0,COUNTIF($N356:$U356,"DNA")=0),1,0)+COUNTIF($N356:$U356,"DNA")+COUNTIF($V356:$Z356,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A356&lt;&gt;"",OR($G356="",$G356="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M356:$U356)+($M356:$U356="DNA")),$M356:$U356),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M356:$U356)+($M356:$U356="DNA")),$M356:$U356),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M356:$U356)+($M356:$U356="DNA")),$M356:$U356),"")&lt;TODAY())),1,0)+COUNTIF($V356:$Z356,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J356" s="32">
@@ -17438,7 +17449,7 @@
         <v/>
       </c>
       <c r="K356" s="32">
-        <f>IF(NOT(AND($A356&lt;&gt;"",OR($G356="",$G356="Active"))),"",IF($L356&lt;&gt;"",IF($L356=$M356,"Booking",INDEX($N$4:$U$4,MATCH($L356,$N356:$U356,0))),IF(COUNTIF($N356:$U356,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N356:$U356)=0,"All done",IF(MAX($M356:$U356)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A356&lt;&gt;"",OR($G356="",$G356="Active"))),"",IF($L356&lt;&gt;"",IF($L356=$M356,"Booking",INDEX($N$4:$U$4,MATCH($L356,$N356:$U356,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M356:$U356)+($M356:$U356="DNA")),$M356:$U356),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M356:$U356)+($M356:$U356="DNA")),$M356:$U356),"")),IF(ISNUMBER($U356),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L356" s="33">
@@ -17476,7 +17487,7 @@
         <v/>
       </c>
       <c r="I357" s="32">
-        <f>IF(NOT(AND($A357&lt;&gt;"",OR($G357="",$G357="Active"))),"",IF(AND(MAX($M357:$U357)&gt;0,MAX($M357:$U357)&lt;TODAY(),COUNTBLANK($N357:$U357)&gt;0,COUNTIF($N357:$U357,"DNA")=0),1,0)+COUNTIF($N357:$U357,"DNA")+COUNTIF($V357:$Z357,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A357&lt;&gt;"",OR($G357="",$G357="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M357:$U357)+($M357:$U357="DNA")),$M357:$U357),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M357:$U357)+($M357:$U357="DNA")),$M357:$U357),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M357:$U357)+($M357:$U357="DNA")),$M357:$U357),"")&lt;TODAY())),1,0)+COUNTIF($V357:$Z357,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J357" s="32">
@@ -17484,7 +17495,7 @@
         <v/>
       </c>
       <c r="K357" s="32">
-        <f>IF(NOT(AND($A357&lt;&gt;"",OR($G357="",$G357="Active"))),"",IF($L357&lt;&gt;"",IF($L357=$M357,"Booking",INDEX($N$4:$U$4,MATCH($L357,$N357:$U357,0))),IF(COUNTIF($N357:$U357,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N357:$U357)=0,"All done",IF(MAX($M357:$U357)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A357&lt;&gt;"",OR($G357="",$G357="Active"))),"",IF($L357&lt;&gt;"",IF($L357=$M357,"Booking",INDEX($N$4:$U$4,MATCH($L357,$N357:$U357,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M357:$U357)+($M357:$U357="DNA")),$M357:$U357),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M357:$U357)+($M357:$U357="DNA")),$M357:$U357),"")),IF(ISNUMBER($U357),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L357" s="33">
@@ -17522,7 +17533,7 @@
         <v/>
       </c>
       <c r="I358" s="32">
-        <f>IF(NOT(AND($A358&lt;&gt;"",OR($G358="",$G358="Active"))),"",IF(AND(MAX($M358:$U358)&gt;0,MAX($M358:$U358)&lt;TODAY(),COUNTBLANK($N358:$U358)&gt;0,COUNTIF($N358:$U358,"DNA")=0),1,0)+COUNTIF($N358:$U358,"DNA")+COUNTIF($V358:$Z358,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A358&lt;&gt;"",OR($G358="",$G358="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M358:$U358)+($M358:$U358="DNA")),$M358:$U358),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M358:$U358)+($M358:$U358="DNA")),$M358:$U358),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M358:$U358)+($M358:$U358="DNA")),$M358:$U358),"")&lt;TODAY())),1,0)+COUNTIF($V358:$Z358,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J358" s="32">
@@ -17530,7 +17541,7 @@
         <v/>
       </c>
       <c r="K358" s="32">
-        <f>IF(NOT(AND($A358&lt;&gt;"",OR($G358="",$G358="Active"))),"",IF($L358&lt;&gt;"",IF($L358=$M358,"Booking",INDEX($N$4:$U$4,MATCH($L358,$N358:$U358,0))),IF(COUNTIF($N358:$U358,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N358:$U358)=0,"All done",IF(MAX($M358:$U358)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A358&lt;&gt;"",OR($G358="",$G358="Active"))),"",IF($L358&lt;&gt;"",IF($L358=$M358,"Booking",INDEX($N$4:$U$4,MATCH($L358,$N358:$U358,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M358:$U358)+($M358:$U358="DNA")),$M358:$U358),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M358:$U358)+($M358:$U358="DNA")),$M358:$U358),"")),IF(ISNUMBER($U358),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L358" s="33">
@@ -17568,7 +17579,7 @@
         <v/>
       </c>
       <c r="I359" s="32">
-        <f>IF(NOT(AND($A359&lt;&gt;"",OR($G359="",$G359="Active"))),"",IF(AND(MAX($M359:$U359)&gt;0,MAX($M359:$U359)&lt;TODAY(),COUNTBLANK($N359:$U359)&gt;0,COUNTIF($N359:$U359,"DNA")=0),1,0)+COUNTIF($N359:$U359,"DNA")+COUNTIF($V359:$Z359,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A359&lt;&gt;"",OR($G359="",$G359="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M359:$U359)+($M359:$U359="DNA")),$M359:$U359),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M359:$U359)+($M359:$U359="DNA")),$M359:$U359),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M359:$U359)+($M359:$U359="DNA")),$M359:$U359),"")&lt;TODAY())),1,0)+COUNTIF($V359:$Z359,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J359" s="32">
@@ -17576,7 +17587,7 @@
         <v/>
       </c>
       <c r="K359" s="32">
-        <f>IF(NOT(AND($A359&lt;&gt;"",OR($G359="",$G359="Active"))),"",IF($L359&lt;&gt;"",IF($L359=$M359,"Booking",INDEX($N$4:$U$4,MATCH($L359,$N359:$U359,0))),IF(COUNTIF($N359:$U359,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N359:$U359)=0,"All done",IF(MAX($M359:$U359)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A359&lt;&gt;"",OR($G359="",$G359="Active"))),"",IF($L359&lt;&gt;"",IF($L359=$M359,"Booking",INDEX($N$4:$U$4,MATCH($L359,$N359:$U359,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M359:$U359)+($M359:$U359="DNA")),$M359:$U359),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M359:$U359)+($M359:$U359="DNA")),$M359:$U359),"")),IF(ISNUMBER($U359),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L359" s="33">
@@ -17614,7 +17625,7 @@
         <v/>
       </c>
       <c r="I360" s="32">
-        <f>IF(NOT(AND($A360&lt;&gt;"",OR($G360="",$G360="Active"))),"",IF(AND(MAX($M360:$U360)&gt;0,MAX($M360:$U360)&lt;TODAY(),COUNTBLANK($N360:$U360)&gt;0,COUNTIF($N360:$U360,"DNA")=0),1,0)+COUNTIF($N360:$U360,"DNA")+COUNTIF($V360:$Z360,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A360&lt;&gt;"",OR($G360="",$G360="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M360:$U360)+($M360:$U360="DNA")),$M360:$U360),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M360:$U360)+($M360:$U360="DNA")),$M360:$U360),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M360:$U360)+($M360:$U360="DNA")),$M360:$U360),"")&lt;TODAY())),1,0)+COUNTIF($V360:$Z360,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J360" s="32">
@@ -17622,7 +17633,7 @@
         <v/>
       </c>
       <c r="K360" s="32">
-        <f>IF(NOT(AND($A360&lt;&gt;"",OR($G360="",$G360="Active"))),"",IF($L360&lt;&gt;"",IF($L360=$M360,"Booking",INDEX($N$4:$U$4,MATCH($L360,$N360:$U360,0))),IF(COUNTIF($N360:$U360,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N360:$U360)=0,"All done",IF(MAX($M360:$U360)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A360&lt;&gt;"",OR($G360="",$G360="Active"))),"",IF($L360&lt;&gt;"",IF($L360=$M360,"Booking",INDEX($N$4:$U$4,MATCH($L360,$N360:$U360,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M360:$U360)+($M360:$U360="DNA")),$M360:$U360),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M360:$U360)+($M360:$U360="DNA")),$M360:$U360),"")),IF(ISNUMBER($U360),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L360" s="33">
@@ -17660,7 +17671,7 @@
         <v/>
       </c>
       <c r="I361" s="32">
-        <f>IF(NOT(AND($A361&lt;&gt;"",OR($G361="",$G361="Active"))),"",IF(AND(MAX($M361:$U361)&gt;0,MAX($M361:$U361)&lt;TODAY(),COUNTBLANK($N361:$U361)&gt;0,COUNTIF($N361:$U361,"DNA")=0),1,0)+COUNTIF($N361:$U361,"DNA")+COUNTIF($V361:$Z361,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A361&lt;&gt;"",OR($G361="",$G361="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M361:$U361)+($M361:$U361="DNA")),$M361:$U361),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M361:$U361)+($M361:$U361="DNA")),$M361:$U361),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M361:$U361)+($M361:$U361="DNA")),$M361:$U361),"")&lt;TODAY())),1,0)+COUNTIF($V361:$Z361,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J361" s="32">
@@ -17668,7 +17679,7 @@
         <v/>
       </c>
       <c r="K361" s="32">
-        <f>IF(NOT(AND($A361&lt;&gt;"",OR($G361="",$G361="Active"))),"",IF($L361&lt;&gt;"",IF($L361=$M361,"Booking",INDEX($N$4:$U$4,MATCH($L361,$N361:$U361,0))),IF(COUNTIF($N361:$U361,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N361:$U361)=0,"All done",IF(MAX($M361:$U361)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A361&lt;&gt;"",OR($G361="",$G361="Active"))),"",IF($L361&lt;&gt;"",IF($L361=$M361,"Booking",INDEX($N$4:$U$4,MATCH($L361,$N361:$U361,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M361:$U361)+($M361:$U361="DNA")),$M361:$U361),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M361:$U361)+($M361:$U361="DNA")),$M361:$U361),"")),IF(ISNUMBER($U361),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L361" s="33">
@@ -17706,7 +17717,7 @@
         <v/>
       </c>
       <c r="I362" s="32">
-        <f>IF(NOT(AND($A362&lt;&gt;"",OR($G362="",$G362="Active"))),"",IF(AND(MAX($M362:$U362)&gt;0,MAX($M362:$U362)&lt;TODAY(),COUNTBLANK($N362:$U362)&gt;0,COUNTIF($N362:$U362,"DNA")=0),1,0)+COUNTIF($N362:$U362,"DNA")+COUNTIF($V362:$Z362,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A362&lt;&gt;"",OR($G362="",$G362="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M362:$U362)+($M362:$U362="DNA")),$M362:$U362),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M362:$U362)+($M362:$U362="DNA")),$M362:$U362),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M362:$U362)+($M362:$U362="DNA")),$M362:$U362),"")&lt;TODAY())),1,0)+COUNTIF($V362:$Z362,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J362" s="32">
@@ -17714,7 +17725,7 @@
         <v/>
       </c>
       <c r="K362" s="32">
-        <f>IF(NOT(AND($A362&lt;&gt;"",OR($G362="",$G362="Active"))),"",IF($L362&lt;&gt;"",IF($L362=$M362,"Booking",INDEX($N$4:$U$4,MATCH($L362,$N362:$U362,0))),IF(COUNTIF($N362:$U362,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N362:$U362)=0,"All done",IF(MAX($M362:$U362)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A362&lt;&gt;"",OR($G362="",$G362="Active"))),"",IF($L362&lt;&gt;"",IF($L362=$M362,"Booking",INDEX($N$4:$U$4,MATCH($L362,$N362:$U362,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M362:$U362)+($M362:$U362="DNA")),$M362:$U362),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M362:$U362)+($M362:$U362="DNA")),$M362:$U362),"")),IF(ISNUMBER($U362),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L362" s="33">
@@ -17752,7 +17763,7 @@
         <v/>
       </c>
       <c r="I363" s="32">
-        <f>IF(NOT(AND($A363&lt;&gt;"",OR($G363="",$G363="Active"))),"",IF(AND(MAX($M363:$U363)&gt;0,MAX($M363:$U363)&lt;TODAY(),COUNTBLANK($N363:$U363)&gt;0,COUNTIF($N363:$U363,"DNA")=0),1,0)+COUNTIF($N363:$U363,"DNA")+COUNTIF($V363:$Z363,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A363&lt;&gt;"",OR($G363="",$G363="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M363:$U363)+($M363:$U363="DNA")),$M363:$U363),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M363:$U363)+($M363:$U363="DNA")),$M363:$U363),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M363:$U363)+($M363:$U363="DNA")),$M363:$U363),"")&lt;TODAY())),1,0)+COUNTIF($V363:$Z363,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J363" s="32">
@@ -17760,7 +17771,7 @@
         <v/>
       </c>
       <c r="K363" s="32">
-        <f>IF(NOT(AND($A363&lt;&gt;"",OR($G363="",$G363="Active"))),"",IF($L363&lt;&gt;"",IF($L363=$M363,"Booking",INDEX($N$4:$U$4,MATCH($L363,$N363:$U363,0))),IF(COUNTIF($N363:$U363,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N363:$U363)=0,"All done",IF(MAX($M363:$U363)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A363&lt;&gt;"",OR($G363="",$G363="Active"))),"",IF($L363&lt;&gt;"",IF($L363=$M363,"Booking",INDEX($N$4:$U$4,MATCH($L363,$N363:$U363,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M363:$U363)+($M363:$U363="DNA")),$M363:$U363),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M363:$U363)+($M363:$U363="DNA")),$M363:$U363),"")),IF(ISNUMBER($U363),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L363" s="33">
@@ -17798,7 +17809,7 @@
         <v/>
       </c>
       <c r="I364" s="32">
-        <f>IF(NOT(AND($A364&lt;&gt;"",OR($G364="",$G364="Active"))),"",IF(AND(MAX($M364:$U364)&gt;0,MAX($M364:$U364)&lt;TODAY(),COUNTBLANK($N364:$U364)&gt;0,COUNTIF($N364:$U364,"DNA")=0),1,0)+COUNTIF($N364:$U364,"DNA")+COUNTIF($V364:$Z364,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A364&lt;&gt;"",OR($G364="",$G364="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M364:$U364)+($M364:$U364="DNA")),$M364:$U364),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M364:$U364)+($M364:$U364="DNA")),$M364:$U364),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M364:$U364)+($M364:$U364="DNA")),$M364:$U364),"")&lt;TODAY())),1,0)+COUNTIF($V364:$Z364,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J364" s="32">
@@ -17806,7 +17817,7 @@
         <v/>
       </c>
       <c r="K364" s="32">
-        <f>IF(NOT(AND($A364&lt;&gt;"",OR($G364="",$G364="Active"))),"",IF($L364&lt;&gt;"",IF($L364=$M364,"Booking",INDEX($N$4:$U$4,MATCH($L364,$N364:$U364,0))),IF(COUNTIF($N364:$U364,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N364:$U364)=0,"All done",IF(MAX($M364:$U364)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A364&lt;&gt;"",OR($G364="",$G364="Active"))),"",IF($L364&lt;&gt;"",IF($L364=$M364,"Booking",INDEX($N$4:$U$4,MATCH($L364,$N364:$U364,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M364:$U364)+($M364:$U364="DNA")),$M364:$U364),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M364:$U364)+($M364:$U364="DNA")),$M364:$U364),"")),IF(ISNUMBER($U364),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L364" s="33">
@@ -17844,7 +17855,7 @@
         <v/>
       </c>
       <c r="I365" s="32">
-        <f>IF(NOT(AND($A365&lt;&gt;"",OR($G365="",$G365="Active"))),"",IF(AND(MAX($M365:$U365)&gt;0,MAX($M365:$U365)&lt;TODAY(),COUNTBLANK($N365:$U365)&gt;0,COUNTIF($N365:$U365,"DNA")=0),1,0)+COUNTIF($N365:$U365,"DNA")+COUNTIF($V365:$Z365,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A365&lt;&gt;"",OR($G365="",$G365="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M365:$U365)+($M365:$U365="DNA")),$M365:$U365),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M365:$U365)+($M365:$U365="DNA")),$M365:$U365),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M365:$U365)+($M365:$U365="DNA")),$M365:$U365),"")&lt;TODAY())),1,0)+COUNTIF($V365:$Z365,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J365" s="32">
@@ -17852,7 +17863,7 @@
         <v/>
       </c>
       <c r="K365" s="32">
-        <f>IF(NOT(AND($A365&lt;&gt;"",OR($G365="",$G365="Active"))),"",IF($L365&lt;&gt;"",IF($L365=$M365,"Booking",INDEX($N$4:$U$4,MATCH($L365,$N365:$U365,0))),IF(COUNTIF($N365:$U365,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N365:$U365)=0,"All done",IF(MAX($M365:$U365)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A365&lt;&gt;"",OR($G365="",$G365="Active"))),"",IF($L365&lt;&gt;"",IF($L365=$M365,"Booking",INDEX($N$4:$U$4,MATCH($L365,$N365:$U365,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M365:$U365)+($M365:$U365="DNA")),$M365:$U365),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M365:$U365)+($M365:$U365="DNA")),$M365:$U365),"")),IF(ISNUMBER($U365),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L365" s="33">
@@ -17890,7 +17901,7 @@
         <v/>
       </c>
       <c r="I366" s="32">
-        <f>IF(NOT(AND($A366&lt;&gt;"",OR($G366="",$G366="Active"))),"",IF(AND(MAX($M366:$U366)&gt;0,MAX($M366:$U366)&lt;TODAY(),COUNTBLANK($N366:$U366)&gt;0,COUNTIF($N366:$U366,"DNA")=0),1,0)+COUNTIF($N366:$U366,"DNA")+COUNTIF($V366:$Z366,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A366&lt;&gt;"",OR($G366="",$G366="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M366:$U366)+($M366:$U366="DNA")),$M366:$U366),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M366:$U366)+($M366:$U366="DNA")),$M366:$U366),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M366:$U366)+($M366:$U366="DNA")),$M366:$U366),"")&lt;TODAY())),1,0)+COUNTIF($V366:$Z366,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J366" s="32">
@@ -17898,7 +17909,7 @@
         <v/>
       </c>
       <c r="K366" s="32">
-        <f>IF(NOT(AND($A366&lt;&gt;"",OR($G366="",$G366="Active"))),"",IF($L366&lt;&gt;"",IF($L366=$M366,"Booking",INDEX($N$4:$U$4,MATCH($L366,$N366:$U366,0))),IF(COUNTIF($N366:$U366,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N366:$U366)=0,"All done",IF(MAX($M366:$U366)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A366&lt;&gt;"",OR($G366="",$G366="Active"))),"",IF($L366&lt;&gt;"",IF($L366=$M366,"Booking",INDEX($N$4:$U$4,MATCH($L366,$N366:$U366,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M366:$U366)+($M366:$U366="DNA")),$M366:$U366),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M366:$U366)+($M366:$U366="DNA")),$M366:$U366),"")),IF(ISNUMBER($U366),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L366" s="33">
@@ -17936,7 +17947,7 @@
         <v/>
       </c>
       <c r="I367" s="32">
-        <f>IF(NOT(AND($A367&lt;&gt;"",OR($G367="",$G367="Active"))),"",IF(AND(MAX($M367:$U367)&gt;0,MAX($M367:$U367)&lt;TODAY(),COUNTBLANK($N367:$U367)&gt;0,COUNTIF($N367:$U367,"DNA")=0),1,0)+COUNTIF($N367:$U367,"DNA")+COUNTIF($V367:$Z367,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A367&lt;&gt;"",OR($G367="",$G367="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M367:$U367)+($M367:$U367="DNA")),$M367:$U367),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M367:$U367)+($M367:$U367="DNA")),$M367:$U367),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M367:$U367)+($M367:$U367="DNA")),$M367:$U367),"")&lt;TODAY())),1,0)+COUNTIF($V367:$Z367,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J367" s="32">
@@ -17944,7 +17955,7 @@
         <v/>
       </c>
       <c r="K367" s="32">
-        <f>IF(NOT(AND($A367&lt;&gt;"",OR($G367="",$G367="Active"))),"",IF($L367&lt;&gt;"",IF($L367=$M367,"Booking",INDEX($N$4:$U$4,MATCH($L367,$N367:$U367,0))),IF(COUNTIF($N367:$U367,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N367:$U367)=0,"All done",IF(MAX($M367:$U367)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A367&lt;&gt;"",OR($G367="",$G367="Active"))),"",IF($L367&lt;&gt;"",IF($L367=$M367,"Booking",INDEX($N$4:$U$4,MATCH($L367,$N367:$U367,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M367:$U367)+($M367:$U367="DNA")),$M367:$U367),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M367:$U367)+($M367:$U367="DNA")),$M367:$U367),"")),IF(ISNUMBER($U367),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L367" s="33">
@@ -17982,7 +17993,7 @@
         <v/>
       </c>
       <c r="I368" s="32">
-        <f>IF(NOT(AND($A368&lt;&gt;"",OR($G368="",$G368="Active"))),"",IF(AND(MAX($M368:$U368)&gt;0,MAX($M368:$U368)&lt;TODAY(),COUNTBLANK($N368:$U368)&gt;0,COUNTIF($N368:$U368,"DNA")=0),1,0)+COUNTIF($N368:$U368,"DNA")+COUNTIF($V368:$Z368,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A368&lt;&gt;"",OR($G368="",$G368="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M368:$U368)+($M368:$U368="DNA")),$M368:$U368),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M368:$U368)+($M368:$U368="DNA")),$M368:$U368),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M368:$U368)+($M368:$U368="DNA")),$M368:$U368),"")&lt;TODAY())),1,0)+COUNTIF($V368:$Z368,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J368" s="32">
@@ -17990,7 +18001,7 @@
         <v/>
       </c>
       <c r="K368" s="32">
-        <f>IF(NOT(AND($A368&lt;&gt;"",OR($G368="",$G368="Active"))),"",IF($L368&lt;&gt;"",IF($L368=$M368,"Booking",INDEX($N$4:$U$4,MATCH($L368,$N368:$U368,0))),IF(COUNTIF($N368:$U368,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N368:$U368)=0,"All done",IF(MAX($M368:$U368)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A368&lt;&gt;"",OR($G368="",$G368="Active"))),"",IF($L368&lt;&gt;"",IF($L368=$M368,"Booking",INDEX($N$4:$U$4,MATCH($L368,$N368:$U368,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M368:$U368)+($M368:$U368="DNA")),$M368:$U368),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M368:$U368)+($M368:$U368="DNA")),$M368:$U368),"")),IF(ISNUMBER($U368),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L368" s="33">
@@ -18028,7 +18039,7 @@
         <v/>
       </c>
       <c r="I369" s="32">
-        <f>IF(NOT(AND($A369&lt;&gt;"",OR($G369="",$G369="Active"))),"",IF(AND(MAX($M369:$U369)&gt;0,MAX($M369:$U369)&lt;TODAY(),COUNTBLANK($N369:$U369)&gt;0,COUNTIF($N369:$U369,"DNA")=0),1,0)+COUNTIF($N369:$U369,"DNA")+COUNTIF($V369:$Z369,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A369&lt;&gt;"",OR($G369="",$G369="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M369:$U369)+($M369:$U369="DNA")),$M369:$U369),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M369:$U369)+($M369:$U369="DNA")),$M369:$U369),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M369:$U369)+($M369:$U369="DNA")),$M369:$U369),"")&lt;TODAY())),1,0)+COUNTIF($V369:$Z369,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J369" s="32">
@@ -18036,7 +18047,7 @@
         <v/>
       </c>
       <c r="K369" s="32">
-        <f>IF(NOT(AND($A369&lt;&gt;"",OR($G369="",$G369="Active"))),"",IF($L369&lt;&gt;"",IF($L369=$M369,"Booking",INDEX($N$4:$U$4,MATCH($L369,$N369:$U369,0))),IF(COUNTIF($N369:$U369,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N369:$U369)=0,"All done",IF(MAX($M369:$U369)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A369&lt;&gt;"",OR($G369="",$G369="Active"))),"",IF($L369&lt;&gt;"",IF($L369=$M369,"Booking",INDEX($N$4:$U$4,MATCH($L369,$N369:$U369,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M369:$U369)+($M369:$U369="DNA")),$M369:$U369),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M369:$U369)+($M369:$U369="DNA")),$M369:$U369),"")),IF(ISNUMBER($U369),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L369" s="33">
@@ -18074,7 +18085,7 @@
         <v/>
       </c>
       <c r="I370" s="32">
-        <f>IF(NOT(AND($A370&lt;&gt;"",OR($G370="",$G370="Active"))),"",IF(AND(MAX($M370:$U370)&gt;0,MAX($M370:$U370)&lt;TODAY(),COUNTBLANK($N370:$U370)&gt;0,COUNTIF($N370:$U370,"DNA")=0),1,0)+COUNTIF($N370:$U370,"DNA")+COUNTIF($V370:$Z370,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A370&lt;&gt;"",OR($G370="",$G370="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M370:$U370)+($M370:$U370="DNA")),$M370:$U370),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M370:$U370)+($M370:$U370="DNA")),$M370:$U370),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M370:$U370)+($M370:$U370="DNA")),$M370:$U370),"")&lt;TODAY())),1,0)+COUNTIF($V370:$Z370,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J370" s="32">
@@ -18082,7 +18093,7 @@
         <v/>
       </c>
       <c r="K370" s="32">
-        <f>IF(NOT(AND($A370&lt;&gt;"",OR($G370="",$G370="Active"))),"",IF($L370&lt;&gt;"",IF($L370=$M370,"Booking",INDEX($N$4:$U$4,MATCH($L370,$N370:$U370,0))),IF(COUNTIF($N370:$U370,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N370:$U370)=0,"All done",IF(MAX($M370:$U370)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A370&lt;&gt;"",OR($G370="",$G370="Active"))),"",IF($L370&lt;&gt;"",IF($L370=$M370,"Booking",INDEX($N$4:$U$4,MATCH($L370,$N370:$U370,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M370:$U370)+($M370:$U370="DNA")),$M370:$U370),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M370:$U370)+($M370:$U370="DNA")),$M370:$U370),"")),IF(ISNUMBER($U370),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L370" s="33">
@@ -18120,7 +18131,7 @@
         <v/>
       </c>
       <c r="I371" s="32">
-        <f>IF(NOT(AND($A371&lt;&gt;"",OR($G371="",$G371="Active"))),"",IF(AND(MAX($M371:$U371)&gt;0,MAX($M371:$U371)&lt;TODAY(),COUNTBLANK($N371:$U371)&gt;0,COUNTIF($N371:$U371,"DNA")=0),1,0)+COUNTIF($N371:$U371,"DNA")+COUNTIF($V371:$Z371,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A371&lt;&gt;"",OR($G371="",$G371="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M371:$U371)+($M371:$U371="DNA")),$M371:$U371),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M371:$U371)+($M371:$U371="DNA")),$M371:$U371),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M371:$U371)+($M371:$U371="DNA")),$M371:$U371),"")&lt;TODAY())),1,0)+COUNTIF($V371:$Z371,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J371" s="32">
@@ -18128,7 +18139,7 @@
         <v/>
       </c>
       <c r="K371" s="32">
-        <f>IF(NOT(AND($A371&lt;&gt;"",OR($G371="",$G371="Active"))),"",IF($L371&lt;&gt;"",IF($L371=$M371,"Booking",INDEX($N$4:$U$4,MATCH($L371,$N371:$U371,0))),IF(COUNTIF($N371:$U371,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N371:$U371)=0,"All done",IF(MAX($M371:$U371)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A371&lt;&gt;"",OR($G371="",$G371="Active"))),"",IF($L371&lt;&gt;"",IF($L371=$M371,"Booking",INDEX($N$4:$U$4,MATCH($L371,$N371:$U371,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M371:$U371)+($M371:$U371="DNA")),$M371:$U371),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M371:$U371)+($M371:$U371="DNA")),$M371:$U371),"")),IF(ISNUMBER($U371),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L371" s="33">
@@ -18166,7 +18177,7 @@
         <v/>
       </c>
       <c r="I372" s="32">
-        <f>IF(NOT(AND($A372&lt;&gt;"",OR($G372="",$G372="Active"))),"",IF(AND(MAX($M372:$U372)&gt;0,MAX($M372:$U372)&lt;TODAY(),COUNTBLANK($N372:$U372)&gt;0,COUNTIF($N372:$U372,"DNA")=0),1,0)+COUNTIF($N372:$U372,"DNA")+COUNTIF($V372:$Z372,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A372&lt;&gt;"",OR($G372="",$G372="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M372:$U372)+($M372:$U372="DNA")),$M372:$U372),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M372:$U372)+($M372:$U372="DNA")),$M372:$U372),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M372:$U372)+($M372:$U372="DNA")),$M372:$U372),"")&lt;TODAY())),1,0)+COUNTIF($V372:$Z372,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J372" s="32">
@@ -18174,7 +18185,7 @@
         <v/>
       </c>
       <c r="K372" s="32">
-        <f>IF(NOT(AND($A372&lt;&gt;"",OR($G372="",$G372="Active"))),"",IF($L372&lt;&gt;"",IF($L372=$M372,"Booking",INDEX($N$4:$U$4,MATCH($L372,$N372:$U372,0))),IF(COUNTIF($N372:$U372,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N372:$U372)=0,"All done",IF(MAX($M372:$U372)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A372&lt;&gt;"",OR($G372="",$G372="Active"))),"",IF($L372&lt;&gt;"",IF($L372=$M372,"Booking",INDEX($N$4:$U$4,MATCH($L372,$N372:$U372,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M372:$U372)+($M372:$U372="DNA")),$M372:$U372),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M372:$U372)+($M372:$U372="DNA")),$M372:$U372),"")),IF(ISNUMBER($U372),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L372" s="33">
@@ -18212,7 +18223,7 @@
         <v/>
       </c>
       <c r="I373" s="32">
-        <f>IF(NOT(AND($A373&lt;&gt;"",OR($G373="",$G373="Active"))),"",IF(AND(MAX($M373:$U373)&gt;0,MAX($M373:$U373)&lt;TODAY(),COUNTBLANK($N373:$U373)&gt;0,COUNTIF($N373:$U373,"DNA")=0),1,0)+COUNTIF($N373:$U373,"DNA")+COUNTIF($V373:$Z373,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A373&lt;&gt;"",OR($G373="",$G373="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M373:$U373)+($M373:$U373="DNA")),$M373:$U373),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M373:$U373)+($M373:$U373="DNA")),$M373:$U373),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M373:$U373)+($M373:$U373="DNA")),$M373:$U373),"")&lt;TODAY())),1,0)+COUNTIF($V373:$Z373,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J373" s="32">
@@ -18220,7 +18231,7 @@
         <v/>
       </c>
       <c r="K373" s="32">
-        <f>IF(NOT(AND($A373&lt;&gt;"",OR($G373="",$G373="Active"))),"",IF($L373&lt;&gt;"",IF($L373=$M373,"Booking",INDEX($N$4:$U$4,MATCH($L373,$N373:$U373,0))),IF(COUNTIF($N373:$U373,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N373:$U373)=0,"All done",IF(MAX($M373:$U373)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A373&lt;&gt;"",OR($G373="",$G373="Active"))),"",IF($L373&lt;&gt;"",IF($L373=$M373,"Booking",INDEX($N$4:$U$4,MATCH($L373,$N373:$U373,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M373:$U373)+($M373:$U373="DNA")),$M373:$U373),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M373:$U373)+($M373:$U373="DNA")),$M373:$U373),"")),IF(ISNUMBER($U373),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L373" s="33">
@@ -18258,7 +18269,7 @@
         <v/>
       </c>
       <c r="I374" s="32">
-        <f>IF(NOT(AND($A374&lt;&gt;"",OR($G374="",$G374="Active"))),"",IF(AND(MAX($M374:$U374)&gt;0,MAX($M374:$U374)&lt;TODAY(),COUNTBLANK($N374:$U374)&gt;0,COUNTIF($N374:$U374,"DNA")=0),1,0)+COUNTIF($N374:$U374,"DNA")+COUNTIF($V374:$Z374,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A374&lt;&gt;"",OR($G374="",$G374="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M374:$U374)+($M374:$U374="DNA")),$M374:$U374),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M374:$U374)+($M374:$U374="DNA")),$M374:$U374),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M374:$U374)+($M374:$U374="DNA")),$M374:$U374),"")&lt;TODAY())),1,0)+COUNTIF($V374:$Z374,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J374" s="32">
@@ -18266,7 +18277,7 @@
         <v/>
       </c>
       <c r="K374" s="32">
-        <f>IF(NOT(AND($A374&lt;&gt;"",OR($G374="",$G374="Active"))),"",IF($L374&lt;&gt;"",IF($L374=$M374,"Booking",INDEX($N$4:$U$4,MATCH($L374,$N374:$U374,0))),IF(COUNTIF($N374:$U374,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N374:$U374)=0,"All done",IF(MAX($M374:$U374)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A374&lt;&gt;"",OR($G374="",$G374="Active"))),"",IF($L374&lt;&gt;"",IF($L374=$M374,"Booking",INDEX($N$4:$U$4,MATCH($L374,$N374:$U374,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M374:$U374)+($M374:$U374="DNA")),$M374:$U374),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M374:$U374)+($M374:$U374="DNA")),$M374:$U374),"")),IF(ISNUMBER($U374),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L374" s="33">
@@ -18304,7 +18315,7 @@
         <v/>
       </c>
       <c r="I375" s="32">
-        <f>IF(NOT(AND($A375&lt;&gt;"",OR($G375="",$G375="Active"))),"",IF(AND(MAX($M375:$U375)&gt;0,MAX($M375:$U375)&lt;TODAY(),COUNTBLANK($N375:$U375)&gt;0,COUNTIF($N375:$U375,"DNA")=0),1,0)+COUNTIF($N375:$U375,"DNA")+COUNTIF($V375:$Z375,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A375&lt;&gt;"",OR($G375="",$G375="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M375:$U375)+($M375:$U375="DNA")),$M375:$U375),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M375:$U375)+($M375:$U375="DNA")),$M375:$U375),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M375:$U375)+($M375:$U375="DNA")),$M375:$U375),"")&lt;TODAY())),1,0)+COUNTIF($V375:$Z375,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J375" s="32">
@@ -18312,7 +18323,7 @@
         <v/>
       </c>
       <c r="K375" s="32">
-        <f>IF(NOT(AND($A375&lt;&gt;"",OR($G375="",$G375="Active"))),"",IF($L375&lt;&gt;"",IF($L375=$M375,"Booking",INDEX($N$4:$U$4,MATCH($L375,$N375:$U375,0))),IF(COUNTIF($N375:$U375,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N375:$U375)=0,"All done",IF(MAX($M375:$U375)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A375&lt;&gt;"",OR($G375="",$G375="Active"))),"",IF($L375&lt;&gt;"",IF($L375=$M375,"Booking",INDEX($N$4:$U$4,MATCH($L375,$N375:$U375,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M375:$U375)+($M375:$U375="DNA")),$M375:$U375),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M375:$U375)+($M375:$U375="DNA")),$M375:$U375),"")),IF(ISNUMBER($U375),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L375" s="33">
@@ -18350,7 +18361,7 @@
         <v/>
       </c>
       <c r="I376" s="32">
-        <f>IF(NOT(AND($A376&lt;&gt;"",OR($G376="",$G376="Active"))),"",IF(AND(MAX($M376:$U376)&gt;0,MAX($M376:$U376)&lt;TODAY(),COUNTBLANK($N376:$U376)&gt;0,COUNTIF($N376:$U376,"DNA")=0),1,0)+COUNTIF($N376:$U376,"DNA")+COUNTIF($V376:$Z376,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A376&lt;&gt;"",OR($G376="",$G376="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M376:$U376)+($M376:$U376="DNA")),$M376:$U376),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M376:$U376)+($M376:$U376="DNA")),$M376:$U376),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M376:$U376)+($M376:$U376="DNA")),$M376:$U376),"")&lt;TODAY())),1,0)+COUNTIF($V376:$Z376,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J376" s="32">
@@ -18358,7 +18369,7 @@
         <v/>
       </c>
       <c r="K376" s="32">
-        <f>IF(NOT(AND($A376&lt;&gt;"",OR($G376="",$G376="Active"))),"",IF($L376&lt;&gt;"",IF($L376=$M376,"Booking",INDEX($N$4:$U$4,MATCH($L376,$N376:$U376,0))),IF(COUNTIF($N376:$U376,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N376:$U376)=0,"All done",IF(MAX($M376:$U376)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A376&lt;&gt;"",OR($G376="",$G376="Active"))),"",IF($L376&lt;&gt;"",IF($L376=$M376,"Booking",INDEX($N$4:$U$4,MATCH($L376,$N376:$U376,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M376:$U376)+($M376:$U376="DNA")),$M376:$U376),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M376:$U376)+($M376:$U376="DNA")),$M376:$U376),"")),IF(ISNUMBER($U376),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L376" s="33">
@@ -18396,7 +18407,7 @@
         <v/>
       </c>
       <c r="I377" s="32">
-        <f>IF(NOT(AND($A377&lt;&gt;"",OR($G377="",$G377="Active"))),"",IF(AND(MAX($M377:$U377)&gt;0,MAX($M377:$U377)&lt;TODAY(),COUNTBLANK($N377:$U377)&gt;0,COUNTIF($N377:$U377,"DNA")=0),1,0)+COUNTIF($N377:$U377,"DNA")+COUNTIF($V377:$Z377,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A377&lt;&gt;"",OR($G377="",$G377="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M377:$U377)+($M377:$U377="DNA")),$M377:$U377),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M377:$U377)+($M377:$U377="DNA")),$M377:$U377),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M377:$U377)+($M377:$U377="DNA")),$M377:$U377),"")&lt;TODAY())),1,0)+COUNTIF($V377:$Z377,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J377" s="32">
@@ -18404,7 +18415,7 @@
         <v/>
       </c>
       <c r="K377" s="32">
-        <f>IF(NOT(AND($A377&lt;&gt;"",OR($G377="",$G377="Active"))),"",IF($L377&lt;&gt;"",IF($L377=$M377,"Booking",INDEX($N$4:$U$4,MATCH($L377,$N377:$U377,0))),IF(COUNTIF($N377:$U377,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N377:$U377)=0,"All done",IF(MAX($M377:$U377)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A377&lt;&gt;"",OR($G377="",$G377="Active"))),"",IF($L377&lt;&gt;"",IF($L377=$M377,"Booking",INDEX($N$4:$U$4,MATCH($L377,$N377:$U377,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M377:$U377)+($M377:$U377="DNA")),$M377:$U377),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M377:$U377)+($M377:$U377="DNA")),$M377:$U377),"")),IF(ISNUMBER($U377),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L377" s="33">
@@ -18442,7 +18453,7 @@
         <v/>
       </c>
       <c r="I378" s="32">
-        <f>IF(NOT(AND($A378&lt;&gt;"",OR($G378="",$G378="Active"))),"",IF(AND(MAX($M378:$U378)&gt;0,MAX($M378:$U378)&lt;TODAY(),COUNTBLANK($N378:$U378)&gt;0,COUNTIF($N378:$U378,"DNA")=0),1,0)+COUNTIF($N378:$U378,"DNA")+COUNTIF($V378:$Z378,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A378&lt;&gt;"",OR($G378="",$G378="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M378:$U378)+($M378:$U378="DNA")),$M378:$U378),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M378:$U378)+($M378:$U378="DNA")),$M378:$U378),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M378:$U378)+($M378:$U378="DNA")),$M378:$U378),"")&lt;TODAY())),1,0)+COUNTIF($V378:$Z378,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J378" s="32">
@@ -18450,7 +18461,7 @@
         <v/>
       </c>
       <c r="K378" s="32">
-        <f>IF(NOT(AND($A378&lt;&gt;"",OR($G378="",$G378="Active"))),"",IF($L378&lt;&gt;"",IF($L378=$M378,"Booking",INDEX($N$4:$U$4,MATCH($L378,$N378:$U378,0))),IF(COUNTIF($N378:$U378,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N378:$U378)=0,"All done",IF(MAX($M378:$U378)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A378&lt;&gt;"",OR($G378="",$G378="Active"))),"",IF($L378&lt;&gt;"",IF($L378=$M378,"Booking",INDEX($N$4:$U$4,MATCH($L378,$N378:$U378,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M378:$U378)+($M378:$U378="DNA")),$M378:$U378),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M378:$U378)+($M378:$U378="DNA")),$M378:$U378),"")),IF(ISNUMBER($U378),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L378" s="33">
@@ -18488,7 +18499,7 @@
         <v/>
       </c>
       <c r="I379" s="32">
-        <f>IF(NOT(AND($A379&lt;&gt;"",OR($G379="",$G379="Active"))),"",IF(AND(MAX($M379:$U379)&gt;0,MAX($M379:$U379)&lt;TODAY(),COUNTBLANK($N379:$U379)&gt;0,COUNTIF($N379:$U379,"DNA")=0),1,0)+COUNTIF($N379:$U379,"DNA")+COUNTIF($V379:$Z379,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A379&lt;&gt;"",OR($G379="",$G379="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M379:$U379)+($M379:$U379="DNA")),$M379:$U379),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M379:$U379)+($M379:$U379="DNA")),$M379:$U379),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M379:$U379)+($M379:$U379="DNA")),$M379:$U379),"")&lt;TODAY())),1,0)+COUNTIF($V379:$Z379,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J379" s="32">
@@ -18496,7 +18507,7 @@
         <v/>
       </c>
       <c r="K379" s="32">
-        <f>IF(NOT(AND($A379&lt;&gt;"",OR($G379="",$G379="Active"))),"",IF($L379&lt;&gt;"",IF($L379=$M379,"Booking",INDEX($N$4:$U$4,MATCH($L379,$N379:$U379,0))),IF(COUNTIF($N379:$U379,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N379:$U379)=0,"All done",IF(MAX($M379:$U379)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A379&lt;&gt;"",OR($G379="",$G379="Active"))),"",IF($L379&lt;&gt;"",IF($L379=$M379,"Booking",INDEX($N$4:$U$4,MATCH($L379,$N379:$U379,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M379:$U379)+($M379:$U379="DNA")),$M379:$U379),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M379:$U379)+($M379:$U379="DNA")),$M379:$U379),"")),IF(ISNUMBER($U379),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L379" s="33">
@@ -18534,7 +18545,7 @@
         <v/>
       </c>
       <c r="I380" s="32">
-        <f>IF(NOT(AND($A380&lt;&gt;"",OR($G380="",$G380="Active"))),"",IF(AND(MAX($M380:$U380)&gt;0,MAX($M380:$U380)&lt;TODAY(),COUNTBLANK($N380:$U380)&gt;0,COUNTIF($N380:$U380,"DNA")=0),1,0)+COUNTIF($N380:$U380,"DNA")+COUNTIF($V380:$Z380,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A380&lt;&gt;"",OR($G380="",$G380="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M380:$U380)+($M380:$U380="DNA")),$M380:$U380),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M380:$U380)+($M380:$U380="DNA")),$M380:$U380),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M380:$U380)+($M380:$U380="DNA")),$M380:$U380),"")&lt;TODAY())),1,0)+COUNTIF($V380:$Z380,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J380" s="32">
@@ -18542,7 +18553,7 @@
         <v/>
       </c>
       <c r="K380" s="32">
-        <f>IF(NOT(AND($A380&lt;&gt;"",OR($G380="",$G380="Active"))),"",IF($L380&lt;&gt;"",IF($L380=$M380,"Booking",INDEX($N$4:$U$4,MATCH($L380,$N380:$U380,0))),IF(COUNTIF($N380:$U380,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N380:$U380)=0,"All done",IF(MAX($M380:$U380)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A380&lt;&gt;"",OR($G380="",$G380="Active"))),"",IF($L380&lt;&gt;"",IF($L380=$M380,"Booking",INDEX($N$4:$U$4,MATCH($L380,$N380:$U380,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M380:$U380)+($M380:$U380="DNA")),$M380:$U380),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M380:$U380)+($M380:$U380="DNA")),$M380:$U380),"")),IF(ISNUMBER($U380),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L380" s="33">
@@ -18580,7 +18591,7 @@
         <v/>
       </c>
       <c r="I381" s="32">
-        <f>IF(NOT(AND($A381&lt;&gt;"",OR($G381="",$G381="Active"))),"",IF(AND(MAX($M381:$U381)&gt;0,MAX($M381:$U381)&lt;TODAY(),COUNTBLANK($N381:$U381)&gt;0,COUNTIF($N381:$U381,"DNA")=0),1,0)+COUNTIF($N381:$U381,"DNA")+COUNTIF($V381:$Z381,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A381&lt;&gt;"",OR($G381="",$G381="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M381:$U381)+($M381:$U381="DNA")),$M381:$U381),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M381:$U381)+($M381:$U381="DNA")),$M381:$U381),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M381:$U381)+($M381:$U381="DNA")),$M381:$U381),"")&lt;TODAY())),1,0)+COUNTIF($V381:$Z381,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J381" s="32">
@@ -18588,7 +18599,7 @@
         <v/>
       </c>
       <c r="K381" s="32">
-        <f>IF(NOT(AND($A381&lt;&gt;"",OR($G381="",$G381="Active"))),"",IF($L381&lt;&gt;"",IF($L381=$M381,"Booking",INDEX($N$4:$U$4,MATCH($L381,$N381:$U381,0))),IF(COUNTIF($N381:$U381,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N381:$U381)=0,"All done",IF(MAX($M381:$U381)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A381&lt;&gt;"",OR($G381="",$G381="Active"))),"",IF($L381&lt;&gt;"",IF($L381=$M381,"Booking",INDEX($N$4:$U$4,MATCH($L381,$N381:$U381,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M381:$U381)+($M381:$U381="DNA")),$M381:$U381),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M381:$U381)+($M381:$U381="DNA")),$M381:$U381),"")),IF(ISNUMBER($U381),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L381" s="33">
@@ -18626,7 +18637,7 @@
         <v/>
       </c>
       <c r="I382" s="32">
-        <f>IF(NOT(AND($A382&lt;&gt;"",OR($G382="",$G382="Active"))),"",IF(AND(MAX($M382:$U382)&gt;0,MAX($M382:$U382)&lt;TODAY(),COUNTBLANK($N382:$U382)&gt;0,COUNTIF($N382:$U382,"DNA")=0),1,0)+COUNTIF($N382:$U382,"DNA")+COUNTIF($V382:$Z382,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A382&lt;&gt;"",OR($G382="",$G382="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M382:$U382)+($M382:$U382="DNA")),$M382:$U382),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M382:$U382)+($M382:$U382="DNA")),$M382:$U382),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M382:$U382)+($M382:$U382="DNA")),$M382:$U382),"")&lt;TODAY())),1,0)+COUNTIF($V382:$Z382,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J382" s="32">
@@ -18634,7 +18645,7 @@
         <v/>
       </c>
       <c r="K382" s="32">
-        <f>IF(NOT(AND($A382&lt;&gt;"",OR($G382="",$G382="Active"))),"",IF($L382&lt;&gt;"",IF($L382=$M382,"Booking",INDEX($N$4:$U$4,MATCH($L382,$N382:$U382,0))),IF(COUNTIF($N382:$U382,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N382:$U382)=0,"All done",IF(MAX($M382:$U382)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A382&lt;&gt;"",OR($G382="",$G382="Active"))),"",IF($L382&lt;&gt;"",IF($L382=$M382,"Booking",INDEX($N$4:$U$4,MATCH($L382,$N382:$U382,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M382:$U382)+($M382:$U382="DNA")),$M382:$U382),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M382:$U382)+($M382:$U382="DNA")),$M382:$U382),"")),IF(ISNUMBER($U382),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L382" s="33">
@@ -18672,7 +18683,7 @@
         <v/>
       </c>
       <c r="I383" s="32">
-        <f>IF(NOT(AND($A383&lt;&gt;"",OR($G383="",$G383="Active"))),"",IF(AND(MAX($M383:$U383)&gt;0,MAX($M383:$U383)&lt;TODAY(),COUNTBLANK($N383:$U383)&gt;0,COUNTIF($N383:$U383,"DNA")=0),1,0)+COUNTIF($N383:$U383,"DNA")+COUNTIF($V383:$Z383,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A383&lt;&gt;"",OR($G383="",$G383="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M383:$U383)+($M383:$U383="DNA")),$M383:$U383),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M383:$U383)+($M383:$U383="DNA")),$M383:$U383),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M383:$U383)+($M383:$U383="DNA")),$M383:$U383),"")&lt;TODAY())),1,0)+COUNTIF($V383:$Z383,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J383" s="32">
@@ -18680,7 +18691,7 @@
         <v/>
       </c>
       <c r="K383" s="32">
-        <f>IF(NOT(AND($A383&lt;&gt;"",OR($G383="",$G383="Active"))),"",IF($L383&lt;&gt;"",IF($L383=$M383,"Booking",INDEX($N$4:$U$4,MATCH($L383,$N383:$U383,0))),IF(COUNTIF($N383:$U383,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N383:$U383)=0,"All done",IF(MAX($M383:$U383)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A383&lt;&gt;"",OR($G383="",$G383="Active"))),"",IF($L383&lt;&gt;"",IF($L383=$M383,"Booking",INDEX($N$4:$U$4,MATCH($L383,$N383:$U383,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M383:$U383)+($M383:$U383="DNA")),$M383:$U383),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M383:$U383)+($M383:$U383="DNA")),$M383:$U383),"")),IF(ISNUMBER($U383),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L383" s="33">
@@ -18718,7 +18729,7 @@
         <v/>
       </c>
       <c r="I384" s="32">
-        <f>IF(NOT(AND($A384&lt;&gt;"",OR($G384="",$G384="Active"))),"",IF(AND(MAX($M384:$U384)&gt;0,MAX($M384:$U384)&lt;TODAY(),COUNTBLANK($N384:$U384)&gt;0,COUNTIF($N384:$U384,"DNA")=0),1,0)+COUNTIF($N384:$U384,"DNA")+COUNTIF($V384:$Z384,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A384&lt;&gt;"",OR($G384="",$G384="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M384:$U384)+($M384:$U384="DNA")),$M384:$U384),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M384:$U384)+($M384:$U384="DNA")),$M384:$U384),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M384:$U384)+($M384:$U384="DNA")),$M384:$U384),"")&lt;TODAY())),1,0)+COUNTIF($V384:$Z384,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J384" s="32">
@@ -18726,7 +18737,7 @@
         <v/>
       </c>
       <c r="K384" s="32">
-        <f>IF(NOT(AND($A384&lt;&gt;"",OR($G384="",$G384="Active"))),"",IF($L384&lt;&gt;"",IF($L384=$M384,"Booking",INDEX($N$4:$U$4,MATCH($L384,$N384:$U384,0))),IF(COUNTIF($N384:$U384,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N384:$U384)=0,"All done",IF(MAX($M384:$U384)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A384&lt;&gt;"",OR($G384="",$G384="Active"))),"",IF($L384&lt;&gt;"",IF($L384=$M384,"Booking",INDEX($N$4:$U$4,MATCH($L384,$N384:$U384,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M384:$U384)+($M384:$U384="DNA")),$M384:$U384),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M384:$U384)+($M384:$U384="DNA")),$M384:$U384),"")),IF(ISNUMBER($U384),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L384" s="33">
@@ -18764,7 +18775,7 @@
         <v/>
       </c>
       <c r="I385" s="32">
-        <f>IF(NOT(AND($A385&lt;&gt;"",OR($G385="",$G385="Active"))),"",IF(AND(MAX($M385:$U385)&gt;0,MAX($M385:$U385)&lt;TODAY(),COUNTBLANK($N385:$U385)&gt;0,COUNTIF($N385:$U385,"DNA")=0),1,0)+COUNTIF($N385:$U385,"DNA")+COUNTIF($V385:$Z385,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A385&lt;&gt;"",OR($G385="",$G385="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M385:$U385)+($M385:$U385="DNA")),$M385:$U385),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M385:$U385)+($M385:$U385="DNA")),$M385:$U385),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M385:$U385)+($M385:$U385="DNA")),$M385:$U385),"")&lt;TODAY())),1,0)+COUNTIF($V385:$Z385,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J385" s="32">
@@ -18772,7 +18783,7 @@
         <v/>
       </c>
       <c r="K385" s="32">
-        <f>IF(NOT(AND($A385&lt;&gt;"",OR($G385="",$G385="Active"))),"",IF($L385&lt;&gt;"",IF($L385=$M385,"Booking",INDEX($N$4:$U$4,MATCH($L385,$N385:$U385,0))),IF(COUNTIF($N385:$U385,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N385:$U385)=0,"All done",IF(MAX($M385:$U385)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A385&lt;&gt;"",OR($G385="",$G385="Active"))),"",IF($L385&lt;&gt;"",IF($L385=$M385,"Booking",INDEX($N$4:$U$4,MATCH($L385,$N385:$U385,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M385:$U385)+($M385:$U385="DNA")),$M385:$U385),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M385:$U385)+($M385:$U385="DNA")),$M385:$U385),"")),IF(ISNUMBER($U385),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L385" s="33">
@@ -18810,7 +18821,7 @@
         <v/>
       </c>
       <c r="I386" s="32">
-        <f>IF(NOT(AND($A386&lt;&gt;"",OR($G386="",$G386="Active"))),"",IF(AND(MAX($M386:$U386)&gt;0,MAX($M386:$U386)&lt;TODAY(),COUNTBLANK($N386:$U386)&gt;0,COUNTIF($N386:$U386,"DNA")=0),1,0)+COUNTIF($N386:$U386,"DNA")+COUNTIF($V386:$Z386,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A386&lt;&gt;"",OR($G386="",$G386="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M386:$U386)+($M386:$U386="DNA")),$M386:$U386),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M386:$U386)+($M386:$U386="DNA")),$M386:$U386),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M386:$U386)+($M386:$U386="DNA")),$M386:$U386),"")&lt;TODAY())),1,0)+COUNTIF($V386:$Z386,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J386" s="32">
@@ -18818,7 +18829,7 @@
         <v/>
       </c>
       <c r="K386" s="32">
-        <f>IF(NOT(AND($A386&lt;&gt;"",OR($G386="",$G386="Active"))),"",IF($L386&lt;&gt;"",IF($L386=$M386,"Booking",INDEX($N$4:$U$4,MATCH($L386,$N386:$U386,0))),IF(COUNTIF($N386:$U386,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N386:$U386)=0,"All done",IF(MAX($M386:$U386)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A386&lt;&gt;"",OR($G386="",$G386="Active"))),"",IF($L386&lt;&gt;"",IF($L386=$M386,"Booking",INDEX($N$4:$U$4,MATCH($L386,$N386:$U386,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M386:$U386)+($M386:$U386="DNA")),$M386:$U386),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M386:$U386)+($M386:$U386="DNA")),$M386:$U386),"")),IF(ISNUMBER($U386),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L386" s="33">
@@ -18856,7 +18867,7 @@
         <v/>
       </c>
       <c r="I387" s="32">
-        <f>IF(NOT(AND($A387&lt;&gt;"",OR($G387="",$G387="Active"))),"",IF(AND(MAX($M387:$U387)&gt;0,MAX($M387:$U387)&lt;TODAY(),COUNTBLANK($N387:$U387)&gt;0,COUNTIF($N387:$U387,"DNA")=0),1,0)+COUNTIF($N387:$U387,"DNA")+COUNTIF($V387:$Z387,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A387&lt;&gt;"",OR($G387="",$G387="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M387:$U387)+($M387:$U387="DNA")),$M387:$U387),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M387:$U387)+($M387:$U387="DNA")),$M387:$U387),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M387:$U387)+($M387:$U387="DNA")),$M387:$U387),"")&lt;TODAY())),1,0)+COUNTIF($V387:$Z387,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J387" s="32">
@@ -18864,7 +18875,7 @@
         <v/>
       </c>
       <c r="K387" s="32">
-        <f>IF(NOT(AND($A387&lt;&gt;"",OR($G387="",$G387="Active"))),"",IF($L387&lt;&gt;"",IF($L387=$M387,"Booking",INDEX($N$4:$U$4,MATCH($L387,$N387:$U387,0))),IF(COUNTIF($N387:$U387,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N387:$U387)=0,"All done",IF(MAX($M387:$U387)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A387&lt;&gt;"",OR($G387="",$G387="Active"))),"",IF($L387&lt;&gt;"",IF($L387=$M387,"Booking",INDEX($N$4:$U$4,MATCH($L387,$N387:$U387,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M387:$U387)+($M387:$U387="DNA")),$M387:$U387),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M387:$U387)+($M387:$U387="DNA")),$M387:$U387),"")),IF(ISNUMBER($U387),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L387" s="33">
@@ -18902,7 +18913,7 @@
         <v/>
       </c>
       <c r="I388" s="32">
-        <f>IF(NOT(AND($A388&lt;&gt;"",OR($G388="",$G388="Active"))),"",IF(AND(MAX($M388:$U388)&gt;0,MAX($M388:$U388)&lt;TODAY(),COUNTBLANK($N388:$U388)&gt;0,COUNTIF($N388:$U388,"DNA")=0),1,0)+COUNTIF($N388:$U388,"DNA")+COUNTIF($V388:$Z388,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A388&lt;&gt;"",OR($G388="",$G388="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M388:$U388)+($M388:$U388="DNA")),$M388:$U388),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M388:$U388)+($M388:$U388="DNA")),$M388:$U388),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M388:$U388)+($M388:$U388="DNA")),$M388:$U388),"")&lt;TODAY())),1,0)+COUNTIF($V388:$Z388,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J388" s="32">
@@ -18910,7 +18921,7 @@
         <v/>
       </c>
       <c r="K388" s="32">
-        <f>IF(NOT(AND($A388&lt;&gt;"",OR($G388="",$G388="Active"))),"",IF($L388&lt;&gt;"",IF($L388=$M388,"Booking",INDEX($N$4:$U$4,MATCH($L388,$N388:$U388,0))),IF(COUNTIF($N388:$U388,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N388:$U388)=0,"All done",IF(MAX($M388:$U388)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A388&lt;&gt;"",OR($G388="",$G388="Active"))),"",IF($L388&lt;&gt;"",IF($L388=$M388,"Booking",INDEX($N$4:$U$4,MATCH($L388,$N388:$U388,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M388:$U388)+($M388:$U388="DNA")),$M388:$U388),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M388:$U388)+($M388:$U388="DNA")),$M388:$U388),"")),IF(ISNUMBER($U388),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L388" s="33">
@@ -18948,7 +18959,7 @@
         <v/>
       </c>
       <c r="I389" s="32">
-        <f>IF(NOT(AND($A389&lt;&gt;"",OR($G389="",$G389="Active"))),"",IF(AND(MAX($M389:$U389)&gt;0,MAX($M389:$U389)&lt;TODAY(),COUNTBLANK($N389:$U389)&gt;0,COUNTIF($N389:$U389,"DNA")=0),1,0)+COUNTIF($N389:$U389,"DNA")+COUNTIF($V389:$Z389,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A389&lt;&gt;"",OR($G389="",$G389="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M389:$U389)+($M389:$U389="DNA")),$M389:$U389),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M389:$U389)+($M389:$U389="DNA")),$M389:$U389),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M389:$U389)+($M389:$U389="DNA")),$M389:$U389),"")&lt;TODAY())),1,0)+COUNTIF($V389:$Z389,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J389" s="32">
@@ -18956,7 +18967,7 @@
         <v/>
       </c>
       <c r="K389" s="32">
-        <f>IF(NOT(AND($A389&lt;&gt;"",OR($G389="",$G389="Active"))),"",IF($L389&lt;&gt;"",IF($L389=$M389,"Booking",INDEX($N$4:$U$4,MATCH($L389,$N389:$U389,0))),IF(COUNTIF($N389:$U389,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N389:$U389)=0,"All done",IF(MAX($M389:$U389)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A389&lt;&gt;"",OR($G389="",$G389="Active"))),"",IF($L389&lt;&gt;"",IF($L389=$M389,"Booking",INDEX($N$4:$U$4,MATCH($L389,$N389:$U389,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M389:$U389)+($M389:$U389="DNA")),$M389:$U389),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M389:$U389)+($M389:$U389="DNA")),$M389:$U389),"")),IF(ISNUMBER($U389),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L389" s="33">
@@ -18994,7 +19005,7 @@
         <v/>
       </c>
       <c r="I390" s="32">
-        <f>IF(NOT(AND($A390&lt;&gt;"",OR($G390="",$G390="Active"))),"",IF(AND(MAX($M390:$U390)&gt;0,MAX($M390:$U390)&lt;TODAY(),COUNTBLANK($N390:$U390)&gt;0,COUNTIF($N390:$U390,"DNA")=0),1,0)+COUNTIF($N390:$U390,"DNA")+COUNTIF($V390:$Z390,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A390&lt;&gt;"",OR($G390="",$G390="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M390:$U390)+($M390:$U390="DNA")),$M390:$U390),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M390:$U390)+($M390:$U390="DNA")),$M390:$U390),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M390:$U390)+($M390:$U390="DNA")),$M390:$U390),"")&lt;TODAY())),1,0)+COUNTIF($V390:$Z390,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J390" s="32">
@@ -19002,7 +19013,7 @@
         <v/>
       </c>
       <c r="K390" s="32">
-        <f>IF(NOT(AND($A390&lt;&gt;"",OR($G390="",$G390="Active"))),"",IF($L390&lt;&gt;"",IF($L390=$M390,"Booking",INDEX($N$4:$U$4,MATCH($L390,$N390:$U390,0))),IF(COUNTIF($N390:$U390,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N390:$U390)=0,"All done",IF(MAX($M390:$U390)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A390&lt;&gt;"",OR($G390="",$G390="Active"))),"",IF($L390&lt;&gt;"",IF($L390=$M390,"Booking",INDEX($N$4:$U$4,MATCH($L390,$N390:$U390,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M390:$U390)+($M390:$U390="DNA")),$M390:$U390),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M390:$U390)+($M390:$U390="DNA")),$M390:$U390),"")),IF(ISNUMBER($U390),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L390" s="33">
@@ -19040,7 +19051,7 @@
         <v/>
       </c>
       <c r="I391" s="32">
-        <f>IF(NOT(AND($A391&lt;&gt;"",OR($G391="",$G391="Active"))),"",IF(AND(MAX($M391:$U391)&gt;0,MAX($M391:$U391)&lt;TODAY(),COUNTBLANK($N391:$U391)&gt;0,COUNTIF($N391:$U391,"DNA")=0),1,0)+COUNTIF($N391:$U391,"DNA")+COUNTIF($V391:$Z391,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A391&lt;&gt;"",OR($G391="",$G391="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M391:$U391)+($M391:$U391="DNA")),$M391:$U391),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M391:$U391)+($M391:$U391="DNA")),$M391:$U391),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M391:$U391)+($M391:$U391="DNA")),$M391:$U391),"")&lt;TODAY())),1,0)+COUNTIF($V391:$Z391,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J391" s="32">
@@ -19048,7 +19059,7 @@
         <v/>
       </c>
       <c r="K391" s="32">
-        <f>IF(NOT(AND($A391&lt;&gt;"",OR($G391="",$G391="Active"))),"",IF($L391&lt;&gt;"",IF($L391=$M391,"Booking",INDEX($N$4:$U$4,MATCH($L391,$N391:$U391,0))),IF(COUNTIF($N391:$U391,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N391:$U391)=0,"All done",IF(MAX($M391:$U391)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A391&lt;&gt;"",OR($G391="",$G391="Active"))),"",IF($L391&lt;&gt;"",IF($L391=$M391,"Booking",INDEX($N$4:$U$4,MATCH($L391,$N391:$U391,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M391:$U391)+($M391:$U391="DNA")),$M391:$U391),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M391:$U391)+($M391:$U391="DNA")),$M391:$U391),"")),IF(ISNUMBER($U391),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L391" s="33">
@@ -19086,7 +19097,7 @@
         <v/>
       </c>
       <c r="I392" s="32">
-        <f>IF(NOT(AND($A392&lt;&gt;"",OR($G392="",$G392="Active"))),"",IF(AND(MAX($M392:$U392)&gt;0,MAX($M392:$U392)&lt;TODAY(),COUNTBLANK($N392:$U392)&gt;0,COUNTIF($N392:$U392,"DNA")=0),1,0)+COUNTIF($N392:$U392,"DNA")+COUNTIF($V392:$Z392,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A392&lt;&gt;"",OR($G392="",$G392="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M392:$U392)+($M392:$U392="DNA")),$M392:$U392),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M392:$U392)+($M392:$U392="DNA")),$M392:$U392),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M392:$U392)+($M392:$U392="DNA")),$M392:$U392),"")&lt;TODAY())),1,0)+COUNTIF($V392:$Z392,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J392" s="32">
@@ -19094,7 +19105,7 @@
         <v/>
       </c>
       <c r="K392" s="32">
-        <f>IF(NOT(AND($A392&lt;&gt;"",OR($G392="",$G392="Active"))),"",IF($L392&lt;&gt;"",IF($L392=$M392,"Booking",INDEX($N$4:$U$4,MATCH($L392,$N392:$U392,0))),IF(COUNTIF($N392:$U392,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N392:$U392)=0,"All done",IF(MAX($M392:$U392)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A392&lt;&gt;"",OR($G392="",$G392="Active"))),"",IF($L392&lt;&gt;"",IF($L392=$M392,"Booking",INDEX($N$4:$U$4,MATCH($L392,$N392:$U392,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M392:$U392)+($M392:$U392="DNA")),$M392:$U392),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M392:$U392)+($M392:$U392="DNA")),$M392:$U392),"")),IF(ISNUMBER($U392),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L392" s="33">
@@ -19132,7 +19143,7 @@
         <v/>
       </c>
       <c r="I393" s="32">
-        <f>IF(NOT(AND($A393&lt;&gt;"",OR($G393="",$G393="Active"))),"",IF(AND(MAX($M393:$U393)&gt;0,MAX($M393:$U393)&lt;TODAY(),COUNTBLANK($N393:$U393)&gt;0,COUNTIF($N393:$U393,"DNA")=0),1,0)+COUNTIF($N393:$U393,"DNA")+COUNTIF($V393:$Z393,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A393&lt;&gt;"",OR($G393="",$G393="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M393:$U393)+($M393:$U393="DNA")),$M393:$U393),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M393:$U393)+($M393:$U393="DNA")),$M393:$U393),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M393:$U393)+($M393:$U393="DNA")),$M393:$U393),"")&lt;TODAY())),1,0)+COUNTIF($V393:$Z393,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J393" s="32">
@@ -19140,7 +19151,7 @@
         <v/>
       </c>
       <c r="K393" s="32">
-        <f>IF(NOT(AND($A393&lt;&gt;"",OR($G393="",$G393="Active"))),"",IF($L393&lt;&gt;"",IF($L393=$M393,"Booking",INDEX($N$4:$U$4,MATCH($L393,$N393:$U393,0))),IF(COUNTIF($N393:$U393,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N393:$U393)=0,"All done",IF(MAX($M393:$U393)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A393&lt;&gt;"",OR($G393="",$G393="Active"))),"",IF($L393&lt;&gt;"",IF($L393=$M393,"Booking",INDEX($N$4:$U$4,MATCH($L393,$N393:$U393,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M393:$U393)+($M393:$U393="DNA")),$M393:$U393),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M393:$U393)+($M393:$U393="DNA")),$M393:$U393),"")),IF(ISNUMBER($U393),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L393" s="33">
@@ -19178,7 +19189,7 @@
         <v/>
       </c>
       <c r="I394" s="32">
-        <f>IF(NOT(AND($A394&lt;&gt;"",OR($G394="",$G394="Active"))),"",IF(AND(MAX($M394:$U394)&gt;0,MAX($M394:$U394)&lt;TODAY(),COUNTBLANK($N394:$U394)&gt;0,COUNTIF($N394:$U394,"DNA")=0),1,0)+COUNTIF($N394:$U394,"DNA")+COUNTIF($V394:$Z394,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A394&lt;&gt;"",OR($G394="",$G394="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M394:$U394)+($M394:$U394="DNA")),$M394:$U394),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M394:$U394)+($M394:$U394="DNA")),$M394:$U394),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M394:$U394)+($M394:$U394="DNA")),$M394:$U394),"")&lt;TODAY())),1,0)+COUNTIF($V394:$Z394,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J394" s="32">
@@ -19186,7 +19197,7 @@
         <v/>
       </c>
       <c r="K394" s="32">
-        <f>IF(NOT(AND($A394&lt;&gt;"",OR($G394="",$G394="Active"))),"",IF($L394&lt;&gt;"",IF($L394=$M394,"Booking",INDEX($N$4:$U$4,MATCH($L394,$N394:$U394,0))),IF(COUNTIF($N394:$U394,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N394:$U394)=0,"All done",IF(MAX($M394:$U394)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A394&lt;&gt;"",OR($G394="",$G394="Active"))),"",IF($L394&lt;&gt;"",IF($L394=$M394,"Booking",INDEX($N$4:$U$4,MATCH($L394,$N394:$U394,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M394:$U394)+($M394:$U394="DNA")),$M394:$U394),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M394:$U394)+($M394:$U394="DNA")),$M394:$U394),"")),IF(ISNUMBER($U394),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L394" s="33">
@@ -19224,7 +19235,7 @@
         <v/>
       </c>
       <c r="I395" s="32">
-        <f>IF(NOT(AND($A395&lt;&gt;"",OR($G395="",$G395="Active"))),"",IF(AND(MAX($M395:$U395)&gt;0,MAX($M395:$U395)&lt;TODAY(),COUNTBLANK($N395:$U395)&gt;0,COUNTIF($N395:$U395,"DNA")=0),1,0)+COUNTIF($N395:$U395,"DNA")+COUNTIF($V395:$Z395,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A395&lt;&gt;"",OR($G395="",$G395="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M395:$U395)+($M395:$U395="DNA")),$M395:$U395),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M395:$U395)+($M395:$U395="DNA")),$M395:$U395),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M395:$U395)+($M395:$U395="DNA")),$M395:$U395),"")&lt;TODAY())),1,0)+COUNTIF($V395:$Z395,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J395" s="32">
@@ -19232,7 +19243,7 @@
         <v/>
       </c>
       <c r="K395" s="32">
-        <f>IF(NOT(AND($A395&lt;&gt;"",OR($G395="",$G395="Active"))),"",IF($L395&lt;&gt;"",IF($L395=$M395,"Booking",INDEX($N$4:$U$4,MATCH($L395,$N395:$U395,0))),IF(COUNTIF($N395:$U395,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N395:$U395)=0,"All done",IF(MAX($M395:$U395)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A395&lt;&gt;"",OR($G395="",$G395="Active"))),"",IF($L395&lt;&gt;"",IF($L395=$M395,"Booking",INDEX($N$4:$U$4,MATCH($L395,$N395:$U395,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M395:$U395)+($M395:$U395="DNA")),$M395:$U395),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M395:$U395)+($M395:$U395="DNA")),$M395:$U395),"")),IF(ISNUMBER($U395),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L395" s="33">
@@ -19270,7 +19281,7 @@
         <v/>
       </c>
       <c r="I396" s="32">
-        <f>IF(NOT(AND($A396&lt;&gt;"",OR($G396="",$G396="Active"))),"",IF(AND(MAX($M396:$U396)&gt;0,MAX($M396:$U396)&lt;TODAY(),COUNTBLANK($N396:$U396)&gt;0,COUNTIF($N396:$U396,"DNA")=0),1,0)+COUNTIF($N396:$U396,"DNA")+COUNTIF($V396:$Z396,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A396&lt;&gt;"",OR($G396="",$G396="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M396:$U396)+($M396:$U396="DNA")),$M396:$U396),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M396:$U396)+($M396:$U396="DNA")),$M396:$U396),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M396:$U396)+($M396:$U396="DNA")),$M396:$U396),"")&lt;TODAY())),1,0)+COUNTIF($V396:$Z396,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J396" s="32">
@@ -19278,7 +19289,7 @@
         <v/>
       </c>
       <c r="K396" s="32">
-        <f>IF(NOT(AND($A396&lt;&gt;"",OR($G396="",$G396="Active"))),"",IF($L396&lt;&gt;"",IF($L396=$M396,"Booking",INDEX($N$4:$U$4,MATCH($L396,$N396:$U396,0))),IF(COUNTIF($N396:$U396,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N396:$U396)=0,"All done",IF(MAX($M396:$U396)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A396&lt;&gt;"",OR($G396="",$G396="Active"))),"",IF($L396&lt;&gt;"",IF($L396=$M396,"Booking",INDEX($N$4:$U$4,MATCH($L396,$N396:$U396,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M396:$U396)+($M396:$U396="DNA")),$M396:$U396),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M396:$U396)+($M396:$U396="DNA")),$M396:$U396),"")),IF(ISNUMBER($U396),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L396" s="33">
@@ -19316,7 +19327,7 @@
         <v/>
       </c>
       <c r="I397" s="32">
-        <f>IF(NOT(AND($A397&lt;&gt;"",OR($G397="",$G397="Active"))),"",IF(AND(MAX($M397:$U397)&gt;0,MAX($M397:$U397)&lt;TODAY(),COUNTBLANK($N397:$U397)&gt;0,COUNTIF($N397:$U397,"DNA")=0),1,0)+COUNTIF($N397:$U397,"DNA")+COUNTIF($V397:$Z397,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A397&lt;&gt;"",OR($G397="",$G397="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M397:$U397)+($M397:$U397="DNA")),$M397:$U397),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M397:$U397)+($M397:$U397="DNA")),$M397:$U397),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M397:$U397)+($M397:$U397="DNA")),$M397:$U397),"")&lt;TODAY())),1,0)+COUNTIF($V397:$Z397,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J397" s="32">
@@ -19324,7 +19335,7 @@
         <v/>
       </c>
       <c r="K397" s="32">
-        <f>IF(NOT(AND($A397&lt;&gt;"",OR($G397="",$G397="Active"))),"",IF($L397&lt;&gt;"",IF($L397=$M397,"Booking",INDEX($N$4:$U$4,MATCH($L397,$N397:$U397,0))),IF(COUNTIF($N397:$U397,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N397:$U397)=0,"All done",IF(MAX($M397:$U397)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A397&lt;&gt;"",OR($G397="",$G397="Active"))),"",IF($L397&lt;&gt;"",IF($L397=$M397,"Booking",INDEX($N$4:$U$4,MATCH($L397,$N397:$U397,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M397:$U397)+($M397:$U397="DNA")),$M397:$U397),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M397:$U397)+($M397:$U397="DNA")),$M397:$U397),"")),IF(ISNUMBER($U397),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L397" s="33">
@@ -19362,7 +19373,7 @@
         <v/>
       </c>
       <c r="I398" s="32">
-        <f>IF(NOT(AND($A398&lt;&gt;"",OR($G398="",$G398="Active"))),"",IF(AND(MAX($M398:$U398)&gt;0,MAX($M398:$U398)&lt;TODAY(),COUNTBLANK($N398:$U398)&gt;0,COUNTIF($N398:$U398,"DNA")=0),1,0)+COUNTIF($N398:$U398,"DNA")+COUNTIF($V398:$Z398,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A398&lt;&gt;"",OR($G398="",$G398="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M398:$U398)+($M398:$U398="DNA")),$M398:$U398),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M398:$U398)+($M398:$U398="DNA")),$M398:$U398),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M398:$U398)+($M398:$U398="DNA")),$M398:$U398),"")&lt;TODAY())),1,0)+COUNTIF($V398:$Z398,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J398" s="32">
@@ -19370,7 +19381,7 @@
         <v/>
       </c>
       <c r="K398" s="32">
-        <f>IF(NOT(AND($A398&lt;&gt;"",OR($G398="",$G398="Active"))),"",IF($L398&lt;&gt;"",IF($L398=$M398,"Booking",INDEX($N$4:$U$4,MATCH($L398,$N398:$U398,0))),IF(COUNTIF($N398:$U398,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N398:$U398)=0,"All done",IF(MAX($M398:$U398)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A398&lt;&gt;"",OR($G398="",$G398="Active"))),"",IF($L398&lt;&gt;"",IF($L398=$M398,"Booking",INDEX($N$4:$U$4,MATCH($L398,$N398:$U398,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M398:$U398)+($M398:$U398="DNA")),$M398:$U398),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M398:$U398)+($M398:$U398="DNA")),$M398:$U398),"")),IF(ISNUMBER($U398),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L398" s="33">
@@ -19408,7 +19419,7 @@
         <v/>
       </c>
       <c r="I399" s="32">
-        <f>IF(NOT(AND($A399&lt;&gt;"",OR($G399="",$G399="Active"))),"",IF(AND(MAX($M399:$U399)&gt;0,MAX($M399:$U399)&lt;TODAY(),COUNTBLANK($N399:$U399)&gt;0,COUNTIF($N399:$U399,"DNA")=0),1,0)+COUNTIF($N399:$U399,"DNA")+COUNTIF($V399:$Z399,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A399&lt;&gt;"",OR($G399="",$G399="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M399:$U399)+($M399:$U399="DNA")),$M399:$U399),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M399:$U399)+($M399:$U399="DNA")),$M399:$U399),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M399:$U399)+($M399:$U399="DNA")),$M399:$U399),"")&lt;TODAY())),1,0)+COUNTIF($V399:$Z399,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J399" s="32">
@@ -19416,7 +19427,7 @@
         <v/>
       </c>
       <c r="K399" s="32">
-        <f>IF(NOT(AND($A399&lt;&gt;"",OR($G399="",$G399="Active"))),"",IF($L399&lt;&gt;"",IF($L399=$M399,"Booking",INDEX($N$4:$U$4,MATCH($L399,$N399:$U399,0))),IF(COUNTIF($N399:$U399,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N399:$U399)=0,"All done",IF(MAX($M399:$U399)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A399&lt;&gt;"",OR($G399="",$G399="Active"))),"",IF($L399&lt;&gt;"",IF($L399=$M399,"Booking",INDEX($N$4:$U$4,MATCH($L399,$N399:$U399,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M399:$U399)+($M399:$U399="DNA")),$M399:$U399),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M399:$U399)+($M399:$U399="DNA")),$M399:$U399),"")),IF(ISNUMBER($U399),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L399" s="33">
@@ -19454,7 +19465,7 @@
         <v/>
       </c>
       <c r="I400" s="32">
-        <f>IF(NOT(AND($A400&lt;&gt;"",OR($G400="",$G400="Active"))),"",IF(AND(MAX($M400:$U400)&gt;0,MAX($M400:$U400)&lt;TODAY(),COUNTBLANK($N400:$U400)&gt;0,COUNTIF($N400:$U400,"DNA")=0),1,0)+COUNTIF($N400:$U400,"DNA")+COUNTIF($V400:$Z400,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A400&lt;&gt;"",OR($G400="",$G400="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M400:$U400)+($M400:$U400="DNA")),$M400:$U400),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M400:$U400)+($M400:$U400="DNA")),$M400:$U400),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M400:$U400)+($M400:$U400="DNA")),$M400:$U400),"")&lt;TODAY())),1,0)+COUNTIF($V400:$Z400,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J400" s="32">
@@ -19462,7 +19473,7 @@
         <v/>
       </c>
       <c r="K400" s="32">
-        <f>IF(NOT(AND($A400&lt;&gt;"",OR($G400="",$G400="Active"))),"",IF($L400&lt;&gt;"",IF($L400=$M400,"Booking",INDEX($N$4:$U$4,MATCH($L400,$N400:$U400,0))),IF(COUNTIF($N400:$U400,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N400:$U400)=0,"All done",IF(MAX($M400:$U400)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A400&lt;&gt;"",OR($G400="",$G400="Active"))),"",IF($L400&lt;&gt;"",IF($L400=$M400,"Booking",INDEX($N$4:$U$4,MATCH($L400,$N400:$U400,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M400:$U400)+($M400:$U400="DNA")),$M400:$U400),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M400:$U400)+($M400:$U400="DNA")),$M400:$U400),"")),IF(ISNUMBER($U400),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L400" s="33">
@@ -19500,7 +19511,7 @@
         <v/>
       </c>
       <c r="I401" s="32">
-        <f>IF(NOT(AND($A401&lt;&gt;"",OR($G401="",$G401="Active"))),"",IF(AND(MAX($M401:$U401)&gt;0,MAX($M401:$U401)&lt;TODAY(),COUNTBLANK($N401:$U401)&gt;0,COUNTIF($N401:$U401,"DNA")=0),1,0)+COUNTIF($N401:$U401,"DNA")+COUNTIF($V401:$Z401,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A401&lt;&gt;"",OR($G401="",$G401="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M401:$U401)+($M401:$U401="DNA")),$M401:$U401),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M401:$U401)+($M401:$U401="DNA")),$M401:$U401),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M401:$U401)+($M401:$U401="DNA")),$M401:$U401),"")&lt;TODAY())),1,0)+COUNTIF($V401:$Z401,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J401" s="32">
@@ -19508,7 +19519,7 @@
         <v/>
       </c>
       <c r="K401" s="32">
-        <f>IF(NOT(AND($A401&lt;&gt;"",OR($G401="",$G401="Active"))),"",IF($L401&lt;&gt;"",IF($L401=$M401,"Booking",INDEX($N$4:$U$4,MATCH($L401,$N401:$U401,0))),IF(COUNTIF($N401:$U401,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N401:$U401)=0,"All done",IF(MAX($M401:$U401)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A401&lt;&gt;"",OR($G401="",$G401="Active"))),"",IF($L401&lt;&gt;"",IF($L401=$M401,"Booking",INDEX($N$4:$U$4,MATCH($L401,$N401:$U401,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M401:$U401)+($M401:$U401="DNA")),$M401:$U401),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M401:$U401)+($M401:$U401="DNA")),$M401:$U401),"")),IF(ISNUMBER($U401),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L401" s="33">
@@ -19546,7 +19557,7 @@
         <v/>
       </c>
       <c r="I402" s="32">
-        <f>IF(NOT(AND($A402&lt;&gt;"",OR($G402="",$G402="Active"))),"",IF(AND(MAX($M402:$U402)&gt;0,MAX($M402:$U402)&lt;TODAY(),COUNTBLANK($N402:$U402)&gt;0,COUNTIF($N402:$U402,"DNA")=0),1,0)+COUNTIF($N402:$U402,"DNA")+COUNTIF($V402:$Z402,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A402&lt;&gt;"",OR($G402="",$G402="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M402:$U402)+($M402:$U402="DNA")),$M402:$U402),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M402:$U402)+($M402:$U402="DNA")),$M402:$U402),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M402:$U402)+($M402:$U402="DNA")),$M402:$U402),"")&lt;TODAY())),1,0)+COUNTIF($V402:$Z402,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J402" s="32">
@@ -19554,7 +19565,7 @@
         <v/>
       </c>
       <c r="K402" s="32">
-        <f>IF(NOT(AND($A402&lt;&gt;"",OR($G402="",$G402="Active"))),"",IF($L402&lt;&gt;"",IF($L402=$M402,"Booking",INDEX($N$4:$U$4,MATCH($L402,$N402:$U402,0))),IF(COUNTIF($N402:$U402,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N402:$U402)=0,"All done",IF(MAX($M402:$U402)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A402&lt;&gt;"",OR($G402="",$G402="Active"))),"",IF($L402&lt;&gt;"",IF($L402=$M402,"Booking",INDEX($N$4:$U$4,MATCH($L402,$N402:$U402,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M402:$U402)+($M402:$U402="DNA")),$M402:$U402),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M402:$U402)+($M402:$U402="DNA")),$M402:$U402),"")),IF(ISNUMBER($U402),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L402" s="33">
@@ -19592,7 +19603,7 @@
         <v/>
       </c>
       <c r="I403" s="32">
-        <f>IF(NOT(AND($A403&lt;&gt;"",OR($G403="",$G403="Active"))),"",IF(AND(MAX($M403:$U403)&gt;0,MAX($M403:$U403)&lt;TODAY(),COUNTBLANK($N403:$U403)&gt;0,COUNTIF($N403:$U403,"DNA")=0),1,0)+COUNTIF($N403:$U403,"DNA")+COUNTIF($V403:$Z403,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A403&lt;&gt;"",OR($G403="",$G403="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M403:$U403)+($M403:$U403="DNA")),$M403:$U403),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M403:$U403)+($M403:$U403="DNA")),$M403:$U403),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M403:$U403)+($M403:$U403="DNA")),$M403:$U403),"")&lt;TODAY())),1,0)+COUNTIF($V403:$Z403,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J403" s="32">
@@ -19600,7 +19611,7 @@
         <v/>
       </c>
       <c r="K403" s="32">
-        <f>IF(NOT(AND($A403&lt;&gt;"",OR($G403="",$G403="Active"))),"",IF($L403&lt;&gt;"",IF($L403=$M403,"Booking",INDEX($N$4:$U$4,MATCH($L403,$N403:$U403,0))),IF(COUNTIF($N403:$U403,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N403:$U403)=0,"All done",IF(MAX($M403:$U403)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A403&lt;&gt;"",OR($G403="",$G403="Active"))),"",IF($L403&lt;&gt;"",IF($L403=$M403,"Booking",INDEX($N$4:$U$4,MATCH($L403,$N403:$U403,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M403:$U403)+($M403:$U403="DNA")),$M403:$U403),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M403:$U403)+($M403:$U403="DNA")),$M403:$U403),"")),IF(ISNUMBER($U403),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L403" s="33">
@@ -19638,7 +19649,7 @@
         <v/>
       </c>
       <c r="I404" s="32">
-        <f>IF(NOT(AND($A404&lt;&gt;"",OR($G404="",$G404="Active"))),"",IF(AND(MAX($M404:$U404)&gt;0,MAX($M404:$U404)&lt;TODAY(),COUNTBLANK($N404:$U404)&gt;0,COUNTIF($N404:$U404,"DNA")=0),1,0)+COUNTIF($N404:$U404,"DNA")+COUNTIF($V404:$Z404,"&lt;"&amp;TODAY()))</f>
+        <f>IF(NOT(AND($A404&lt;&gt;"",OR($G404="",$G404="Active"))),"",IF(OR(IFERROR(LOOKUP(2,1/(ISNUMBER($M404:$U404)+($M404:$U404="DNA")),$M404:$U404),"")="DNA",AND(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M404:$U404)+($M404:$U404="DNA")),$M404:$U404),"")),IFERROR(LOOKUP(2,1/(ISNUMBER($M404:$U404)+($M404:$U404="DNA")),$M404:$U404),"")&lt;TODAY())),1,0)+COUNTIF($V404:$Z404,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
       <c r="J404" s="32">
@@ -19646,7 +19657,7 @@
         <v/>
       </c>
       <c r="K404" s="32">
-        <f>IF(NOT(AND($A404&lt;&gt;"",OR($G404="",$G404="Active"))),"",IF($L404&lt;&gt;"",IF($L404=$M404,"Booking",INDEX($N$4:$U$4,MATCH($L404,$N404:$U404,0))),IF(COUNTIF($N404:$U404,"DNA")&gt;0,"Rebook DNA",IF(COUNTBLANK($N404:$U404)=0,"All done",IF(MAX($M404:$U404)&gt;0,"Not booked","")))))</f>
+        <f>IF(NOT(AND($A404&lt;&gt;"",OR($G404="",$G404="Active"))),"",IF($L404&lt;&gt;"",IF($L404=$M404,"Booking",INDEX($N$4:$U$4,MATCH($L404,$N404:$U404,0))),IF(IFERROR(LOOKUP(2,1/(ISNUMBER($M404:$U404)+($M404:$U404="DNA")),$M404:$U404),"")="DNA","Rebook DNA",IF(ISNUMBER(IFERROR(LOOKUP(2,1/(ISNUMBER($M404:$U404)+($M404:$U404="DNA")),$M404:$U404),"")),IF(ISNUMBER($U404),"Update status","Missed/not booked?"),""))))</f>
         <v/>
       </c>
       <c r="L404" s="33">
@@ -19672,84 +19683,105 @@
       <c r="AC404" s="31" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N5:U404">
+  <conditionalFormatting sqref="M5:T404">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>N5="N/A"</formula>
+      <formula>M5="N/A"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),N5="DNA")</formula>
+      <formula>AND(M5="DNA",(COUNT(N5:$U5)+COUNTIF(N5:$U5,"DNA"))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),N5="",M5&lt;&gt;"",M5&lt;&gt;"DNA",MAX($M5:$U5)&gt;0,MAX($M5:$U5)&lt;TODAY())</formula>
+      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),M5="DNA")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(M5),M5&lt;TODAY(),NOT((COUNT(N5:$U5)+COUNTIF(N5:$U5,"DNA"))&gt;0))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
-      <formula>AND(ISNUMBER(N5),N5&lt;TODAY())</formula>
+      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(M5),M5&gt;=TODAY(),M5&lt;=TODAY()+7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(M5),M5&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:U404">
-    <cfRule type="expression" priority="4" dxfId="4" stopIfTrue="1">
-      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(M5),M5&gt;=TODAY(),M5&lt;=TODAY()+7)</formula>
+  <conditionalFormatting sqref="U5:U404">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>U5="N/A"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
+      <formula>AND(U5="DNA",FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),U5="DNA")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
+      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(U5),U5&lt;TODAY(),NOT(FALSE))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="3" stopIfTrue="1">
+      <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(U5),U5&gt;=TODAY(),U5&lt;=TODAY()+7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(U5),U5&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:Z404">
-    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
       <formula>V5="N/A"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="14" dxfId="5" stopIfTrue="1">
       <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(V5),V5&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="5" stopIfTrue="1">
+    <cfRule type="expression" priority="15" dxfId="6" stopIfTrue="1">
       <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(V5),V5&gt;=TODAY(),V5&lt;=TODAY()+7)</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="3" stopIfTrue="1">
+    <cfRule type="expression" priority="16" dxfId="4" stopIfTrue="1">
       <formula>AND(ISTEXT(V5),V5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I404">
-    <cfRule type="expression" priority="10" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="17" dxfId="2" stopIfTrue="1">
       <formula>AND(ISNUMBER(I5),I5&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:J404">
-    <cfRule type="expression" priority="11" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="18" dxfId="3" stopIfTrue="1">
       <formula>AND(ISNUMBER(J5),J5&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K404">
-    <cfRule type="expression" priority="12" dxfId="1" stopIfTrue="1">
-      <formula>OR(K5="Not booked",K5="Rebook DNA")</formula>
+    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
+      <formula>OR(K5="Missed/not booked?",K5="Rebook DNA",K5="Update status")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L404">
-    <cfRule type="expression" priority="13" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="20" dxfId="3" stopIfTrue="1">
       <formula>AND(ISNUMBER(L5),L5&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F404">
-    <cfRule type="expression" priority="14" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="21" dxfId="3" stopIfTrue="1">
       <formula>AND(AND($A5&lt;&gt;"",OR($G5="",$G5="Active")),ISNUMBER(F5),F5&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B404">
-    <cfRule type="expression" priority="15" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="7" stopIfTrue="1">
       <formula>AND(B5&lt;&gt;"",NOT(IFERROR(AND(LEN(SUBSTITUTE(B5," ",""))=10,ISNUMBER(VALUE(SUBSTITUTE(B5," ",""))),MOD(11-MOD(MID(SUBSTITUTE(B5," ",""),1,1)*10+MID(SUBSTITUTE(B5," ",""),2,1)*9+MID(SUBSTITUTE(B5," ",""),3,1)*8+MID(SUBSTITUTE(B5," ",""),4,1)*7+MID(SUBSTITUTE(B5," ",""),5,1)*6+MID(SUBSTITUTE(B5," ",""),6,1)*5+MID(SUBSTITUTE(B5," ",""),7,1)*4+MID(SUBSTITUTE(B5," ",""),8,1)*3+MID(SUBSTITUTE(B5," ",""),9,1)*2,11),11)=VALUE(RIGHT(SUBSTITUTE(B5," ",""),1))),FALSE)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" dxfId="7" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="8" stopIfTrue="1">
       <formula>AND(B5&lt;&gt;"",COUNTIF($B$5:$B$404,B5)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A404">
-    <cfRule type="expression" priority="17" dxfId="8" stopIfTrue="1">
+    <cfRule type="expression" priority="24" dxfId="9" stopIfTrue="1">
       <formula>AND(ISNUMBER($B$2),ISNUMBER($AC5),$AC5&gt;=$B$2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB5:AC404">
-    <cfRule type="expression" priority="18" dxfId="8" stopIfTrue="1">
+    <cfRule type="expression" priority="25" dxfId="9" stopIfTrue="1">
       <formula>AND(ISNUMBER($B$2),ISNUMBER($AC5),$AC5&gt;=$B$2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:AC404">
-    <cfRule type="expression" priority="19" dxfId="9" stopIfTrue="1">
+    <cfRule type="expression" priority="26" dxfId="10" stopIfTrue="1">
       <formula>AND($A5&lt;&gt;"",$G5&lt;&gt;"",$G5&lt;&gt;"Active")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19779,7 +19811,7 @@
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
-    <dataValidation sqref="N5:U404" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Appointment" error="Expected a date, DNA or N/A." promptTitle="Appointment" prompt="Enter the date once it's booked (usually at the previous appointment). DNA if missed: replace with the new date once rebooked. N/A if not needed." type="custom" errorStyle="warning">
+    <dataValidation sqref="N5:U404" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Appointment" error="Expected a date, DNA or N/A." promptTitle="Appointment" prompt="Enter the date once it's booked (usually at the previous appointment). Adding it confirms the previous one happened. DNA if missed. N/A if not needed." type="custom" errorStyle="warning">
       <formula1>OR(N5="",ISNUMBER(N5),N5="DNA",N5="N/A")</formula1>
     </dataValidation>
     <dataValidation sqref="V5:Z404" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Action" prompt="Enter the date booked/due. Once complete, type Done (or e.g. 'Done 12/3 SW'). N/A if not needed." type="custom">
@@ -23725,7 +23757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B36"/>
+  <dimension ref="B2:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -23812,166 +23844,180 @@
     <row r="13">
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  – Amber: the appointment is in the next 7 days. Green: the date has passed (seen). Plain: booked, more than a week away.</t>
+          <t xml:space="preserve">  – An appointment only counts as attended once a later date has been entered, because the next date can only be booked at that appointment. So a past date turns green only when something is entered after it.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  – Red empty cell: the last appointment has passed and the next one hasn't been added yet. Only the first empty slot turns red, and N/A slots are skipped (e.g. 25/40 or 31/40 for multips).</t>
+          <t xml:space="preserve">  – Red date: the appointment date has passed and nothing later has been entered. Either it was missed (type DNA over it) or the next appointment hasn't been booked yet (add it). 'Next appt' shows 'Missed/not booked?'.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  – DNA: type DNA over the date. It stays red, and 'Next appt' says Rebook DNA, until you replace it with the rebooked date. Note the DNA in Info or the Log so it isn't lost.</t>
+          <t xml:space="preserve">  – Amber: the appointment is in the next 7 days. Plain: booked, more than a week away. N/A slots are skipped (e.g. 25/40 or 31/40 for multips).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>• Action columns (GTT, Anti-D, BP, Bloods, IOL): enter the date it's booked or due. It turns amber within 7 days and red once the date has passed. When it's done, overwrite it with 'Done' (or 'Done 12/3 SW'), which turns it green. N/A turns it grey.</t>
+          <t xml:space="preserve">  – DNA: red until a later date is entered. Either type the rebooked date over the DNA, or leave DNA in place and put the new date in the next column; the DNA then stays visible in grey.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>• NHS number: orange means it isn't a valid 10-digit NHS number (checksum). Purple means it appears twice.</t>
+          <t xml:space="preserve">  – 40/40 has nothing after it, so once it has passed it stays red ('Update status') until Status is changed, e.g. to Delivered.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="34" t="inlineStr">
         <is>
+          <t>• Action columns (GTT, Anti-D, BP, Bloods, IOL): enter the date it's booked or due. It turns amber within 7 days and red once the date has passed. When it's done, overwrite it with 'Done' (or 'Done 12/3 SW'), which turns it green. N/A turns it grey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>• NHS number: orange means it isn't a valid 10-digit NHS number (checksum). Purple means it appears twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="34" t="inlineStr">
+        <is>
           <t>• EDD turns amber if it has passed and the patient is still Active, as a reminder to update Status.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="42" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>Colour key</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="43" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>Red: next appointment not booked, DNA, or an action date that has passed and isn't marked Done</t>
+          <t>Red: appointment passed but not confirmed (nothing entered after it), DNA not yet rebooked, or an action date that has passed and isn't marked Done</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="44" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>Amber: due in the next 7 days</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="45" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="45" t="inlineStr">
         <is>
-          <t>Green: done / seen</t>
+          <t>Green: appointment confirmed (a later date has been entered) or action Done</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="46" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>Grey: N/A, or the patient is no longer active</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="47" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>Blue: row updated on or after the date in cell B2</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="42" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="42" t="inlineStr">
         <is>
           <t>Example row (format only, fictional)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="34" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="34" t="inlineStr">
         <is>
           <t>Jane Example | 943 476 5919 | 02/05/1994 | G2P1 | MLC | 10/01/2027 | (Status blank) | Booking date: 18/06/2026 | 16/40: 11/08/2026 | 25/40: N/A | 28/40: 01/10/2026 | GTT booked: 14/10/2026 | Anti-D ordered: Done 20/09 | BP fortnightly: N/A | Last updated by: (your name) | Last updated on: 26/09/2026</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="42" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="42" t="inlineStr">
         <is>
           <t>Seeing exactly who changed what</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="34" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>If the file is stored on SharePoint, OneDrive or Teams (not a shared drive), Excel keeps a full audit trail automatically:</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="34" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>• Review ▸ Show Changes lists every edit with who made it and when. Right-click a cell and choose Show Changes to see that cell's history.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="34" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>• File ▸ Info ▸ Version History lets you open or restore any earlier version.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="34" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>• @mentioning a colleague in a comment (Review ▸ New Comment) sends them an email.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="34" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>The 'Last updated by' columns and the Log are the human-readable layer on top of that.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="42" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Adding rows</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="34" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>The table is pre-formatted for 400 patients. Don't insert or reorder columns between Booking date and 40/40, because the red 'not booked' check reads them left to right.</t>
+          <t>The table is pre-formatted for 400 patients. Don't insert or reorder columns between Booking date and 40/40, because the confirmation check reads them left to right.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="42" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="42" t="inlineStr">
         <is>
           <t>Information governance</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="34" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="34" t="inlineStr">
         <is>
           <t>This holds patient-identifiable data. Keep it in the approved team location with access limited to the team, and follow your trust's IG policy.</t>
         </is>
